--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631EC830-92AA-4DBA-8B39-98F379AD3B84}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B04735-E917-495F-B722-E92A28A980CC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="26" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="27" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="486">
   <si>
     <t>Codigo</t>
   </si>
@@ -1472,6 +1472,18 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790070432551.png</t>
+  </si>
+  <si>
+    <t>7791122005945</t>
+  </si>
+  <si>
+    <t>sin sabor</t>
+  </si>
+  <si>
+    <t>Vélez</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7791122005945.png</t>
   </si>
 </sst>
 </file>
@@ -1823,8 +1835,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126E8DAC-AC80-401A-8D77-4359E0E311B3}">
-  <dimension ref="A1:Q86"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{512BC88A-0D92-4830-AD6C-93A4FDB37F1C}">
+  <dimension ref="A1:Q87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3067,34 +3079,34 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>359</v>
+        <v>482</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>327</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>483</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>484</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I24" t="s">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="J24" t="s">
-        <v>22</v>
+        <v>330</v>
       </c>
       <c r="K24" t="s">
         <v>23</v>
@@ -3109,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>251</v>
+        <v>485</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
@@ -3120,34 +3132,34 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K25" t="s">
         <v>23</v>
@@ -3162,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
@@ -3173,41 +3185,41 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>360</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26">
         <v>12</v>
       </c>
-      <c r="B26" t="s">
-        <v>361</v>
-      </c>
-      <c r="C26" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" t="s">
-        <v>33</v>
-      </c>
-      <c r="F26" t="s">
-        <v>34</v>
-      </c>
-      <c r="G26">
-        <v>500</v>
-      </c>
-      <c r="H26" t="s">
-        <v>35</v>
-      </c>
-      <c r="I26" t="s">
-        <v>36</v>
-      </c>
-      <c r="J26" t="s">
-        <v>37</v>
-      </c>
-      <c r="K26" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26">
-        <v>6</v>
-      </c>
       <c r="M26" t="b">
         <v>0</v>
       </c>
@@ -3215,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -3226,40 +3238,40 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G27">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I27" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J27" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K27" t="s">
         <v>23</v>
       </c>
       <c r="L27">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M27" t="b">
         <v>0</v>
@@ -3268,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -3279,40 +3291,40 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F28" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
       </c>
       <c r="J28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K28" t="s">
         <v>23</v>
       </c>
       <c r="L28">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
@@ -3321,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -3332,40 +3344,40 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C29" t="s">
-        <v>241</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>242</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="G29">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="K29" t="s">
         <v>23</v>
       </c>
       <c r="L29">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
@@ -3374,7 +3386,7 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
@@ -3385,49 +3397,49 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C30" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="D30" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="E30" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F30" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="H30" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I30" t="s">
         <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K30" t="s">
         <v>23</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
       <c r="N30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -3438,34 +3450,34 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H31" t="s">
         <v>20</v>
       </c>
       <c r="I31" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>49</v>
+        <v>245</v>
       </c>
       <c r="K31" t="s">
         <v>23</v>
@@ -3477,10 +3489,10 @@
         <v>0</v>
       </c>
       <c r="N31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -3491,34 +3503,34 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E32" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I32" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J32" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K32" t="s">
         <v>23</v>
@@ -3533,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -3544,34 +3556,34 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G33">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I33" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J33" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K33" t="s">
         <v>23</v>
@@ -3586,51 +3598,51 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
       </c>
       <c r="Q33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F34" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H34" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I34" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J34" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K34" t="s">
         <v>23</v>
       </c>
       <c r="L34">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
@@ -3639,45 +3651,45 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
       </c>
       <c r="Q34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E35" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G35">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I35" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J35" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K35" t="s">
         <v>23</v>
@@ -3692,51 +3704,51 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
       </c>
       <c r="Q35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F36" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G36">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H36" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I36" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J36" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K36" t="s">
         <v>23</v>
       </c>
       <c r="L36">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
@@ -3745,45 +3757,45 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
       </c>
       <c r="Q36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E37" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F37" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G37">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H37" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s">
         <v>53</v>
       </c>
       <c r="J37" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K37" t="s">
         <v>23</v>
@@ -3798,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -3809,40 +3821,40 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E38" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F38" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I38" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J38" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K38" t="s">
         <v>23</v>
       </c>
       <c r="L38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
@@ -3851,7 +3863,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -3862,40 +3874,40 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F39" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G39">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I39" t="s">
         <v>21</v>
       </c>
       <c r="J39" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K39" t="s">
         <v>23</v>
       </c>
       <c r="L39">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
@@ -3904,7 +3916,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
@@ -3915,34 +3927,34 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E40" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F40" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H40" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I40" t="s">
         <v>21</v>
       </c>
       <c r="J40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
@@ -3957,7 +3969,7 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
@@ -3968,40 +3980,40 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E41" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F41" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G41">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H41" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I41" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
@@ -4010,51 +4022,51 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
       </c>
       <c r="Q41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E42" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F42" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G42">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I42" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J42" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
       </c>
       <c r="L42">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
@@ -4063,7 +4075,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
@@ -4074,41 +4086,41 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E43" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F43" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H43" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I43" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J43" t="s">
+        <v>66</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43">
         <v>30</v>
       </c>
-      <c r="K43" t="s">
-        <v>23</v>
-      </c>
-      <c r="L43">
-        <v>12</v>
-      </c>
       <c r="M43" t="b">
         <v>0</v>
       </c>
@@ -4116,113 +4128,113 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
       </c>
       <c r="Q43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
+        <v>29</v>
+      </c>
+      <c r="B44" t="s">
+        <v>378</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" t="s">
+        <v>55</v>
+      </c>
+      <c r="F44" t="s">
+        <v>61</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>28</v>
+      </c>
+      <c r="I44" t="s">
+        <v>96</v>
+      </c>
+      <c r="J44" t="s">
         <v>30</v>
       </c>
-      <c r="B44" t="s">
-        <v>379</v>
-      </c>
-      <c r="C44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" t="s">
-        <v>98</v>
-      </c>
-      <c r="E44" t="s">
-        <v>99</v>
-      </c>
-      <c r="F44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G44">
-        <v>100</v>
-      </c>
-      <c r="H44" t="s">
-        <v>20</v>
-      </c>
-      <c r="I44" t="s">
-        <v>101</v>
-      </c>
-      <c r="J44" t="s">
-        <v>102</v>
-      </c>
       <c r="K44" t="s">
         <v>23</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
       </c>
       <c r="N44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
       </c>
       <c r="Q44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E45" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F45" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G45">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H45" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I45" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J45" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
       </c>
       <c r="L45">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
       </c>
       <c r="N45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -4233,22 +4245,22 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E46" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F46" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G46">
         <v>500</v>
@@ -4260,13 +4272,13 @@
         <v>107</v>
       </c>
       <c r="J46" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
@@ -4275,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
@@ -4286,40 +4298,40 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E47" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F47" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H47" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I47" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J47" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
       </c>
       <c r="L47">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
@@ -4328,51 +4340,51 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
       </c>
       <c r="Q47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E48" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F48" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G48">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I48" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J48" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
@@ -4381,51 +4393,51 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
       </c>
       <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
+        <v>383</v>
+      </c>
+      <c r="C49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" t="s">
+        <v>113</v>
+      </c>
+      <c r="E49" t="s">
+        <v>114</v>
+      </c>
+      <c r="F49" t="s">
+        <v>115</v>
+      </c>
+      <c r="G49">
+        <v>300</v>
+      </c>
+      <c r="H49" t="s">
         <v>35</v>
       </c>
-      <c r="B49" t="s">
-        <v>384</v>
-      </c>
-      <c r="C49" t="s">
-        <v>117</v>
-      </c>
-      <c r="D49" t="s">
-        <v>118</v>
-      </c>
-      <c r="E49" t="s">
-        <v>119</v>
-      </c>
-      <c r="F49" t="s">
-        <v>120</v>
-      </c>
-      <c r="G49">
-        <v>500</v>
-      </c>
-      <c r="H49" t="s">
-        <v>42</v>
-      </c>
       <c r="I49" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J49" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -4434,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
@@ -4445,40 +4457,40 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E50" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F50" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G50">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H50" t="s">
         <v>42</v>
       </c>
       <c r="I50" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J50" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -4487,51 +4499,51 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
       </c>
       <c r="Q50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B51" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C51" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D51" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E51" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F51" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G51">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H51" t="s">
         <v>42</v>
       </c>
       <c r="I51" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J51" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -4540,45 +4552,45 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
       </c>
       <c r="Q51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B52" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E52" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F52" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G52">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H52" t="s">
         <v>42</v>
       </c>
       <c r="I52" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J52" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
@@ -4593,51 +4605,51 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
       </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C53" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F53" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G53">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H53" t="s">
         <v>42</v>
       </c>
       <c r="I53" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -4646,7 +4658,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -4657,40 +4669,40 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D54" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E54" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F54" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H54" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I54" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J54" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4699,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -4710,63 +4722,63 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C55" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E55" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F55" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G55">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I55" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
       </c>
       <c r="Q55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C56" t="s">
         <v>138</v>
@@ -4775,10 +4787,10 @@
         <v>139</v>
       </c>
       <c r="E56" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F56" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G56">
         <v>1000</v>
@@ -4802,10 +4814,10 @@
         <v>1</v>
       </c>
       <c r="N56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
@@ -4816,22 +4828,22 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B57" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C57" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D57" t="s">
         <v>139</v>
       </c>
       <c r="E57" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F57" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G57">
         <v>1000</v>
@@ -4843,7 +4855,7 @@
         <v>142</v>
       </c>
       <c r="J57" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
@@ -4858,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -4869,193 +4881,193 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B58" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C58" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D58" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E58" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F58" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G58">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H58" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J58" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B59" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D59" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E59" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F59" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H59" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I59" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J59" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K59" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L59">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
       </c>
       <c r="N59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C60" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E60" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F60" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G60">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I60" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J60" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K60" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L60">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
       </c>
       <c r="N60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B61" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C61" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E61" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F61" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G61">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H61" t="s">
         <v>42</v>
       </c>
       <c r="I61" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J61" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
@@ -5070,7 +5082,7 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -5081,22 +5093,22 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B62" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C62" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D62" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E62" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F62" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G62">
         <v>500</v>
@@ -5108,7 +5120,7 @@
         <v>21</v>
       </c>
       <c r="J62" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
@@ -5123,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5134,25 +5146,25 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B63" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C63" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D63" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E63" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F63" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G63">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H63" t="s">
         <v>42</v>
@@ -5161,7 +5173,7 @@
         <v>21</v>
       </c>
       <c r="J63" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
@@ -5176,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5187,37 +5199,37 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
+        <v>49</v>
+      </c>
+      <c r="B64" t="s">
+        <v>398</v>
+      </c>
+      <c r="C64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D64" t="s">
+        <v>176</v>
+      </c>
+      <c r="E64" t="s">
+        <v>177</v>
+      </c>
+      <c r="F64" t="s">
+        <v>178</v>
+      </c>
+      <c r="G64">
         <v>50</v>
       </c>
-      <c r="B64" t="s">
-        <v>399</v>
-      </c>
-      <c r="C64" t="s">
-        <v>180</v>
-      </c>
-      <c r="D64" t="s">
-        <v>181</v>
-      </c>
-      <c r="E64" t="s">
-        <v>182</v>
-      </c>
-      <c r="F64" t="s">
-        <v>183</v>
-      </c>
-      <c r="G64">
-        <v>12</v>
-      </c>
       <c r="H64" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K64" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L64">
         <v>12</v>
@@ -5229,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5240,40 +5252,40 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B65" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C65" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D65" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E65" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F65" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G65">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H65" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I65" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J65" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K65" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -5282,7 +5294,7 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5293,40 +5305,40 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B66" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C66" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D66" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E66" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F66" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G66">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H66" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I66" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J66" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5335,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5346,40 +5358,40 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
+        <v>52</v>
+      </c>
+      <c r="B67" t="s">
+        <v>401</v>
+      </c>
+      <c r="C67" t="s">
+        <v>193</v>
+      </c>
+      <c r="D67" t="s">
+        <v>181</v>
+      </c>
+      <c r="E67" t="s">
+        <v>182</v>
+      </c>
+      <c r="F67" t="s">
+        <v>183</v>
+      </c>
+      <c r="G67">
+        <v>24</v>
+      </c>
+      <c r="H67" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" t="s">
         <v>53</v>
       </c>
-      <c r="B67" t="s">
-        <v>402</v>
-      </c>
-      <c r="C67" t="s">
-        <v>31</v>
-      </c>
-      <c r="D67" t="s">
-        <v>194</v>
-      </c>
-      <c r="E67" t="s">
-        <v>195</v>
-      </c>
-      <c r="F67" t="s">
-        <v>196</v>
-      </c>
-      <c r="G67">
-        <v>1.5</v>
-      </c>
-      <c r="H67" t="s">
-        <v>28</v>
-      </c>
-      <c r="I67" t="s">
-        <v>36</v>
-      </c>
       <c r="J67" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5388,7 +5400,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5399,52 +5411,52 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B68" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C68" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D68" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E68" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F68" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G68">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H68" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I68" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J68" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
       </c>
       <c r="N68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" t="b">
         <v>1</v>
@@ -5452,93 +5464,93 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B69" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C69" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E69" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F69" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G69">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H69" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
       </c>
       <c r="N69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B70" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C70" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D70" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E70" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F70" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G70">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H70" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J70" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -5547,7 +5559,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -5558,19 +5570,19 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B71" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C71" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D71" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E71" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F71" t="s">
         <v>208</v>
@@ -5600,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -5611,19 +5623,19 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B72" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D72" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E72" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F72" t="s">
         <v>208</v>
@@ -5644,7 +5656,7 @@
         <v>23</v>
       </c>
       <c r="L72">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -5653,7 +5665,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -5664,34 +5676,34 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B73" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C73" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D73" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E73" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F73" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H73" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I73" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J73" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
@@ -5706,45 +5718,45 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B74" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C74" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E74" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F74" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G74">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I74" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J74" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
@@ -5759,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -5770,49 +5782,49 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B75" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C75" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D75" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E75" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F75" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G75">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H75" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J75" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
       <c r="N75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -5823,22 +5835,22 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B76" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C76" t="s">
         <v>217</v>
       </c>
       <c r="D76" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E76" t="s">
         <v>219</v>
       </c>
       <c r="F76" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G76">
         <v>20</v>
@@ -5865,60 +5877,60 @@
         <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B77" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C77" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D77" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E77" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F77" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G77">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H77" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I77" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J77" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -5929,34 +5941,34 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B78" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C78" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D78" t="s">
         <v>202</v>
       </c>
       <c r="E78" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F78" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G78">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H78" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I78" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J78" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
@@ -5971,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -5982,40 +5994,40 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B79" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C79" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D79" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E79" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F79" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G79">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H79" t="s">
         <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J79" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6024,51 +6036,51 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B80" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C80" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D80" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E80" t="s">
         <v>229</v>
       </c>
       <c r="F80" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H80" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J80" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6077,7 +6089,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6088,40 +6100,40 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B81" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C81" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E81" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F81" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G81">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I81" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J81" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6130,45 +6142,45 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B82" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C82" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D82" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E82" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F82" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G82">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H82" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I82" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J82" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -6183,7 +6195,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6194,10 +6206,10 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B83" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C83" t="s">
         <v>186</v>
@@ -6206,13 +6218,13 @@
         <v>202</v>
       </c>
       <c r="E83" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F83" t="s">
         <v>204</v>
       </c>
       <c r="G83">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H83" t="s">
         <v>35</v>
@@ -6236,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6247,10 +6259,10 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B84" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C84" t="s">
         <v>186</v>
@@ -6265,7 +6277,7 @@
         <v>204</v>
       </c>
       <c r="G84">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H84" t="s">
         <v>35</v>
@@ -6289,7 +6301,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6300,41 +6312,41 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B85" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C85" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D85" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E85" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F85" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G85">
+        <v>250</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85" t="s">
+        <v>191</v>
+      </c>
+      <c r="J85" t="s">
+        <v>192</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85">
         <v>6</v>
       </c>
-      <c r="H85" t="s">
-        <v>20</v>
-      </c>
-      <c r="I85" t="s">
-        <v>239</v>
-      </c>
-      <c r="J85" t="s">
-        <v>235</v>
-      </c>
-      <c r="K85" t="s">
-        <v>23</v>
-      </c>
-      <c r="L85">
-        <v>1</v>
-      </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
@@ -6342,65 +6354,118 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C86" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D86" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F86" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G86">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H86" t="s">
         <v>20</v>
       </c>
       <c r="I86" t="s">
+        <v>239</v>
+      </c>
+      <c r="J86" t="s">
+        <v>235</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86" t="b">
+        <v>0</v>
+      </c>
+      <c r="N86" t="b">
+        <v>1</v>
+      </c>
+      <c r="O86" t="s">
+        <v>311</v>
+      </c>
+      <c r="P86" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>72</v>
+      </c>
+      <c r="B87" t="s">
+        <v>421</v>
+      </c>
+      <c r="C87" t="s">
+        <v>197</v>
+      </c>
+      <c r="D87" t="s">
+        <v>198</v>
+      </c>
+      <c r="E87" t="s">
+        <v>199</v>
+      </c>
+      <c r="F87" t="s">
+        <v>240</v>
+      </c>
+      <c r="G87">
+        <v>4</v>
+      </c>
+      <c r="H87" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" t="s">
         <v>21</v>
       </c>
-      <c r="J86" t="s">
+      <c r="J87" t="s">
         <v>201</v>
       </c>
-      <c r="K86" t="s">
-        <v>23</v>
-      </c>
-      <c r="L86">
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87">
         <v>10</v>
       </c>
-      <c r="M86" t="b">
-        <v>0</v>
-      </c>
-      <c r="N86" t="b">
-        <v>0</v>
-      </c>
-      <c r="O86" t="s">
+      <c r="M87" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" t="b">
+        <v>0</v>
+      </c>
+      <c r="O87" t="s">
         <v>312</v>
       </c>
-      <c r="P86" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q86" t="b">
+      <c r="P87" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B04735-E917-495F-B722-E92A28A980CC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0891B9-594D-4F51-A14E-275C5E850BB7}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="27" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="29" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="489">
   <si>
     <t>Codigo</t>
   </si>
@@ -1484,6 +1484,15 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7791122005945.png</t>
+  </si>
+  <si>
+    <t>7791708001248</t>
+  </si>
+  <si>
+    <t>hamburguesas</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7791708001248.png</t>
   </si>
 </sst>
 </file>
@@ -1835,8 +1844,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{512BC88A-0D92-4830-AD6C-93A4FDB37F1C}">
-  <dimension ref="A1:Q87"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6031AD-E2E8-40E5-851D-8D752CD0A303}">
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3132,10 +3141,10 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>359</v>
+        <v>486</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
@@ -3144,13 +3153,13 @@
         <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>487</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H25" t="s">
         <v>20</v>
@@ -3165,7 +3174,7 @@
         <v>23</v>
       </c>
       <c r="L25">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
@@ -3174,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>251</v>
+        <v>488</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
@@ -3185,34 +3194,34 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I26" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K26" t="s">
         <v>23</v>
@@ -3227,7 +3236,7 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -3238,41 +3247,41 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
+        <v>360</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27">
         <v>12</v>
       </c>
-      <c r="B27" t="s">
-        <v>361</v>
-      </c>
-      <c r="C27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" t="s">
-        <v>33</v>
-      </c>
-      <c r="F27" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27">
-        <v>500</v>
-      </c>
-      <c r="H27" t="s">
-        <v>35</v>
-      </c>
-      <c r="I27" t="s">
-        <v>36</v>
-      </c>
-      <c r="J27" t="s">
-        <v>37</v>
-      </c>
-      <c r="K27" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27">
-        <v>6</v>
-      </c>
       <c r="M27" t="b">
         <v>0</v>
       </c>
@@ -3280,7 +3289,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -3291,40 +3300,40 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I28" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J28" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K28" t="s">
         <v>23</v>
       </c>
       <c r="L28">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
@@ -3333,7 +3342,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -3344,40 +3353,40 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K29" t="s">
         <v>23</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
@@ -3386,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
@@ -3397,40 +3406,40 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C30" t="s">
-        <v>241</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>242</v>
+        <v>45</v>
       </c>
       <c r="E30" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="G30">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I30" t="s">
         <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="K30" t="s">
         <v>23</v>
       </c>
       <c r="L30">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
@@ -3439,7 +3448,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -3450,49 +3459,49 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C31" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="D31" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="E31" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F31" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G31">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="H31" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I31" t="s">
         <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K31" t="s">
         <v>23</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
       </c>
       <c r="N31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -3503,34 +3512,34 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>197</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H32" t="s">
         <v>20</v>
       </c>
       <c r="I32" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>49</v>
+        <v>245</v>
       </c>
       <c r="K32" t="s">
         <v>23</v>
@@ -3542,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="N32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -3556,34 +3565,34 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I33" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J33" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K33" t="s">
         <v>23</v>
@@ -3598,7 +3607,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -3609,34 +3618,34 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E34" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F34" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G34">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I34" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J34" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K34" t="s">
         <v>23</v>
@@ -3651,51 +3660,51 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
       </c>
       <c r="Q34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F35" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H35" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I35" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J35" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K35" t="s">
         <v>23</v>
       </c>
       <c r="L35">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
@@ -3704,45 +3713,45 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
       </c>
       <c r="Q35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E36" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G36">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I36" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J36" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K36" t="s">
         <v>23</v>
@@ -3757,51 +3766,51 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
       </c>
       <c r="Q36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E37" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H37" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I37" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J37" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K37" t="s">
         <v>23</v>
       </c>
       <c r="L37">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
@@ -3810,45 +3819,45 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
       </c>
       <c r="Q37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E38" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F38" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G38">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H38" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I38" t="s">
         <v>53</v>
       </c>
       <c r="J38" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K38" t="s">
         <v>23</v>
@@ -3863,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -3874,40 +3883,40 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F39" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I39" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J39" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K39" t="s">
         <v>23</v>
       </c>
       <c r="L39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
@@ -3916,7 +3925,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
@@ -3927,40 +3936,40 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F40" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G40">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I40" t="s">
         <v>21</v>
       </c>
       <c r="J40" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
       </c>
       <c r="L40">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
@@ -3969,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
@@ -3980,34 +3989,34 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D41" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E41" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H41" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I41" t="s">
         <v>21</v>
       </c>
       <c r="J41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
@@ -4022,7 +4031,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
@@ -4033,40 +4042,40 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E42" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G42">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H42" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I42" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
@@ -4075,51 +4084,51 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
       </c>
       <c r="Q42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C43" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E43" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F43" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G43">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I43" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J43" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
       </c>
       <c r="L43">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
@@ -4128,7 +4137,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
@@ -4139,41 +4148,41 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E44" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F44" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I44" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J44" t="s">
+        <v>66</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44">
         <v>30</v>
       </c>
-      <c r="K44" t="s">
-        <v>23</v>
-      </c>
-      <c r="L44">
-        <v>12</v>
-      </c>
       <c r="M44" t="b">
         <v>0</v>
       </c>
@@ -4181,113 +4190,113 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
       </c>
       <c r="Q44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
+        <v>29</v>
+      </c>
+      <c r="B45" t="s">
+        <v>378</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" t="s">
+        <v>61</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45" t="s">
+        <v>96</v>
+      </c>
+      <c r="J45" t="s">
         <v>30</v>
       </c>
-      <c r="B45" t="s">
-        <v>379</v>
-      </c>
-      <c r="C45" t="s">
-        <v>97</v>
-      </c>
-      <c r="D45" t="s">
-        <v>98</v>
-      </c>
-      <c r="E45" t="s">
-        <v>99</v>
-      </c>
-      <c r="F45" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45">
-        <v>100</v>
-      </c>
-      <c r="H45" t="s">
-        <v>20</v>
-      </c>
-      <c r="I45" t="s">
-        <v>101</v>
-      </c>
-      <c r="J45" t="s">
-        <v>102</v>
-      </c>
       <c r="K45" t="s">
         <v>23</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
       </c>
       <c r="N45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
       </c>
       <c r="Q45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E46" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F46" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G46">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H46" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J46" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
       </c>
       <c r="L46">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
       <c r="N46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
@@ -4298,22 +4307,22 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C47" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E47" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F47" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G47">
         <v>500</v>
@@ -4325,13 +4334,13 @@
         <v>107</v>
       </c>
       <c r="J47" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
@@ -4340,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
@@ -4351,40 +4360,40 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F48" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H48" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I48" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J48" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
       </c>
       <c r="L48">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
@@ -4393,51 +4402,51 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
       </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C49" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E49" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G49">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I49" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -4446,51 +4455,51 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>383</v>
+      </c>
+      <c r="C50" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" t="s">
+        <v>113</v>
+      </c>
+      <c r="E50" t="s">
+        <v>114</v>
+      </c>
+      <c r="F50" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50">
+        <v>300</v>
+      </c>
+      <c r="H50" t="s">
         <v>35</v>
       </c>
-      <c r="B50" t="s">
-        <v>384</v>
-      </c>
-      <c r="C50" t="s">
-        <v>117</v>
-      </c>
-      <c r="D50" t="s">
-        <v>118</v>
-      </c>
-      <c r="E50" t="s">
-        <v>119</v>
-      </c>
-      <c r="F50" t="s">
-        <v>120</v>
-      </c>
-      <c r="G50">
-        <v>500</v>
-      </c>
-      <c r="H50" t="s">
-        <v>42</v>
-      </c>
       <c r="I50" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
       </c>
       <c r="L50">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -4499,7 +4508,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
@@ -4510,40 +4519,40 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E51" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F51" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G51">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H51" t="s">
         <v>42</v>
       </c>
       <c r="I51" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J51" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -4552,51 +4561,51 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
       </c>
       <c r="Q51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B52" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D52" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E52" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F52" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G52">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H52" t="s">
         <v>42</v>
       </c>
       <c r="I52" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J52" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
       </c>
       <c r="L52">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
@@ -4605,45 +4614,45 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
       </c>
       <c r="Q52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C53" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D53" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E53" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F53" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G53">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H53" t="s">
         <v>42</v>
       </c>
       <c r="I53" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J53" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
@@ -4658,51 +4667,51 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
       </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F54" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G54">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H54" t="s">
         <v>42</v>
       </c>
       <c r="I54" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4711,7 +4720,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -4722,40 +4731,40 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D55" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E55" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F55" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H55" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I55" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J55" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -4764,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
@@ -4775,63 +4784,63 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E56" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F56" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G56">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I56" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
       </c>
       <c r="Q56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>
@@ -4840,10 +4849,10 @@
         <v>139</v>
       </c>
       <c r="E57" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F57" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G57">
         <v>1000</v>
@@ -4867,10 +4876,10 @@
         <v>1</v>
       </c>
       <c r="N57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -4881,22 +4890,22 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C58" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D58" t="s">
         <v>139</v>
       </c>
       <c r="E58" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F58" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G58">
         <v>1000</v>
@@ -4908,7 +4917,7 @@
         <v>142</v>
       </c>
       <c r="J58" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
@@ -4923,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -4934,193 +4943,193 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B59" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C59" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D59" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E59" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F59" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G59">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H59" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I59" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J59" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" t="b">
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D60" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E60" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F60" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H60" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I60" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J60" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K60" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L60">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
       </c>
       <c r="N60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D61" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E61" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F61" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G61">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I61" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J61" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K61" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L61">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
       </c>
       <c r="N61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C62" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D62" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E62" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F62" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G62">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H62" t="s">
         <v>42</v>
       </c>
       <c r="I62" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J62" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
@@ -5135,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5146,22 +5155,22 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B63" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C63" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D63" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E63" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F63" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G63">
         <v>500</v>
@@ -5173,7 +5182,7 @@
         <v>21</v>
       </c>
       <c r="J63" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
@@ -5188,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5199,25 +5208,25 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B64" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C64" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D64" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E64" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F64" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G64">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H64" t="s">
         <v>42</v>
@@ -5226,7 +5235,7 @@
         <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
@@ -5241,7 +5250,7 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5252,37 +5261,37 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
+        <v>49</v>
+      </c>
+      <c r="B65" t="s">
+        <v>398</v>
+      </c>
+      <c r="C65" t="s">
+        <v>175</v>
+      </c>
+      <c r="D65" t="s">
+        <v>176</v>
+      </c>
+      <c r="E65" t="s">
+        <v>177</v>
+      </c>
+      <c r="F65" t="s">
+        <v>178</v>
+      </c>
+      <c r="G65">
         <v>50</v>
       </c>
-      <c r="B65" t="s">
-        <v>399</v>
-      </c>
-      <c r="C65" t="s">
-        <v>180</v>
-      </c>
-      <c r="D65" t="s">
-        <v>181</v>
-      </c>
-      <c r="E65" t="s">
-        <v>182</v>
-      </c>
-      <c r="F65" t="s">
-        <v>183</v>
-      </c>
-      <c r="G65">
-        <v>12</v>
-      </c>
       <c r="H65" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K65" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L65">
         <v>12</v>
@@ -5294,7 +5303,7 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5305,40 +5314,40 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B66" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C66" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D66" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E66" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F66" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G66">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H66" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I66" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J66" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K66" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5347,7 +5356,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5358,40 +5367,40 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B67" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C67" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D67" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E67" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F67" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G67">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H67" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I67" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J67" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5400,7 +5409,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5411,40 +5420,40 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
+        <v>52</v>
+      </c>
+      <c r="B68" t="s">
+        <v>401</v>
+      </c>
+      <c r="C68" t="s">
+        <v>193</v>
+      </c>
+      <c r="D68" t="s">
+        <v>181</v>
+      </c>
+      <c r="E68" t="s">
+        <v>182</v>
+      </c>
+      <c r="F68" t="s">
+        <v>183</v>
+      </c>
+      <c r="G68">
+        <v>24</v>
+      </c>
+      <c r="H68" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" t="s">
         <v>53</v>
       </c>
-      <c r="B68" t="s">
-        <v>402</v>
-      </c>
-      <c r="C68" t="s">
-        <v>31</v>
-      </c>
-      <c r="D68" t="s">
-        <v>194</v>
-      </c>
-      <c r="E68" t="s">
-        <v>195</v>
-      </c>
-      <c r="F68" t="s">
-        <v>196</v>
-      </c>
-      <c r="G68">
-        <v>1.5</v>
-      </c>
-      <c r="H68" t="s">
-        <v>28</v>
-      </c>
-      <c r="I68" t="s">
-        <v>36</v>
-      </c>
       <c r="J68" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -5453,7 +5462,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -5464,52 +5473,52 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B69" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C69" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E69" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F69" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G69">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H69" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I69" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J69" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
       </c>
       <c r="N69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" t="b">
         <v>1</v>
@@ -5517,93 +5526,93 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B70" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C70" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D70" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E70" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F70" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G70">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H70" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I70" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
       </c>
       <c r="N70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B71" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C71" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D71" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E71" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F71" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G71">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H71" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J71" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -5612,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -5623,19 +5632,19 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B72" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C72" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D72" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E72" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F72" t="s">
         <v>208</v>
@@ -5665,7 +5674,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -5676,19 +5685,19 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B73" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C73" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D73" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F73" t="s">
         <v>208</v>
@@ -5709,7 +5718,7 @@
         <v>23</v>
       </c>
       <c r="L73">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -5718,7 +5727,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -5729,34 +5738,34 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B74" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C74" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D74" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E74" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F74" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H74" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J74" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
@@ -5771,45 +5780,45 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B75" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C75" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D75" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E75" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F75" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G75">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I75" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J75" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
@@ -5824,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -5835,49 +5844,49 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B76" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D76" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E76" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F76" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G76">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J76" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
       </c>
       <c r="N76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -5888,22 +5897,22 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B77" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C77" t="s">
         <v>217</v>
       </c>
       <c r="D77" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E77" t="s">
         <v>219</v>
       </c>
       <c r="F77" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G77">
         <v>20</v>
@@ -5930,60 +5939,60 @@
         <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B78" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C78" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D78" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E78" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F78" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G78">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H78" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J78" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
       </c>
       <c r="N78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -5994,34 +6003,34 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B79" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C79" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D79" t="s">
         <v>202</v>
       </c>
       <c r="E79" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F79" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G79">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H79" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J79" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
@@ -6036,7 +6045,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6047,40 +6056,40 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B80" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C80" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D80" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E80" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F80" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G80">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H80" t="s">
         <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J80" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6089,51 +6098,51 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B81" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C81" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D81" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E81" t="s">
         <v>229</v>
       </c>
       <c r="F81" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H81" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J81" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6142,7 +6151,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6153,40 +6162,40 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B82" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C82" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D82" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E82" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F82" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G82">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I82" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J82" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -6195,45 +6204,45 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B83" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E83" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F83" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G83">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H83" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I83" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J83" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
@@ -6248,7 +6257,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6259,10 +6268,10 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B84" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C84" t="s">
         <v>186</v>
@@ -6271,13 +6280,13 @@
         <v>202</v>
       </c>
       <c r="E84" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F84" t="s">
         <v>204</v>
       </c>
       <c r="G84">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H84" t="s">
         <v>35</v>
@@ -6301,7 +6310,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6312,10 +6321,10 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B85" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C85" t="s">
         <v>186</v>
@@ -6330,7 +6339,7 @@
         <v>204</v>
       </c>
       <c r="G85">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H85" t="s">
         <v>35</v>
@@ -6354,7 +6363,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6365,41 +6374,41 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C86" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D86" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E86" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F86" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G86">
+        <v>250</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86" t="s">
+        <v>191</v>
+      </c>
+      <c r="J86" t="s">
+        <v>192</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86">
         <v>6</v>
       </c>
-      <c r="H86" t="s">
-        <v>20</v>
-      </c>
-      <c r="I86" t="s">
-        <v>239</v>
-      </c>
-      <c r="J86" t="s">
-        <v>235</v>
-      </c>
-      <c r="K86" t="s">
-        <v>23</v>
-      </c>
-      <c r="L86">
-        <v>1</v>
-      </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
@@ -6407,65 +6416,118 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C87" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D87" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E87" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G87">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H87" t="s">
         <v>20</v>
       </c>
       <c r="I87" t="s">
+        <v>239</v>
+      </c>
+      <c r="J87" t="s">
+        <v>235</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" t="b">
+        <v>1</v>
+      </c>
+      <c r="O87" t="s">
+        <v>311</v>
+      </c>
+      <c r="P87" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>72</v>
+      </c>
+      <c r="B88" t="s">
+        <v>421</v>
+      </c>
+      <c r="C88" t="s">
+        <v>197</v>
+      </c>
+      <c r="D88" t="s">
+        <v>198</v>
+      </c>
+      <c r="E88" t="s">
+        <v>199</v>
+      </c>
+      <c r="F88" t="s">
+        <v>240</v>
+      </c>
+      <c r="G88">
+        <v>4</v>
+      </c>
+      <c r="H88" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" t="s">
         <v>21</v>
       </c>
-      <c r="J87" t="s">
+      <c r="J88" t="s">
         <v>201</v>
       </c>
-      <c r="K87" t="s">
-        <v>23</v>
-      </c>
-      <c r="L87">
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88">
         <v>10</v>
       </c>
-      <c r="M87" t="b">
-        <v>0</v>
-      </c>
-      <c r="N87" t="b">
-        <v>0</v>
-      </c>
-      <c r="O87" t="s">
+      <c r="M88" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" t="b">
+        <v>0</v>
+      </c>
+      <c r="O88" t="s">
         <v>312</v>
       </c>
-      <c r="P87" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q87" t="b">
+      <c r="P88" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0891B9-594D-4F51-A14E-275C5E850BB7}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF2F0EE-4510-4F8D-8A8D-F9FE17512058}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="29" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="32" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="500">
   <si>
     <t>Codigo</t>
   </si>
@@ -1493,6 +1493,39 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7791708001248.png</t>
+  </si>
+  <si>
+    <t>77953537</t>
+  </si>
+  <si>
+    <t>Bombón</t>
+  </si>
+  <si>
+    <t>de chocolate</t>
+  </si>
+  <si>
+    <t>rosa</t>
+  </si>
+  <si>
+    <t>Bon O Bon</t>
+  </si>
+  <si>
+    <t>flow-pack</t>
+  </si>
+  <si>
+    <t>Bombones</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\77953537.png</t>
+  </si>
+  <si>
+    <t>77958921</t>
+  </si>
+  <si>
+    <t>leche</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\77958921.png</t>
   </si>
 </sst>
 </file>
@@ -1844,8 +1877,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6031AD-E2E8-40E5-851D-8D752CD0A303}">
-  <dimension ref="A1:Q88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280DF2F5-498C-48C5-BB25-0AA30838372D}">
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3194,40 +3227,40 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>359</v>
+        <v>489</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>491</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>492</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>493</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H26" t="s">
         <v>20</v>
       </c>
       <c r="I26" t="s">
-        <v>21</v>
+        <v>494</v>
       </c>
       <c r="J26" t="s">
-        <v>22</v>
+        <v>495</v>
       </c>
       <c r="K26" t="s">
         <v>23</v>
       </c>
       <c r="L26">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M26" t="b">
         <v>0</v>
@@ -3236,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>251</v>
+        <v>496</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -3247,41 +3280,41 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>360</v>
+        <v>497</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>490</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>491</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>498</v>
       </c>
       <c r="F27" t="s">
-        <v>27</v>
+        <v>493</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I27" t="s">
-        <v>29</v>
+        <v>494</v>
       </c>
       <c r="J27" t="s">
+        <v>495</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27">
         <v>30</v>
       </c>
-      <c r="K27" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27">
-        <v>12</v>
-      </c>
       <c r="M27" t="b">
         <v>0</v>
       </c>
@@ -3289,7 +3322,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>252</v>
+        <v>499</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -3300,41 +3333,41 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s">
+        <v>359</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s">
+        <v>22</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28">
         <v>12</v>
       </c>
-      <c r="B28" t="s">
-        <v>361</v>
-      </c>
-      <c r="C28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" t="s">
-        <v>33</v>
-      </c>
-      <c r="F28" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28">
-        <v>500</v>
-      </c>
-      <c r="H28" t="s">
-        <v>35</v>
-      </c>
-      <c r="I28" t="s">
-        <v>36</v>
-      </c>
-      <c r="J28" t="s">
-        <v>37</v>
-      </c>
-      <c r="K28" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28">
-        <v>6</v>
-      </c>
       <c r="M28" t="b">
         <v>0</v>
       </c>
@@ -3342,7 +3375,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -3353,40 +3386,40 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I29" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J29" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K29" t="s">
         <v>23</v>
       </c>
       <c r="L29">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
@@ -3395,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
@@ -3406,40 +3439,40 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H30" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J30" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K30" t="s">
         <v>23</v>
       </c>
       <c r="L30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
@@ -3448,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -3459,25 +3492,25 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C31" t="s">
-        <v>241</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>242</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="F31" t="s">
-        <v>243</v>
+        <v>41</v>
       </c>
       <c r="G31">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="H31" t="s">
         <v>42</v>
@@ -3486,13 +3519,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="K31" t="s">
         <v>23</v>
       </c>
       <c r="L31">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
@@ -3501,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -3512,49 +3545,49 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C32" t="s">
-        <v>197</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>198</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>199</v>
+        <v>46</v>
       </c>
       <c r="F32" t="s">
-        <v>200</v>
+        <v>47</v>
       </c>
       <c r="G32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>245</v>
+        <v>44</v>
       </c>
       <c r="K32" t="s">
         <v>23</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
       </c>
       <c r="N32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -3565,40 +3598,40 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>241</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>242</v>
       </c>
       <c r="E33" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>243</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>170</v>
       </c>
       <c r="H33" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I33" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J33" t="s">
-        <v>49</v>
+        <v>244</v>
       </c>
       <c r="K33" t="s">
         <v>23</v>
       </c>
       <c r="L33">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -3607,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -3618,34 +3651,34 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>197</v>
       </c>
       <c r="D34" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>199</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>200</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H34" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I34" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>30</v>
+        <v>245</v>
       </c>
       <c r="K34" t="s">
         <v>23</v>
@@ -3657,10 +3690,10 @@
         <v>0</v>
       </c>
       <c r="N34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -3671,34 +3704,34 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="G35">
-        <v>400</v>
+        <v>3</v>
       </c>
       <c r="H35" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J35" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="K35" t="s">
         <v>23</v>
@@ -3713,21 +3746,21 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
       </c>
       <c r="Q35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C36" t="s">
         <v>24</v>
@@ -3739,7 +3772,7 @@
         <v>55</v>
       </c>
       <c r="F36" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -3748,7 +3781,7 @@
         <v>28</v>
       </c>
       <c r="I36" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="J36" t="s">
         <v>30</v>
@@ -3757,7 +3790,7 @@
         <v>23</v>
       </c>
       <c r="L36">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
@@ -3766,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -3777,22 +3810,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E37" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F37" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="G37">
         <v>400</v>
@@ -3804,13 +3837,13 @@
         <v>60</v>
       </c>
       <c r="J37" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K37" t="s">
         <v>23</v>
       </c>
       <c r="L37">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
@@ -3819,7 +3852,7 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -3830,40 +3863,40 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C38" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F38" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G38">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I38" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="J38" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="K38" t="s">
         <v>23</v>
       </c>
       <c r="L38">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
@@ -3872,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -3883,40 +3916,40 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D39" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E39" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F39" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G39">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="H39" t="s">
         <v>42</v>
       </c>
       <c r="I39" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J39" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="K39" t="s">
         <v>23</v>
       </c>
       <c r="L39">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
@@ -3925,51 +3958,51 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
       </c>
       <c r="Q39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E40" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H40" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I40" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J40" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
       </c>
       <c r="L40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
@@ -3978,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
@@ -3989,40 +4022,40 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C41" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="F41" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G41">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s">
         <v>42</v>
       </c>
       <c r="I41" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J41" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
       </c>
       <c r="L41">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
@@ -4031,7 +4064,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
@@ -4042,40 +4075,40 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E42" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F42" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I42" t="s">
         <v>21</v>
       </c>
       <c r="J42" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
       </c>
       <c r="L42">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
@@ -4084,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
@@ -4095,40 +4128,40 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D43" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E43" t="s">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="F43" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G43">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I43" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
       </c>
       <c r="L43">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
@@ -4137,51 +4170,51 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
       </c>
       <c r="Q43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E44" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F44" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G44">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H44" t="s">
         <v>20</v>
       </c>
       <c r="I44" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
       </c>
       <c r="L44">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
@@ -4190,51 +4223,51 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
       </c>
       <c r="Q44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="E45" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="F45" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H45" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I45" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J45" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
       </c>
       <c r="L45">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -4243,60 +4276,60 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
       </c>
       <c r="Q45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E46" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F46" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G46">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="H46" t="s">
         <v>20</v>
       </c>
       <c r="I46" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J46" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
       <c r="N46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
@@ -4307,34 +4340,34 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="E47" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="G47">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I47" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="J47" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
@@ -4349,45 +4382,45 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
       </c>
       <c r="Q47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B48" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E48" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F48" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="G48">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H48" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I48" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J48" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
@@ -4399,10 +4432,10 @@
         <v>0</v>
       </c>
       <c r="N48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
@@ -4413,40 +4446,40 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="D49" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E49" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="F49" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H49" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I49" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J49" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -4455,45 +4488,45 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
       </c>
       <c r="Q49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
+        <v>32</v>
+      </c>
+      <c r="B50" t="s">
+        <v>381</v>
+      </c>
+      <c r="C50" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" t="s">
+        <v>109</v>
+      </c>
+      <c r="E50" t="s">
+        <v>110</v>
+      </c>
+      <c r="F50" t="s">
         <v>34</v>
       </c>
-      <c r="B50" t="s">
-        <v>383</v>
-      </c>
-      <c r="C50" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50" t="s">
-        <v>114</v>
-      </c>
-      <c r="F50" t="s">
-        <v>115</v>
-      </c>
       <c r="G50">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H50" t="s">
         <v>35</v>
       </c>
       <c r="I50" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="J50" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
@@ -4508,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
@@ -4519,40 +4552,40 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="E51" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="F51" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G51">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I51" t="s">
         <v>21</v>
       </c>
       <c r="J51" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -4561,45 +4594,45 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
       </c>
       <c r="Q51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s">
+        <v>383</v>
+      </c>
+      <c r="C52" t="s">
+        <v>112</v>
+      </c>
+      <c r="D52" t="s">
+        <v>113</v>
+      </c>
+      <c r="E52" t="s">
+        <v>114</v>
+      </c>
+      <c r="F52" t="s">
+        <v>115</v>
+      </c>
+      <c r="G52">
+        <v>300</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52" t="s">
         <v>36</v>
       </c>
-      <c r="B52" t="s">
-        <v>385</v>
-      </c>
-      <c r="C52" t="s">
-        <v>121</v>
-      </c>
-      <c r="D52" t="s">
-        <v>122</v>
-      </c>
-      <c r="E52" t="s">
-        <v>32</v>
-      </c>
-      <c r="F52" t="s">
-        <v>123</v>
-      </c>
-      <c r="G52">
-        <v>250</v>
-      </c>
-      <c r="H52" t="s">
-        <v>42</v>
-      </c>
-      <c r="I52" t="s">
-        <v>124</v>
-      </c>
       <c r="J52" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
@@ -4614,51 +4647,51 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
       </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B53" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C53" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E53" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F53" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="G53">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="H53" t="s">
         <v>42</v>
       </c>
       <c r="I53" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -4667,7 +4700,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -4678,40 +4711,40 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B54" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C54" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="D54" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="E54" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="F54" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="G54">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H54" t="s">
         <v>42</v>
       </c>
       <c r="I54" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="J54" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4720,7 +4753,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -4731,40 +4764,40 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D55" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E55" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F55" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G55">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="H55" t="s">
         <v>42</v>
       </c>
       <c r="I55" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J55" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -4773,51 +4806,51 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
       </c>
       <c r="Q55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D56" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E56" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="F56" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="H56" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I56" t="s">
         <v>21</v>
       </c>
       <c r="J56" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -4826,7 +4859,7 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
@@ -4837,128 +4870,128 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B57" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D57" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E57" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="F57" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G57">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="H57" t="s">
         <v>42</v>
       </c>
       <c r="I57" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="J57" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
       </c>
       <c r="Q57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E58" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="F58" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="G58">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I58" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B59" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C59" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D59" t="s">
         <v>139</v>
       </c>
       <c r="E59" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F59" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G59">
         <v>1000</v>
@@ -4970,7 +5003,7 @@
         <v>142</v>
       </c>
       <c r="J59" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
@@ -4982,10 +5015,10 @@
         <v>1</v>
       </c>
       <c r="N59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -4996,102 +5029,102 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B60" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D60" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E60" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F60" t="s">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="G60">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H60" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J60" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B61" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D61" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="E61" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F61" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I61" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J61" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="K61" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L61">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -5102,34 +5135,34 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B62" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C62" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D62" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="E62" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="F62" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G62">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H62" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I62" t="s">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="J62" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
@@ -5144,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5155,87 +5188,87 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C63" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D63" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E63" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="F63" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="G63">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I63" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="J63" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="K63" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L63">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
       </c>
       <c r="N63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B64" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C64" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E64" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F64" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="G64">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H64" t="s">
         <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J64" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
@@ -5250,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5261,25 +5294,25 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B65" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C65" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="D65" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="E65" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="F65" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="G65">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H65" t="s">
         <v>42</v>
@@ -5288,7 +5321,7 @@
         <v>21</v>
       </c>
       <c r="J65" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
@@ -5303,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5314,37 +5347,37 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B66" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C66" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D66" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="E66" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F66" t="s">
-        <v>183</v>
+        <v>70</v>
       </c>
       <c r="G66">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H66" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="K66" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L66">
         <v>12</v>
@@ -5356,7 +5389,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5367,40 +5400,40 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C67" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D67" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E67" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F67" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G67">
-        <v>360</v>
+        <v>50</v>
       </c>
       <c r="H67" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5409,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5420,13 +5453,13 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B68" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C68" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D68" t="s">
         <v>181</v>
@@ -5438,7 +5471,7 @@
         <v>183</v>
       </c>
       <c r="G68">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H68" t="s">
         <v>20</v>
@@ -5450,10 +5483,10 @@
         <v>184</v>
       </c>
       <c r="K68" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L68">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -5462,7 +5495,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -5473,34 +5506,34 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="D69" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E69" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F69" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G69">
-        <v>1.5</v>
+        <v>360</v>
       </c>
       <c r="H69" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="I69" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
       <c r="J69" t="s">
-        <v>37</v>
+        <v>192</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
@@ -5515,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -5526,52 +5559,52 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B70" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C70" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D70" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="E70" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="F70" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="G70">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H70" t="s">
         <v>20</v>
       </c>
       <c r="I70" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J70" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
       </c>
       <c r="N70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="b">
         <v>1</v>
@@ -5579,40 +5612,40 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B71" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C71" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D71" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E71" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F71" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G71">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="H71" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J71" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -5621,104 +5654,104 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B72" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D72" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E72" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F72" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G72">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="H72" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I72" t="s">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
       </c>
       <c r="N72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B73" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C73" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="D73" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E73" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="F73" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G73">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H73" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I73" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J73" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -5727,7 +5760,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -5738,10 +5771,10 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B74" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C74" t="s">
         <v>205</v>
@@ -5750,7 +5783,7 @@
         <v>206</v>
       </c>
       <c r="E74" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F74" t="s">
         <v>208</v>
@@ -5771,7 +5804,7 @@
         <v>23</v>
       </c>
       <c r="L74">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -5780,7 +5813,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -5791,40 +5824,40 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B75" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C75" t="s">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="D75" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E75" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F75" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H75" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J75" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -5833,45 +5866,45 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B76" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>205</v>
       </c>
       <c r="D76" t="s">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="E76" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F76" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G76">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H76" t="s">
         <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="J76" t="s">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
@@ -5886,60 +5919,60 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B77" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C77" t="s">
-        <v>217</v>
+        <v>145</v>
       </c>
       <c r="D77" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E77" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F77" t="s">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="G77">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H77" t="s">
         <v>20</v>
       </c>
       <c r="I77" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="J77" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -5950,155 +5983,155 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B78" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C78" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D78" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="E78" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F78" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="G78">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H78" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J78" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
       </c>
       <c r="N78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B79" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C79" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D79" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E79" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F79" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="G79">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H79" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I79" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J79" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B80" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D80" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E80" t="s">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="F80" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G80">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="H80" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I80" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="J80" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6109,40 +6142,40 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B81" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C81" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D81" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E81" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="F81" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="G81">
-        <v>237</v>
+        <v>60</v>
       </c>
       <c r="H81" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I81" t="s">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="J81" t="s">
-        <v>125</v>
+        <v>224</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6151,51 +6184,51 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B82" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C82" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D82" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="E82" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F82" t="s">
-        <v>47</v>
+        <v>226</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H82" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J82" t="s">
-        <v>44</v>
+        <v>192</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -6204,51 +6237,51 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C83" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D83" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="E83" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F83" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="G83">
-        <v>1.5</v>
+        <v>237</v>
       </c>
       <c r="H83" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="J83" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -6257,51 +6290,51 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C84" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="E84" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F84" t="s">
-        <v>204</v>
+        <v>47</v>
       </c>
       <c r="G84">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I84" t="s">
-        <v>191</v>
+        <v>60</v>
       </c>
       <c r="J84" t="s">
-        <v>192</v>
+        <v>44</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -6310,45 +6343,45 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C85" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E85" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F85" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G85">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="H85" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I85" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J85" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
@@ -6363,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6374,10 +6407,10 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B86" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C86" t="s">
         <v>186</v>
@@ -6386,7 +6419,7 @@
         <v>202</v>
       </c>
       <c r="E86" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F86" t="s">
         <v>204</v>
@@ -6416,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -6427,41 +6460,41 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B87" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C87" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D87" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E87" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F87" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G87">
+        <v>150</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87" t="s">
+        <v>191</v>
+      </c>
+      <c r="J87" t="s">
+        <v>192</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87">
         <v>6</v>
       </c>
-      <c r="H87" t="s">
-        <v>20</v>
-      </c>
-      <c r="I87" t="s">
-        <v>239</v>
-      </c>
-      <c r="J87" t="s">
-        <v>235</v>
-      </c>
-      <c r="K87" t="s">
-        <v>23</v>
-      </c>
-      <c r="L87">
-        <v>1</v>
-      </c>
       <c r="M87" t="b">
         <v>0</v>
       </c>
@@ -6469,65 +6502,171 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
+        <v>70</v>
+      </c>
+      <c r="B88" t="s">
+        <v>419</v>
+      </c>
+      <c r="C88" t="s">
+        <v>186</v>
+      </c>
+      <c r="D88" t="s">
+        <v>202</v>
+      </c>
+      <c r="E88" t="s">
+        <v>234</v>
+      </c>
+      <c r="F88" t="s">
+        <v>204</v>
+      </c>
+      <c r="G88">
+        <v>250</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88" t="s">
+        <v>191</v>
+      </c>
+      <c r="J88" t="s">
+        <v>192</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88">
+        <v>6</v>
+      </c>
+      <c r="M88" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" t="b">
+        <v>1</v>
+      </c>
+      <c r="O88" t="s">
+        <v>310</v>
+      </c>
+      <c r="P88" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>71</v>
+      </c>
+      <c r="B89" t="s">
+        <v>420</v>
+      </c>
+      <c r="C89" t="s">
+        <v>235</v>
+      </c>
+      <c r="D89" t="s">
+        <v>236</v>
+      </c>
+      <c r="E89" t="s">
+        <v>237</v>
+      </c>
+      <c r="F89" t="s">
+        <v>238</v>
+      </c>
+      <c r="G89">
+        <v>6</v>
+      </c>
+      <c r="H89" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" t="s">
+        <v>239</v>
+      </c>
+      <c r="J89" t="s">
+        <v>235</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89" t="b">
+        <v>0</v>
+      </c>
+      <c r="N89" t="b">
+        <v>1</v>
+      </c>
+      <c r="O89" t="s">
+        <v>311</v>
+      </c>
+      <c r="P89" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
         <v>72</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B90" t="s">
         <v>421</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C90" t="s">
         <v>197</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D90" t="s">
         <v>198</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E90" t="s">
         <v>199</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F90" t="s">
         <v>240</v>
       </c>
-      <c r="G88">
+      <c r="G90">
         <v>4</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H90" t="s">
         <v>20</v>
       </c>
-      <c r="I88" t="s">
+      <c r="I90" t="s">
         <v>21</v>
       </c>
-      <c r="J88" t="s">
+      <c r="J90" t="s">
         <v>201</v>
       </c>
-      <c r="K88" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88">
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90">
         <v>10</v>
       </c>
-      <c r="M88" t="b">
-        <v>0</v>
-      </c>
-      <c r="N88" t="b">
-        <v>0</v>
-      </c>
-      <c r="O88" t="s">
+      <c r="M90" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" t="b">
+        <v>0</v>
+      </c>
+      <c r="O90" t="s">
         <v>312</v>
       </c>
-      <c r="P88" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q88" t="b">
+      <c r="P90" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q90" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF2F0EE-4510-4F8D-8A8D-F9FE17512058}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0557DC84-2DE3-4EB3-B1D2-B622238E81A8}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="32" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="33" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="503">
   <si>
     <t>Codigo</t>
   </si>
@@ -1526,6 +1526,15 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\77958921.png</t>
+  </si>
+  <si>
+    <t>7793253006822</t>
+  </si>
+  <si>
+    <t>Selton</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7793253006822.png</t>
   </si>
 </sst>
 </file>
@@ -1877,8 +1886,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280DF2F5-498C-48C5-BB25-0AA30838372D}">
-  <dimension ref="A1:Q90"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA53027-F7D8-4A70-9EEA-701DAD25978D}">
+  <dimension ref="A1:Q91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3333,37 +3342,37 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>359</v>
+        <v>500</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="F28" t="s">
-        <v>19</v>
+        <v>501</v>
       </c>
       <c r="G28">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H28" t="s">
         <v>20</v>
       </c>
       <c r="I28" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J28" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="K28" t="s">
-        <v>23</v>
+        <v>323</v>
       </c>
       <c r="L28">
         <v>12</v>
@@ -3375,7 +3384,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>251</v>
+        <v>502</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -3386,34 +3395,34 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H29" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I29" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K29" t="s">
         <v>23</v>
@@ -3428,7 +3437,7 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
@@ -3439,41 +3448,41 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>360</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" t="s">
+        <v>29</v>
+      </c>
+      <c r="J30" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30">
         <v>12</v>
       </c>
-      <c r="B30" t="s">
-        <v>361</v>
-      </c>
-      <c r="C30" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" t="s">
-        <v>33</v>
-      </c>
-      <c r="F30" t="s">
-        <v>34</v>
-      </c>
-      <c r="G30">
-        <v>500</v>
-      </c>
-      <c r="H30" t="s">
-        <v>35</v>
-      </c>
-      <c r="I30" t="s">
-        <v>36</v>
-      </c>
-      <c r="J30" t="s">
-        <v>37</v>
-      </c>
-      <c r="K30" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30">
-        <v>6</v>
-      </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
@@ -3481,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -3492,40 +3501,40 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I31" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J31" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K31" t="s">
         <v>23</v>
       </c>
       <c r="L31">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
@@ -3534,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -3545,40 +3554,40 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F32" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K32" t="s">
         <v>23</v>
       </c>
       <c r="L32">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
@@ -3587,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -3598,40 +3607,40 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C33" t="s">
-        <v>241</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>242</v>
+        <v>45</v>
       </c>
       <c r="E33" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="F33" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="G33">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
       </c>
       <c r="J33" t="s">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="K33" t="s">
         <v>23</v>
       </c>
       <c r="L33">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -3640,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -3651,49 +3660,49 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C34" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="D34" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="E34" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F34" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I34" t="s">
         <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K34" t="s">
         <v>23</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
       </c>
       <c r="N34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -3704,34 +3713,34 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>197</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="E35" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H35" t="s">
         <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s">
-        <v>49</v>
+        <v>245</v>
       </c>
       <c r="K35" t="s">
         <v>23</v>
@@ -3743,10 +3752,10 @@
         <v>0</v>
       </c>
       <c r="N35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -3757,34 +3766,34 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E36" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H36" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I36" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J36" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K36" t="s">
         <v>23</v>
@@ -3799,7 +3808,7 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -3810,34 +3819,34 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E37" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F37" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G37">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I37" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J37" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K37" t="s">
         <v>23</v>
@@ -3852,51 +3861,51 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
       </c>
       <c r="Q37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F38" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H38" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I38" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J38" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K38" t="s">
         <v>23</v>
       </c>
       <c r="L38">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
@@ -3905,45 +3914,45 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
       </c>
       <c r="Q38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E39" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G39">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I39" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J39" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K39" t="s">
         <v>23</v>
@@ -3958,51 +3967,51 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
       </c>
       <c r="Q39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D40" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E40" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F40" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G40">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H40" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I40" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J40" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
       </c>
       <c r="L40">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
@@ -4011,45 +4020,45 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
       </c>
       <c r="Q40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E41" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F41" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G41">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H41" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I41" t="s">
         <v>53</v>
       </c>
       <c r="J41" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
@@ -4064,7 +4073,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
@@ -4075,40 +4084,40 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D42" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E42" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F42" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I42" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J42" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
       </c>
       <c r="L42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
@@ -4117,7 +4126,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
@@ -4128,40 +4137,40 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F43" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G43">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I43" t="s">
         <v>21</v>
       </c>
       <c r="J43" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
       </c>
       <c r="L43">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
@@ -4170,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
@@ -4181,34 +4190,34 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D44" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E44" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F44" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G44">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H44" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I44" t="s">
         <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
@@ -4223,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -4234,40 +4243,40 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D45" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F45" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G45">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H45" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I45" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -4276,51 +4285,51 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
       </c>
       <c r="Q45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C46" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D46" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E46" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F46" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G46">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H46" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I46" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J46" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
       </c>
       <c r="L46">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
@@ -4329,7 +4338,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
@@ -4340,41 +4349,41 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E47" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F47" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H47" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I47" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J47" t="s">
+        <v>66</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47">
         <v>30</v>
       </c>
-      <c r="K47" t="s">
-        <v>23</v>
-      </c>
-      <c r="L47">
-        <v>12</v>
-      </c>
       <c r="M47" t="b">
         <v>0</v>
       </c>
@@ -4382,113 +4391,113 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
       </c>
       <c r="Q47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
+        <v>29</v>
+      </c>
+      <c r="B48" t="s">
+        <v>378</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48" t="s">
+        <v>55</v>
+      </c>
+      <c r="F48" t="s">
+        <v>61</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48" t="s">
+        <v>96</v>
+      </c>
+      <c r="J48" t="s">
         <v>30</v>
       </c>
-      <c r="B48" t="s">
-        <v>379</v>
-      </c>
-      <c r="C48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D48" t="s">
-        <v>98</v>
-      </c>
-      <c r="E48" t="s">
-        <v>99</v>
-      </c>
-      <c r="F48" t="s">
-        <v>100</v>
-      </c>
-      <c r="G48">
-        <v>100</v>
-      </c>
-      <c r="H48" t="s">
-        <v>20</v>
-      </c>
-      <c r="I48" t="s">
-        <v>101</v>
-      </c>
-      <c r="J48" t="s">
-        <v>102</v>
-      </c>
       <c r="K48" t="s">
         <v>23</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
       </c>
       <c r="N48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
       </c>
       <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E49" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F49" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G49">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H49" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J49" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
       </c>
       <c r="N49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
@@ -4499,22 +4508,22 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E50" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F50" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G50">
         <v>500</v>
@@ -4526,13 +4535,13 @@
         <v>107</v>
       </c>
       <c r="J50" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -4541,7 +4550,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
@@ -4552,40 +4561,40 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E51" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F51" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H51" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I51" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J51" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -4594,51 +4603,51 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
       </c>
       <c r="Q51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C52" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E52" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F52" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G52">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I52" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J52" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
@@ -4647,51 +4656,51 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
       </c>
       <c r="Q52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
+        <v>34</v>
+      </c>
+      <c r="B53" t="s">
+        <v>383</v>
+      </c>
+      <c r="C53" t="s">
+        <v>112</v>
+      </c>
+      <c r="D53" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" t="s">
+        <v>114</v>
+      </c>
+      <c r="F53" t="s">
+        <v>115</v>
+      </c>
+      <c r="G53">
+        <v>300</v>
+      </c>
+      <c r="H53" t="s">
         <v>35</v>
       </c>
-      <c r="B53" t="s">
-        <v>384</v>
-      </c>
-      <c r="C53" t="s">
-        <v>117</v>
-      </c>
-      <c r="D53" t="s">
-        <v>118</v>
-      </c>
-      <c r="E53" t="s">
-        <v>119</v>
-      </c>
-      <c r="F53" t="s">
-        <v>120</v>
-      </c>
-      <c r="G53">
-        <v>500</v>
-      </c>
-      <c r="H53" t="s">
-        <v>42</v>
-      </c>
       <c r="I53" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -4700,7 +4709,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -4711,40 +4720,40 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B54" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C54" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F54" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G54">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H54" t="s">
         <v>42</v>
       </c>
       <c r="I54" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4753,51 +4762,51 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
       </c>
       <c r="Q54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B55" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D55" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E55" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F55" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G55">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H55" t="s">
         <v>42</v>
       </c>
       <c r="I55" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J55" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -4806,45 +4815,45 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
       </c>
       <c r="Q55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B56" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C56" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D56" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E56" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F56" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G56">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H56" t="s">
         <v>42</v>
       </c>
       <c r="I56" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J56" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
@@ -4859,51 +4868,51 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
       </c>
       <c r="Q56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B57" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C57" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D57" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E57" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F57" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G57">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H57" t="s">
         <v>42</v>
       </c>
       <c r="I57" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
       </c>
       <c r="L57">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
@@ -4912,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -4923,40 +4932,40 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C58" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D58" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E58" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F58" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H58" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J58" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -4965,7 +4974,7 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -4976,63 +4985,63 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E59" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F59" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G59">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I59" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J59" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B60" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C60" t="s">
         <v>138</v>
@@ -5041,10 +5050,10 @@
         <v>139</v>
       </c>
       <c r="E60" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F60" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G60">
         <v>1000</v>
@@ -5068,10 +5077,10 @@
         <v>1</v>
       </c>
       <c r="N60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
@@ -5082,22 +5091,22 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B61" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C61" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D61" t="s">
         <v>139</v>
       </c>
       <c r="E61" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F61" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G61">
         <v>1000</v>
@@ -5109,7 +5118,7 @@
         <v>142</v>
       </c>
       <c r="J61" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
@@ -5124,7 +5133,7 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -5135,193 +5144,193 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B62" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C62" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D62" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E62" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F62" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G62">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H62" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I62" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J62" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B63" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C63" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D63" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E63" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F63" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H63" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I63" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J63" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K63" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L63">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
       </c>
       <c r="N63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C64" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D64" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E64" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F64" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G64">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I64" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J64" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K64" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L64">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B65" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C65" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D65" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E65" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F65" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G65">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H65" t="s">
         <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J65" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
@@ -5336,7 +5345,7 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5347,22 +5356,22 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B66" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C66" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E66" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F66" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G66">
         <v>500</v>
@@ -5374,7 +5383,7 @@
         <v>21</v>
       </c>
       <c r="J66" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
@@ -5389,7 +5398,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5400,25 +5409,25 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B67" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C67" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D67" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E67" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F67" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G67">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H67" t="s">
         <v>42</v>
@@ -5427,7 +5436,7 @@
         <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
@@ -5442,7 +5451,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5453,37 +5462,37 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
+        <v>49</v>
+      </c>
+      <c r="B68" t="s">
+        <v>398</v>
+      </c>
+      <c r="C68" t="s">
+        <v>175</v>
+      </c>
+      <c r="D68" t="s">
+        <v>176</v>
+      </c>
+      <c r="E68" t="s">
+        <v>177</v>
+      </c>
+      <c r="F68" t="s">
+        <v>178</v>
+      </c>
+      <c r="G68">
         <v>50</v>
       </c>
-      <c r="B68" t="s">
-        <v>399</v>
-      </c>
-      <c r="C68" t="s">
-        <v>180</v>
-      </c>
-      <c r="D68" t="s">
-        <v>181</v>
-      </c>
-      <c r="E68" t="s">
-        <v>182</v>
-      </c>
-      <c r="F68" t="s">
-        <v>183</v>
-      </c>
-      <c r="G68">
-        <v>12</v>
-      </c>
       <c r="H68" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K68" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L68">
         <v>12</v>
@@ -5495,7 +5504,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -5506,40 +5515,40 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B69" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C69" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D69" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E69" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F69" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G69">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H69" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J69" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K69" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -5548,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -5559,40 +5568,40 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C70" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D70" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E70" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F70" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G70">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H70" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I70" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J70" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -5601,7 +5610,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -5612,40 +5621,40 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
+        <v>52</v>
+      </c>
+      <c r="B71" t="s">
+        <v>401</v>
+      </c>
+      <c r="C71" t="s">
+        <v>193</v>
+      </c>
+      <c r="D71" t="s">
+        <v>181</v>
+      </c>
+      <c r="E71" t="s">
+        <v>182</v>
+      </c>
+      <c r="F71" t="s">
+        <v>183</v>
+      </c>
+      <c r="G71">
+        <v>24</v>
+      </c>
+      <c r="H71" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s">
         <v>53</v>
       </c>
-      <c r="B71" t="s">
-        <v>402</v>
-      </c>
-      <c r="C71" t="s">
-        <v>31</v>
-      </c>
-      <c r="D71" t="s">
-        <v>194</v>
-      </c>
-      <c r="E71" t="s">
-        <v>195</v>
-      </c>
-      <c r="F71" t="s">
-        <v>196</v>
-      </c>
-      <c r="G71">
-        <v>1.5</v>
-      </c>
-      <c r="H71" t="s">
-        <v>28</v>
-      </c>
-      <c r="I71" t="s">
-        <v>36</v>
-      </c>
       <c r="J71" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -5654,7 +5663,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -5665,52 +5674,52 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B72" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C72" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D72" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E72" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F72" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G72">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H72" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I72" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J72" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
       </c>
       <c r="N72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" t="b">
         <v>1</v>
@@ -5718,93 +5727,93 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B73" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C73" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D73" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E73" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F73" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G73">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H73" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I73" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
       </c>
       <c r="N73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B74" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D74" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E74" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F74" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G74">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H74" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I74" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J74" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -5813,7 +5822,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -5824,19 +5833,19 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B75" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C75" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D75" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E75" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F75" t="s">
         <v>208</v>
@@ -5866,7 +5875,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -5877,19 +5886,19 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B76" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C76" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D76" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E76" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F76" t="s">
         <v>208</v>
@@ -5910,7 +5919,7 @@
         <v>23</v>
       </c>
       <c r="L76">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -5919,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -5930,34 +5939,34 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B77" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C77" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D77" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E77" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F77" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H77" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J77" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
@@ -5972,45 +5981,45 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C78" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D78" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E78" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F78" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G78">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J78" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
@@ -6025,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6036,49 +6045,49 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B79" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C79" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D79" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E79" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F79" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G79">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H79" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J79" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6089,22 +6098,22 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C80" t="s">
         <v>217</v>
       </c>
       <c r="D80" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E80" t="s">
         <v>219</v>
       </c>
       <c r="F80" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G80">
         <v>20</v>
@@ -6131,60 +6140,60 @@
         <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B81" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C81" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D81" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E81" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F81" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G81">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H81" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I81" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J81" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6195,34 +6204,34 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B82" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C82" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D82" t="s">
         <v>202</v>
       </c>
       <c r="E82" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F82" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G82">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H82" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J82" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -6237,7 +6246,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6248,40 +6257,40 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B83" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C83" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D83" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E83" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F83" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G83">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H83" t="s">
         <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J83" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -6290,51 +6299,51 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C84" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D84" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E84" t="s">
         <v>229</v>
       </c>
       <c r="F84" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H84" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J84" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -6343,7 +6352,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6354,40 +6363,40 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B85" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E85" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F85" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G85">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I85" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J85" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -6396,45 +6405,45 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B86" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C86" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D86" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E86" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F86" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G86">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H86" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I86" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J86" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
@@ -6449,7 +6458,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -6460,10 +6469,10 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B87" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C87" t="s">
         <v>186</v>
@@ -6472,13 +6481,13 @@
         <v>202</v>
       </c>
       <c r="E87" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F87" t="s">
         <v>204</v>
       </c>
       <c r="G87">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H87" t="s">
         <v>35</v>
@@ -6502,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -6513,10 +6522,10 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B88" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C88" t="s">
         <v>186</v>
@@ -6531,7 +6540,7 @@
         <v>204</v>
       </c>
       <c r="G88">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H88" t="s">
         <v>35</v>
@@ -6555,7 +6564,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -6566,41 +6575,41 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B89" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C89" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E89" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F89" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G89">
+        <v>250</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="I89" t="s">
+        <v>191</v>
+      </c>
+      <c r="J89" t="s">
+        <v>192</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89">
         <v>6</v>
       </c>
-      <c r="H89" t="s">
-        <v>20</v>
-      </c>
-      <c r="I89" t="s">
-        <v>239</v>
-      </c>
-      <c r="J89" t="s">
-        <v>235</v>
-      </c>
-      <c r="K89" t="s">
-        <v>23</v>
-      </c>
-      <c r="L89">
-        <v>1</v>
-      </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
@@ -6608,65 +6617,118 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C90" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D90" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E90" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F90" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G90">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H90" t="s">
         <v>20</v>
       </c>
       <c r="I90" t="s">
+        <v>239</v>
+      </c>
+      <c r="J90" t="s">
+        <v>235</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" t="b">
+        <v>1</v>
+      </c>
+      <c r="O90" t="s">
+        <v>311</v>
+      </c>
+      <c r="P90" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>72</v>
+      </c>
+      <c r="B91" t="s">
+        <v>421</v>
+      </c>
+      <c r="C91" t="s">
+        <v>197</v>
+      </c>
+      <c r="D91" t="s">
+        <v>198</v>
+      </c>
+      <c r="E91" t="s">
+        <v>199</v>
+      </c>
+      <c r="F91" t="s">
+        <v>240</v>
+      </c>
+      <c r="G91">
+        <v>4</v>
+      </c>
+      <c r="H91" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" t="s">
         <v>21</v>
       </c>
-      <c r="J90" t="s">
+      <c r="J91" t="s">
         <v>201</v>
       </c>
-      <c r="K90" t="s">
-        <v>23</v>
-      </c>
-      <c r="L90">
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91">
         <v>10</v>
       </c>
-      <c r="M90" t="b">
-        <v>0</v>
-      </c>
-      <c r="N90" t="b">
-        <v>0</v>
-      </c>
-      <c r="O90" t="s">
+      <c r="M91" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" t="b">
+        <v>0</v>
+      </c>
+      <c r="O91" t="s">
         <v>312</v>
       </c>
-      <c r="P90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q90" t="b">
+      <c r="P91" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0557DC84-2DE3-4EB3-B1D2-B622238E81A8}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FD3919-A901-4AEB-840A-8C9DF606497F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="33" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="34" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="506">
   <si>
     <t>Codigo</t>
   </si>
@@ -1535,6 +1535,15 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7793253006822.png</t>
+  </si>
+  <si>
+    <t>7793890258806</t>
+  </si>
+  <si>
+    <t>Lactal</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7793890258806.png</t>
   </si>
 </sst>
 </file>
@@ -1886,8 +1895,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA53027-F7D8-4A70-9EEA-701DAD25978D}">
-  <dimension ref="A1:Q91"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04119B7-04BF-436C-AE4B-FA2EA85EDCA5}">
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3395,10 +3404,10 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
-        <v>359</v>
+        <v>503</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
@@ -3407,13 +3416,13 @@
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>487</v>
       </c>
       <c r="F29" t="s">
-        <v>19</v>
+        <v>504</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H29" t="s">
         <v>20</v>
@@ -3428,19 +3437,19 @@
         <v>23</v>
       </c>
       <c r="L29">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
       </c>
       <c r="N29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>251</v>
+        <v>505</v>
       </c>
       <c r="P29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
@@ -3448,34 +3457,34 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H30" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I30" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K30" t="s">
         <v>23</v>
@@ -3490,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -3501,41 +3510,41 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>360</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>28</v>
+      </c>
+      <c r="I31" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31">
         <v>12</v>
       </c>
-      <c r="B31" t="s">
-        <v>361</v>
-      </c>
-      <c r="C31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" t="s">
-        <v>34</v>
-      </c>
-      <c r="G31">
-        <v>500</v>
-      </c>
-      <c r="H31" t="s">
-        <v>35</v>
-      </c>
-      <c r="I31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J31" t="s">
-        <v>37</v>
-      </c>
-      <c r="K31" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31">
-        <v>6</v>
-      </c>
       <c r="M31" t="b">
         <v>0</v>
       </c>
@@ -3543,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -3554,40 +3563,40 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G32">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I32" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J32" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K32" t="s">
         <v>23</v>
       </c>
       <c r="L32">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
@@ -3596,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -3607,40 +3616,40 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F33" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H33" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I33" t="s">
         <v>21</v>
       </c>
       <c r="J33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K33" t="s">
         <v>23</v>
       </c>
       <c r="L33">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -3649,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -3660,40 +3669,40 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C34" t="s">
-        <v>241</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>242</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="F34" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="G34">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I34" t="s">
         <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="K34" t="s">
         <v>23</v>
       </c>
       <c r="L34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
@@ -3702,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -3713,49 +3722,49 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C35" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="D35" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="E35" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F35" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="H35" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I35" t="s">
         <v>21</v>
       </c>
       <c r="J35" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K35" t="s">
         <v>23</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
       </c>
       <c r="N35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -3766,34 +3775,34 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C36" t="s">
-        <v>49</v>
+        <v>197</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="E36" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H36" t="s">
         <v>20</v>
       </c>
       <c r="I36" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J36" t="s">
-        <v>49</v>
+        <v>245</v>
       </c>
       <c r="K36" t="s">
         <v>23</v>
@@ -3805,10 +3814,10 @@
         <v>0</v>
       </c>
       <c r="N36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -3819,34 +3828,34 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E37" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J37" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K37" t="s">
         <v>23</v>
@@ -3861,7 +3870,7 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -3872,34 +3881,34 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E38" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F38" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G38">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I38" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J38" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K38" t="s">
         <v>23</v>
@@ -3914,51 +3923,51 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
       </c>
       <c r="Q38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F39" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H39" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I39" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J39" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K39" t="s">
         <v>23</v>
       </c>
       <c r="L39">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
@@ -3967,45 +3976,45 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
       </c>
       <c r="Q39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E40" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F40" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G40">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J40" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
@@ -4020,51 +4029,51 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
       </c>
       <c r="Q40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C41" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D41" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E41" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F41" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H41" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I41" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J41" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
@@ -4073,45 +4082,45 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
       </c>
       <c r="Q41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D42" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E42" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F42" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G42">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H42" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I42" t="s">
         <v>53</v>
       </c>
       <c r="J42" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
@@ -4126,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
@@ -4137,40 +4146,40 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D43" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E43" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F43" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I43" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J43" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
       </c>
       <c r="L43">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
@@ -4179,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
@@ -4190,40 +4199,40 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B44" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F44" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G44">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I44" t="s">
         <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
       </c>
       <c r="L44">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
@@ -4232,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -4243,34 +4252,34 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E45" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F45" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G45">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H45" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I45" t="s">
         <v>21</v>
       </c>
       <c r="J45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
@@ -4285,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -4296,40 +4305,40 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D46" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E46" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F46" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G46">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H46" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
@@ -4338,51 +4347,51 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
       </c>
       <c r="Q46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D47" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E47" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F47" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G47">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H47" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I47" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J47" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
       </c>
       <c r="L47">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
@@ -4391,7 +4400,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
@@ -4402,41 +4411,41 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F48" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H48" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I48" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J48" t="s">
+        <v>66</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48">
         <v>30</v>
       </c>
-      <c r="K48" t="s">
-        <v>23</v>
-      </c>
-      <c r="L48">
-        <v>12</v>
-      </c>
       <c r="M48" t="b">
         <v>0</v>
       </c>
@@ -4444,113 +4453,113 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
       </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
+        <v>29</v>
+      </c>
+      <c r="B49" t="s">
+        <v>378</v>
+      </c>
+      <c r="C49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" t="s">
+        <v>54</v>
+      </c>
+      <c r="E49" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" t="s">
+        <v>61</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" t="s">
+        <v>96</v>
+      </c>
+      <c r="J49" t="s">
         <v>30</v>
       </c>
-      <c r="B49" t="s">
-        <v>379</v>
-      </c>
-      <c r="C49" t="s">
-        <v>97</v>
-      </c>
-      <c r="D49" t="s">
-        <v>98</v>
-      </c>
-      <c r="E49" t="s">
-        <v>99</v>
-      </c>
-      <c r="F49" t="s">
-        <v>100</v>
-      </c>
-      <c r="G49">
-        <v>100</v>
-      </c>
-      <c r="H49" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" t="s">
-        <v>101</v>
-      </c>
-      <c r="J49" t="s">
-        <v>102</v>
-      </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
       </c>
       <c r="N49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E50" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F50" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G50">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H50" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J50" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
       </c>
       <c r="L50">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
       </c>
       <c r="N50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
@@ -4561,22 +4570,22 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C51" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E51" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F51" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G51">
         <v>500</v>
@@ -4588,13 +4597,13 @@
         <v>107</v>
       </c>
       <c r="J51" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -4603,7 +4612,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
@@ -4614,40 +4623,40 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F52" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H52" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I52" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J52" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
       </c>
       <c r="L52">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
@@ -4656,51 +4665,51 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
       </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E53" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F53" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G53">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I53" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -4709,51 +4718,51 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
       </c>
       <c r="Q53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
+        <v>34</v>
+      </c>
+      <c r="B54" t="s">
+        <v>383</v>
+      </c>
+      <c r="C54" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" t="s">
+        <v>114</v>
+      </c>
+      <c r="F54" t="s">
+        <v>115</v>
+      </c>
+      <c r="G54">
+        <v>300</v>
+      </c>
+      <c r="H54" t="s">
         <v>35</v>
       </c>
-      <c r="B54" t="s">
-        <v>384</v>
-      </c>
-      <c r="C54" t="s">
-        <v>117</v>
-      </c>
-      <c r="D54" t="s">
-        <v>118</v>
-      </c>
-      <c r="E54" t="s">
-        <v>119</v>
-      </c>
-      <c r="F54" t="s">
-        <v>120</v>
-      </c>
-      <c r="G54">
-        <v>500</v>
-      </c>
-      <c r="H54" t="s">
-        <v>42</v>
-      </c>
       <c r="I54" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4762,7 +4771,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -4773,40 +4782,40 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B55" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C55" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D55" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E55" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F55" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G55">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H55" t="s">
         <v>42</v>
       </c>
       <c r="I55" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -4815,51 +4824,51 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
       </c>
       <c r="Q55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B56" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C56" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E56" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F56" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G56">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H56" t="s">
         <v>42</v>
       </c>
       <c r="I56" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J56" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -4868,45 +4877,45 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
       </c>
       <c r="Q56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C57" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D57" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E57" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F57" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G57">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H57" t="s">
         <v>42</v>
       </c>
       <c r="I57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J57" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
@@ -4921,51 +4930,51 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
       </c>
       <c r="Q57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C58" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D58" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E58" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F58" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G58">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H58" t="s">
         <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -4974,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -4985,40 +4994,40 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C59" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D59" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E59" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F59" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H59" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I59" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J59" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -5027,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -5038,63 +5047,63 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E60" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F60" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G60">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I60" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J60" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C61" t="s">
         <v>138</v>
@@ -5103,10 +5112,10 @@
         <v>139</v>
       </c>
       <c r="E61" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F61" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G61">
         <v>1000</v>
@@ -5130,10 +5139,10 @@
         <v>1</v>
       </c>
       <c r="N61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -5144,22 +5153,22 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B62" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C62" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D62" t="s">
         <v>139</v>
       </c>
       <c r="E62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F62" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G62">
         <v>1000</v>
@@ -5171,7 +5180,7 @@
         <v>142</v>
       </c>
       <c r="J62" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
@@ -5186,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5197,193 +5206,193 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B63" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C63" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D63" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E63" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F63" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G63">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H63" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J63" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
       </c>
       <c r="L63">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B64" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C64" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D64" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E64" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F64" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H64" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J64" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K64" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L64">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C65" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D65" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E65" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F65" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G65">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I65" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J65" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K65" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L65">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
       </c>
       <c r="N65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B66" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C66" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D66" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E66" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F66" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G66">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H66" t="s">
         <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J66" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
@@ -5398,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5409,22 +5418,22 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B67" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C67" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D67" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E67" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F67" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G67">
         <v>500</v>
@@ -5436,7 +5445,7 @@
         <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
@@ -5451,7 +5460,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5462,25 +5471,25 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B68" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C68" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D68" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E68" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F68" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G68">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H68" t="s">
         <v>42</v>
@@ -5489,7 +5498,7 @@
         <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
@@ -5504,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -5515,37 +5524,37 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
+        <v>49</v>
+      </c>
+      <c r="B69" t="s">
+        <v>398</v>
+      </c>
+      <c r="C69" t="s">
+        <v>175</v>
+      </c>
+      <c r="D69" t="s">
+        <v>176</v>
+      </c>
+      <c r="E69" t="s">
+        <v>177</v>
+      </c>
+      <c r="F69" t="s">
+        <v>178</v>
+      </c>
+      <c r="G69">
         <v>50</v>
       </c>
-      <c r="B69" t="s">
-        <v>399</v>
-      </c>
-      <c r="C69" t="s">
-        <v>180</v>
-      </c>
-      <c r="D69" t="s">
-        <v>181</v>
-      </c>
-      <c r="E69" t="s">
-        <v>182</v>
-      </c>
-      <c r="F69" t="s">
-        <v>183</v>
-      </c>
-      <c r="G69">
-        <v>12</v>
-      </c>
       <c r="H69" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I69" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K69" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L69">
         <v>12</v>
@@ -5557,7 +5566,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -5568,40 +5577,40 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B70" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C70" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D70" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E70" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F70" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G70">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H70" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I70" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J70" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K70" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -5610,7 +5619,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -5621,40 +5630,40 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B71" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C71" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D71" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E71" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F71" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G71">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H71" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I71" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J71" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -5663,7 +5672,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -5674,40 +5683,40 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
+        <v>52</v>
+      </c>
+      <c r="B72" t="s">
+        <v>401</v>
+      </c>
+      <c r="C72" t="s">
+        <v>193</v>
+      </c>
+      <c r="D72" t="s">
+        <v>181</v>
+      </c>
+      <c r="E72" t="s">
+        <v>182</v>
+      </c>
+      <c r="F72" t="s">
+        <v>183</v>
+      </c>
+      <c r="G72">
+        <v>24</v>
+      </c>
+      <c r="H72" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s">
         <v>53</v>
       </c>
-      <c r="B72" t="s">
-        <v>402</v>
-      </c>
-      <c r="C72" t="s">
-        <v>31</v>
-      </c>
-      <c r="D72" t="s">
-        <v>194</v>
-      </c>
-      <c r="E72" t="s">
-        <v>195</v>
-      </c>
-      <c r="F72" t="s">
-        <v>196</v>
-      </c>
-      <c r="G72">
-        <v>1.5</v>
-      </c>
-      <c r="H72" t="s">
-        <v>28</v>
-      </c>
-      <c r="I72" t="s">
-        <v>36</v>
-      </c>
       <c r="J72" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -5716,7 +5725,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -5727,52 +5736,52 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B73" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C73" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D73" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E73" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F73" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G73">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J73" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
       </c>
       <c r="N73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="b">
         <v>1</v>
@@ -5780,93 +5789,93 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B74" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C74" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D74" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E74" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F74" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G74">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H74" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I74" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
       </c>
       <c r="N74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B75" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D75" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E75" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F75" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G75">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H75" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I75" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J75" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -5875,7 +5884,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -5886,19 +5895,19 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B76" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D76" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E76" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F76" t="s">
         <v>208</v>
@@ -5928,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -5939,19 +5948,19 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B77" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C77" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D77" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E77" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F77" t="s">
         <v>208</v>
@@ -5972,7 +5981,7 @@
         <v>23</v>
       </c>
       <c r="L77">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -5981,7 +5990,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -5992,34 +6001,34 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B78" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C78" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D78" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E78" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F78" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H78" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J78" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
@@ -6034,45 +6043,45 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C79" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D79" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E79" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F79" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G79">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I79" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J79" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
@@ -6087,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6098,49 +6107,49 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B80" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C80" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D80" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E80" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F80" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G80">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H80" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J80" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6151,22 +6160,22 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B81" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C81" t="s">
         <v>217</v>
       </c>
       <c r="D81" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E81" t="s">
         <v>219</v>
       </c>
       <c r="F81" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G81">
         <v>20</v>
@@ -6193,60 +6202,60 @@
         <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B82" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C82" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D82" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E82" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F82" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G82">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J82" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
       <c r="N82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6257,34 +6266,34 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B83" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C83" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D83" t="s">
         <v>202</v>
       </c>
       <c r="E83" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F83" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G83">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H83" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I83" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J83" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
@@ -6299,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6310,40 +6319,40 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B84" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C84" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D84" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E84" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F84" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G84">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H84" t="s">
         <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J84" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -6352,51 +6361,51 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B85" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C85" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D85" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E85" t="s">
         <v>229</v>
       </c>
       <c r="F85" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H85" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J85" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -6405,7 +6414,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6416,40 +6425,40 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B86" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C86" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E86" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F86" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G86">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I86" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J86" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -6458,45 +6467,45 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B87" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C87" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E87" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F87" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G87">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H87" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I87" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J87" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
@@ -6511,7 +6520,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -6522,10 +6531,10 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B88" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C88" t="s">
         <v>186</v>
@@ -6534,13 +6543,13 @@
         <v>202</v>
       </c>
       <c r="E88" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F88" t="s">
         <v>204</v>
       </c>
       <c r="G88">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H88" t="s">
         <v>35</v>
@@ -6564,7 +6573,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -6575,10 +6584,10 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B89" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C89" t="s">
         <v>186</v>
@@ -6593,7 +6602,7 @@
         <v>204</v>
       </c>
       <c r="G89">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H89" t="s">
         <v>35</v>
@@ -6617,7 +6626,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -6628,41 +6637,41 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B90" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C90" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D90" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E90" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F90" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G90">
+        <v>250</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90" t="s">
+        <v>191</v>
+      </c>
+      <c r="J90" t="s">
+        <v>192</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90">
         <v>6</v>
       </c>
-      <c r="H90" t="s">
-        <v>20</v>
-      </c>
-      <c r="I90" t="s">
-        <v>239</v>
-      </c>
-      <c r="J90" t="s">
-        <v>235</v>
-      </c>
-      <c r="K90" t="s">
-        <v>23</v>
-      </c>
-      <c r="L90">
-        <v>1</v>
-      </c>
       <c r="M90" t="b">
         <v>0</v>
       </c>
@@ -6670,65 +6679,118 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C91" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D91" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E91" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F91" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G91">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H91" t="s">
         <v>20</v>
       </c>
       <c r="I91" t="s">
+        <v>239</v>
+      </c>
+      <c r="J91" t="s">
+        <v>235</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" t="b">
+        <v>1</v>
+      </c>
+      <c r="O91" t="s">
+        <v>311</v>
+      </c>
+      <c r="P91" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>72</v>
+      </c>
+      <c r="B92" t="s">
+        <v>421</v>
+      </c>
+      <c r="C92" t="s">
+        <v>197</v>
+      </c>
+      <c r="D92" t="s">
+        <v>198</v>
+      </c>
+      <c r="E92" t="s">
+        <v>199</v>
+      </c>
+      <c r="F92" t="s">
+        <v>240</v>
+      </c>
+      <c r="G92">
+        <v>4</v>
+      </c>
+      <c r="H92" t="s">
+        <v>20</v>
+      </c>
+      <c r="I92" t="s">
         <v>21</v>
       </c>
-      <c r="J91" t="s">
+      <c r="J92" t="s">
         <v>201</v>
       </c>
-      <c r="K91" t="s">
-        <v>23</v>
-      </c>
-      <c r="L91">
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92">
         <v>10</v>
       </c>
-      <c r="M91" t="b">
-        <v>0</v>
-      </c>
-      <c r="N91" t="b">
-        <v>0</v>
-      </c>
-      <c r="O91" t="s">
+      <c r="M92" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" t="b">
+        <v>0</v>
+      </c>
+      <c r="O92" t="s">
         <v>312</v>
       </c>
-      <c r="P91" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q91" t="b">
+      <c r="P92" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q92" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FD3919-A901-4AEB-840A-8C9DF606497F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D47CAB6-E6C4-4359-9D4F-C655935FC75A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="34" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="35" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="513">
   <si>
     <t>Codigo</t>
   </si>
@@ -1544,6 +1544,27 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7793890258806.png</t>
+  </si>
+  <si>
+    <t>7790480089963</t>
+  </si>
+  <si>
+    <t>Yerba mate</t>
+  </si>
+  <si>
+    <t>con palo</t>
+  </si>
+  <si>
+    <t>liviana</t>
+  </si>
+  <si>
+    <t>La Tranquera</t>
+  </si>
+  <si>
+    <t>Yerbas</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790480089963.png</t>
   </si>
 </sst>
 </file>
@@ -1895,8 +1916,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04119B7-04BF-436C-AE4B-FA2EA85EDCA5}">
-  <dimension ref="A1:Q92"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31AD94A-3D6D-4BD5-9330-A38BFDD033D1}">
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3457,40 +3478,40 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>359</v>
+        <v>506</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>507</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>508</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>509</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>510</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I30" t="s">
         <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>22</v>
+        <v>511</v>
       </c>
       <c r="K30" t="s">
         <v>23</v>
       </c>
       <c r="L30">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
@@ -3499,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>251</v>
+        <v>512</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -3510,34 +3531,34 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H31" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I31" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K31" t="s">
         <v>23</v>
@@ -3552,7 +3573,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -3563,41 +3584,41 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>360</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32">
         <v>12</v>
       </c>
-      <c r="B32" t="s">
-        <v>361</v>
-      </c>
-      <c r="C32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" t="s">
-        <v>33</v>
-      </c>
-      <c r="F32" t="s">
-        <v>34</v>
-      </c>
-      <c r="G32">
-        <v>500</v>
-      </c>
-      <c r="H32" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" t="s">
-        <v>36</v>
-      </c>
-      <c r="J32" t="s">
-        <v>37</v>
-      </c>
-      <c r="K32" t="s">
-        <v>23</v>
-      </c>
-      <c r="L32">
-        <v>6</v>
-      </c>
       <c r="M32" t="b">
         <v>0</v>
       </c>
@@ -3605,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -3616,40 +3637,40 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G33">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H33" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J33" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K33" t="s">
         <v>23</v>
       </c>
       <c r="L33">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
@@ -3658,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -3669,40 +3690,40 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F34" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H34" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I34" t="s">
         <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K34" t="s">
         <v>23</v>
       </c>
       <c r="L34">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
@@ -3711,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -3722,40 +3743,40 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C35" t="s">
-        <v>241</v>
+        <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>242</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="F35" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="G35">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I35" t="s">
         <v>21</v>
       </c>
       <c r="J35" t="s">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="K35" t="s">
         <v>23</v>
       </c>
       <c r="L35">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
@@ -3764,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -3775,49 +3796,49 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C36" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="D36" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="E36" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F36" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="H36" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I36" t="s">
         <v>21</v>
       </c>
       <c r="J36" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K36" t="s">
         <v>23</v>
       </c>
       <c r="L36">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
       </c>
       <c r="N36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -3828,34 +3849,34 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>197</v>
       </c>
       <c r="D37" t="s">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="E37" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H37" t="s">
         <v>20</v>
       </c>
       <c r="I37" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J37" t="s">
-        <v>49</v>
+        <v>245</v>
       </c>
       <c r="K37" t="s">
         <v>23</v>
@@ -3867,10 +3888,10 @@
         <v>0</v>
       </c>
       <c r="N37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -3881,34 +3902,34 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I38" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J38" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K38" t="s">
         <v>23</v>
@@ -3923,7 +3944,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -3934,34 +3955,34 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E39" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G39">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I39" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J39" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K39" t="s">
         <v>23</v>
@@ -3976,51 +3997,51 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
       </c>
       <c r="Q39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F40" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H40" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I40" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J40" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
       </c>
       <c r="L40">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
@@ -4029,45 +4050,45 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
       </c>
       <c r="Q40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C41" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E41" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F41" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G41">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I41" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J41" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
@@ -4082,51 +4103,51 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
       </c>
       <c r="Q41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C42" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D42" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E42" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F42" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G42">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I42" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J42" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
@@ -4135,45 +4156,45 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
       </c>
       <c r="Q42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C43" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D43" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E43" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F43" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G43">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H43" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I43" t="s">
         <v>53</v>
       </c>
       <c r="J43" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
@@ -4188,7 +4209,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
@@ -4199,40 +4220,40 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D44" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E44" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F44" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I44" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J44" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
       </c>
       <c r="L44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
@@ -4241,7 +4262,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -4252,40 +4273,40 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F45" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G45">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I45" t="s">
         <v>21</v>
       </c>
       <c r="J45" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
       </c>
       <c r="L45">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -4294,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -4305,34 +4326,34 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C46" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E46" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F46" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G46">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H46" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I46" t="s">
         <v>21</v>
       </c>
       <c r="J46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
@@ -4347,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
@@ -4358,40 +4379,40 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C47" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D47" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E47" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F47" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G47">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H47" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I47" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
@@ -4400,51 +4421,51 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
       </c>
       <c r="Q47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D48" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E48" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F48" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G48">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I48" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J48" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
       </c>
       <c r="L48">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
@@ -4453,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
@@ -4464,41 +4485,41 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E49" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F49" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H49" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J49" t="s">
+        <v>66</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49">
         <v>30</v>
       </c>
-      <c r="K49" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49">
-        <v>12</v>
-      </c>
       <c r="M49" t="b">
         <v>0</v>
       </c>
@@ -4506,113 +4527,113 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
       </c>
       <c r="Q49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
+        <v>29</v>
+      </c>
+      <c r="B50" t="s">
+        <v>378</v>
+      </c>
+      <c r="C50" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" t="s">
+        <v>61</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" t="s">
+        <v>96</v>
+      </c>
+      <c r="J50" t="s">
         <v>30</v>
       </c>
-      <c r="B50" t="s">
-        <v>379</v>
-      </c>
-      <c r="C50" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" t="s">
-        <v>98</v>
-      </c>
-      <c r="E50" t="s">
-        <v>99</v>
-      </c>
-      <c r="F50" t="s">
-        <v>100</v>
-      </c>
-      <c r="G50">
-        <v>100</v>
-      </c>
-      <c r="H50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I50" t="s">
-        <v>101</v>
-      </c>
-      <c r="J50" t="s">
-        <v>102</v>
-      </c>
       <c r="K50" t="s">
         <v>23</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
       </c>
       <c r="N50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
       </c>
       <c r="Q50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E51" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F51" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G51">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H51" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I51" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J51" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
       </c>
       <c r="N51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
@@ -4623,22 +4644,22 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C52" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E52" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F52" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G52">
         <v>500</v>
@@ -4650,13 +4671,13 @@
         <v>107</v>
       </c>
       <c r="J52" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
@@ -4665,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -4676,40 +4697,40 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E53" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F53" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H53" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I53" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J53" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -4718,51 +4739,51 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
       </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C54" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E54" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F54" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G54">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I54" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4771,51 +4792,51 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
       </c>
       <c r="Q54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
+        <v>34</v>
+      </c>
+      <c r="B55" t="s">
+        <v>383</v>
+      </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" t="s">
+        <v>114</v>
+      </c>
+      <c r="F55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G55">
+        <v>300</v>
+      </c>
+      <c r="H55" t="s">
         <v>35</v>
       </c>
-      <c r="B55" t="s">
-        <v>384</v>
-      </c>
-      <c r="C55" t="s">
-        <v>117</v>
-      </c>
-      <c r="D55" t="s">
-        <v>118</v>
-      </c>
-      <c r="E55" t="s">
-        <v>119</v>
-      </c>
-      <c r="F55" t="s">
-        <v>120</v>
-      </c>
-      <c r="G55">
-        <v>500</v>
-      </c>
-      <c r="H55" t="s">
-        <v>42</v>
-      </c>
       <c r="I55" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -4824,7 +4845,7 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
@@ -4835,40 +4856,40 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D56" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E56" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F56" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G56">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H56" t="s">
         <v>42</v>
       </c>
       <c r="I56" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -4877,51 +4898,51 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
       </c>
       <c r="Q56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C57" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E57" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F57" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G57">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H57" t="s">
         <v>42</v>
       </c>
       <c r="I57" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J57" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
       </c>
       <c r="L57">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
@@ -4930,45 +4951,45 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
       </c>
       <c r="Q57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B58" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C58" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E58" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F58" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G58">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H58" t="s">
         <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
@@ -4983,51 +5004,51 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D59" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F59" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G59">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H59" t="s">
         <v>42</v>
       </c>
       <c r="I59" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J59" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -5036,7 +5057,7 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -5047,40 +5068,40 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C60" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D60" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E60" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F60" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J60" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -5089,7 +5110,7 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
@@ -5100,63 +5121,63 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B61" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E61" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F61" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G61">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I61" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B62" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C62" t="s">
         <v>138</v>
@@ -5165,10 +5186,10 @@
         <v>139</v>
       </c>
       <c r="E62" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F62" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G62">
         <v>1000</v>
@@ -5192,10 +5213,10 @@
         <v>1</v>
       </c>
       <c r="N62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5206,22 +5227,22 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B63" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C63" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D63" t="s">
         <v>139</v>
       </c>
       <c r="E63" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F63" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G63">
         <v>1000</v>
@@ -5233,7 +5254,7 @@
         <v>142</v>
       </c>
       <c r="J63" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
@@ -5248,7 +5269,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5259,193 +5280,193 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B64" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D64" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E64" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F64" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G64">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H64" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J64" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C65" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D65" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E65" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F65" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H65" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J65" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K65" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L65">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
       </c>
       <c r="N65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C66" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D66" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E66" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F66" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G66">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I66" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J66" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K66" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L66">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
       </c>
       <c r="N66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B67" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C67" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D67" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E67" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F67" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G67">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H67" t="s">
         <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J67" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
@@ -5460,7 +5481,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5471,22 +5492,22 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B68" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C68" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D68" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E68" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F68" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G68">
         <v>500</v>
@@ -5498,7 +5519,7 @@
         <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
@@ -5513,7 +5534,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -5524,25 +5545,25 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B69" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C69" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D69" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E69" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F69" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G69">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H69" t="s">
         <v>42</v>
@@ -5551,7 +5572,7 @@
         <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
@@ -5566,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -5577,37 +5598,37 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
+        <v>49</v>
+      </c>
+      <c r="B70" t="s">
+        <v>398</v>
+      </c>
+      <c r="C70" t="s">
+        <v>175</v>
+      </c>
+      <c r="D70" t="s">
+        <v>176</v>
+      </c>
+      <c r="E70" t="s">
+        <v>177</v>
+      </c>
+      <c r="F70" t="s">
+        <v>178</v>
+      </c>
+      <c r="G70">
         <v>50</v>
       </c>
-      <c r="B70" t="s">
-        <v>399</v>
-      </c>
-      <c r="C70" t="s">
-        <v>180</v>
-      </c>
-      <c r="D70" t="s">
-        <v>181</v>
-      </c>
-      <c r="E70" t="s">
-        <v>182</v>
-      </c>
-      <c r="F70" t="s">
-        <v>183</v>
-      </c>
-      <c r="G70">
-        <v>12</v>
-      </c>
       <c r="H70" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I70" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K70" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L70">
         <v>12</v>
@@ -5619,7 +5640,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -5630,40 +5651,40 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B71" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C71" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D71" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E71" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F71" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G71">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H71" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I71" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J71" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K71" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -5672,7 +5693,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -5683,40 +5704,40 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C72" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D72" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E72" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F72" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G72">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H72" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I72" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J72" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -5725,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -5736,40 +5757,40 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
+        <v>52</v>
+      </c>
+      <c r="B73" t="s">
+        <v>401</v>
+      </c>
+      <c r="C73" t="s">
+        <v>193</v>
+      </c>
+      <c r="D73" t="s">
+        <v>181</v>
+      </c>
+      <c r="E73" t="s">
+        <v>182</v>
+      </c>
+      <c r="F73" t="s">
+        <v>183</v>
+      </c>
+      <c r="G73">
+        <v>24</v>
+      </c>
+      <c r="H73" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s">
         <v>53</v>
       </c>
-      <c r="B73" t="s">
-        <v>402</v>
-      </c>
-      <c r="C73" t="s">
-        <v>31</v>
-      </c>
-      <c r="D73" t="s">
-        <v>194</v>
-      </c>
-      <c r="E73" t="s">
-        <v>195</v>
-      </c>
-      <c r="F73" t="s">
-        <v>196</v>
-      </c>
-      <c r="G73">
-        <v>1.5</v>
-      </c>
-      <c r="H73" t="s">
-        <v>28</v>
-      </c>
-      <c r="I73" t="s">
-        <v>36</v>
-      </c>
       <c r="J73" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -5778,7 +5799,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -5789,52 +5810,52 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B74" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C74" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D74" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E74" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F74" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G74">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H74" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I74" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J74" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
       </c>
       <c r="N74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="b">
         <v>1</v>
@@ -5842,93 +5863,93 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B75" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C75" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D75" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E75" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F75" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G75">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H75" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I75" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
       <c r="N75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B76" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C76" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D76" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E76" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F76" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G76">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H76" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I76" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J76" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -5937,7 +5958,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -5948,19 +5969,19 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C77" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D77" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E77" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F77" t="s">
         <v>208</v>
@@ -5990,7 +6011,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6001,19 +6022,19 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B78" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C78" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D78" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E78" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F78" t="s">
         <v>208</v>
@@ -6034,7 +6055,7 @@
         <v>23</v>
       </c>
       <c r="L78">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6043,7 +6064,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6054,34 +6075,34 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B79" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C79" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D79" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E79" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F79" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H79" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J79" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
@@ -6096,45 +6117,45 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B80" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D80" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E80" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F80" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G80">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I80" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J80" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
@@ -6149,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6160,49 +6181,49 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B81" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C81" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E81" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F81" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G81">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H81" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J81" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6213,22 +6234,22 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B82" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C82" t="s">
         <v>217</v>
       </c>
       <c r="D82" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E82" t="s">
         <v>219</v>
       </c>
       <c r="F82" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G82">
         <v>20</v>
@@ -6255,60 +6276,60 @@
         <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C83" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D83" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E83" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F83" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G83">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H83" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I83" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J83" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
       </c>
       <c r="N83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6319,34 +6340,34 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B84" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C84" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D84" t="s">
         <v>202</v>
       </c>
       <c r="E84" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F84" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G84">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H84" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J84" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
@@ -6361,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6372,40 +6393,40 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B85" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C85" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D85" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E85" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F85" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G85">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H85" t="s">
         <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J85" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -6414,51 +6435,51 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B86" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C86" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D86" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E86" t="s">
         <v>229</v>
       </c>
       <c r="F86" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H86" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I86" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J86" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -6467,7 +6488,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -6478,40 +6499,40 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B87" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C87" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D87" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E87" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F87" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G87">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I87" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J87" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -6520,45 +6541,45 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B88" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C88" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E88" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F88" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G88">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H88" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J88" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
@@ -6573,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -6584,10 +6605,10 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B89" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C89" t="s">
         <v>186</v>
@@ -6596,13 +6617,13 @@
         <v>202</v>
       </c>
       <c r="E89" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F89" t="s">
         <v>204</v>
       </c>
       <c r="G89">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H89" t="s">
         <v>35</v>
@@ -6626,7 +6647,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -6637,10 +6658,10 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B90" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C90" t="s">
         <v>186</v>
@@ -6655,7 +6676,7 @@
         <v>204</v>
       </c>
       <c r="G90">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H90" t="s">
         <v>35</v>
@@ -6679,7 +6700,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -6690,41 +6711,41 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B91" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C91" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D91" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E91" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F91" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G91">
+        <v>250</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91" t="s">
+        <v>191</v>
+      </c>
+      <c r="J91" t="s">
+        <v>192</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91">
         <v>6</v>
       </c>
-      <c r="H91" t="s">
-        <v>20</v>
-      </c>
-      <c r="I91" t="s">
-        <v>239</v>
-      </c>
-      <c r="J91" t="s">
-        <v>235</v>
-      </c>
-      <c r="K91" t="s">
-        <v>23</v>
-      </c>
-      <c r="L91">
-        <v>1</v>
-      </c>
       <c r="M91" t="b">
         <v>0</v>
       </c>
@@ -6732,65 +6753,118 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C92" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D92" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E92" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F92" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G92">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H92" t="s">
         <v>20</v>
       </c>
       <c r="I92" t="s">
+        <v>239</v>
+      </c>
+      <c r="J92" t="s">
+        <v>235</v>
+      </c>
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" t="b">
+        <v>1</v>
+      </c>
+      <c r="O92" t="s">
+        <v>311</v>
+      </c>
+      <c r="P92" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>72</v>
+      </c>
+      <c r="B93" t="s">
+        <v>421</v>
+      </c>
+      <c r="C93" t="s">
+        <v>197</v>
+      </c>
+      <c r="D93" t="s">
+        <v>198</v>
+      </c>
+      <c r="E93" t="s">
+        <v>199</v>
+      </c>
+      <c r="F93" t="s">
+        <v>240</v>
+      </c>
+      <c r="G93">
+        <v>4</v>
+      </c>
+      <c r="H93" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s">
         <v>21</v>
       </c>
-      <c r="J92" t="s">
+      <c r="J93" t="s">
         <v>201</v>
       </c>
-      <c r="K92" t="s">
-        <v>23</v>
-      </c>
-      <c r="L92">
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93">
         <v>10</v>
       </c>
-      <c r="M92" t="b">
-        <v>0</v>
-      </c>
-      <c r="N92" t="b">
-        <v>0</v>
-      </c>
-      <c r="O92" t="s">
+      <c r="M93" t="b">
+        <v>0</v>
+      </c>
+      <c r="N93" t="b">
+        <v>0</v>
+      </c>
+      <c r="O93" t="s">
         <v>312</v>
       </c>
-      <c r="P92" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q92" t="b">
+      <c r="P93" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q93" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D47CAB6-E6C4-4359-9D4F-C655935FC75A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6CA857-3B72-4661-9F5D-654284B01FFE}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="35" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="36" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="517">
   <si>
     <t>Codigo</t>
   </si>
@@ -1565,6 +1565,18 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790480089963.png</t>
+  </si>
+  <si>
+    <t>7791070000856</t>
+  </si>
+  <si>
+    <t>doble hoja</t>
+  </si>
+  <si>
+    <t>"ultra"</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7791070000856.png</t>
   </si>
 </sst>
 </file>
@@ -1916,8 +1928,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31AD94A-3D6D-4BD5-9330-A38BFDD033D1}">
-  <dimension ref="A1:Q93"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38046B79-A607-4D28-AECB-80F3895B2123}">
+  <dimension ref="A1:Q94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3531,25 +3543,25 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="B31" t="s">
-        <v>359</v>
+        <v>513</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>514</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>515</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="G31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H31" t="s">
         <v>20</v>
@@ -3558,7 +3570,7 @@
         <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>22</v>
+        <v>245</v>
       </c>
       <c r="K31" t="s">
         <v>23</v>
@@ -3570,10 +3582,10 @@
         <v>0</v>
       </c>
       <c r="N31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>251</v>
+        <v>516</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -3584,34 +3596,34 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H32" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I32" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K32" t="s">
         <v>23</v>
@@ -3626,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -3637,41 +3649,41 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>360</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" t="s">
+        <v>30</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33">
         <v>12</v>
       </c>
-      <c r="B33" t="s">
-        <v>361</v>
-      </c>
-      <c r="C33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" t="s">
-        <v>33</v>
-      </c>
-      <c r="F33" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33">
-        <v>500</v>
-      </c>
-      <c r="H33" t="s">
-        <v>35</v>
-      </c>
-      <c r="I33" t="s">
-        <v>36</v>
-      </c>
-      <c r="J33" t="s">
-        <v>37</v>
-      </c>
-      <c r="K33" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33">
-        <v>6</v>
-      </c>
       <c r="M33" t="b">
         <v>0</v>
       </c>
@@ -3679,7 +3691,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -3690,40 +3702,40 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G34">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H34" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I34" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J34" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K34" t="s">
         <v>23</v>
       </c>
       <c r="L34">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
@@ -3732,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -3743,40 +3755,40 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F35" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H35" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I35" t="s">
         <v>21</v>
       </c>
       <c r="J35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K35" t="s">
         <v>23</v>
       </c>
       <c r="L35">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
@@ -3785,7 +3797,7 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -3796,40 +3808,40 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C36" t="s">
-        <v>241</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
-        <v>242</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="F36" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="G36">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I36" t="s">
         <v>21</v>
       </c>
       <c r="J36" t="s">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="K36" t="s">
         <v>23</v>
       </c>
       <c r="L36">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
@@ -3838,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -3849,49 +3861,49 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C37" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="D37" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="E37" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="F37" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G37">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="H37" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I37" t="s">
         <v>21</v>
       </c>
       <c r="J37" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K37" t="s">
         <v>23</v>
       </c>
       <c r="L37">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
       </c>
       <c r="N37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -3902,34 +3914,34 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C38" t="s">
-        <v>49</v>
+        <v>197</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H38" t="s">
         <v>20</v>
       </c>
       <c r="I38" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s">
-        <v>49</v>
+        <v>245</v>
       </c>
       <c r="K38" t="s">
         <v>23</v>
@@ -3941,10 +3953,10 @@
         <v>0</v>
       </c>
       <c r="N38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -3955,34 +3967,34 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F39" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I39" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J39" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K39" t="s">
         <v>23</v>
@@ -3997,7 +4009,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
@@ -4008,34 +4020,34 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D40" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E40" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G40">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J40" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
@@ -4050,51 +4062,51 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
       </c>
       <c r="Q40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F41" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H41" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I41" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J41" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
       </c>
       <c r="L41">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
@@ -4103,45 +4115,45 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
       </c>
       <c r="Q41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E42" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F42" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G42">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I42" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J42" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
@@ -4156,51 +4168,51 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
       </c>
       <c r="Q42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C43" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F43" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I43" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J43" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
       </c>
       <c r="L43">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
@@ -4209,45 +4221,45 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
       </c>
       <c r="Q43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E44" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F44" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G44">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H44" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I44" t="s">
         <v>53</v>
       </c>
       <c r="J44" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
@@ -4262,7 +4274,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -4273,40 +4285,40 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D45" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E45" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F45" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I45" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J45" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
       </c>
       <c r="L45">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -4315,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -4326,40 +4338,40 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F46" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G46">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I46" t="s">
         <v>21</v>
       </c>
       <c r="J46" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
       </c>
       <c r="L46">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
@@ -4368,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
@@ -4379,34 +4391,34 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D47" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E47" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F47" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G47">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H47" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I47" t="s">
         <v>21</v>
       </c>
       <c r="J47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
@@ -4421,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
@@ -4432,40 +4444,40 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D48" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E48" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F48" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G48">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H48" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I48" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J48" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
@@ -4474,51 +4486,51 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
       </c>
       <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D49" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E49" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F49" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G49">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H49" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I49" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J49" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -4527,7 +4539,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
@@ -4538,41 +4550,41 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B50" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C50" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E50" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F50" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H50" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J50" t="s">
+        <v>66</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50">
         <v>30</v>
       </c>
-      <c r="K50" t="s">
-        <v>23</v>
-      </c>
-      <c r="L50">
-        <v>12</v>
-      </c>
       <c r="M50" t="b">
         <v>0</v>
       </c>
@@ -4580,113 +4592,113 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
       </c>
       <c r="Q50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
+        <v>29</v>
+      </c>
+      <c r="B51" t="s">
+        <v>378</v>
+      </c>
+      <c r="C51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" t="s">
+        <v>96</v>
+      </c>
+      <c r="J51" t="s">
         <v>30</v>
       </c>
-      <c r="B51" t="s">
-        <v>379</v>
-      </c>
-      <c r="C51" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" t="s">
-        <v>98</v>
-      </c>
-      <c r="E51" t="s">
-        <v>99</v>
-      </c>
-      <c r="F51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G51">
-        <v>100</v>
-      </c>
-      <c r="H51" t="s">
-        <v>20</v>
-      </c>
-      <c r="I51" t="s">
-        <v>101</v>
-      </c>
-      <c r="J51" t="s">
-        <v>102</v>
-      </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
       </c>
       <c r="N51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
       </c>
       <c r="Q51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D52" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E52" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F52" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G52">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H52" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I52" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J52" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
       </c>
       <c r="L52">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
       </c>
       <c r="N52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -4697,22 +4709,22 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D53" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E53" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F53" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G53">
         <v>500</v>
@@ -4724,13 +4736,13 @@
         <v>107</v>
       </c>
       <c r="J53" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -4739,7 +4751,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -4750,40 +4762,40 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E54" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F54" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H54" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J54" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4792,51 +4804,51 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
       </c>
       <c r="Q54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E55" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G55">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I55" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -4845,51 +4857,51 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
       </c>
       <c r="Q55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
+        <v>34</v>
+      </c>
+      <c r="B56" t="s">
+        <v>383</v>
+      </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E56" t="s">
+        <v>114</v>
+      </c>
+      <c r="F56" t="s">
+        <v>115</v>
+      </c>
+      <c r="G56">
+        <v>300</v>
+      </c>
+      <c r="H56" t="s">
         <v>35</v>
       </c>
-      <c r="B56" t="s">
-        <v>384</v>
-      </c>
-      <c r="C56" t="s">
-        <v>117</v>
-      </c>
-      <c r="D56" t="s">
-        <v>118</v>
-      </c>
-      <c r="E56" t="s">
-        <v>119</v>
-      </c>
-      <c r="F56" t="s">
-        <v>120</v>
-      </c>
-      <c r="G56">
-        <v>500</v>
-      </c>
-      <c r="H56" t="s">
-        <v>42</v>
-      </c>
       <c r="I56" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -4898,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
@@ -4909,40 +4921,40 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D57" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E57" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F57" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G57">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H57" t="s">
         <v>42</v>
       </c>
       <c r="I57" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
       </c>
       <c r="L57">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
@@ -4951,51 +4963,51 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
       </c>
       <c r="Q57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C58" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D58" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E58" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F58" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G58">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H58" t="s">
         <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J58" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -5004,45 +5016,45 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C59" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D59" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E59" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F59" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G59">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H59" t="s">
         <v>42</v>
       </c>
       <c r="I59" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J59" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
@@ -5057,51 +5069,51 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F60" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G60">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H60" t="s">
         <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J60" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -5110,7 +5122,7 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
@@ -5121,40 +5133,40 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C61" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D61" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E61" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F61" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H61" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I61" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J61" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -5163,7 +5175,7 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -5174,63 +5186,63 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B62" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C62" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E62" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F62" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G62">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I62" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C63" t="s">
         <v>138</v>
@@ -5239,10 +5251,10 @@
         <v>139</v>
       </c>
       <c r="E63" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F63" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G63">
         <v>1000</v>
@@ -5266,10 +5278,10 @@
         <v>1</v>
       </c>
       <c r="N63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5280,22 +5292,22 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B64" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C64" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D64" t="s">
         <v>139</v>
       </c>
       <c r="E64" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F64" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G64">
         <v>1000</v>
@@ -5307,7 +5319,7 @@
         <v>142</v>
       </c>
       <c r="J64" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
@@ -5322,7 +5334,7 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5333,193 +5345,193 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B65" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C65" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D65" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E65" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F65" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G65">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H65" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J65" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="b">
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C66" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D66" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E66" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F66" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H66" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J66" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K66" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L66">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
       </c>
       <c r="N66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C67" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D67" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E67" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F67" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G67">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I67" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J67" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K67" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L67">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
       </c>
       <c r="N67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B68" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C68" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D68" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E68" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F68" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G68">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H68" t="s">
         <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J68" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
@@ -5534,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -5545,22 +5557,22 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B69" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C69" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D69" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E69" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F69" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G69">
         <v>500</v>
@@ -5572,7 +5584,7 @@
         <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
@@ -5587,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -5598,25 +5610,25 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B70" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C70" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D70" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E70" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F70" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G70">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H70" t="s">
         <v>42</v>
@@ -5625,7 +5637,7 @@
         <v>21</v>
       </c>
       <c r="J70" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
@@ -5640,7 +5652,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -5651,37 +5663,37 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
+        <v>49</v>
+      </c>
+      <c r="B71" t="s">
+        <v>398</v>
+      </c>
+      <c r="C71" t="s">
+        <v>175</v>
+      </c>
+      <c r="D71" t="s">
+        <v>176</v>
+      </c>
+      <c r="E71" t="s">
+        <v>177</v>
+      </c>
+      <c r="F71" t="s">
+        <v>178</v>
+      </c>
+      <c r="G71">
         <v>50</v>
       </c>
-      <c r="B71" t="s">
-        <v>399</v>
-      </c>
-      <c r="C71" t="s">
-        <v>180</v>
-      </c>
-      <c r="D71" t="s">
-        <v>181</v>
-      </c>
-      <c r="E71" t="s">
-        <v>182</v>
-      </c>
-      <c r="F71" t="s">
-        <v>183</v>
-      </c>
-      <c r="G71">
-        <v>12</v>
-      </c>
       <c r="H71" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J71" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K71" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L71">
         <v>12</v>
@@ -5693,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -5704,40 +5716,40 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B72" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C72" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D72" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E72" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F72" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G72">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H72" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I72" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J72" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K72" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -5746,7 +5758,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -5757,40 +5769,40 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C73" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D73" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E73" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F73" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G73">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H73" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I73" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J73" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -5799,7 +5811,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -5810,40 +5822,40 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
+        <v>52</v>
+      </c>
+      <c r="B74" t="s">
+        <v>401</v>
+      </c>
+      <c r="C74" t="s">
+        <v>193</v>
+      </c>
+      <c r="D74" t="s">
+        <v>181</v>
+      </c>
+      <c r="E74" t="s">
+        <v>182</v>
+      </c>
+      <c r="F74" t="s">
+        <v>183</v>
+      </c>
+      <c r="G74">
+        <v>24</v>
+      </c>
+      <c r="H74" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s">
         <v>53</v>
       </c>
-      <c r="B74" t="s">
-        <v>402</v>
-      </c>
-      <c r="C74" t="s">
-        <v>31</v>
-      </c>
-      <c r="D74" t="s">
-        <v>194</v>
-      </c>
-      <c r="E74" t="s">
-        <v>195</v>
-      </c>
-      <c r="F74" t="s">
-        <v>196</v>
-      </c>
-      <c r="G74">
-        <v>1.5</v>
-      </c>
-      <c r="H74" t="s">
-        <v>28</v>
-      </c>
-      <c r="I74" t="s">
-        <v>36</v>
-      </c>
       <c r="J74" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -5852,7 +5864,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -5863,52 +5875,52 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B75" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C75" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D75" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E75" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F75" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G75">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H75" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I75" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J75" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
       <c r="N75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="b">
         <v>1</v>
@@ -5916,93 +5928,93 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B76" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C76" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D76" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E76" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F76" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G76">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H76" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I76" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
       </c>
       <c r="N76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B77" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C77" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D77" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E77" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F77" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G77">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H77" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I77" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J77" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6011,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6022,19 +6034,19 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B78" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C78" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D78" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E78" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F78" t="s">
         <v>208</v>
@@ -6064,7 +6076,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6075,19 +6087,19 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B79" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C79" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D79" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E79" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F79" t="s">
         <v>208</v>
@@ -6108,7 +6120,7 @@
         <v>23</v>
       </c>
       <c r="L79">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6117,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6128,34 +6140,34 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B80" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C80" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D80" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E80" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F80" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H80" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J80" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
@@ -6170,45 +6182,45 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B81" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D81" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E81" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F81" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G81">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I81" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J81" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
@@ -6223,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6234,49 +6246,49 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B82" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C82" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D82" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E82" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F82" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G82">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H82" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J82" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
       <c r="N82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6287,22 +6299,22 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B83" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C83" t="s">
         <v>217</v>
       </c>
       <c r="D83" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E83" t="s">
         <v>219</v>
       </c>
       <c r="F83" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G83">
         <v>20</v>
@@ -6329,60 +6341,60 @@
         <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B84" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C84" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D84" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E84" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F84" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G84">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H84" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J84" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
       </c>
       <c r="N84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6393,34 +6405,34 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B85" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C85" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D85" t="s">
         <v>202</v>
       </c>
       <c r="E85" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F85" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G85">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H85" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J85" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
@@ -6435,7 +6447,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6446,40 +6458,40 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B86" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C86" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D86" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E86" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F86" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G86">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H86" t="s">
         <v>42</v>
       </c>
       <c r="I86" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J86" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -6488,51 +6500,51 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B87" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C87" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D87" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E87" t="s">
         <v>229</v>
       </c>
       <c r="F87" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H87" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I87" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J87" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -6541,7 +6553,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -6552,40 +6564,40 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B88" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C88" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D88" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E88" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F88" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G88">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I88" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J88" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -6594,45 +6606,45 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B89" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C89" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E89" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F89" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G89">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H89" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I89" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J89" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
@@ -6647,7 +6659,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -6658,10 +6670,10 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B90" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C90" t="s">
         <v>186</v>
@@ -6670,13 +6682,13 @@
         <v>202</v>
       </c>
       <c r="E90" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F90" t="s">
         <v>204</v>
       </c>
       <c r="G90">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H90" t="s">
         <v>35</v>
@@ -6700,7 +6712,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -6711,10 +6723,10 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B91" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C91" t="s">
         <v>186</v>
@@ -6729,7 +6741,7 @@
         <v>204</v>
       </c>
       <c r="G91">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H91" t="s">
         <v>35</v>
@@ -6753,7 +6765,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -6764,41 +6776,41 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B92" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C92" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D92" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E92" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F92" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G92">
+        <v>250</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92" t="s">
+        <v>191</v>
+      </c>
+      <c r="J92" t="s">
+        <v>192</v>
+      </c>
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92">
         <v>6</v>
       </c>
-      <c r="H92" t="s">
-        <v>20</v>
-      </c>
-      <c r="I92" t="s">
-        <v>239</v>
-      </c>
-      <c r="J92" t="s">
-        <v>235</v>
-      </c>
-      <c r="K92" t="s">
-        <v>23</v>
-      </c>
-      <c r="L92">
-        <v>1</v>
-      </c>
       <c r="M92" t="b">
         <v>0</v>
       </c>
@@ -6806,65 +6818,118 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C93" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D93" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E93" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G93">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H93" t="s">
         <v>20</v>
       </c>
       <c r="I93" t="s">
+        <v>239</v>
+      </c>
+      <c r="J93" t="s">
+        <v>235</v>
+      </c>
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93" t="b">
+        <v>0</v>
+      </c>
+      <c r="N93" t="b">
+        <v>1</v>
+      </c>
+      <c r="O93" t="s">
+        <v>311</v>
+      </c>
+      <c r="P93" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>72</v>
+      </c>
+      <c r="B94" t="s">
+        <v>421</v>
+      </c>
+      <c r="C94" t="s">
+        <v>197</v>
+      </c>
+      <c r="D94" t="s">
+        <v>198</v>
+      </c>
+      <c r="E94" t="s">
+        <v>199</v>
+      </c>
+      <c r="F94" t="s">
+        <v>240</v>
+      </c>
+      <c r="G94">
+        <v>4</v>
+      </c>
+      <c r="H94" t="s">
+        <v>20</v>
+      </c>
+      <c r="I94" t="s">
         <v>21</v>
       </c>
-      <c r="J93" t="s">
+      <c r="J94" t="s">
         <v>201</v>
       </c>
-      <c r="K93" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93">
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94">
         <v>10</v>
       </c>
-      <c r="M93" t="b">
-        <v>0</v>
-      </c>
-      <c r="N93" t="b">
-        <v>0</v>
-      </c>
-      <c r="O93" t="s">
+      <c r="M94" t="b">
+        <v>0</v>
+      </c>
+      <c r="N94" t="b">
+        <v>0</v>
+      </c>
+      <c r="O94" t="s">
         <v>312</v>
       </c>
-      <c r="P93" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q93" t="b">
+      <c r="P94" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q94" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6CA857-3B72-4661-9F5D-654284B01FFE}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D23ECFE-1807-46EB-B644-64037EDDF17F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="36" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="37" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="524">
   <si>
     <t>Codigo</t>
   </si>
@@ -1577,6 +1577,27 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7791070000856.png</t>
+  </si>
+  <si>
+    <t>7790360964557</t>
+  </si>
+  <si>
+    <t>Jamón</t>
+  </si>
+  <si>
+    <t>del</t>
+  </si>
+  <si>
+    <t>diablo</t>
+  </si>
+  <si>
+    <t>Swift</t>
+  </si>
+  <si>
+    <t>Untables</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790360964557.png</t>
   </si>
 </sst>
 </file>
@@ -1928,8 +1949,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38046B79-A607-4D28-AECB-80F3895B2123}">
-  <dimension ref="A1:Q94"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8408CCB1-D88D-4719-B036-3D0A4ECB95C0}">
+  <dimension ref="A1:Q95"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3967,34 +3988,34 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
-        <v>366</v>
+        <v>517</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>518</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>519</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>520</v>
       </c>
       <c r="F39" t="s">
-        <v>52</v>
+        <v>521</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I39" t="s">
-        <v>53</v>
+        <v>318</v>
       </c>
       <c r="J39" t="s">
-        <v>49</v>
+        <v>522</v>
       </c>
       <c r="K39" t="s">
         <v>23</v>
@@ -4009,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>257</v>
+        <v>523</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
@@ -4020,34 +4041,34 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F40" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I40" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J40" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
@@ -4062,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
@@ -4073,34 +4094,34 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B41" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E41" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F41" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G41">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I41" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J41" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
@@ -4115,51 +4136,51 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
       </c>
       <c r="Q41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H42" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I42" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J42" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
       </c>
       <c r="L42">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
@@ -4168,45 +4189,45 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
       </c>
       <c r="Q42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C43" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G43">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I43" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J43" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
@@ -4221,51 +4242,51 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
       </c>
       <c r="Q43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D44" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E44" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F44" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G44">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H44" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I44" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J44" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
@@ -4274,45 +4295,45 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
       </c>
       <c r="Q44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C45" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E45" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F45" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G45">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H45" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I45" t="s">
         <v>53</v>
       </c>
       <c r="J45" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
@@ -4327,7 +4348,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -4338,40 +4359,40 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D46" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E46" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F46" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I46" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J46" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
       </c>
       <c r="L46">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
@@ -4380,7 +4401,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
@@ -4391,40 +4412,40 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C47" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F47" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G47">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I47" t="s">
         <v>21</v>
       </c>
       <c r="J47" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
       </c>
       <c r="L47">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
@@ -4433,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
@@ -4444,34 +4465,34 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C48" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E48" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F48" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G48">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I48" t="s">
         <v>21</v>
       </c>
       <c r="J48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
@@ -4486,7 +4507,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
@@ -4497,40 +4518,40 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C49" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D49" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E49" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F49" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G49">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H49" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -4539,51 +4560,51 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D50" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F50" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G50">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H50" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I50" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J50" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
       </c>
       <c r="L50">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -4592,7 +4613,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
@@ -4603,41 +4624,41 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B51" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E51" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F51" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H51" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I51" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J51" t="s">
+        <v>66</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51">
         <v>30</v>
       </c>
-      <c r="K51" t="s">
-        <v>23</v>
-      </c>
-      <c r="L51">
-        <v>12</v>
-      </c>
       <c r="M51" t="b">
         <v>0</v>
       </c>
@@ -4645,113 +4666,113 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
       </c>
       <c r="Q51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
+        <v>29</v>
+      </c>
+      <c r="B52" t="s">
+        <v>378</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" t="s">
+        <v>61</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
+        <v>28</v>
+      </c>
+      <c r="I52" t="s">
+        <v>96</v>
+      </c>
+      <c r="J52" t="s">
         <v>30</v>
       </c>
-      <c r="B52" t="s">
-        <v>379</v>
-      </c>
-      <c r="C52" t="s">
-        <v>97</v>
-      </c>
-      <c r="D52" t="s">
-        <v>98</v>
-      </c>
-      <c r="E52" t="s">
-        <v>99</v>
-      </c>
-      <c r="F52" t="s">
-        <v>100</v>
-      </c>
-      <c r="G52">
-        <v>100</v>
-      </c>
-      <c r="H52" t="s">
-        <v>20</v>
-      </c>
-      <c r="I52" t="s">
-        <v>101</v>
-      </c>
-      <c r="J52" t="s">
-        <v>102</v>
-      </c>
       <c r="K52" t="s">
         <v>23</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
       </c>
       <c r="N52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
       </c>
       <c r="Q52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D53" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F53" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G53">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H53" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I53" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J53" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
       </c>
       <c r="N53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -4762,22 +4783,22 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D54" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E54" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F54" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G54">
         <v>500</v>
@@ -4789,13 +4810,13 @@
         <v>107</v>
       </c>
       <c r="J54" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4804,7 +4825,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -4815,40 +4836,40 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E55" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F55" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H55" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I55" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J55" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -4857,51 +4878,51 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
       </c>
       <c r="Q55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G56">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I56" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -4910,51 +4931,51 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
       </c>
       <c r="Q56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
+        <v>34</v>
+      </c>
+      <c r="B57" t="s">
+        <v>383</v>
+      </c>
+      <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" t="s">
+        <v>115</v>
+      </c>
+      <c r="G57">
+        <v>300</v>
+      </c>
+      <c r="H57" t="s">
         <v>35</v>
       </c>
-      <c r="B57" t="s">
-        <v>384</v>
-      </c>
-      <c r="C57" t="s">
-        <v>117</v>
-      </c>
-      <c r="D57" t="s">
-        <v>118</v>
-      </c>
-      <c r="E57" t="s">
-        <v>119</v>
-      </c>
-      <c r="F57" t="s">
-        <v>120</v>
-      </c>
-      <c r="G57">
-        <v>500</v>
-      </c>
-      <c r="H57" t="s">
-        <v>42</v>
-      </c>
       <c r="I57" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
       </c>
       <c r="L57">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
@@ -4963,7 +4984,7 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -4974,40 +4995,40 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B58" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D58" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E58" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F58" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G58">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H58" t="s">
         <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -5016,51 +5037,51 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C59" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D59" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E59" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F59" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G59">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H59" t="s">
         <v>42</v>
       </c>
       <c r="I59" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J59" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -5069,45 +5090,45 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C60" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D60" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E60" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F60" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G60">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H60" t="s">
         <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J60" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
@@ -5122,51 +5143,51 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B61" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C61" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F61" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G61">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H61" t="s">
         <v>42</v>
       </c>
       <c r="I61" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -5175,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -5186,40 +5207,40 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B62" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C62" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D62" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E62" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F62" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H62" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I62" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J62" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -5228,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5239,63 +5260,63 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B63" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E63" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F63" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G63">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I63" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J63" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
       </c>
       <c r="L63">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C64" t="s">
         <v>138</v>
@@ -5304,10 +5325,10 @@
         <v>139</v>
       </c>
       <c r="E64" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F64" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G64">
         <v>1000</v>
@@ -5331,10 +5352,10 @@
         <v>1</v>
       </c>
       <c r="N64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5345,22 +5366,22 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B65" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C65" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D65" t="s">
         <v>139</v>
       </c>
       <c r="E65" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F65" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G65">
         <v>1000</v>
@@ -5372,7 +5393,7 @@
         <v>142</v>
       </c>
       <c r="J65" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
@@ -5387,7 +5408,7 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5398,193 +5419,193 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B66" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D66" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E66" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F66" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G66">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H66" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J66" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B67" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C67" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D67" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E67" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F67" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H67" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I67" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J67" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K67" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L67">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
       </c>
       <c r="N67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C68" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D68" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E68" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F68" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G68">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I68" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J68" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K68" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L68">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
       </c>
       <c r="N68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B69" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C69" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D69" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E69" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F69" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G69">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H69" t="s">
         <v>42</v>
       </c>
       <c r="I69" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J69" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
@@ -5599,7 +5620,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -5610,22 +5631,22 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B70" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C70" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D70" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E70" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F70" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G70">
         <v>500</v>
@@ -5637,7 +5658,7 @@
         <v>21</v>
       </c>
       <c r="J70" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
@@ -5652,7 +5673,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -5663,25 +5684,25 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B71" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C71" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D71" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E71" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F71" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G71">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H71" t="s">
         <v>42</v>
@@ -5690,7 +5711,7 @@
         <v>21</v>
       </c>
       <c r="J71" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
@@ -5705,7 +5726,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -5716,37 +5737,37 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
+        <v>49</v>
+      </c>
+      <c r="B72" t="s">
+        <v>398</v>
+      </c>
+      <c r="C72" t="s">
+        <v>175</v>
+      </c>
+      <c r="D72" t="s">
+        <v>176</v>
+      </c>
+      <c r="E72" t="s">
+        <v>177</v>
+      </c>
+      <c r="F72" t="s">
+        <v>178</v>
+      </c>
+      <c r="G72">
         <v>50</v>
       </c>
-      <c r="B72" t="s">
-        <v>399</v>
-      </c>
-      <c r="C72" t="s">
-        <v>180</v>
-      </c>
-      <c r="D72" t="s">
-        <v>181</v>
-      </c>
-      <c r="E72" t="s">
-        <v>182</v>
-      </c>
-      <c r="F72" t="s">
-        <v>183</v>
-      </c>
-      <c r="G72">
-        <v>12</v>
-      </c>
       <c r="H72" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I72" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K72" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L72">
         <v>12</v>
@@ -5758,7 +5779,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -5769,40 +5790,40 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B73" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C73" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D73" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E73" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F73" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G73">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H73" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I73" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J73" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K73" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -5811,7 +5832,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -5822,40 +5843,40 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B74" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C74" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D74" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E74" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F74" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G74">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H74" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I74" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J74" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -5864,7 +5885,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -5875,40 +5896,40 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
+        <v>52</v>
+      </c>
+      <c r="B75" t="s">
+        <v>401</v>
+      </c>
+      <c r="C75" t="s">
+        <v>193</v>
+      </c>
+      <c r="D75" t="s">
+        <v>181</v>
+      </c>
+      <c r="E75" t="s">
+        <v>182</v>
+      </c>
+      <c r="F75" t="s">
+        <v>183</v>
+      </c>
+      <c r="G75">
+        <v>24</v>
+      </c>
+      <c r="H75" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s">
         <v>53</v>
       </c>
-      <c r="B75" t="s">
-        <v>402</v>
-      </c>
-      <c r="C75" t="s">
-        <v>31</v>
-      </c>
-      <c r="D75" t="s">
-        <v>194</v>
-      </c>
-      <c r="E75" t="s">
-        <v>195</v>
-      </c>
-      <c r="F75" t="s">
-        <v>196</v>
-      </c>
-      <c r="G75">
-        <v>1.5</v>
-      </c>
-      <c r="H75" t="s">
-        <v>28</v>
-      </c>
-      <c r="I75" t="s">
-        <v>36</v>
-      </c>
       <c r="J75" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -5917,7 +5938,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -5928,52 +5949,52 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B76" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C76" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D76" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E76" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F76" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G76">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I76" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J76" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
       </c>
       <c r="N76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="b">
         <v>1</v>
@@ -5981,93 +6002,93 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B77" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C77" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D77" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E77" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F77" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G77">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H77" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I77" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C78" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D78" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E78" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F78" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G78">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H78" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I78" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J78" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6076,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6087,19 +6108,19 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B79" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C79" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D79" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E79" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F79" t="s">
         <v>208</v>
@@ -6129,7 +6150,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6140,19 +6161,19 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B80" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C80" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D80" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E80" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F80" t="s">
         <v>208</v>
@@ -6173,7 +6194,7 @@
         <v>23</v>
       </c>
       <c r="L80">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6182,7 +6203,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6193,34 +6214,34 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B81" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C81" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D81" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E81" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F81" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H81" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J81" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
@@ -6235,45 +6256,45 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B82" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D82" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E82" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F82" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G82">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J82" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -6288,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6299,49 +6320,49 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C83" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D83" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E83" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F83" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G83">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H83" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J83" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
       </c>
       <c r="N83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6352,22 +6373,22 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B84" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C84" t="s">
         <v>217</v>
       </c>
       <c r="D84" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E84" t="s">
         <v>219</v>
       </c>
       <c r="F84" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G84">
         <v>20</v>
@@ -6394,60 +6415,60 @@
         <v>0</v>
       </c>
       <c r="O84" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B85" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C85" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D85" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E85" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F85" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G85">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H85" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I85" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J85" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
       <c r="N85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6458,34 +6479,34 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B86" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C86" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D86" t="s">
         <v>202</v>
       </c>
       <c r="E86" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F86" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G86">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H86" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I86" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J86" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
@@ -6500,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -6511,40 +6532,40 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B87" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C87" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D87" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E87" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F87" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G87">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H87" t="s">
         <v>42</v>
       </c>
       <c r="I87" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J87" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -6553,51 +6574,51 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B88" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C88" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D88" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E88" t="s">
         <v>229</v>
       </c>
       <c r="F88" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H88" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J88" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -6606,7 +6627,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -6617,40 +6638,40 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B89" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C89" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E89" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F89" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G89">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H89" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I89" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J89" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -6659,45 +6680,45 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B90" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C90" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E90" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F90" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G90">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H90" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I90" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J90" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
@@ -6712,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -6723,10 +6744,10 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B91" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C91" t="s">
         <v>186</v>
@@ -6735,13 +6756,13 @@
         <v>202</v>
       </c>
       <c r="E91" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F91" t="s">
         <v>204</v>
       </c>
       <c r="G91">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H91" t="s">
         <v>35</v>
@@ -6765,7 +6786,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -6776,10 +6797,10 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B92" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C92" t="s">
         <v>186</v>
@@ -6794,7 +6815,7 @@
         <v>204</v>
       </c>
       <c r="G92">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H92" t="s">
         <v>35</v>
@@ -6818,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -6829,41 +6850,41 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B93" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C93" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D93" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E93" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F93" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G93">
+        <v>250</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93" t="s">
+        <v>191</v>
+      </c>
+      <c r="J93" t="s">
+        <v>192</v>
+      </c>
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93">
         <v>6</v>
       </c>
-      <c r="H93" t="s">
-        <v>20</v>
-      </c>
-      <c r="I93" t="s">
-        <v>239</v>
-      </c>
-      <c r="J93" t="s">
-        <v>235</v>
-      </c>
-      <c r="K93" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93">
-        <v>1</v>
-      </c>
       <c r="M93" t="b">
         <v>0</v>
       </c>
@@ -6871,65 +6892,118 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C94" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D94" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E94" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F94" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G94">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H94" t="s">
         <v>20</v>
       </c>
       <c r="I94" t="s">
+        <v>239</v>
+      </c>
+      <c r="J94" t="s">
+        <v>235</v>
+      </c>
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94" t="b">
+        <v>0</v>
+      </c>
+      <c r="N94" t="b">
+        <v>1</v>
+      </c>
+      <c r="O94" t="s">
+        <v>311</v>
+      </c>
+      <c r="P94" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>72</v>
+      </c>
+      <c r="B95" t="s">
+        <v>421</v>
+      </c>
+      <c r="C95" t="s">
+        <v>197</v>
+      </c>
+      <c r="D95" t="s">
+        <v>198</v>
+      </c>
+      <c r="E95" t="s">
+        <v>199</v>
+      </c>
+      <c r="F95" t="s">
+        <v>240</v>
+      </c>
+      <c r="G95">
+        <v>4</v>
+      </c>
+      <c r="H95" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" t="s">
         <v>21</v>
       </c>
-      <c r="J94" t="s">
+      <c r="J95" t="s">
         <v>201</v>
       </c>
-      <c r="K94" t="s">
-        <v>23</v>
-      </c>
-      <c r="L94">
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95">
         <v>10</v>
       </c>
-      <c r="M94" t="b">
-        <v>0</v>
-      </c>
-      <c r="N94" t="b">
-        <v>0</v>
-      </c>
-      <c r="O94" t="s">
+      <c r="M95" t="b">
+        <v>0</v>
+      </c>
+      <c r="N95" t="b">
+        <v>0</v>
+      </c>
+      <c r="O95" t="s">
         <v>312</v>
       </c>
-      <c r="P94" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q94" t="b">
+      <c r="P95" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q95" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D23ECFE-1807-46EB-B644-64037EDDF17F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06466A3A-A8AF-46DA-A003-D8C2F13B9F55}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="37" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="38" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="530">
   <si>
     <t>Codigo</t>
   </si>
@@ -1598,6 +1598,24 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790360964557.png</t>
+  </si>
+  <si>
+    <t>7794866020748</t>
+  </si>
+  <si>
+    <t>Aceite para motos</t>
+  </si>
+  <si>
+    <t>actevo</t>
+  </si>
+  <si>
+    <t>sae 20w-50 4t</t>
+  </si>
+  <si>
+    <t>Castrol</t>
+  </si>
+  <si>
+    <t>Aceites para vehículos</t>
   </si>
 </sst>
 </file>
@@ -1949,8 +1967,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8408CCB1-D88D-4719-B036-3D0A4ECB95C0}">
-  <dimension ref="A1:Q95"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B328F1-CB3A-4988-AF15-90AB4B7C2859}">
+  <dimension ref="A1:Q96"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -1962,7 +1980,7 @@
     <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -4041,34 +4059,34 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
-        <v>366</v>
+        <v>524</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>525</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>526</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>527</v>
       </c>
       <c r="F40" t="s">
-        <v>52</v>
+        <v>528</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J40" t="s">
-        <v>49</v>
+        <v>529</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
@@ -4080,10 +4098,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="b">
-        <v>1</v>
-      </c>
-      <c r="O40" t="s">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
@@ -4094,34 +4109,34 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F41" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I41" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J41" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
@@ -4136,7 +4151,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
@@ -4147,34 +4162,34 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E42" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G42">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I42" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J42" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
@@ -4189,51 +4204,51 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
       </c>
       <c r="Q42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E43" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F43" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H43" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I43" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J43" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
       </c>
       <c r="L43">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
@@ -4242,45 +4257,45 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
       </c>
       <c r="Q43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F44" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G44">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I44" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J44" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
@@ -4295,51 +4310,51 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
       </c>
       <c r="Q44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C45" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F45" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G45">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H45" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I45" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J45" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
       </c>
       <c r="L45">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -4348,45 +4363,45 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
       </c>
       <c r="Q45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C46" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D46" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E46" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F46" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G46">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H46" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s">
         <v>53</v>
       </c>
       <c r="J46" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
@@ -4401,7 +4416,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
@@ -4412,40 +4427,40 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D47" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E47" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F47" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I47" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J47" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
       </c>
       <c r="L47">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
@@ -4454,7 +4469,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
@@ -4465,40 +4480,40 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C48" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E48" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F48" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G48">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I48" t="s">
         <v>21</v>
       </c>
       <c r="J48" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
       </c>
       <c r="L48">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
@@ -4507,7 +4522,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
@@ -4518,34 +4533,34 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C49" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D49" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E49" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F49" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H49" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I49" t="s">
         <v>21</v>
       </c>
       <c r="J49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
@@ -4560,7 +4575,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
@@ -4571,40 +4586,40 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B50" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D50" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E50" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F50" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G50">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J50" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -4613,51 +4628,51 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
       </c>
       <c r="Q50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D51" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E51" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F51" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G51">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H51" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I51" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J51" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -4666,7 +4681,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
@@ -4677,41 +4692,41 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B52" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D52" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E52" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F52" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H52" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I52" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J52" t="s">
+        <v>66</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52">
         <v>30</v>
       </c>
-      <c r="K52" t="s">
-        <v>23</v>
-      </c>
-      <c r="L52">
-        <v>12</v>
-      </c>
       <c r="M52" t="b">
         <v>0</v>
       </c>
@@ -4719,113 +4734,113 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
       </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
+        <v>29</v>
+      </c>
+      <c r="B53" t="s">
+        <v>378</v>
+      </c>
+      <c r="C53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F53" t="s">
+        <v>61</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>28</v>
+      </c>
+      <c r="I53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J53" t="s">
         <v>30</v>
       </c>
-      <c r="B53" t="s">
-        <v>379</v>
-      </c>
-      <c r="C53" t="s">
-        <v>97</v>
-      </c>
-      <c r="D53" t="s">
-        <v>98</v>
-      </c>
-      <c r="E53" t="s">
-        <v>99</v>
-      </c>
-      <c r="F53" t="s">
-        <v>100</v>
-      </c>
-      <c r="G53">
-        <v>100</v>
-      </c>
-      <c r="H53" t="s">
-        <v>20</v>
-      </c>
-      <c r="I53" t="s">
-        <v>101</v>
-      </c>
-      <c r="J53" t="s">
-        <v>102</v>
-      </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
       </c>
       <c r="N53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
       </c>
       <c r="Q53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B54" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D54" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E54" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F54" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G54">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H54" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I54" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J54" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
       </c>
       <c r="N54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -4836,22 +4851,22 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D55" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E55" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F55" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G55">
         <v>500</v>
@@ -4863,13 +4878,13 @@
         <v>107</v>
       </c>
       <c r="J55" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -4878,7 +4893,7 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
@@ -4889,40 +4904,40 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E56" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F56" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H56" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J56" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -4931,51 +4946,51 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
       </c>
       <c r="Q56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G57">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I57" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
       </c>
       <c r="L57">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
@@ -4984,51 +4999,51 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
       </c>
       <c r="Q57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
+        <v>34</v>
+      </c>
+      <c r="B58" t="s">
+        <v>383</v>
+      </c>
+      <c r="C58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" t="s">
+        <v>113</v>
+      </c>
+      <c r="E58" t="s">
+        <v>114</v>
+      </c>
+      <c r="F58" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58">
+        <v>300</v>
+      </c>
+      <c r="H58" t="s">
         <v>35</v>
       </c>
-      <c r="B58" t="s">
-        <v>384</v>
-      </c>
-      <c r="C58" t="s">
-        <v>117</v>
-      </c>
-      <c r="D58" t="s">
-        <v>118</v>
-      </c>
-      <c r="E58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F58" t="s">
-        <v>120</v>
-      </c>
-      <c r="G58">
-        <v>500</v>
-      </c>
-      <c r="H58" t="s">
-        <v>42</v>
-      </c>
       <c r="I58" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -5037,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -5048,40 +5063,40 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B59" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D59" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F59" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G59">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H59" t="s">
         <v>42</v>
       </c>
       <c r="I59" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J59" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -5090,51 +5105,51 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B60" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C60" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D60" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E60" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F60" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G60">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H60" t="s">
         <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J60" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -5143,45 +5158,45 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D61" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E61" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F61" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G61">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H61" t="s">
         <v>42</v>
       </c>
       <c r="I61" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J61" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
@@ -5196,51 +5211,51 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B62" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D62" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E62" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F62" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G62">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H62" t="s">
         <v>42</v>
       </c>
       <c r="I62" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -5249,7 +5264,7 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5260,40 +5275,40 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B63" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C63" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D63" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E63" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F63" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H63" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J63" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
       </c>
       <c r="L63">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -5302,7 +5317,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5313,63 +5328,63 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B64" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C64" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E64" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F64" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G64">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I64" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B65" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C65" t="s">
         <v>138</v>
@@ -5378,10 +5393,10 @@
         <v>139</v>
       </c>
       <c r="E65" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F65" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G65">
         <v>1000</v>
@@ -5405,10 +5420,10 @@
         <v>1</v>
       </c>
       <c r="N65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5419,22 +5434,22 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B66" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C66" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D66" t="s">
         <v>139</v>
       </c>
       <c r="E66" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F66" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G66">
         <v>1000</v>
@@ -5446,7 +5461,7 @@
         <v>142</v>
       </c>
       <c r="J66" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
@@ -5461,7 +5476,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5472,193 +5487,193 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B67" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C67" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D67" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E67" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F67" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G67">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H67" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J67" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B68" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C68" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D68" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E68" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F68" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H68" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I68" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J68" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K68" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L68">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
       </c>
       <c r="N68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C69" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D69" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E69" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F69" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G69">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J69" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K69" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L69">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
       </c>
       <c r="N69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B70" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C70" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D70" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E70" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F70" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G70">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H70" t="s">
         <v>42</v>
       </c>
       <c r="I70" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J70" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
@@ -5673,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -5684,22 +5699,22 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B71" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C71" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D71" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E71" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F71" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G71">
         <v>500</v>
@@ -5711,7 +5726,7 @@
         <v>21</v>
       </c>
       <c r="J71" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
@@ -5726,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -5737,25 +5752,25 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B72" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C72" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D72" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E72" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F72" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G72">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H72" t="s">
         <v>42</v>
@@ -5764,7 +5779,7 @@
         <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
@@ -5779,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -5790,37 +5805,37 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
+        <v>49</v>
+      </c>
+      <c r="B73" t="s">
+        <v>398</v>
+      </c>
+      <c r="C73" t="s">
+        <v>175</v>
+      </c>
+      <c r="D73" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73" t="s">
+        <v>177</v>
+      </c>
+      <c r="F73" t="s">
+        <v>178</v>
+      </c>
+      <c r="G73">
         <v>50</v>
       </c>
-      <c r="B73" t="s">
-        <v>399</v>
-      </c>
-      <c r="C73" t="s">
-        <v>180</v>
-      </c>
-      <c r="D73" t="s">
-        <v>181</v>
-      </c>
-      <c r="E73" t="s">
-        <v>182</v>
-      </c>
-      <c r="F73" t="s">
-        <v>183</v>
-      </c>
-      <c r="G73">
-        <v>12</v>
-      </c>
       <c r="H73" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I73" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K73" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L73">
         <v>12</v>
@@ -5832,7 +5847,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -5843,40 +5858,40 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B74" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C74" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D74" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E74" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F74" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G74">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H74" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I74" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J74" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K74" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -5885,7 +5900,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -5896,40 +5911,40 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C75" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D75" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E75" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F75" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G75">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H75" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I75" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J75" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -5938,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -5949,40 +5964,40 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
+        <v>52</v>
+      </c>
+      <c r="B76" t="s">
+        <v>401</v>
+      </c>
+      <c r="C76" t="s">
+        <v>193</v>
+      </c>
+      <c r="D76" t="s">
+        <v>181</v>
+      </c>
+      <c r="E76" t="s">
+        <v>182</v>
+      </c>
+      <c r="F76" t="s">
+        <v>183</v>
+      </c>
+      <c r="G76">
+        <v>24</v>
+      </c>
+      <c r="H76" t="s">
+        <v>20</v>
+      </c>
+      <c r="I76" t="s">
         <v>53</v>
       </c>
-      <c r="B76" t="s">
-        <v>402</v>
-      </c>
-      <c r="C76" t="s">
-        <v>31</v>
-      </c>
-      <c r="D76" t="s">
-        <v>194</v>
-      </c>
-      <c r="E76" t="s">
-        <v>195</v>
-      </c>
-      <c r="F76" t="s">
-        <v>196</v>
-      </c>
-      <c r="G76">
-        <v>1.5</v>
-      </c>
-      <c r="H76" t="s">
-        <v>28</v>
-      </c>
-      <c r="I76" t="s">
-        <v>36</v>
-      </c>
       <c r="J76" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -5991,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6002,52 +6017,52 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B77" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C77" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D77" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E77" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F77" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G77">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H77" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J77" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="b">
         <v>1</v>
@@ -6055,93 +6070,93 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B78" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C78" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D78" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E78" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F78" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G78">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H78" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
       </c>
       <c r="N78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B79" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C79" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D79" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E79" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F79" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G79">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H79" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J79" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6150,7 +6165,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6161,19 +6176,19 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B80" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C80" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D80" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E80" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F80" t="s">
         <v>208</v>
@@ -6203,7 +6218,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6214,19 +6229,19 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B81" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D81" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E81" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F81" t="s">
         <v>208</v>
@@ -6247,7 +6262,7 @@
         <v>23</v>
       </c>
       <c r="L81">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6256,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6267,34 +6282,34 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B82" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C82" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D82" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E82" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F82" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H82" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J82" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -6309,45 +6324,45 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B83" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C83" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D83" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E83" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F83" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G83">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H83" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I83" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J83" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
@@ -6362,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6373,49 +6388,49 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C84" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D84" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E84" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F84" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G84">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H84" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J84" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
       </c>
       <c r="N84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6426,22 +6441,22 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B85" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C85" t="s">
         <v>217</v>
       </c>
       <c r="D85" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E85" t="s">
         <v>219</v>
       </c>
       <c r="F85" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G85">
         <v>20</v>
@@ -6468,60 +6483,60 @@
         <v>0</v>
       </c>
       <c r="O85" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B86" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C86" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D86" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E86" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F86" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G86">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H86" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J86" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
       <c r="N86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -6532,34 +6547,34 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B87" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C87" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D87" t="s">
         <v>202</v>
       </c>
       <c r="E87" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F87" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G87">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H87" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J87" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
@@ -6574,7 +6589,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -6585,40 +6600,40 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B88" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C88" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D88" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E88" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F88" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G88">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H88" t="s">
         <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J88" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -6627,51 +6642,51 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B89" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C89" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D89" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E89" t="s">
         <v>229</v>
       </c>
       <c r="F89" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H89" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I89" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J89" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -6680,7 +6695,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -6691,40 +6706,40 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B90" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C90" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E90" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F90" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G90">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H90" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I90" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J90" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -6733,45 +6748,45 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C91" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E91" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F91" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G91">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H91" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J91" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
@@ -6786,7 +6801,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -6797,10 +6812,10 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B92" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C92" t="s">
         <v>186</v>
@@ -6809,13 +6824,13 @@
         <v>202</v>
       </c>
       <c r="E92" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F92" t="s">
         <v>204</v>
       </c>
       <c r="G92">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H92" t="s">
         <v>35</v>
@@ -6839,7 +6854,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -6850,10 +6865,10 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B93" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C93" t="s">
         <v>186</v>
@@ -6868,7 +6883,7 @@
         <v>204</v>
       </c>
       <c r="G93">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H93" t="s">
         <v>35</v>
@@ -6892,7 +6907,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -6903,41 +6918,41 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B94" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C94" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D94" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E94" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F94" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G94">
+        <v>250</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94" t="s">
+        <v>191</v>
+      </c>
+      <c r="J94" t="s">
+        <v>192</v>
+      </c>
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94">
         <v>6</v>
       </c>
-      <c r="H94" t="s">
-        <v>20</v>
-      </c>
-      <c r="I94" t="s">
-        <v>239</v>
-      </c>
-      <c r="J94" t="s">
-        <v>235</v>
-      </c>
-      <c r="K94" t="s">
-        <v>23</v>
-      </c>
-      <c r="L94">
-        <v>1</v>
-      </c>
       <c r="M94" t="b">
         <v>0</v>
       </c>
@@ -6945,65 +6960,118 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B95" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C95" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D95" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E95" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F95" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G95">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H95" t="s">
         <v>20</v>
       </c>
       <c r="I95" t="s">
+        <v>239</v>
+      </c>
+      <c r="J95" t="s">
+        <v>235</v>
+      </c>
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95" t="b">
+        <v>0</v>
+      </c>
+      <c r="N95" t="b">
+        <v>1</v>
+      </c>
+      <c r="O95" t="s">
+        <v>311</v>
+      </c>
+      <c r="P95" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>72</v>
+      </c>
+      <c r="B96" t="s">
+        <v>421</v>
+      </c>
+      <c r="C96" t="s">
+        <v>197</v>
+      </c>
+      <c r="D96" t="s">
+        <v>198</v>
+      </c>
+      <c r="E96" t="s">
+        <v>199</v>
+      </c>
+      <c r="F96" t="s">
+        <v>240</v>
+      </c>
+      <c r="G96">
+        <v>4</v>
+      </c>
+      <c r="H96" t="s">
+        <v>20</v>
+      </c>
+      <c r="I96" t="s">
         <v>21</v>
       </c>
-      <c r="J95" t="s">
+      <c r="J96" t="s">
         <v>201</v>
       </c>
-      <c r="K95" t="s">
-        <v>23</v>
-      </c>
-      <c r="L95">
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96">
         <v>10</v>
       </c>
-      <c r="M95" t="b">
-        <v>0</v>
-      </c>
-      <c r="N95" t="b">
-        <v>0</v>
-      </c>
-      <c r="O95" t="s">
+      <c r="M96" t="b">
+        <v>0</v>
+      </c>
+      <c r="N96" t="b">
+        <v>0</v>
+      </c>
+      <c r="O96" t="s">
         <v>312</v>
       </c>
-      <c r="P95" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q95" t="b">
+      <c r="P96" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q96" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06466A3A-A8AF-46DA-A003-D8C2F13B9F55}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9403B5B7-6A2A-4E0A-ABE1-FC6724C0DCEE}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="38" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="40" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="536">
   <si>
     <t>Codigo</t>
   </si>
@@ -1616,6 +1616,24 @@
   </si>
   <si>
     <t>Aceites para vehículos</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7794866020748.png</t>
+  </si>
+  <si>
+    <t>7790150555446</t>
+  </si>
+  <si>
+    <t>Pimienta</t>
+  </si>
+  <si>
+    <t>negra</t>
+  </si>
+  <si>
+    <t>molida</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790150555446.png</t>
   </si>
 </sst>
 </file>
@@ -1967,8 +1985,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B328F1-CB3A-4988-AF15-90AB4B7C2859}">
-  <dimension ref="A1:Q96"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F7C218F-5FF7-43F9-903D-835A7B6E27B0}">
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -4100,6 +4118,9 @@
       <c r="N40" t="b">
         <v>0</v>
       </c>
+      <c r="O40" t="s">
+        <v>530</v>
+      </c>
       <c r="P40" t="b">
         <v>1</v>
       </c>
@@ -4109,40 +4130,40 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
-        <v>366</v>
+        <v>531</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>532</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>533</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>534</v>
       </c>
       <c r="F41" t="s">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H41" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I41" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
@@ -4151,7 +4172,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>257</v>
+        <v>535</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
@@ -4162,34 +4183,34 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I42" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J42" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
@@ -4204,7 +4225,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
@@ -4215,34 +4236,34 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G43">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I43" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J43" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
@@ -4257,51 +4278,51 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
       </c>
       <c r="Q43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E44" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F44" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H44" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I44" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J44" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
       </c>
       <c r="L44">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
@@ -4310,45 +4331,45 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
       </c>
       <c r="Q44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C45" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E45" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G45">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I45" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J45" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
@@ -4363,51 +4384,51 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
       </c>
       <c r="Q45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C46" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E46" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F46" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G46">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H46" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I46" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J46" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
@@ -4416,45 +4437,45 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
       </c>
       <c r="Q46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D47" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E47" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F47" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G47">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H47" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I47" t="s">
         <v>53</v>
       </c>
       <c r="J47" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
@@ -4469,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
@@ -4480,40 +4501,40 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F48" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I48" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J48" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
       </c>
       <c r="L48">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
@@ -4522,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
@@ -4533,40 +4554,40 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C49" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E49" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F49" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G49">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I49" t="s">
         <v>21</v>
       </c>
       <c r="J49" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -4575,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
@@ -4586,34 +4607,34 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D50" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E50" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F50" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H50" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I50" t="s">
         <v>21</v>
       </c>
       <c r="J50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
@@ -4628,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
@@ -4639,40 +4660,40 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C51" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D51" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E51" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F51" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G51">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H51" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I51" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J51" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -4681,51 +4702,51 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
       </c>
       <c r="Q51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C52" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D52" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E52" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F52" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G52">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H52" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I52" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J52" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
       </c>
       <c r="L52">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
@@ -4734,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -4745,41 +4766,41 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B53" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C53" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E53" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F53" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H53" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I53" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J53" t="s">
+        <v>66</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53">
         <v>30</v>
       </c>
-      <c r="K53" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53">
-        <v>12</v>
-      </c>
       <c r="M53" t="b">
         <v>0</v>
       </c>
@@ -4787,113 +4808,113 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
       </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
+        <v>29</v>
+      </c>
+      <c r="B54" t="s">
+        <v>378</v>
+      </c>
+      <c r="C54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" t="s">
+        <v>54</v>
+      </c>
+      <c r="E54" t="s">
+        <v>55</v>
+      </c>
+      <c r="F54" t="s">
+        <v>61</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" t="s">
+        <v>96</v>
+      </c>
+      <c r="J54" t="s">
         <v>30</v>
       </c>
-      <c r="B54" t="s">
-        <v>379</v>
-      </c>
-      <c r="C54" t="s">
-        <v>97</v>
-      </c>
-      <c r="D54" t="s">
-        <v>98</v>
-      </c>
-      <c r="E54" t="s">
-        <v>99</v>
-      </c>
-      <c r="F54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G54">
-        <v>100</v>
-      </c>
-      <c r="H54" t="s">
-        <v>20</v>
-      </c>
-      <c r="I54" t="s">
-        <v>101</v>
-      </c>
-      <c r="J54" t="s">
-        <v>102</v>
-      </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
       </c>
       <c r="N54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
       </c>
       <c r="Q54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C55" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E55" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F55" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G55">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H55" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I55" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J55" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
       </c>
       <c r="N55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
@@ -4904,22 +4925,22 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D56" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E56" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F56" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G56">
         <v>500</v>
@@ -4931,13 +4952,13 @@
         <v>107</v>
       </c>
       <c r="J56" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -4946,7 +4967,7 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
@@ -4957,40 +4978,40 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E57" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F57" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H57" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I57" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J57" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
       </c>
       <c r="L57">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
@@ -4999,51 +5020,51 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
       </c>
       <c r="Q57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E58" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G58">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I58" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -5052,51 +5073,51 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
+        <v>34</v>
+      </c>
+      <c r="B59" t="s">
+        <v>383</v>
+      </c>
+      <c r="C59" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" t="s">
+        <v>113</v>
+      </c>
+      <c r="E59" t="s">
+        <v>114</v>
+      </c>
+      <c r="F59" t="s">
+        <v>115</v>
+      </c>
+      <c r="G59">
+        <v>300</v>
+      </c>
+      <c r="H59" t="s">
         <v>35</v>
       </c>
-      <c r="B59" t="s">
-        <v>384</v>
-      </c>
-      <c r="C59" t="s">
-        <v>117</v>
-      </c>
-      <c r="D59" t="s">
-        <v>118</v>
-      </c>
-      <c r="E59" t="s">
-        <v>119</v>
-      </c>
-      <c r="F59" t="s">
-        <v>120</v>
-      </c>
-      <c r="G59">
-        <v>500</v>
-      </c>
-      <c r="H59" t="s">
-        <v>42</v>
-      </c>
       <c r="I59" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J59" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -5105,7 +5126,7 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -5116,40 +5137,40 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B60" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D60" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F60" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G60">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H60" t="s">
         <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J60" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -5158,51 +5179,51 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B61" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C61" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D61" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E61" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F61" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G61">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H61" t="s">
         <v>42</v>
       </c>
       <c r="I61" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J61" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -5211,45 +5232,45 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C62" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D62" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E62" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F62" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G62">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H62" t="s">
         <v>42</v>
       </c>
       <c r="I62" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J62" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
@@ -5264,51 +5285,51 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C63" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D63" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E63" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F63" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G63">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H63" t="s">
         <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J63" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
       </c>
       <c r="L63">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -5317,7 +5338,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5328,40 +5349,40 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B64" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C64" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D64" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E64" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F64" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H64" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J64" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
@@ -5370,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5381,63 +5402,63 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B65" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C65" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E65" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F65" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G65">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I65" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B66" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C66" t="s">
         <v>138</v>
@@ -5446,10 +5467,10 @@
         <v>139</v>
       </c>
       <c r="E66" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F66" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G66">
         <v>1000</v>
@@ -5473,10 +5494,10 @@
         <v>1</v>
       </c>
       <c r="N66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5487,22 +5508,22 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B67" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D67" t="s">
         <v>139</v>
       </c>
       <c r="E67" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F67" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G67">
         <v>1000</v>
@@ -5514,7 +5535,7 @@
         <v>142</v>
       </c>
       <c r="J67" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
@@ -5529,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5540,193 +5561,193 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B68" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C68" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D68" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E68" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F68" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G68">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H68" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J68" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B69" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C69" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D69" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E69" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F69" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H69" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I69" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J69" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K69" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L69">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
       </c>
       <c r="N69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C70" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D70" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E70" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F70" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G70">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I70" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J70" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K70" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L70">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
       </c>
       <c r="N70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B71" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C71" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D71" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E71" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F71" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G71">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H71" t="s">
         <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J71" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
@@ -5741,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -5752,22 +5773,22 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B72" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C72" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E72" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F72" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G72">
         <v>500</v>
@@ -5779,7 +5800,7 @@
         <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
@@ -5794,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -5805,25 +5826,25 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B73" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C73" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D73" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E73" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F73" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G73">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H73" t="s">
         <v>42</v>
@@ -5832,7 +5853,7 @@
         <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
@@ -5847,7 +5868,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -5858,37 +5879,37 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
+        <v>49</v>
+      </c>
+      <c r="B74" t="s">
+        <v>398</v>
+      </c>
+      <c r="C74" t="s">
+        <v>175</v>
+      </c>
+      <c r="D74" t="s">
+        <v>176</v>
+      </c>
+      <c r="E74" t="s">
+        <v>177</v>
+      </c>
+      <c r="F74" t="s">
+        <v>178</v>
+      </c>
+      <c r="G74">
         <v>50</v>
       </c>
-      <c r="B74" t="s">
-        <v>399</v>
-      </c>
-      <c r="C74" t="s">
-        <v>180</v>
-      </c>
-      <c r="D74" t="s">
-        <v>181</v>
-      </c>
-      <c r="E74" t="s">
-        <v>182</v>
-      </c>
-      <c r="F74" t="s">
-        <v>183</v>
-      </c>
-      <c r="G74">
-        <v>12</v>
-      </c>
       <c r="H74" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K74" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L74">
         <v>12</v>
@@ -5900,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -5911,40 +5932,40 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B75" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C75" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D75" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E75" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F75" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G75">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H75" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I75" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J75" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K75" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -5953,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -5964,40 +5985,40 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C76" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D76" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E76" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F76" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G76">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I76" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J76" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6006,7 +6027,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6017,40 +6038,40 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
+        <v>52</v>
+      </c>
+      <c r="B77" t="s">
+        <v>401</v>
+      </c>
+      <c r="C77" t="s">
+        <v>193</v>
+      </c>
+      <c r="D77" t="s">
+        <v>181</v>
+      </c>
+      <c r="E77" t="s">
+        <v>182</v>
+      </c>
+      <c r="F77" t="s">
+        <v>183</v>
+      </c>
+      <c r="G77">
+        <v>24</v>
+      </c>
+      <c r="H77" t="s">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s">
         <v>53</v>
       </c>
-      <c r="B77" t="s">
-        <v>402</v>
-      </c>
-      <c r="C77" t="s">
-        <v>31</v>
-      </c>
-      <c r="D77" t="s">
-        <v>194</v>
-      </c>
-      <c r="E77" t="s">
-        <v>195</v>
-      </c>
-      <c r="F77" t="s">
-        <v>196</v>
-      </c>
-      <c r="G77">
-        <v>1.5</v>
-      </c>
-      <c r="H77" t="s">
-        <v>28</v>
-      </c>
-      <c r="I77" t="s">
-        <v>36</v>
-      </c>
       <c r="J77" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6059,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6070,52 +6091,52 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B78" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C78" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D78" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E78" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F78" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G78">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H78" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J78" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
       </c>
       <c r="N78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" t="b">
         <v>1</v>
@@ -6123,93 +6144,93 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B79" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C79" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D79" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E79" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F79" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G79">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H79" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I79" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B80" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C80" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D80" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E80" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F80" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G80">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H80" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J80" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6218,7 +6239,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6229,19 +6250,19 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B81" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C81" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D81" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E81" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F81" t="s">
         <v>208</v>
@@ -6271,7 +6292,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6282,19 +6303,19 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C82" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D82" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E82" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F82" t="s">
         <v>208</v>
@@ -6315,7 +6336,7 @@
         <v>23</v>
       </c>
       <c r="L82">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -6324,7 +6345,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6335,34 +6356,34 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B83" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C83" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D83" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E83" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F83" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H83" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J83" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
@@ -6377,45 +6398,45 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B84" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D84" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E84" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F84" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G84">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J84" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
@@ -6430,7 +6451,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6441,49 +6462,49 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B85" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C85" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D85" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E85" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F85" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G85">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H85" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J85" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
       <c r="N85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6494,22 +6515,22 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B86" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C86" t="s">
         <v>217</v>
       </c>
       <c r="D86" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E86" t="s">
         <v>219</v>
       </c>
       <c r="F86" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G86">
         <v>20</v>
@@ -6536,60 +6557,60 @@
         <v>0</v>
       </c>
       <c r="O86" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B87" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C87" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D87" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E87" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F87" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G87">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H87" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I87" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J87" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
       </c>
       <c r="N87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -6600,34 +6621,34 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B88" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C88" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D88" t="s">
         <v>202</v>
       </c>
       <c r="E88" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F88" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G88">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H88" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J88" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
@@ -6642,7 +6663,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -6653,40 +6674,40 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B89" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C89" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D89" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E89" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F89" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G89">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H89" t="s">
         <v>42</v>
       </c>
       <c r="I89" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J89" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -6695,51 +6716,51 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B90" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D90" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E90" t="s">
         <v>229</v>
       </c>
       <c r="F90" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H90" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I90" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J90" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -6748,7 +6769,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -6759,40 +6780,40 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B91" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C91" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E91" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F91" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G91">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I91" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J91" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -6801,45 +6822,45 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C92" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E92" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F92" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G92">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H92" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J92" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
@@ -6854,7 +6875,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -6865,10 +6886,10 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B93" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C93" t="s">
         <v>186</v>
@@ -6877,13 +6898,13 @@
         <v>202</v>
       </c>
       <c r="E93" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F93" t="s">
         <v>204</v>
       </c>
       <c r="G93">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H93" t="s">
         <v>35</v>
@@ -6907,7 +6928,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -6918,10 +6939,10 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B94" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C94" t="s">
         <v>186</v>
@@ -6936,7 +6957,7 @@
         <v>204</v>
       </c>
       <c r="G94">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H94" t="s">
         <v>35</v>
@@ -6960,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -6971,41 +6992,41 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B95" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C95" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D95" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E95" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F95" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G95">
+        <v>250</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95" t="s">
+        <v>191</v>
+      </c>
+      <c r="J95" t="s">
+        <v>192</v>
+      </c>
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95">
         <v>6</v>
       </c>
-      <c r="H95" t="s">
-        <v>20</v>
-      </c>
-      <c r="I95" t="s">
-        <v>239</v>
-      </c>
-      <c r="J95" t="s">
-        <v>235</v>
-      </c>
-      <c r="K95" t="s">
-        <v>23</v>
-      </c>
-      <c r="L95">
-        <v>1</v>
-      </c>
       <c r="M95" t="b">
         <v>0</v>
       </c>
@@ -7013,65 +7034,118 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B96" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C96" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D96" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E96" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G96">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H96" t="s">
         <v>20</v>
       </c>
       <c r="I96" t="s">
+        <v>239</v>
+      </c>
+      <c r="J96" t="s">
+        <v>235</v>
+      </c>
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96" t="b">
+        <v>0</v>
+      </c>
+      <c r="N96" t="b">
+        <v>1</v>
+      </c>
+      <c r="O96" t="s">
+        <v>311</v>
+      </c>
+      <c r="P96" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>72</v>
+      </c>
+      <c r="B97" t="s">
+        <v>421</v>
+      </c>
+      <c r="C97" t="s">
+        <v>197</v>
+      </c>
+      <c r="D97" t="s">
+        <v>198</v>
+      </c>
+      <c r="E97" t="s">
+        <v>199</v>
+      </c>
+      <c r="F97" t="s">
+        <v>240</v>
+      </c>
+      <c r="G97">
+        <v>4</v>
+      </c>
+      <c r="H97" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" t="s">
         <v>21</v>
       </c>
-      <c r="J96" t="s">
+      <c r="J97" t="s">
         <v>201</v>
       </c>
-      <c r="K96" t="s">
-        <v>23</v>
-      </c>
-      <c r="L96">
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97">
         <v>10</v>
       </c>
-      <c r="M96" t="b">
-        <v>0</v>
-      </c>
-      <c r="N96" t="b">
-        <v>0</v>
-      </c>
-      <c r="O96" t="s">
+      <c r="M97" t="b">
+        <v>0</v>
+      </c>
+      <c r="N97" t="b">
+        <v>0</v>
+      </c>
+      <c r="O97" t="s">
         <v>312</v>
       </c>
-      <c r="P96" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q96" t="b">
+      <c r="P97" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q97" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9403B5B7-6A2A-4E0A-ABE1-FC6724C0DCEE}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065AAEC0-38A7-42F8-9895-1FC6CAE72A10}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="40" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="41" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="543">
   <si>
     <t>Codigo</t>
   </si>
@@ -1634,6 +1634,27 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790150555446.png</t>
+  </si>
+  <si>
+    <t>7793377000317</t>
+  </si>
+  <si>
+    <t>Aceite</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>girasol</t>
+  </si>
+  <si>
+    <t>Lágrimas Del Sol</t>
+  </si>
+  <si>
+    <t>Aceites</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7793377000317.png</t>
   </si>
 </sst>
 </file>
@@ -1985,8 +2006,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F7C218F-5FF7-43F9-903D-835A7B6E27B0}">
-  <dimension ref="A1:Q97"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA88175A-D1DD-45AF-90F3-536F7993E224}">
+  <dimension ref="A1:Q98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -1994,7 +2015,7 @@
     <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -4183,34 +4204,34 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
-        <v>366</v>
+        <v>536</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>537</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>538</v>
       </c>
       <c r="E42" t="s">
-        <v>51</v>
+        <v>539</v>
       </c>
       <c r="F42" t="s">
-        <v>52</v>
+        <v>540</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>900</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I42" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J42" t="s">
-        <v>49</v>
+        <v>541</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
@@ -4225,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>257</v>
+        <v>542</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
@@ -4236,34 +4257,34 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E43" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F43" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I43" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J43" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
@@ -4278,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
@@ -4289,34 +4310,34 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B44" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E44" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G44">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I44" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J44" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
@@ -4331,51 +4352,51 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
       </c>
       <c r="Q44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E45" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F45" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H45" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I45" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J45" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
       </c>
       <c r="L45">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -4384,45 +4405,45 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
       </c>
       <c r="Q45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C46" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E46" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F46" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G46">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I46" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J46" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
@@ -4437,51 +4458,51 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
       </c>
       <c r="Q46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C47" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E47" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F47" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G47">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H47" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I47" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J47" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
@@ -4490,45 +4511,45 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
       </c>
       <c r="Q47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D48" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E48" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F48" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G48">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H48" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I48" t="s">
         <v>53</v>
       </c>
       <c r="J48" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
@@ -4543,7 +4564,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
@@ -4554,40 +4575,40 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E49" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F49" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I49" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J49" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -4596,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
@@ -4607,40 +4628,40 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E50" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F50" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G50">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I50" t="s">
         <v>21</v>
       </c>
       <c r="J50" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
       </c>
       <c r="L50">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -4649,7 +4670,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
@@ -4660,34 +4681,34 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C51" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D51" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E51" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F51" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G51">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H51" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I51" t="s">
         <v>21</v>
       </c>
       <c r="J51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
@@ -4702,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
@@ -4713,40 +4734,40 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E52" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F52" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G52">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H52" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I52" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J52" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
@@ -4755,51 +4776,51 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
       </c>
       <c r="Q52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C53" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D53" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E53" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F53" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G53">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I53" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J53" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -4808,7 +4829,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -4819,41 +4840,41 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D54" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E54" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F54" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H54" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I54" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J54" t="s">
+        <v>66</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54">
         <v>30</v>
       </c>
-      <c r="K54" t="s">
-        <v>23</v>
-      </c>
-      <c r="L54">
-        <v>12</v>
-      </c>
       <c r="M54" t="b">
         <v>0</v>
       </c>
@@ -4861,113 +4882,113 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
       </c>
       <c r="Q54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
+        <v>29</v>
+      </c>
+      <c r="B55" t="s">
+        <v>378</v>
+      </c>
+      <c r="C55" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>54</v>
+      </c>
+      <c r="E55" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>28</v>
+      </c>
+      <c r="I55" t="s">
+        <v>96</v>
+      </c>
+      <c r="J55" t="s">
         <v>30</v>
       </c>
-      <c r="B55" t="s">
-        <v>379</v>
-      </c>
-      <c r="C55" t="s">
-        <v>97</v>
-      </c>
-      <c r="D55" t="s">
-        <v>98</v>
-      </c>
-      <c r="E55" t="s">
-        <v>99</v>
-      </c>
-      <c r="F55" t="s">
-        <v>100</v>
-      </c>
-      <c r="G55">
-        <v>100</v>
-      </c>
-      <c r="H55" t="s">
-        <v>20</v>
-      </c>
-      <c r="I55" t="s">
-        <v>101</v>
-      </c>
-      <c r="J55" t="s">
-        <v>102</v>
-      </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
       </c>
       <c r="N55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
       </c>
       <c r="Q55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B56" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E56" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F56" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G56">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H56" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I56" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J56" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
       </c>
       <c r="N56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
@@ -4978,22 +4999,22 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D57" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E57" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F57" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G57">
         <v>500</v>
@@ -5005,13 +5026,13 @@
         <v>107</v>
       </c>
       <c r="J57" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
       </c>
       <c r="L57">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
@@ -5020,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -5031,40 +5052,40 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C58" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D58" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E58" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F58" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H58" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I58" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J58" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -5073,51 +5094,51 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G59">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I59" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J59" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -5126,51 +5147,51 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
+        <v>34</v>
+      </c>
+      <c r="B60" t="s">
+        <v>383</v>
+      </c>
+      <c r="C60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" t="s">
+        <v>113</v>
+      </c>
+      <c r="E60" t="s">
+        <v>114</v>
+      </c>
+      <c r="F60" t="s">
+        <v>115</v>
+      </c>
+      <c r="G60">
+        <v>300</v>
+      </c>
+      <c r="H60" t="s">
         <v>35</v>
       </c>
-      <c r="B60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C60" t="s">
-        <v>117</v>
-      </c>
-      <c r="D60" t="s">
-        <v>118</v>
-      </c>
-      <c r="E60" t="s">
-        <v>119</v>
-      </c>
-      <c r="F60" t="s">
-        <v>120</v>
-      </c>
-      <c r="G60">
-        <v>500</v>
-      </c>
-      <c r="H60" t="s">
-        <v>42</v>
-      </c>
       <c r="I60" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J60" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -5179,7 +5200,7 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
@@ -5190,40 +5211,40 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B61" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D61" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F61" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G61">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H61" t="s">
         <v>42</v>
       </c>
       <c r="I61" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -5232,51 +5253,51 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B62" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C62" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D62" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E62" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F62" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G62">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H62" t="s">
         <v>42</v>
       </c>
       <c r="I62" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J62" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -5285,45 +5306,45 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B63" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C63" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D63" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E63" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F63" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G63">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H63" t="s">
         <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J63" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
@@ -5338,51 +5359,51 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D64" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E64" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F64" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G64">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H64" t="s">
         <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
@@ -5391,7 +5412,7 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5402,40 +5423,40 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C65" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D65" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E65" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F65" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H65" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J65" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -5444,7 +5465,7 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5455,63 +5476,63 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B66" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C66" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D66" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E66" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F66" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G66">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I66" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C67" t="s">
         <v>138</v>
@@ -5520,10 +5541,10 @@
         <v>139</v>
       </c>
       <c r="E67" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F67" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G67">
         <v>1000</v>
@@ -5547,10 +5568,10 @@
         <v>1</v>
       </c>
       <c r="N67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5561,22 +5582,22 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B68" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C68" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D68" t="s">
         <v>139</v>
       </c>
       <c r="E68" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F68" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G68">
         <v>1000</v>
@@ -5588,7 +5609,7 @@
         <v>142</v>
       </c>
       <c r="J68" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
@@ -5603,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -5614,193 +5635,193 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B69" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C69" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D69" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E69" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F69" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G69">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H69" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I69" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J69" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B70" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C70" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D70" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E70" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F70" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H70" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J70" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K70" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L70">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
       </c>
       <c r="N70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C71" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D71" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E71" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F71" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G71">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I71" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J71" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K71" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L71">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
       </c>
       <c r="N71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B72" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C72" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D72" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E72" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F72" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G72">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H72" t="s">
         <v>42</v>
       </c>
       <c r="I72" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J72" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
@@ -5815,7 +5836,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -5826,22 +5847,22 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B73" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C73" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D73" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E73" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F73" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G73">
         <v>500</v>
@@ -5853,7 +5874,7 @@
         <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
@@ -5868,7 +5889,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -5879,25 +5900,25 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B74" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C74" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D74" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E74" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F74" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G74">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H74" t="s">
         <v>42</v>
@@ -5906,7 +5927,7 @@
         <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
@@ -5921,7 +5942,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -5932,37 +5953,37 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
+        <v>49</v>
+      </c>
+      <c r="B75" t="s">
+        <v>398</v>
+      </c>
+      <c r="C75" t="s">
+        <v>175</v>
+      </c>
+      <c r="D75" t="s">
+        <v>176</v>
+      </c>
+      <c r="E75" t="s">
+        <v>177</v>
+      </c>
+      <c r="F75" t="s">
+        <v>178</v>
+      </c>
+      <c r="G75">
         <v>50</v>
       </c>
-      <c r="B75" t="s">
-        <v>399</v>
-      </c>
-      <c r="C75" t="s">
-        <v>180</v>
-      </c>
-      <c r="D75" t="s">
-        <v>181</v>
-      </c>
-      <c r="E75" t="s">
-        <v>182</v>
-      </c>
-      <c r="F75" t="s">
-        <v>183</v>
-      </c>
-      <c r="G75">
-        <v>12</v>
-      </c>
       <c r="H75" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K75" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L75">
         <v>12</v>
@@ -5974,7 +5995,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -5985,40 +6006,40 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B76" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C76" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D76" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E76" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F76" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G76">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H76" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I76" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J76" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K76" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6027,7 +6048,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6038,40 +6059,40 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B77" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C77" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D77" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E77" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F77" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G77">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H77" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I77" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J77" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6080,7 +6101,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6091,40 +6112,40 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
+        <v>52</v>
+      </c>
+      <c r="B78" t="s">
+        <v>401</v>
+      </c>
+      <c r="C78" t="s">
+        <v>193</v>
+      </c>
+      <c r="D78" t="s">
+        <v>181</v>
+      </c>
+      <c r="E78" t="s">
+        <v>182</v>
+      </c>
+      <c r="F78" t="s">
+        <v>183</v>
+      </c>
+      <c r="G78">
+        <v>24</v>
+      </c>
+      <c r="H78" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" t="s">
         <v>53</v>
       </c>
-      <c r="B78" t="s">
-        <v>402</v>
-      </c>
-      <c r="C78" t="s">
-        <v>31</v>
-      </c>
-      <c r="D78" t="s">
-        <v>194</v>
-      </c>
-      <c r="E78" t="s">
-        <v>195</v>
-      </c>
-      <c r="F78" t="s">
-        <v>196</v>
-      </c>
-      <c r="G78">
-        <v>1.5</v>
-      </c>
-      <c r="H78" t="s">
-        <v>28</v>
-      </c>
-      <c r="I78" t="s">
-        <v>36</v>
-      </c>
       <c r="J78" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6133,7 +6154,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6144,52 +6165,52 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B79" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C79" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D79" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E79" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F79" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G79">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H79" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J79" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="b">
         <v>1</v>
@@ -6197,93 +6218,93 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B80" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C80" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D80" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E80" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F80" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G80">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H80" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I80" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B81" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D81" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E81" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F81" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G81">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H81" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I81" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J81" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6292,7 +6313,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6303,19 +6324,19 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B82" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C82" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D82" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E82" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F82" t="s">
         <v>208</v>
@@ -6345,7 +6366,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6356,19 +6377,19 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B83" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C83" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D83" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E83" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F83" t="s">
         <v>208</v>
@@ -6389,7 +6410,7 @@
         <v>23</v>
       </c>
       <c r="L83">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -6398,7 +6419,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6409,34 +6430,34 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B84" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C84" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D84" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E84" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F84" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H84" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J84" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
@@ -6451,45 +6472,45 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B85" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D85" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E85" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F85" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G85">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I85" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J85" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
@@ -6504,7 +6525,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6515,49 +6536,49 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B86" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C86" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D86" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E86" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F86" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G86">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H86" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I86" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J86" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
       <c r="N86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -6568,22 +6589,22 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B87" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C87" t="s">
         <v>217</v>
       </c>
       <c r="D87" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E87" t="s">
         <v>219</v>
       </c>
       <c r="F87" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G87">
         <v>20</v>
@@ -6610,60 +6631,60 @@
         <v>0</v>
       </c>
       <c r="O87" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B88" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C88" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D88" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E88" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F88" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G88">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H88" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I88" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J88" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
       <c r="N88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -6674,34 +6695,34 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B89" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C89" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D89" t="s">
         <v>202</v>
       </c>
       <c r="E89" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F89" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G89">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H89" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J89" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
@@ -6716,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -6727,40 +6748,40 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B90" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C90" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D90" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E90" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F90" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G90">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H90" t="s">
         <v>42</v>
       </c>
       <c r="I90" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J90" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -6769,51 +6790,51 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B91" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C91" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D91" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E91" t="s">
         <v>229</v>
       </c>
       <c r="F91" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H91" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J91" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -6822,7 +6843,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -6833,40 +6854,40 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B92" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C92" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E92" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F92" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G92">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H92" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I92" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J92" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -6875,45 +6896,45 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C93" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E93" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F93" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G93">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H93" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J93" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
@@ -6928,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -6939,10 +6960,10 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C94" t="s">
         <v>186</v>
@@ -6951,13 +6972,13 @@
         <v>202</v>
       </c>
       <c r="E94" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F94" t="s">
         <v>204</v>
       </c>
       <c r="G94">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H94" t="s">
         <v>35</v>
@@ -6981,7 +7002,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -6992,10 +7013,10 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B95" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C95" t="s">
         <v>186</v>
@@ -7010,7 +7031,7 @@
         <v>204</v>
       </c>
       <c r="G95">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H95" t="s">
         <v>35</v>
@@ -7034,7 +7055,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7045,41 +7066,41 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B96" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C96" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D96" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E96" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F96" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G96">
+        <v>250</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96" t="s">
+        <v>191</v>
+      </c>
+      <c r="J96" t="s">
+        <v>192</v>
+      </c>
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96">
         <v>6</v>
       </c>
-      <c r="H96" t="s">
-        <v>20</v>
-      </c>
-      <c r="I96" t="s">
-        <v>239</v>
-      </c>
-      <c r="J96" t="s">
-        <v>235</v>
-      </c>
-      <c r="K96" t="s">
-        <v>23</v>
-      </c>
-      <c r="L96">
-        <v>1</v>
-      </c>
       <c r="M96" t="b">
         <v>0</v>
       </c>
@@ -7087,65 +7108,118 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B97" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C97" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D97" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E97" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G97">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H97" t="s">
         <v>20</v>
       </c>
       <c r="I97" t="s">
+        <v>239</v>
+      </c>
+      <c r="J97" t="s">
+        <v>235</v>
+      </c>
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97" t="b">
+        <v>0</v>
+      </c>
+      <c r="N97" t="b">
+        <v>1</v>
+      </c>
+      <c r="O97" t="s">
+        <v>311</v>
+      </c>
+      <c r="P97" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>72</v>
+      </c>
+      <c r="B98" t="s">
+        <v>421</v>
+      </c>
+      <c r="C98" t="s">
+        <v>197</v>
+      </c>
+      <c r="D98" t="s">
+        <v>198</v>
+      </c>
+      <c r="E98" t="s">
+        <v>199</v>
+      </c>
+      <c r="F98" t="s">
+        <v>240</v>
+      </c>
+      <c r="G98">
+        <v>4</v>
+      </c>
+      <c r="H98" t="s">
+        <v>20</v>
+      </c>
+      <c r="I98" t="s">
         <v>21</v>
       </c>
-      <c r="J97" t="s">
+      <c r="J98" t="s">
         <v>201</v>
       </c>
-      <c r="K97" t="s">
-        <v>23</v>
-      </c>
-      <c r="L97">
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98">
         <v>10</v>
       </c>
-      <c r="M97" t="b">
-        <v>0</v>
-      </c>
-      <c r="N97" t="b">
-        <v>0</v>
-      </c>
-      <c r="O97" t="s">
+      <c r="M98" t="b">
+        <v>0</v>
+      </c>
+      <c r="N98" t="b">
+        <v>0</v>
+      </c>
+      <c r="O98" t="s">
         <v>312</v>
       </c>
-      <c r="P97" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q97" t="b">
+      <c r="P98" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q98" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065AAEC0-38A7-42F8-9895-1FC6CAE72A10}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052BD8F7-3D37-47B0-9D80-05E0AC0E7B9B}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="41" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="42" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="548">
   <si>
     <t>Codigo</t>
   </si>
@@ -1655,6 +1655,21 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7793377000317.png</t>
+  </si>
+  <si>
+    <t>7790360966582</t>
+  </si>
+  <si>
+    <t>Picadillo</t>
+  </si>
+  <si>
+    <t>de carne</t>
+  </si>
+  <si>
+    <t>sabor picante</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790360966582.png</t>
   </si>
 </sst>
 </file>
@@ -2006,8 +2021,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA88175A-D1DD-45AF-90F3-536F7993E224}">
-  <dimension ref="A1:Q98"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603FE7AA-F6BF-48FE-A48F-50AA60D3657E}">
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -4257,34 +4272,34 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>544</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>545</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>546</v>
       </c>
       <c r="F43" t="s">
-        <v>52</v>
+        <v>521</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I43" t="s">
-        <v>53</v>
+        <v>318</v>
       </c>
       <c r="J43" t="s">
-        <v>49</v>
+        <v>522</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
@@ -4299,7 +4314,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>257</v>
+        <v>547</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
@@ -4310,34 +4325,34 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C44" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E44" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I44" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J44" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
@@ -4352,7 +4367,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -4363,34 +4378,34 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E45" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G45">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I45" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J45" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
@@ -4405,51 +4420,51 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
       </c>
       <c r="Q45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F46" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H46" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I46" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J46" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
       </c>
       <c r="L46">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
@@ -4458,45 +4473,45 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
       </c>
       <c r="Q46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E47" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G47">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I47" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J47" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
@@ -4511,51 +4526,51 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
       </c>
       <c r="Q47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E48" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F48" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G48">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I48" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J48" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
@@ -4564,45 +4579,45 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
       </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D49" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E49" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F49" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G49">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H49" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s">
         <v>53</v>
       </c>
       <c r="J49" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
@@ -4617,7 +4632,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
@@ -4628,40 +4643,40 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E50" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F50" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I50" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J50" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
       </c>
       <c r="L50">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -4670,7 +4685,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
@@ -4681,40 +4696,40 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B51" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C51" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E51" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F51" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G51">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I51" t="s">
         <v>21</v>
       </c>
       <c r="J51" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -4723,7 +4738,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
@@ -4734,34 +4749,34 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D52" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E52" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F52" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H52" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I52" t="s">
         <v>21</v>
       </c>
       <c r="J52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
@@ -4776,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -4787,40 +4802,40 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C53" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E53" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F53" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G53">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H53" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I53" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -4829,51 +4844,51 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
       </c>
       <c r="Q53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C54" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D54" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E54" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F54" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G54">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H54" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J54" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4882,7 +4897,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -4893,41 +4908,41 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E55" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F55" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H55" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I55" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J55" t="s">
+        <v>66</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55">
         <v>30</v>
       </c>
-      <c r="K55" t="s">
-        <v>23</v>
-      </c>
-      <c r="L55">
-        <v>12</v>
-      </c>
       <c r="M55" t="b">
         <v>0</v>
       </c>
@@ -4935,113 +4950,113 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
       </c>
       <c r="Q55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
+        <v>29</v>
+      </c>
+      <c r="B56" t="s">
+        <v>378</v>
+      </c>
+      <c r="C56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" t="s">
+        <v>54</v>
+      </c>
+      <c r="E56" t="s">
+        <v>55</v>
+      </c>
+      <c r="F56" t="s">
+        <v>61</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" t="s">
+        <v>96</v>
+      </c>
+      <c r="J56" t="s">
         <v>30</v>
       </c>
-      <c r="B56" t="s">
-        <v>379</v>
-      </c>
-      <c r="C56" t="s">
-        <v>97</v>
-      </c>
-      <c r="D56" t="s">
-        <v>98</v>
-      </c>
-      <c r="E56" t="s">
-        <v>99</v>
-      </c>
-      <c r="F56" t="s">
-        <v>100</v>
-      </c>
-      <c r="G56">
-        <v>100</v>
-      </c>
-      <c r="H56" t="s">
-        <v>20</v>
-      </c>
-      <c r="I56" t="s">
-        <v>101</v>
-      </c>
-      <c r="J56" t="s">
-        <v>102</v>
-      </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
       </c>
       <c r="N56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
       </c>
       <c r="Q56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B57" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D57" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E57" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F57" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G57">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H57" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I57" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J57" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K57" t="s">
         <v>23</v>
       </c>
       <c r="L57">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
       </c>
       <c r="N57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -5052,22 +5067,22 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B58" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E58" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F58" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G58">
         <v>500</v>
@@ -5079,13 +5094,13 @@
         <v>107</v>
       </c>
       <c r="J58" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -5094,7 +5109,7 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -5105,40 +5120,40 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C59" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D59" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E59" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F59" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H59" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I59" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J59" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -5147,51 +5162,51 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E60" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G60">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I60" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J60" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -5200,51 +5215,51 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
+        <v>34</v>
+      </c>
+      <c r="B61" t="s">
+        <v>383</v>
+      </c>
+      <c r="C61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D61" t="s">
+        <v>113</v>
+      </c>
+      <c r="E61" t="s">
+        <v>114</v>
+      </c>
+      <c r="F61" t="s">
+        <v>115</v>
+      </c>
+      <c r="G61">
+        <v>300</v>
+      </c>
+      <c r="H61" t="s">
         <v>35</v>
       </c>
-      <c r="B61" t="s">
-        <v>384</v>
-      </c>
-      <c r="C61" t="s">
-        <v>117</v>
-      </c>
-      <c r="D61" t="s">
-        <v>118</v>
-      </c>
-      <c r="E61" t="s">
-        <v>119</v>
-      </c>
-      <c r="F61" t="s">
-        <v>120</v>
-      </c>
-      <c r="G61">
-        <v>500</v>
-      </c>
-      <c r="H61" t="s">
-        <v>42</v>
-      </c>
       <c r="I61" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -5253,7 +5268,7 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -5264,40 +5279,40 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B62" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D62" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E62" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F62" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G62">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H62" t="s">
         <v>42</v>
       </c>
       <c r="I62" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -5306,51 +5321,51 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B63" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C63" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D63" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E63" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F63" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G63">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H63" t="s">
         <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J63" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
       </c>
       <c r="L63">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -5359,45 +5374,45 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B64" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C64" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D64" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E64" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F64" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G64">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H64" t="s">
         <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J64" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
@@ -5412,51 +5427,51 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C65" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D65" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E65" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F65" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G65">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H65" t="s">
         <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -5465,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5476,40 +5491,40 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C66" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D66" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E66" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F66" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H66" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J66" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5518,7 +5533,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5529,63 +5544,63 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B67" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C67" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E67" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F67" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G67">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I67" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B68" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C68" t="s">
         <v>138</v>
@@ -5594,10 +5609,10 @@
         <v>139</v>
       </c>
       <c r="E68" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F68" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G68">
         <v>1000</v>
@@ -5621,10 +5636,10 @@
         <v>1</v>
       </c>
       <c r="N68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -5635,22 +5650,22 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B69" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D69" t="s">
         <v>139</v>
       </c>
       <c r="E69" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F69" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G69">
         <v>1000</v>
@@ -5662,7 +5677,7 @@
         <v>142</v>
       </c>
       <c r="J69" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
@@ -5677,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -5688,193 +5703,193 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B70" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C70" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D70" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E70" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F70" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G70">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H70" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I70" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J70" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" t="b">
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B71" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C71" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D71" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E71" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F71" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H71" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J71" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K71" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L71">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
       </c>
       <c r="N71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C72" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D72" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E72" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F72" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G72">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I72" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J72" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K72" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L72">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
       </c>
       <c r="N72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B73" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C73" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D73" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F73" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G73">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H73" t="s">
         <v>42</v>
       </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J73" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
@@ -5889,7 +5904,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -5900,22 +5915,22 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B74" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C74" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D74" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E74" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F74" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G74">
         <v>500</v>
@@ -5927,7 +5942,7 @@
         <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
@@ -5942,7 +5957,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -5953,25 +5968,25 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B75" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C75" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D75" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E75" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F75" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G75">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H75" t="s">
         <v>42</v>
@@ -5980,7 +5995,7 @@
         <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
@@ -5995,7 +6010,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6006,37 +6021,37 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
+        <v>49</v>
+      </c>
+      <c r="B76" t="s">
+        <v>398</v>
+      </c>
+      <c r="C76" t="s">
+        <v>175</v>
+      </c>
+      <c r="D76" t="s">
+        <v>176</v>
+      </c>
+      <c r="E76" t="s">
+        <v>177</v>
+      </c>
+      <c r="F76" t="s">
+        <v>178</v>
+      </c>
+      <c r="G76">
         <v>50</v>
       </c>
-      <c r="B76" t="s">
-        <v>399</v>
-      </c>
-      <c r="C76" t="s">
-        <v>180</v>
-      </c>
-      <c r="D76" t="s">
-        <v>181</v>
-      </c>
-      <c r="E76" t="s">
-        <v>182</v>
-      </c>
-      <c r="F76" t="s">
-        <v>183</v>
-      </c>
-      <c r="G76">
-        <v>12</v>
-      </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K76" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L76">
         <v>12</v>
@@ -6048,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6059,40 +6074,40 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B77" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C77" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D77" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E77" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F77" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G77">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H77" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I77" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J77" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K77" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6101,7 +6116,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6112,40 +6127,40 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B78" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C78" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D78" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E78" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F78" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G78">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H78" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I78" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J78" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6154,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6165,40 +6180,40 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
+        <v>52</v>
+      </c>
+      <c r="B79" t="s">
+        <v>401</v>
+      </c>
+      <c r="C79" t="s">
+        <v>193</v>
+      </c>
+      <c r="D79" t="s">
+        <v>181</v>
+      </c>
+      <c r="E79" t="s">
+        <v>182</v>
+      </c>
+      <c r="F79" t="s">
+        <v>183</v>
+      </c>
+      <c r="G79">
+        <v>24</v>
+      </c>
+      <c r="H79" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" t="s">
         <v>53</v>
       </c>
-      <c r="B79" t="s">
-        <v>402</v>
-      </c>
-      <c r="C79" t="s">
-        <v>31</v>
-      </c>
-      <c r="D79" t="s">
-        <v>194</v>
-      </c>
-      <c r="E79" t="s">
-        <v>195</v>
-      </c>
-      <c r="F79" t="s">
-        <v>196</v>
-      </c>
-      <c r="G79">
-        <v>1.5</v>
-      </c>
-      <c r="H79" t="s">
-        <v>28</v>
-      </c>
-      <c r="I79" t="s">
-        <v>36</v>
-      </c>
       <c r="J79" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6207,7 +6222,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6218,52 +6233,52 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B80" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C80" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D80" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E80" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F80" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G80">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H80" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I80" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J80" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="b">
         <v>1</v>
@@ -6271,93 +6286,93 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B81" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C81" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D81" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E81" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F81" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G81">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H81" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I81" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B82" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C82" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D82" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E82" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F82" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G82">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H82" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J82" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -6366,7 +6381,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6377,19 +6392,19 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B83" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C83" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D83" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E83" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F83" t="s">
         <v>208</v>
@@ -6419,7 +6434,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6430,19 +6445,19 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B84" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C84" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D84" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E84" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F84" t="s">
         <v>208</v>
@@ -6463,7 +6478,7 @@
         <v>23</v>
       </c>
       <c r="L84">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -6472,7 +6487,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6483,34 +6498,34 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B85" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C85" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D85" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E85" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F85" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H85" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J85" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
@@ -6525,45 +6540,45 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B86" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D86" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E86" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F86" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G86">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J86" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
@@ -6578,7 +6593,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -6589,49 +6604,49 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B87" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C87" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D87" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E87" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F87" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G87">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H87" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I87" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J87" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
       </c>
       <c r="N87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -6642,22 +6657,22 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B88" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C88" t="s">
         <v>217</v>
       </c>
       <c r="D88" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E88" t="s">
         <v>219</v>
       </c>
       <c r="F88" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G88">
         <v>20</v>
@@ -6684,60 +6699,60 @@
         <v>0</v>
       </c>
       <c r="O88" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B89" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C89" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D89" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E89" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F89" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G89">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H89" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I89" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J89" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
       <c r="N89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -6748,34 +6763,34 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B90" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D90" t="s">
         <v>202</v>
       </c>
       <c r="E90" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F90" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G90">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H90" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I90" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J90" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
@@ -6790,7 +6805,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -6801,40 +6816,40 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B91" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C91" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D91" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E91" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F91" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G91">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H91" t="s">
         <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J91" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -6843,51 +6858,51 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B92" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C92" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D92" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E92" t="s">
         <v>229</v>
       </c>
       <c r="F92" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H92" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J92" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -6896,7 +6911,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -6907,40 +6922,40 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B93" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C93" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E93" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F93" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G93">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H93" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I93" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J93" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -6949,45 +6964,45 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B94" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C94" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E94" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F94" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G94">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H94" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I94" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J94" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
@@ -7002,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7013,10 +7028,10 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C95" t="s">
         <v>186</v>
@@ -7025,13 +7040,13 @@
         <v>202</v>
       </c>
       <c r="E95" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F95" t="s">
         <v>204</v>
       </c>
       <c r="G95">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H95" t="s">
         <v>35</v>
@@ -7055,7 +7070,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7066,10 +7081,10 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B96" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C96" t="s">
         <v>186</v>
@@ -7084,7 +7099,7 @@
         <v>204</v>
       </c>
       <c r="G96">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H96" t="s">
         <v>35</v>
@@ -7108,7 +7123,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7119,41 +7134,41 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B97" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C97" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D97" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E97" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F97" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G97">
+        <v>250</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97" t="s">
+        <v>191</v>
+      </c>
+      <c r="J97" t="s">
+        <v>192</v>
+      </c>
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97">
         <v>6</v>
       </c>
-      <c r="H97" t="s">
-        <v>20</v>
-      </c>
-      <c r="I97" t="s">
-        <v>239</v>
-      </c>
-      <c r="J97" t="s">
-        <v>235</v>
-      </c>
-      <c r="K97" t="s">
-        <v>23</v>
-      </c>
-      <c r="L97">
-        <v>1</v>
-      </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
@@ -7161,65 +7176,118 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C98" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D98" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G98">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H98" t="s">
         <v>20</v>
       </c>
       <c r="I98" t="s">
+        <v>239</v>
+      </c>
+      <c r="J98" t="s">
+        <v>235</v>
+      </c>
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98" t="b">
+        <v>0</v>
+      </c>
+      <c r="N98" t="b">
+        <v>1</v>
+      </c>
+      <c r="O98" t="s">
+        <v>311</v>
+      </c>
+      <c r="P98" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>72</v>
+      </c>
+      <c r="B99" t="s">
+        <v>421</v>
+      </c>
+      <c r="C99" t="s">
+        <v>197</v>
+      </c>
+      <c r="D99" t="s">
+        <v>198</v>
+      </c>
+      <c r="E99" t="s">
+        <v>199</v>
+      </c>
+      <c r="F99" t="s">
+        <v>240</v>
+      </c>
+      <c r="G99">
+        <v>4</v>
+      </c>
+      <c r="H99" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" t="s">
         <v>21</v>
       </c>
-      <c r="J98" t="s">
+      <c r="J99" t="s">
         <v>201</v>
       </c>
-      <c r="K98" t="s">
-        <v>23</v>
-      </c>
-      <c r="L98">
+      <c r="K99" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99">
         <v>10</v>
       </c>
-      <c r="M98" t="b">
-        <v>0</v>
-      </c>
-      <c r="N98" t="b">
-        <v>0</v>
-      </c>
-      <c r="O98" t="s">
+      <c r="M99" t="b">
+        <v>0</v>
+      </c>
+      <c r="N99" t="b">
+        <v>0</v>
+      </c>
+      <c r="O99" t="s">
         <v>312</v>
       </c>
-      <c r="P98" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q98" t="b">
+      <c r="P99" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q99" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052BD8F7-3D37-47B0-9D80-05E0AC0E7B9B}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8BFEA3-EAB2-4B67-9837-FD963EE20FFA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="42" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="43" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -2021,7 +2021,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603FE7AA-F6BF-48FE-A48F-50AA60D3657E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4BB6433-1C97-4784-92E2-40D926D8BB6B}">
   <dimension ref="A1:Q99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6631,7 +6631,7 @@
         <v>60</v>
       </c>
       <c r="J87" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8BFEA3-EAB2-4B67-9837-FD963EE20FFA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A28A6CB-1904-4B33-B988-3E48B3AB799D}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="43" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="44" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="556">
   <si>
     <t>Codigo</t>
   </si>
@@ -1670,6 +1670,30 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790360966582.png</t>
+  </si>
+  <si>
+    <t>77969071</t>
+  </si>
+  <si>
+    <t>Chicle</t>
+  </si>
+  <si>
+    <t>dietético</t>
+  </si>
+  <si>
+    <t>sabor a menta</t>
+  </si>
+  <si>
+    <t>Beldent</t>
+  </si>
+  <si>
+    <t>paquete</t>
+  </si>
+  <si>
+    <t>Chicles</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\77969071.png</t>
   </si>
 </sst>
 </file>
@@ -2021,8 +2045,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4BB6433-1C97-4784-92E2-40D926D8BB6B}">
-  <dimension ref="A1:Q99"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2581E498-9773-44C1-A810-89B3AA62A12C}">
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -4325,40 +4349,40 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>366</v>
+        <v>548</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>549</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>550</v>
       </c>
       <c r="E44" t="s">
-        <v>51</v>
+        <v>551</v>
       </c>
       <c r="F44" t="s">
-        <v>52</v>
+        <v>552</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H44" t="s">
         <v>20</v>
       </c>
       <c r="I44" t="s">
-        <v>53</v>
+        <v>553</v>
       </c>
       <c r="J44" t="s">
-        <v>49</v>
+        <v>554</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
       </c>
       <c r="L44">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
@@ -4367,7 +4391,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>257</v>
+        <v>555</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -4378,34 +4402,34 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E45" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F45" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I45" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J45" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
@@ -4420,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -4431,34 +4455,34 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E46" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G46">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I46" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J46" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
@@ -4473,51 +4497,51 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
       </c>
       <c r="Q46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E47" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F47" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H47" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I47" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J47" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
       </c>
       <c r="L47">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
@@ -4526,45 +4550,45 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
       </c>
       <c r="Q47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E48" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F48" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G48">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I48" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J48" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
@@ -4579,51 +4603,51 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
       </c>
       <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C49" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E49" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F49" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G49">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H49" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I49" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J49" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
@@ -4632,45 +4656,45 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
       </c>
       <c r="Q49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F50" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G50">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H50" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s">
         <v>53</v>
       </c>
       <c r="J50" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
@@ -4685,7 +4709,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
@@ -4696,40 +4720,40 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D51" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E51" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F51" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I51" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J51" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
       </c>
       <c r="L51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M51" t="b">
         <v>0</v>
@@ -4738,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
@@ -4749,40 +4773,40 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E52" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F52" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G52">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I52" t="s">
         <v>21</v>
       </c>
       <c r="J52" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
       </c>
       <c r="L52">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
@@ -4791,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -4802,34 +4826,34 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E53" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F53" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G53">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I53" t="s">
         <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
@@ -4844,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -4855,40 +4879,40 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C54" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D54" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E54" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F54" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G54">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H54" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I54" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4897,51 +4921,51 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
       </c>
       <c r="Q54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D55" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E55" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F55" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G55">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H55" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I55" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J55" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -4950,7 +4974,7 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
@@ -4961,41 +4985,41 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E56" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F56" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I56" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J56" t="s">
+        <v>66</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56">
         <v>30</v>
       </c>
-      <c r="K56" t="s">
-        <v>23</v>
-      </c>
-      <c r="L56">
-        <v>12</v>
-      </c>
       <c r="M56" t="b">
         <v>0</v>
       </c>
@@ -5003,113 +5027,113 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
       </c>
       <c r="Q56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
+        <v>29</v>
+      </c>
+      <c r="B57" t="s">
+        <v>378</v>
+      </c>
+      <c r="C57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" t="s">
+        <v>54</v>
+      </c>
+      <c r="E57" t="s">
+        <v>55</v>
+      </c>
+      <c r="F57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>28</v>
+      </c>
+      <c r="I57" t="s">
+        <v>96</v>
+      </c>
+      <c r="J57" t="s">
         <v>30</v>
       </c>
-      <c r="B57" t="s">
-        <v>379</v>
-      </c>
-      <c r="C57" t="s">
-        <v>97</v>
-      </c>
-      <c r="D57" t="s">
-        <v>98</v>
-      </c>
-      <c r="E57" t="s">
-        <v>99</v>
-      </c>
-      <c r="F57" t="s">
-        <v>100</v>
-      </c>
-      <c r="G57">
-        <v>100</v>
-      </c>
-      <c r="H57" t="s">
-        <v>20</v>
-      </c>
-      <c r="I57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J57" t="s">
-        <v>102</v>
-      </c>
       <c r="K57" t="s">
         <v>23</v>
       </c>
       <c r="L57">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M57" t="b">
         <v>0</v>
       </c>
       <c r="N57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
       </c>
       <c r="Q57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B58" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E58" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F58" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G58">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H58" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I58" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J58" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
       </c>
       <c r="N58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -5120,22 +5144,22 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B59" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E59" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F59" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G59">
         <v>500</v>
@@ -5147,13 +5171,13 @@
         <v>107</v>
       </c>
       <c r="J59" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -5162,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -5173,40 +5197,40 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C60" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E60" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F60" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H60" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I60" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J60" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -5215,51 +5239,51 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E61" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G61">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I61" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -5268,51 +5292,51 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
+        <v>34</v>
+      </c>
+      <c r="B62" t="s">
+        <v>383</v>
+      </c>
+      <c r="C62" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" t="s">
+        <v>113</v>
+      </c>
+      <c r="E62" t="s">
+        <v>114</v>
+      </c>
+      <c r="F62" t="s">
+        <v>115</v>
+      </c>
+      <c r="G62">
+        <v>300</v>
+      </c>
+      <c r="H62" t="s">
         <v>35</v>
       </c>
-      <c r="B62" t="s">
-        <v>384</v>
-      </c>
-      <c r="C62" t="s">
-        <v>117</v>
-      </c>
-      <c r="D62" t="s">
-        <v>118</v>
-      </c>
-      <c r="E62" t="s">
-        <v>119</v>
-      </c>
-      <c r="F62" t="s">
-        <v>120</v>
-      </c>
-      <c r="G62">
-        <v>500</v>
-      </c>
-      <c r="H62" t="s">
-        <v>42</v>
-      </c>
       <c r="I62" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -5321,7 +5345,7 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5332,40 +5356,40 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B63" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E63" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G63">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H63" t="s">
         <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J63" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
       </c>
       <c r="L63">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -5374,51 +5398,51 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B64" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C64" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D64" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E64" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F64" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G64">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H64" t="s">
         <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J64" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
@@ -5427,45 +5451,45 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B65" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C65" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D65" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E65" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F65" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G65">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H65" t="s">
         <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J65" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
@@ -5480,51 +5504,51 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B66" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D66" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E66" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F66" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G66">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H66" t="s">
         <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5533,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5544,40 +5568,40 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B67" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D67" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E67" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F67" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H67" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J67" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5586,7 +5610,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5597,63 +5621,63 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B68" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C68" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E68" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F68" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G68">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I68" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C69" t="s">
         <v>138</v>
@@ -5662,10 +5686,10 @@
         <v>139</v>
       </c>
       <c r="E69" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F69" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G69">
         <v>1000</v>
@@ -5689,10 +5713,10 @@
         <v>1</v>
       </c>
       <c r="N69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -5703,22 +5727,22 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B70" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C70" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D70" t="s">
         <v>139</v>
       </c>
       <c r="E70" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F70" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G70">
         <v>1000</v>
@@ -5730,7 +5754,7 @@
         <v>142</v>
       </c>
       <c r="J70" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
@@ -5745,7 +5769,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -5756,193 +5780,193 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B71" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C71" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D71" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E71" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F71" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G71">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H71" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J71" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B72" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C72" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D72" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E72" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F72" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H72" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J72" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K72" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L72">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
       </c>
       <c r="N72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C73" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D73" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E73" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F73" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G73">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I73" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J73" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K73" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L73">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
       </c>
       <c r="N73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B74" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C74" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D74" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E74" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F74" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G74">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H74" t="s">
         <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J74" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
@@ -5957,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -5968,22 +5992,22 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B75" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C75" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E75" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F75" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G75">
         <v>500</v>
@@ -5995,7 +6019,7 @@
         <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
@@ -6010,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6021,25 +6045,25 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B76" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C76" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D76" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E76" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F76" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G76">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H76" t="s">
         <v>42</v>
@@ -6048,7 +6072,7 @@
         <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
@@ -6063,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6074,37 +6098,37 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
+        <v>49</v>
+      </c>
+      <c r="B77" t="s">
+        <v>398</v>
+      </c>
+      <c r="C77" t="s">
+        <v>175</v>
+      </c>
+      <c r="D77" t="s">
+        <v>176</v>
+      </c>
+      <c r="E77" t="s">
+        <v>177</v>
+      </c>
+      <c r="F77" t="s">
+        <v>178</v>
+      </c>
+      <c r="G77">
         <v>50</v>
       </c>
-      <c r="B77" t="s">
-        <v>399</v>
-      </c>
-      <c r="C77" t="s">
-        <v>180</v>
-      </c>
-      <c r="D77" t="s">
-        <v>181</v>
-      </c>
-      <c r="E77" t="s">
-        <v>182</v>
-      </c>
-      <c r="F77" t="s">
-        <v>183</v>
-      </c>
-      <c r="G77">
-        <v>12</v>
-      </c>
       <c r="H77" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K77" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L77">
         <v>12</v>
@@ -6116,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6127,40 +6151,40 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B78" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C78" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D78" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E78" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F78" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G78">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H78" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J78" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="K78" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6169,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6180,40 +6204,40 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B79" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C79" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D79" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E79" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F79" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G79">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H79" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I79" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J79" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6222,7 +6246,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6233,40 +6257,40 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
+        <v>52</v>
+      </c>
+      <c r="B80" t="s">
+        <v>401</v>
+      </c>
+      <c r="C80" t="s">
+        <v>193</v>
+      </c>
+      <c r="D80" t="s">
+        <v>181</v>
+      </c>
+      <c r="E80" t="s">
+        <v>182</v>
+      </c>
+      <c r="F80" t="s">
+        <v>183</v>
+      </c>
+      <c r="G80">
+        <v>24</v>
+      </c>
+      <c r="H80" t="s">
+        <v>20</v>
+      </c>
+      <c r="I80" t="s">
         <v>53</v>
       </c>
-      <c r="B80" t="s">
-        <v>402</v>
-      </c>
-      <c r="C80" t="s">
-        <v>31</v>
-      </c>
-      <c r="D80" t="s">
-        <v>194</v>
-      </c>
-      <c r="E80" t="s">
-        <v>195</v>
-      </c>
-      <c r="F80" t="s">
-        <v>196</v>
-      </c>
-      <c r="G80">
-        <v>1.5</v>
-      </c>
-      <c r="H80" t="s">
-        <v>28</v>
-      </c>
-      <c r="I80" t="s">
-        <v>36</v>
-      </c>
       <c r="J80" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6275,7 +6299,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6286,52 +6310,52 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B81" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C81" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D81" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E81" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F81" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G81">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H81" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I81" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J81" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="b">
         <v>1</v>
@@ -6339,93 +6363,93 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B82" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C82" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D82" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F82" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G82">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H82" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J82" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
       <c r="N82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C83" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D83" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E83" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F83" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G83">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H83" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I83" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J83" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -6434,7 +6458,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6445,19 +6469,19 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B84" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C84" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D84" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E84" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F84" t="s">
         <v>208</v>
@@ -6487,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6498,19 +6522,19 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B85" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C85" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D85" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E85" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F85" t="s">
         <v>208</v>
@@ -6531,7 +6555,7 @@
         <v>23</v>
       </c>
       <c r="L85">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -6540,7 +6564,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6551,34 +6575,34 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B86" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C86" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D86" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E86" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F86" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H86" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I86" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J86" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
@@ -6593,45 +6617,45 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B87" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E87" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F87" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G87">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I87" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J87" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
@@ -6646,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -6657,49 +6681,49 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B88" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C88" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D88" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E88" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F88" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G88">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H88" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J88" t="s">
-        <v>217</v>
+        <v>30</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
       <c r="N88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -6710,22 +6734,22 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B89" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C89" t="s">
         <v>217</v>
       </c>
       <c r="D89" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E89" t="s">
         <v>219</v>
       </c>
       <c r="F89" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G89">
         <v>20</v>
@@ -6752,60 +6776,60 @@
         <v>0</v>
       </c>
       <c r="O89" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B90" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C90" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E90" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F90" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G90">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H90" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I90" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J90" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
       </c>
       <c r="N90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -6816,34 +6840,34 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B91" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C91" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D91" t="s">
         <v>202</v>
       </c>
       <c r="E91" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F91" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G91">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H91" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I91" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J91" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
@@ -6858,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -6869,40 +6893,40 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B92" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C92" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D92" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E92" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F92" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G92">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H92" t="s">
         <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J92" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -6911,51 +6935,51 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B93" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C93" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D93" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E93" t="s">
         <v>229</v>
       </c>
       <c r="F93" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H93" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I93" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J93" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -6964,7 +6988,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -6975,40 +6999,40 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B94" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C94" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E94" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F94" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G94">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I94" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J94" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7017,45 +7041,45 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B95" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C95" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E95" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F95" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G95">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H95" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I95" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J95" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
@@ -7070,7 +7094,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7081,10 +7105,10 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B96" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C96" t="s">
         <v>186</v>
@@ -7093,13 +7117,13 @@
         <v>202</v>
       </c>
       <c r="E96" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F96" t="s">
         <v>204</v>
       </c>
       <c r="G96">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H96" t="s">
         <v>35</v>
@@ -7123,7 +7147,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7134,10 +7158,10 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B97" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C97" t="s">
         <v>186</v>
@@ -7152,7 +7176,7 @@
         <v>204</v>
       </c>
       <c r="G97">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H97" t="s">
         <v>35</v>
@@ -7176,7 +7200,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7187,41 +7211,41 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B98" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C98" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D98" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E98" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F98" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G98">
+        <v>250</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98" t="s">
+        <v>191</v>
+      </c>
+      <c r="J98" t="s">
+        <v>192</v>
+      </c>
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98">
         <v>6</v>
       </c>
-      <c r="H98" t="s">
-        <v>20</v>
-      </c>
-      <c r="I98" t="s">
-        <v>239</v>
-      </c>
-      <c r="J98" t="s">
-        <v>235</v>
-      </c>
-      <c r="K98" t="s">
-        <v>23</v>
-      </c>
-      <c r="L98">
-        <v>1</v>
-      </c>
       <c r="M98" t="b">
         <v>0</v>
       </c>
@@ -7229,65 +7253,118 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C99" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D99" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E99" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G99">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H99" t="s">
         <v>20</v>
       </c>
       <c r="I99" t="s">
+        <v>239</v>
+      </c>
+      <c r="J99" t="s">
+        <v>235</v>
+      </c>
+      <c r="K99" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99" t="b">
+        <v>0</v>
+      </c>
+      <c r="N99" t="b">
+        <v>1</v>
+      </c>
+      <c r="O99" t="s">
+        <v>311</v>
+      </c>
+      <c r="P99" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>72</v>
+      </c>
+      <c r="B100" t="s">
+        <v>421</v>
+      </c>
+      <c r="C100" t="s">
+        <v>197</v>
+      </c>
+      <c r="D100" t="s">
+        <v>198</v>
+      </c>
+      <c r="E100" t="s">
+        <v>199</v>
+      </c>
+      <c r="F100" t="s">
+        <v>240</v>
+      </c>
+      <c r="G100">
+        <v>4</v>
+      </c>
+      <c r="H100" t="s">
+        <v>20</v>
+      </c>
+      <c r="I100" t="s">
         <v>21</v>
       </c>
-      <c r="J99" t="s">
+      <c r="J100" t="s">
         <v>201</v>
       </c>
-      <c r="K99" t="s">
-        <v>23</v>
-      </c>
-      <c r="L99">
+      <c r="K100" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100">
         <v>10</v>
       </c>
-      <c r="M99" t="b">
-        <v>0</v>
-      </c>
-      <c r="N99" t="b">
-        <v>0</v>
-      </c>
-      <c r="O99" t="s">
+      <c r="M100" t="b">
+        <v>0</v>
+      </c>
+      <c r="N100" t="b">
+        <v>0</v>
+      </c>
+      <c r="O100" t="s">
         <v>312</v>
       </c>
-      <c r="P99" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q99" t="b">
+      <c r="P100" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q100" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A28A6CB-1904-4B33-B988-3E48B3AB799D}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE87B2D-E766-4E88-A9B2-0A3E830F2D18}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="44" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="45" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="557">
   <si>
     <t>Codigo</t>
   </si>
@@ -1694,6 +1694,9 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\77969071.png</t>
+  </si>
+  <si>
+    <t>Desodorantes de ambientes</t>
   </si>
 </sst>
 </file>
@@ -2045,7 +2048,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2581E498-9773-44C1-A810-89B3AA62A12C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F629D551-D696-4844-ACBB-A5E55B456AB1}">
   <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2058,7 +2061,7 @@
     <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -6231,7 +6234,7 @@
         <v>191</v>
       </c>
       <c r="J79" t="s">
-        <v>192</v>
+        <v>556</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE87B2D-E766-4E88-A9B2-0A3E830F2D18}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F25AC90-F0A4-4684-8CC5-5CA898F3743C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="45" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="46" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="558">
   <si>
     <t>Codigo</t>
   </si>
@@ -1697,6 +1697,9 @@
   </si>
   <si>
     <t>Desodorantes de ambientes</t>
+  </si>
+  <si>
+    <t>Leches en polvo</t>
   </si>
 </sst>
 </file>
@@ -2048,7 +2051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F629D551-D696-4844-ACBB-A5E55B456AB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DBA40CB-0FDC-4EE4-87B6-E20FEF9A92DE}">
   <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6711,7 +6714,7 @@
         <v>60</v>
       </c>
       <c r="J88" t="s">
-        <v>30</v>
+        <v>557</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F25AC90-F0A4-4684-8CC5-5CA898F3743C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE03C30-FA56-4FB7-9A88-5B14DE0457D0}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="46" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="47" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="564">
   <si>
     <t>Codigo</t>
   </si>
@@ -1700,6 +1700,24 @@
   </si>
   <si>
     <t>Leches en polvo</t>
+  </si>
+  <si>
+    <t>7790314003226</t>
+  </si>
+  <si>
+    <t>Vino</t>
+  </si>
+  <si>
+    <t>tinto</t>
+  </si>
+  <si>
+    <t>Toro</t>
+  </si>
+  <si>
+    <t>Vinos</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790314003226.png</t>
   </si>
 </sst>
 </file>
@@ -2051,11 +2069,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DBA40CB-0FDC-4EE4-87B6-E20FEF9A92DE}">
-  <dimension ref="A1:Q100"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED6F87E-F266-4C30-8857-52FEC5F32435}">
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
@@ -4408,34 +4426,34 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>366</v>
+        <v>558</v>
       </c>
       <c r="C45" t="s">
-        <v>49</v>
+        <v>559</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="E45" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="F45" t="s">
-        <v>52</v>
+        <v>561</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>750</v>
       </c>
       <c r="H45" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I45" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J45" t="s">
-        <v>49</v>
+        <v>562</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
@@ -4447,10 +4465,10 @@
         <v>0</v>
       </c>
       <c r="N45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>257</v>
+        <v>563</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -4461,34 +4479,34 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F46" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H46" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J46" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
@@ -4503,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
@@ -4514,34 +4532,34 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B47" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E47" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G47">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I47" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J47" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
@@ -4556,51 +4574,51 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
       </c>
       <c r="Q47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F48" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H48" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I48" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J48" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
       </c>
       <c r="L48">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
@@ -4609,45 +4627,45 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
       </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E49" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F49" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G49">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I49" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J49" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
@@ -4662,51 +4680,51 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C50" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G50">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H50" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I50" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J50" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -4715,45 +4733,45 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
       </c>
       <c r="Q50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C51" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D51" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E51" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F51" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G51">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H51" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I51" t="s">
         <v>53</v>
       </c>
       <c r="J51" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K51" t="s">
         <v>23</v>
@@ -4768,7 +4786,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
@@ -4779,40 +4797,40 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D52" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F52" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I52" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J52" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
       </c>
       <c r="L52">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
@@ -4821,7 +4839,7 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -4832,40 +4850,40 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B53" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C53" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F53" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G53">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I53" t="s">
         <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K53" t="s">
         <v>23</v>
       </c>
       <c r="L53">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M53" t="b">
         <v>0</v>
@@ -4874,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -4885,34 +4903,34 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D54" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F54" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G54">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H54" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I54" t="s">
         <v>21</v>
       </c>
       <c r="J54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
@@ -4927,7 +4945,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -4938,40 +4956,40 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C55" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D55" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E55" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F55" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G55">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H55" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I55" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
       </c>
       <c r="L55">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
@@ -4980,51 +4998,51 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
       </c>
       <c r="Q55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D56" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E56" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F56" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G56">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H56" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J56" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K56" t="s">
         <v>23</v>
       </c>
       <c r="L56">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
@@ -5033,7 +5051,7 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
@@ -5044,41 +5062,41 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B57" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E57" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F57" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H57" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I57" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J57" t="s">
+        <v>66</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57">
         <v>30</v>
       </c>
-      <c r="K57" t="s">
-        <v>23</v>
-      </c>
-      <c r="L57">
-        <v>12</v>
-      </c>
       <c r="M57" t="b">
         <v>0</v>
       </c>
@@ -5086,113 +5104,113 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
       </c>
       <c r="Q57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
+        <v>29</v>
+      </c>
+      <c r="B58" t="s">
+        <v>378</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" t="s">
+        <v>54</v>
+      </c>
+      <c r="E58" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58" t="s">
+        <v>61</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>28</v>
+      </c>
+      <c r="I58" t="s">
+        <v>96</v>
+      </c>
+      <c r="J58" t="s">
         <v>30</v>
       </c>
-      <c r="B58" t="s">
-        <v>379</v>
-      </c>
-      <c r="C58" t="s">
-        <v>97</v>
-      </c>
-      <c r="D58" t="s">
-        <v>98</v>
-      </c>
-      <c r="E58" t="s">
-        <v>99</v>
-      </c>
-      <c r="F58" t="s">
-        <v>100</v>
-      </c>
-      <c r="G58">
-        <v>100</v>
-      </c>
-      <c r="H58" t="s">
-        <v>20</v>
-      </c>
-      <c r="I58" t="s">
-        <v>101</v>
-      </c>
-      <c r="J58" t="s">
-        <v>102</v>
-      </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
       </c>
       <c r="N58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B59" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D59" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E59" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F59" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G59">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H59" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I59" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J59" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
       </c>
       <c r="N59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -5203,22 +5221,22 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B60" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E60" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F60" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G60">
         <v>500</v>
@@ -5230,13 +5248,13 @@
         <v>107</v>
       </c>
       <c r="J60" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -5245,7 +5263,7 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
@@ -5256,40 +5274,40 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C61" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E61" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F61" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H61" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J61" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -5298,51 +5316,51 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G62">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I62" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -5351,51 +5369,51 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
+        <v>34</v>
+      </c>
+      <c r="B63" t="s">
+        <v>383</v>
+      </c>
+      <c r="C63" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63" t="s">
+        <v>113</v>
+      </c>
+      <c r="E63" t="s">
+        <v>114</v>
+      </c>
+      <c r="F63" t="s">
+        <v>115</v>
+      </c>
+      <c r="G63">
+        <v>300</v>
+      </c>
+      <c r="H63" t="s">
         <v>35</v>
       </c>
-      <c r="B63" t="s">
-        <v>384</v>
-      </c>
-      <c r="C63" t="s">
-        <v>117</v>
-      </c>
-      <c r="D63" t="s">
-        <v>118</v>
-      </c>
-      <c r="E63" t="s">
-        <v>119</v>
-      </c>
-      <c r="F63" t="s">
-        <v>120</v>
-      </c>
-      <c r="G63">
-        <v>500</v>
-      </c>
-      <c r="H63" t="s">
-        <v>42</v>
-      </c>
       <c r="I63" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
       </c>
       <c r="L63">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -5404,7 +5422,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5415,40 +5433,40 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C64" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D64" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E64" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G64">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H64" t="s">
         <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
@@ -5457,51 +5475,51 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C65" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D65" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E65" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F65" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G65">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H65" t="s">
         <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J65" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -5510,45 +5528,45 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C66" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D66" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E66" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F66" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G66">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H66" t="s">
         <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J66" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
@@ -5563,51 +5581,51 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B67" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D67" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E67" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F67" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G67">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H67" t="s">
         <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5616,7 +5634,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5627,40 +5645,40 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C68" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D68" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E68" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F68" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H68" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J68" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -5669,7 +5687,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -5680,63 +5698,63 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C69" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E69" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F69" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G69">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I69" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C70" t="s">
         <v>138</v>
@@ -5745,10 +5763,10 @@
         <v>139</v>
       </c>
       <c r="E70" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F70" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G70">
         <v>1000</v>
@@ -5772,10 +5790,10 @@
         <v>1</v>
       </c>
       <c r="N70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -5786,22 +5804,22 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C71" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D71" t="s">
         <v>139</v>
       </c>
       <c r="E71" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F71" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G71">
         <v>1000</v>
@@ -5813,7 +5831,7 @@
         <v>142</v>
       </c>
       <c r="J71" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
@@ -5828,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -5839,193 +5857,193 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B72" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C72" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D72" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E72" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F72" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G72">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H72" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I72" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J72" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B73" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C73" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D73" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E73" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F73" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H73" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I73" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J73" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K73" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L73">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
       </c>
       <c r="N73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C74" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D74" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E74" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F74" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G74">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I74" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J74" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K74" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L74">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
       </c>
       <c r="N74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B75" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C75" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D75" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E75" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F75" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G75">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H75" t="s">
         <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J75" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
@@ -6040,7 +6058,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6051,22 +6069,22 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B76" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C76" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D76" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E76" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F76" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G76">
         <v>500</v>
@@ -6078,7 +6096,7 @@
         <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
@@ -6093,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6104,25 +6122,25 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C77" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D77" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E77" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F77" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G77">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H77" t="s">
         <v>42</v>
@@ -6131,7 +6149,7 @@
         <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
@@ -6146,7 +6164,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6157,37 +6175,37 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
+        <v>49</v>
+      </c>
+      <c r="B78" t="s">
+        <v>398</v>
+      </c>
+      <c r="C78" t="s">
+        <v>175</v>
+      </c>
+      <c r="D78" t="s">
+        <v>176</v>
+      </c>
+      <c r="E78" t="s">
+        <v>177</v>
+      </c>
+      <c r="F78" t="s">
+        <v>178</v>
+      </c>
+      <c r="G78">
         <v>50</v>
       </c>
-      <c r="B78" t="s">
-        <v>399</v>
-      </c>
-      <c r="C78" t="s">
-        <v>180</v>
-      </c>
-      <c r="D78" t="s">
-        <v>181</v>
-      </c>
-      <c r="E78" t="s">
-        <v>182</v>
-      </c>
-      <c r="F78" t="s">
-        <v>183</v>
-      </c>
-      <c r="G78">
-        <v>12</v>
-      </c>
       <c r="H78" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K78" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L78">
         <v>12</v>
@@ -6199,7 +6217,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6210,40 +6228,40 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B79" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C79" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D79" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E79" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F79" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G79">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H79" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I79" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J79" t="s">
-        <v>556</v>
+        <v>184</v>
       </c>
       <c r="K79" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6252,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6263,40 +6281,40 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C80" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D80" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E80" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F80" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G80">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H80" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I80" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J80" t="s">
-        <v>184</v>
+        <v>556</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6305,7 +6323,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6316,40 +6334,40 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
+        <v>52</v>
+      </c>
+      <c r="B81" t="s">
+        <v>401</v>
+      </c>
+      <c r="C81" t="s">
+        <v>193</v>
+      </c>
+      <c r="D81" t="s">
+        <v>181</v>
+      </c>
+      <c r="E81" t="s">
+        <v>182</v>
+      </c>
+      <c r="F81" t="s">
+        <v>183</v>
+      </c>
+      <c r="G81">
+        <v>24</v>
+      </c>
+      <c r="H81" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" t="s">
         <v>53</v>
       </c>
-      <c r="B81" t="s">
-        <v>402</v>
-      </c>
-      <c r="C81" t="s">
-        <v>31</v>
-      </c>
-      <c r="D81" t="s">
-        <v>194</v>
-      </c>
-      <c r="E81" t="s">
-        <v>195</v>
-      </c>
-      <c r="F81" t="s">
-        <v>196</v>
-      </c>
-      <c r="G81">
-        <v>1.5</v>
-      </c>
-      <c r="H81" t="s">
-        <v>28</v>
-      </c>
-      <c r="I81" t="s">
-        <v>36</v>
-      </c>
       <c r="J81" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6358,7 +6376,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6369,52 +6387,52 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B82" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C82" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D82" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E82" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F82" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G82">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H82" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I82" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J82" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
       <c r="N82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="b">
         <v>1</v>
@@ -6422,93 +6440,93 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B83" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D83" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G83">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H83" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I83" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
       </c>
       <c r="N83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C84" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D84" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E84" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F84" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G84">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H84" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J84" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -6517,7 +6535,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6528,19 +6546,19 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B85" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C85" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D85" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E85" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F85" t="s">
         <v>208</v>
@@ -6570,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6581,19 +6599,19 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B86" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C86" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D86" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E86" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F86" t="s">
         <v>208</v>
@@ -6614,7 +6632,7 @@
         <v>23</v>
       </c>
       <c r="L86">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -6623,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -6634,34 +6652,34 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B87" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C87" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D87" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E87" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F87" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H87" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I87" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J87" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
@@ -6676,45 +6694,45 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B88" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C88" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D88" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E88" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F88" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G88">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I88" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J88" t="s">
-        <v>557</v>
+        <v>148</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
@@ -6729,7 +6747,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -6740,49 +6758,49 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C89" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D89" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E89" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F89" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G89">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H89" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I89" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J89" t="s">
-        <v>217</v>
+        <v>557</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
       <c r="N89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -6793,22 +6811,22 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B90" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C90" t="s">
         <v>217</v>
       </c>
       <c r="D90" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E90" t="s">
         <v>219</v>
       </c>
       <c r="F90" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G90">
         <v>20</v>
@@ -6835,60 +6853,60 @@
         <v>0</v>
       </c>
       <c r="O90" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C91" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D91" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E91" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F91" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G91">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H91" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I91" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J91" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
       </c>
       <c r="N91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -6899,34 +6917,34 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B92" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C92" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D92" t="s">
         <v>202</v>
       </c>
       <c r="E92" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F92" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G92">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H92" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I92" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J92" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
@@ -6941,7 +6959,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -6952,40 +6970,40 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B93" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C93" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D93" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E93" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F93" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G93">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H93" t="s">
         <v>42</v>
       </c>
       <c r="I93" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J93" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -6994,51 +7012,51 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B94" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C94" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D94" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E94" t="s">
         <v>229</v>
       </c>
       <c r="F94" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H94" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J94" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7047,7 +7065,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7058,40 +7076,40 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B95" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C95" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D95" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E95" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F95" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G95">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H95" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I95" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J95" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7100,45 +7118,45 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B96" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C96" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E96" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F96" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G96">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H96" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I96" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J96" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
@@ -7153,7 +7171,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7164,10 +7182,10 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C97" t="s">
         <v>186</v>
@@ -7176,13 +7194,13 @@
         <v>202</v>
       </c>
       <c r="E97" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F97" t="s">
         <v>204</v>
       </c>
       <c r="G97">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H97" t="s">
         <v>35</v>
@@ -7206,7 +7224,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7217,10 +7235,10 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C98" t="s">
         <v>186</v>
@@ -7235,7 +7253,7 @@
         <v>204</v>
       </c>
       <c r="G98">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H98" t="s">
         <v>35</v>
@@ -7259,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7270,41 +7288,41 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B99" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C99" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E99" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F99" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G99">
+        <v>250</v>
+      </c>
+      <c r="H99" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99" t="s">
+        <v>191</v>
+      </c>
+      <c r="J99" t="s">
+        <v>192</v>
+      </c>
+      <c r="K99" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99">
         <v>6</v>
       </c>
-      <c r="H99" t="s">
-        <v>20</v>
-      </c>
-      <c r="I99" t="s">
-        <v>239</v>
-      </c>
-      <c r="J99" t="s">
-        <v>235</v>
-      </c>
-      <c r="K99" t="s">
-        <v>23</v>
-      </c>
-      <c r="L99">
-        <v>1</v>
-      </c>
       <c r="M99" t="b">
         <v>0</v>
       </c>
@@ -7312,65 +7330,118 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C100" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D100" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E100" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G100">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H100" t="s">
         <v>20</v>
       </c>
       <c r="I100" t="s">
+        <v>239</v>
+      </c>
+      <c r="J100" t="s">
+        <v>235</v>
+      </c>
+      <c r="K100" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100" t="b">
+        <v>0</v>
+      </c>
+      <c r="N100" t="b">
+        <v>1</v>
+      </c>
+      <c r="O100" t="s">
+        <v>311</v>
+      </c>
+      <c r="P100" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>72</v>
+      </c>
+      <c r="B101" t="s">
+        <v>421</v>
+      </c>
+      <c r="C101" t="s">
+        <v>197</v>
+      </c>
+      <c r="D101" t="s">
+        <v>198</v>
+      </c>
+      <c r="E101" t="s">
+        <v>199</v>
+      </c>
+      <c r="F101" t="s">
+        <v>240</v>
+      </c>
+      <c r="G101">
+        <v>4</v>
+      </c>
+      <c r="H101" t="s">
+        <v>20</v>
+      </c>
+      <c r="I101" t="s">
         <v>21</v>
       </c>
-      <c r="J100" t="s">
+      <c r="J101" t="s">
         <v>201</v>
       </c>
-      <c r="K100" t="s">
-        <v>23</v>
-      </c>
-      <c r="L100">
+      <c r="K101" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101">
         <v>10</v>
       </c>
-      <c r="M100" t="b">
-        <v>0</v>
-      </c>
-      <c r="N100" t="b">
-        <v>0</v>
-      </c>
-      <c r="O100" t="s">
+      <c r="M101" t="b">
+        <v>0</v>
+      </c>
+      <c r="N101" t="b">
+        <v>0</v>
+      </c>
+      <c r="O101" t="s">
         <v>312</v>
       </c>
-      <c r="P100" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q100" t="b">
+      <c r="P101" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE03C30-FA56-4FB7-9A88-5B14DE0457D0}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CB77B9-B69D-414A-B2A1-EA770B247578}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="47" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="48" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="575">
   <si>
     <t>Codigo</t>
   </si>
@@ -1718,6 +1718,39 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790314003226.png</t>
+  </si>
+  <si>
+    <t>BloqueoModificaciones</t>
+  </si>
+  <si>
+    <t>7798140257424</t>
+  </si>
+  <si>
+    <t>Bebida</t>
+  </si>
+  <si>
+    <t>hidratante sin alcohol</t>
+  </si>
+  <si>
+    <t>sabor manzana</t>
+  </si>
+  <si>
+    <t>Suerox</t>
+  </si>
+  <si>
+    <t>Bebidas energéticas</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7798140257424.png</t>
+  </si>
+  <si>
+    <t>7793719000049</t>
+  </si>
+  <si>
+    <t>Rocío</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7793719000049.png</t>
   </si>
 </sst>
 </file>
@@ -2069,8 +2102,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED6F87E-F266-4C30-8857-52FEC5F32435}">
-  <dimension ref="A1:Q101"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96C5FAB5-8367-426D-882E-8914F6852FF8}">
+  <dimension ref="A1:R103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2090,9 +2123,10 @@
     <col min="15" max="15" width="50.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>333</v>
       </c>
@@ -2144,8 +2178,11 @@
       <c r="Q1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2197,8 +2234,11 @@
       <c r="Q2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2250,8 +2290,11 @@
       <c r="Q3" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>73</v>
       </c>
@@ -2303,8 +2346,11 @@
       <c r="Q4" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>74</v>
       </c>
@@ -2356,8 +2402,11 @@
       <c r="Q5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>75</v>
       </c>
@@ -2409,8 +2458,11 @@
       <c r="Q6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>76</v>
       </c>
@@ -2462,8 +2514,11 @@
       <c r="Q7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>77</v>
       </c>
@@ -2515,8 +2570,11 @@
       <c r="Q8" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>78</v>
       </c>
@@ -2568,8 +2626,11 @@
       <c r="Q9" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>79</v>
       </c>
@@ -2621,8 +2682,11 @@
       <c r="Q10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>80</v>
       </c>
@@ -2674,8 +2738,11 @@
       <c r="Q11" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>81</v>
       </c>
@@ -2727,8 +2794,11 @@
       <c r="Q12" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>82</v>
       </c>
@@ -2780,8 +2850,11 @@
       <c r="Q13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>83</v>
       </c>
@@ -2833,8 +2906,11 @@
       <c r="Q14" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>84</v>
       </c>
@@ -2886,8 +2962,11 @@
       <c r="Q15" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>85</v>
       </c>
@@ -2939,8 +3018,11 @@
       <c r="Q16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -2992,8 +3074,11 @@
       <c r="Q17" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>4</v>
       </c>
@@ -3045,8 +3130,11 @@
       <c r="Q18" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>5</v>
       </c>
@@ -3098,8 +3186,11 @@
       <c r="Q19" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>6</v>
       </c>
@@ -3151,8 +3242,11 @@
       <c r="Q20" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>7</v>
       </c>
@@ -3204,8 +3298,11 @@
       <c r="Q21" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>8</v>
       </c>
@@ -3257,8 +3354,11 @@
       <c r="Q22" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>9</v>
       </c>
@@ -3310,8 +3410,11 @@
       <c r="Q23" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>86</v>
       </c>
@@ -3363,8 +3466,11 @@
       <c r="Q24" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>87</v>
       </c>
@@ -3416,8 +3522,11 @@
       <c r="Q25" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>88</v>
       </c>
@@ -3469,8 +3578,11 @@
       <c r="Q26" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>89</v>
       </c>
@@ -3522,8 +3634,11 @@
       <c r="Q27" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>90</v>
       </c>
@@ -3575,8 +3690,11 @@
       <c r="Q28" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>91</v>
       </c>
@@ -3628,8 +3746,11 @@
       <c r="Q29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>92</v>
       </c>
@@ -3681,8 +3802,11 @@
       <c r="Q30" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>93</v>
       </c>
@@ -3734,8 +3858,11 @@
       <c r="Q31" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>10</v>
       </c>
@@ -3787,8 +3914,11 @@
       <c r="Q32" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>11</v>
       </c>
@@ -3840,8 +3970,11 @@
       <c r="Q33" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>12</v>
       </c>
@@ -3893,8 +4026,11 @@
       <c r="Q34" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>13</v>
       </c>
@@ -3946,8 +4082,11 @@
       <c r="Q35" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>14</v>
       </c>
@@ -3999,8 +4138,11 @@
       <c r="Q36" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>15</v>
       </c>
@@ -4052,8 +4194,11 @@
       <c r="Q37" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>16</v>
       </c>
@@ -4105,8 +4250,11 @@
       <c r="Q38" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>94</v>
       </c>
@@ -4158,8 +4306,11 @@
       <c r="Q39" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>95</v>
       </c>
@@ -4211,8 +4362,11 @@
       <c r="Q40" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>96</v>
       </c>
@@ -4264,8 +4418,11 @@
       <c r="Q41" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>97</v>
       </c>
@@ -4317,8 +4474,11 @@
       <c r="Q42" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>98</v>
       </c>
@@ -4370,8 +4530,11 @@
       <c r="Q43" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>99</v>
       </c>
@@ -4423,8 +4586,11 @@
       <c r="Q44" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>100</v>
       </c>
@@ -4476,90 +4642,96 @@
       <c r="Q45" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
+        <v>101</v>
+      </c>
+      <c r="B46" t="s">
+        <v>565</v>
+      </c>
+      <c r="C46" t="s">
+        <v>566</v>
+      </c>
+      <c r="D46" t="s">
+        <v>567</v>
+      </c>
+      <c r="E46" t="s">
+        <v>568</v>
+      </c>
+      <c r="F46" t="s">
+        <v>569</v>
+      </c>
+      <c r="G46">
+        <v>630</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46" t="s">
+        <v>36</v>
+      </c>
+      <c r="J46" t="s">
+        <v>570</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46">
+        <v>12</v>
+      </c>
+      <c r="M46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46" t="s">
+        <v>571</v>
+      </c>
+      <c r="P46" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="b">
+        <v>1</v>
+      </c>
+      <c r="R46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>17</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>366</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>49</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>50</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E47" t="s">
         <v>51</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F47" t="s">
         <v>52</v>
       </c>
-      <c r="G46">
+      <c r="G47">
         <v>3</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H47" t="s">
         <v>20</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I47" t="s">
         <v>53</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J47" t="s">
         <v>49</v>
-      </c>
-      <c r="K46" t="s">
-        <v>23</v>
-      </c>
-      <c r="L46">
-        <v>6</v>
-      </c>
-      <c r="M46" t="b">
-        <v>0</v>
-      </c>
-      <c r="N46" t="b">
-        <v>1</v>
-      </c>
-      <c r="O46" t="s">
-        <v>257</v>
-      </c>
-      <c r="P46" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>18</v>
-      </c>
-      <c r="B47" t="s">
-        <v>367</v>
-      </c>
-      <c r="C47" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" t="s">
-        <v>54</v>
-      </c>
-      <c r="E47" t="s">
-        <v>55</v>
-      </c>
-      <c r="F47" t="s">
-        <v>56</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-      <c r="H47" t="s">
-        <v>28</v>
-      </c>
-      <c r="I47" t="s">
-        <v>57</v>
-      </c>
-      <c r="J47" t="s">
-        <v>30</v>
       </c>
       <c r="K47" t="s">
         <v>23</v>
@@ -4574,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
@@ -4582,37 +4754,40 @@
       <c r="Q47" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B48" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E48" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="G48">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I48" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J48" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K48" t="s">
         <v>23</v>
@@ -4627,98 +4802,104 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
+        <v>258</v>
+      </c>
+      <c r="P48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="b">
+        <v>1</v>
+      </c>
+      <c r="R48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>368</v>
+      </c>
+      <c r="C49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49">
+        <v>400</v>
+      </c>
+      <c r="H49" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" t="s">
+        <v>60</v>
+      </c>
+      <c r="J49" t="s">
+        <v>22</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49">
+        <v>6</v>
+      </c>
+      <c r="M49" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49" t="s">
         <v>259</v>
       </c>
-      <c r="P48" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="P49" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
+      <c r="R49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>20</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>369</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C50" t="s">
         <v>24</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>54</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E50" t="s">
         <v>55</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F50" t="s">
         <v>61</v>
       </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
         <v>28</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I50" t="s">
         <v>29</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J50" t="s">
         <v>30</v>
-      </c>
-      <c r="K49" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49">
-        <v>12</v>
-      </c>
-      <c r="M49" t="b">
-        <v>0</v>
-      </c>
-      <c r="N49" t="b">
-        <v>1</v>
-      </c>
-      <c r="O49" t="s">
-        <v>260</v>
-      </c>
-      <c r="P49" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>21</v>
-      </c>
-      <c r="B50" t="s">
-        <v>370</v>
-      </c>
-      <c r="C50" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" t="s">
-        <v>63</v>
-      </c>
-      <c r="E50" t="s">
-        <v>64</v>
-      </c>
-      <c r="F50" t="s">
-        <v>65</v>
-      </c>
-      <c r="G50">
-        <v>400</v>
-      </c>
-      <c r="H50" t="s">
-        <v>42</v>
-      </c>
-      <c r="I50" t="s">
-        <v>60</v>
-      </c>
-      <c r="J50" t="s">
-        <v>66</v>
       </c>
       <c r="K50" t="s">
         <v>23</v>
@@ -4733,98 +4914,104 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
+        <v>260</v>
+      </c>
+      <c r="P50" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="b">
+        <v>1</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>21</v>
+      </c>
+      <c r="B51" t="s">
+        <v>370</v>
+      </c>
+      <c r="C51" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G51">
+        <v>400</v>
+      </c>
+      <c r="H51" t="s">
+        <v>42</v>
+      </c>
+      <c r="I51" t="s">
+        <v>60</v>
+      </c>
+      <c r="J51" t="s">
+        <v>66</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51">
+        <v>12</v>
+      </c>
+      <c r="M51" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51" t="s">
         <v>261</v>
       </c>
-      <c r="P50" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="P51" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="b">
+        <v>0</v>
+      </c>
+      <c r="R51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>22</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>371</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>67</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>68</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E52" t="s">
         <v>69</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F52" t="s">
         <v>70</v>
       </c>
-      <c r="G51">
+      <c r="G52">
         <v>100</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H52" t="s">
         <v>20</v>
-      </c>
-      <c r="I51" t="s">
-        <v>53</v>
-      </c>
-      <c r="J51" t="s">
-        <v>71</v>
-      </c>
-      <c r="K51" t="s">
-        <v>23</v>
-      </c>
-      <c r="L51">
-        <v>6</v>
-      </c>
-      <c r="M51" t="b">
-        <v>0</v>
-      </c>
-      <c r="N51" t="b">
-        <v>1</v>
-      </c>
-      <c r="O51" t="s">
-        <v>262</v>
-      </c>
-      <c r="P51" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>23</v>
-      </c>
-      <c r="B52" t="s">
-        <v>372</v>
-      </c>
-      <c r="C52" t="s">
-        <v>72</v>
-      </c>
-      <c r="D52" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" t="s">
-        <v>74</v>
-      </c>
-      <c r="F52" t="s">
-        <v>75</v>
-      </c>
-      <c r="G52">
-        <v>90</v>
-      </c>
-      <c r="H52" t="s">
-        <v>42</v>
       </c>
       <c r="I52" t="s">
         <v>53</v>
       </c>
       <c r="J52" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K52" t="s">
         <v>23</v>
@@ -4839,104 +5026,110 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
+        <v>262</v>
+      </c>
+      <c r="P52" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="b">
+        <v>1</v>
+      </c>
+      <c r="R52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>23</v>
+      </c>
+      <c r="B53" t="s">
+        <v>372</v>
+      </c>
+      <c r="C53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D53" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" t="s">
+        <v>74</v>
+      </c>
+      <c r="F53" t="s">
+        <v>75</v>
+      </c>
+      <c r="G53">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s">
+        <v>42</v>
+      </c>
+      <c r="I53" t="s">
+        <v>53</v>
+      </c>
+      <c r="J53" t="s">
+        <v>76</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53">
+        <v>6</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53" t="s">
         <v>263</v>
       </c>
-      <c r="P52" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q52" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+      <c r="P53" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="b">
+        <v>1</v>
+      </c>
+      <c r="R53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>24</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B54" t="s">
         <v>373</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C54" t="s">
         <v>44</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>77</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E54" t="s">
         <v>78</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F54" t="s">
         <v>79</v>
       </c>
-      <c r="G53">
-        <v>1</v>
-      </c>
-      <c r="H53" t="s">
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
         <v>48</v>
-      </c>
-      <c r="I53" t="s">
-        <v>21</v>
-      </c>
-      <c r="J53" t="s">
-        <v>44</v>
-      </c>
-      <c r="K53" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53">
-        <v>10</v>
-      </c>
-      <c r="M53" t="b">
-        <v>0</v>
-      </c>
-      <c r="N53" t="b">
-        <v>1</v>
-      </c>
-      <c r="O53" t="s">
-        <v>264</v>
-      </c>
-      <c r="P53" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>25</v>
-      </c>
-      <c r="B54" t="s">
-        <v>374</v>
-      </c>
-      <c r="C54" t="s">
-        <v>80</v>
-      </c>
-      <c r="D54" t="s">
-        <v>81</v>
-      </c>
-      <c r="E54" t="s">
-        <v>32</v>
-      </c>
-      <c r="F54" t="s">
-        <v>82</v>
-      </c>
-      <c r="G54">
-        <v>180</v>
-      </c>
-      <c r="H54" t="s">
-        <v>42</v>
       </c>
       <c r="I54" t="s">
         <v>21</v>
       </c>
       <c r="J54" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M54" t="b">
         <v>0</v>
@@ -4945,7 +5138,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -4953,37 +5146,40 @@
       <c r="Q54" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D55" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E55" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="F55" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G55">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="H55" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I55" t="s">
         <v>21</v>
       </c>
       <c r="J55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s">
         <v>23</v>
@@ -4998,219 +5194,231 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
+        <v>265</v>
+      </c>
+      <c r="P55" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="b">
+        <v>1</v>
+      </c>
+      <c r="R55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>26</v>
+      </c>
+      <c r="B56" t="s">
+        <v>375</v>
+      </c>
+      <c r="C56" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" t="s">
+        <v>85</v>
+      </c>
+      <c r="E56" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" t="s">
+        <v>87</v>
+      </c>
+      <c r="G56">
+        <v>6</v>
+      </c>
+      <c r="H56" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>84</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56">
+        <v>12</v>
+      </c>
+      <c r="M56" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" t="b">
+        <v>1</v>
+      </c>
+      <c r="O56" t="s">
         <v>266</v>
       </c>
-      <c r="P55" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q55" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="P56" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="b">
+        <v>1</v>
+      </c>
+      <c r="R56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>102</v>
+      </c>
+      <c r="B57" t="s">
+        <v>572</v>
+      </c>
+      <c r="C57" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" t="s">
+        <v>78</v>
+      </c>
+      <c r="F57" t="s">
+        <v>573</v>
+      </c>
+      <c r="G57">
+        <v>900</v>
+      </c>
+      <c r="H57" t="s">
+        <v>42</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>44</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57">
+        <v>10</v>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" t="b">
+        <v>1</v>
+      </c>
+      <c r="O57" t="s">
+        <v>574</v>
+      </c>
+      <c r="P57" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="b">
+        <v>1</v>
+      </c>
+      <c r="R57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>27</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B58" t="s">
         <v>376</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C58" t="s">
         <v>88</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D58" t="s">
         <v>89</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E58" t="s">
         <v>90</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F58" t="s">
         <v>91</v>
       </c>
-      <c r="G56">
+      <c r="G58">
         <v>500</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H58" t="s">
         <v>35</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I58" t="s">
         <v>36</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J58" t="s">
         <v>92</v>
       </c>
-      <c r="K56" t="s">
-        <v>23</v>
-      </c>
-      <c r="L56">
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58">
         <v>6</v>
       </c>
-      <c r="M56" t="b">
-        <v>0</v>
-      </c>
-      <c r="N56" t="b">
-        <v>1</v>
-      </c>
-      <c r="O56" t="s">
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="b">
+        <v>1</v>
+      </c>
+      <c r="O58" t="s">
         <v>267</v>
       </c>
-      <c r="P56" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+      <c r="P58" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="b">
+        <v>0</v>
+      </c>
+      <c r="R58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>28</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B59" t="s">
         <v>377</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C59" t="s">
         <v>62</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D59" t="s">
         <v>93</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E59" t="s">
         <v>94</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F59" t="s">
         <v>95</v>
       </c>
-      <c r="G57">
+      <c r="G59">
         <v>12</v>
-      </c>
-      <c r="H57" t="s">
-        <v>20</v>
-      </c>
-      <c r="I57" t="s">
-        <v>60</v>
-      </c>
-      <c r="J57" t="s">
-        <v>66</v>
-      </c>
-      <c r="K57" t="s">
-        <v>23</v>
-      </c>
-      <c r="L57">
-        <v>30</v>
-      </c>
-      <c r="M57" t="b">
-        <v>0</v>
-      </c>
-      <c r="N57" t="b">
-        <v>1</v>
-      </c>
-      <c r="O57" t="s">
-        <v>268</v>
-      </c>
-      <c r="P57" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>29</v>
-      </c>
-      <c r="B58" t="s">
-        <v>378</v>
-      </c>
-      <c r="C58" t="s">
-        <v>24</v>
-      </c>
-      <c r="D58" t="s">
-        <v>54</v>
-      </c>
-      <c r="E58" t="s">
-        <v>55</v>
-      </c>
-      <c r="F58" t="s">
-        <v>61</v>
-      </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-      <c r="H58" t="s">
-        <v>28</v>
-      </c>
-      <c r="I58" t="s">
-        <v>96</v>
-      </c>
-      <c r="J58" t="s">
-        <v>30</v>
-      </c>
-      <c r="K58" t="s">
-        <v>23</v>
-      </c>
-      <c r="L58">
-        <v>12</v>
-      </c>
-      <c r="M58" t="b">
-        <v>0</v>
-      </c>
-      <c r="N58" t="b">
-        <v>1</v>
-      </c>
-      <c r="O58" t="s">
-        <v>269</v>
-      </c>
-      <c r="P58" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>30</v>
-      </c>
-      <c r="B59" t="s">
-        <v>379</v>
-      </c>
-      <c r="C59" t="s">
-        <v>97</v>
-      </c>
-      <c r="D59" t="s">
-        <v>98</v>
-      </c>
-      <c r="E59" t="s">
-        <v>99</v>
-      </c>
-      <c r="F59" t="s">
-        <v>100</v>
-      </c>
-      <c r="G59">
-        <v>100</v>
       </c>
       <c r="H59" t="s">
         <v>20</v>
       </c>
       <c r="I59" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J59" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
       </c>
       <c r="N59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -5218,37 +5426,40 @@
       <c r="Q59" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="E60" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="F60" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="G60">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I60" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="J60" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
@@ -5263,45 +5474,48 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="R60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B61" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E61" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F61" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="G61">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H61" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I61" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J61" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
@@ -5313,10 +5527,10 @@
         <v>0</v>
       </c>
       <c r="N61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -5324,43 +5538,46 @@
       <c r="Q61" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C62" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E62" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="F62" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H62" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I62" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J62" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -5369,45 +5586,48 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="R62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
+        <v>32</v>
+      </c>
+      <c r="B63" t="s">
+        <v>381</v>
+      </c>
+      <c r="C63" t="s">
+        <v>31</v>
+      </c>
+      <c r="D63" t="s">
+        <v>109</v>
+      </c>
+      <c r="E63" t="s">
+        <v>110</v>
+      </c>
+      <c r="F63" t="s">
         <v>34</v>
       </c>
-      <c r="B63" t="s">
-        <v>383</v>
-      </c>
-      <c r="C63" t="s">
-        <v>112</v>
-      </c>
-      <c r="D63" t="s">
-        <v>113</v>
-      </c>
-      <c r="E63" t="s">
-        <v>114</v>
-      </c>
-      <c r="F63" t="s">
-        <v>115</v>
-      </c>
       <c r="G63">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H63" t="s">
         <v>35</v>
       </c>
       <c r="I63" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="J63" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
@@ -5422,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5430,43 +5650,46 @@
       <c r="Q63" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C64" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="D64" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="E64" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="F64" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G64">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I64" t="s">
         <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
@@ -5475,45 +5698,48 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="R64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
+        <v>34</v>
+      </c>
+      <c r="B65" t="s">
+        <v>383</v>
+      </c>
+      <c r="C65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" t="s">
+        <v>114</v>
+      </c>
+      <c r="F65" t="s">
+        <v>115</v>
+      </c>
+      <c r="G65">
+        <v>300</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65" t="s">
         <v>36</v>
       </c>
-      <c r="B65" t="s">
-        <v>385</v>
-      </c>
-      <c r="C65" t="s">
-        <v>121</v>
-      </c>
-      <c r="D65" t="s">
-        <v>122</v>
-      </c>
-      <c r="E65" t="s">
-        <v>32</v>
-      </c>
-      <c r="F65" t="s">
-        <v>123</v>
-      </c>
-      <c r="G65">
-        <v>250</v>
-      </c>
-      <c r="H65" t="s">
-        <v>42</v>
-      </c>
-      <c r="I65" t="s">
-        <v>124</v>
-      </c>
       <c r="J65" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
@@ -5528,51 +5754,54 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="R65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B66" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C66" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D66" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E66" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F66" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="G66">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="H66" t="s">
         <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5581,7 +5810,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5589,43 +5818,46 @@
       <c r="Q66" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B67" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="D67" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="E67" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="F67" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="G67">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H67" t="s">
         <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="J67" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5634,7 +5866,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5642,43 +5874,46 @@
       <c r="Q67" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B68" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C68" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D68" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E68" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F68" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G68">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="H68" t="s">
         <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J68" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -5687,51 +5922,54 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="R68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C69" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D69" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E69" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="F69" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="H69" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I69" t="s">
         <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -5740,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -5748,131 +5986,140 @@
       <c r="Q69" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D70" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E70" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="F70" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G70">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="H70" t="s">
         <v>42</v>
       </c>
       <c r="I70" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="J70" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="R70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B71" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C71" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" t="s">
+        <v>77</v>
+      </c>
+      <c r="E71" t="s">
+        <v>78</v>
+      </c>
+      <c r="F71" t="s">
+        <v>137</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>48</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71">
+        <v>10</v>
+      </c>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" t="b">
+        <v>1</v>
+      </c>
+      <c r="O71" t="s">
+        <v>280</v>
+      </c>
+      <c r="P71" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="b">
+        <v>1</v>
+      </c>
+      <c r="R71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>41</v>
+      </c>
+      <c r="B72" t="s">
+        <v>390</v>
+      </c>
+      <c r="C72" t="s">
         <v>138</v>
-      </c>
-      <c r="D71" t="s">
-        <v>139</v>
-      </c>
-      <c r="E71" t="s">
-        <v>144</v>
-      </c>
-      <c r="F71" t="s">
-        <v>87</v>
-      </c>
-      <c r="G71">
-        <v>1000</v>
-      </c>
-      <c r="H71" t="s">
-        <v>42</v>
-      </c>
-      <c r="I71" t="s">
-        <v>142</v>
-      </c>
-      <c r="J71" t="s">
-        <v>143</v>
-      </c>
-      <c r="K71" t="s">
-        <v>23</v>
-      </c>
-      <c r="L71">
-        <v>1</v>
-      </c>
-      <c r="M71" t="b">
-        <v>1</v>
-      </c>
-      <c r="N71" t="b">
-        <v>1</v>
-      </c>
-      <c r="O71" t="s">
-        <v>282</v>
-      </c>
-      <c r="P71" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q71" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>43</v>
-      </c>
-      <c r="B72" t="s">
-        <v>392</v>
-      </c>
-      <c r="C72" t="s">
-        <v>145</v>
       </c>
       <c r="D72" t="s">
         <v>139</v>
       </c>
       <c r="E72" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F72" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G72">
         <v>1000</v>
@@ -5884,166 +6131,175 @@
         <v>142</v>
       </c>
       <c r="J72" t="s">
+        <v>143</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72" t="b">
+        <v>1</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" t="s">
+        <v>281</v>
+      </c>
+      <c r="P72" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="b">
+        <v>0</v>
+      </c>
+      <c r="R72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>42</v>
+      </c>
+      <c r="B73" t="s">
+        <v>391</v>
+      </c>
+      <c r="C73" t="s">
+        <v>138</v>
+      </c>
+      <c r="D73" t="s">
+        <v>139</v>
+      </c>
+      <c r="E73" t="s">
+        <v>144</v>
+      </c>
+      <c r="F73" t="s">
+        <v>87</v>
+      </c>
+      <c r="G73">
+        <v>1000</v>
+      </c>
+      <c r="H73" t="s">
+        <v>42</v>
+      </c>
+      <c r="I73" t="s">
+        <v>142</v>
+      </c>
+      <c r="J73" t="s">
+        <v>143</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73" t="b">
+        <v>1</v>
+      </c>
+      <c r="N73" t="b">
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
+        <v>282</v>
+      </c>
+      <c r="P73" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="b">
+        <v>0</v>
+      </c>
+      <c r="R73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>43</v>
+      </c>
+      <c r="B74" t="s">
+        <v>392</v>
+      </c>
+      <c r="C74" t="s">
+        <v>145</v>
+      </c>
+      <c r="D74" t="s">
+        <v>139</v>
+      </c>
+      <c r="E74" t="s">
+        <v>146</v>
+      </c>
+      <c r="F74" t="s">
+        <v>147</v>
+      </c>
+      <c r="G74">
+        <v>1000</v>
+      </c>
+      <c r="H74" t="s">
+        <v>42</v>
+      </c>
+      <c r="I74" t="s">
+        <v>142</v>
+      </c>
+      <c r="J74" t="s">
         <v>148</v>
       </c>
-      <c r="K72" t="s">
-        <v>23</v>
-      </c>
-      <c r="L72">
-        <v>1</v>
-      </c>
-      <c r="M72" t="b">
-        <v>1</v>
-      </c>
-      <c r="N72" t="b">
-        <v>1</v>
-      </c>
-      <c r="O72" t="s">
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74" t="b">
+        <v>1</v>
+      </c>
+      <c r="N74" t="b">
+        <v>1</v>
+      </c>
+      <c r="O74" t="s">
         <v>283</v>
       </c>
-      <c r="P72" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
+      <c r="P74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="b">
+        <v>0</v>
+      </c>
+      <c r="R74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>44</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B75" t="s">
         <v>393</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C75" t="s">
         <v>149</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D75" t="s">
         <v>150</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E75" t="s">
         <v>151</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F75" t="s">
         <v>152</v>
       </c>
-      <c r="G73">
+      <c r="G75">
         <v>200</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H75" t="s">
         <v>35</v>
       </c>
-      <c r="I73" t="s">
+      <c r="I75" t="s">
         <v>153</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J75" t="s">
         <v>154</v>
-      </c>
-      <c r="K73" t="s">
-        <v>23</v>
-      </c>
-      <c r="L73">
-        <v>12</v>
-      </c>
-      <c r="M73" t="b">
-        <v>0</v>
-      </c>
-      <c r="N73" t="b">
-        <v>1</v>
-      </c>
-      <c r="O73" t="s">
-        <v>284</v>
-      </c>
-      <c r="P73" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q73" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>45</v>
-      </c>
-      <c r="B74" t="s">
-        <v>394</v>
-      </c>
-      <c r="C74" t="s">
-        <v>155</v>
-      </c>
-      <c r="D74" t="s">
-        <v>156</v>
-      </c>
-      <c r="E74" t="s">
-        <v>157</v>
-      </c>
-      <c r="F74" t="s">
-        <v>158</v>
-      </c>
-      <c r="G74">
-        <v>1</v>
-      </c>
-      <c r="H74" t="s">
-        <v>20</v>
-      </c>
-      <c r="I74" t="s">
-        <v>159</v>
-      </c>
-      <c r="J74" t="s">
-        <v>160</v>
-      </c>
-      <c r="K74" t="s">
-        <v>161</v>
-      </c>
-      <c r="L74">
-        <v>50</v>
-      </c>
-      <c r="M74" t="b">
-        <v>0</v>
-      </c>
-      <c r="N74" t="b">
-        <v>0</v>
-      </c>
-      <c r="O74" t="s">
-        <v>285</v>
-      </c>
-      <c r="P74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>46</v>
-      </c>
-      <c r="B75" t="s">
-        <v>395</v>
-      </c>
-      <c r="C75" t="s">
-        <v>162</v>
-      </c>
-      <c r="D75" t="s">
-        <v>163</v>
-      </c>
-      <c r="E75" t="s">
-        <v>164</v>
-      </c>
-      <c r="F75" t="s">
-        <v>165</v>
-      </c>
-      <c r="G75">
-        <v>210</v>
-      </c>
-      <c r="H75" t="s">
-        <v>42</v>
-      </c>
-      <c r="I75" t="s">
-        <v>29</v>
-      </c>
-      <c r="J75" t="s">
-        <v>162</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
@@ -6058,7 +6314,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6066,90 +6322,96 @@
       <c r="Q75" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C76" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D76" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E76" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="F76" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="G76">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I76" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="J76" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="K76" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L76">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
       </c>
       <c r="N76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="R76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B77" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C77" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D77" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E77" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F77" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="G77">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H77" t="s">
         <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J77" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
@@ -6164,7 +6426,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6172,28 +6434,31 @@
       <c r="Q77" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B78" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C78" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="D78" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="E78" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="F78" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="G78">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H78" t="s">
         <v>42</v>
@@ -6202,7 +6467,7 @@
         <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
@@ -6217,7 +6482,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6225,40 +6490,43 @@
       <c r="Q78" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C79" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D79" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="E79" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F79" t="s">
-        <v>183</v>
+        <v>70</v>
       </c>
       <c r="G79">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H79" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="K79" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L79">
         <v>12</v>
@@ -6270,7 +6538,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6278,43 +6546,46 @@
       <c r="Q79" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B80" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C80" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D80" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E80" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F80" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G80">
-        <v>360</v>
+        <v>50</v>
       </c>
       <c r="H80" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>556</v>
+        <v>179</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6323,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6331,16 +6602,19 @@
       <c r="Q80" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B81" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C81" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D81" t="s">
         <v>181</v>
@@ -6352,7 +6626,7 @@
         <v>183</v>
       </c>
       <c r="G81">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H81" t="s">
         <v>20</v>
@@ -6364,10 +6638,10 @@
         <v>184</v>
       </c>
       <c r="K81" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L81">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6376,7 +6650,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6384,37 +6658,40 @@
       <c r="Q81" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B82" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C82" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="D82" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E82" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F82" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G82">
-        <v>1.5</v>
+        <v>360</v>
       </c>
       <c r="H82" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="I82" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
       <c r="J82" t="s">
-        <v>37</v>
+        <v>556</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -6429,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6437,225 +6714,240 @@
       <c r="Q82" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B83" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C83" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D83" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="E83" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="F83" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="G83">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H83" t="s">
         <v>20</v>
       </c>
       <c r="I83" t="s">
+        <v>53</v>
+      </c>
+      <c r="J83" t="s">
+        <v>184</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83">
+        <v>24</v>
+      </c>
+      <c r="M83" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O83" t="s">
+        <v>292</v>
+      </c>
+      <c r="P83" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="b">
+        <v>1</v>
+      </c>
+      <c r="R83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>53</v>
+      </c>
+      <c r="B84" t="s">
+        <v>402</v>
+      </c>
+      <c r="C84" t="s">
+        <v>31</v>
+      </c>
+      <c r="D84" t="s">
+        <v>194</v>
+      </c>
+      <c r="E84" t="s">
+        <v>195</v>
+      </c>
+      <c r="F84" t="s">
+        <v>196</v>
+      </c>
+      <c r="G84">
+        <v>1.5</v>
+      </c>
+      <c r="H84" t="s">
+        <v>28</v>
+      </c>
+      <c r="I84" t="s">
+        <v>36</v>
+      </c>
+      <c r="J84" t="s">
+        <v>37</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84">
+        <v>6</v>
+      </c>
+      <c r="M84" t="b">
+        <v>0</v>
+      </c>
+      <c r="N84" t="b">
+        <v>1</v>
+      </c>
+      <c r="O84" t="s">
+        <v>293</v>
+      </c>
+      <c r="P84" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>54</v>
+      </c>
+      <c r="B85" t="s">
+        <v>403</v>
+      </c>
+      <c r="C85" t="s">
+        <v>197</v>
+      </c>
+      <c r="D85" t="s">
+        <v>198</v>
+      </c>
+      <c r="E85" t="s">
+        <v>199</v>
+      </c>
+      <c r="F85" t="s">
+        <v>200</v>
+      </c>
+      <c r="G85">
+        <v>12</v>
+      </c>
+      <c r="H85" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" t="s">
         <v>21</v>
       </c>
-      <c r="J83" t="s">
+      <c r="J85" t="s">
         <v>201</v>
       </c>
-      <c r="K83" t="s">
-        <v>23</v>
-      </c>
-      <c r="L83">
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85">
         <v>4</v>
       </c>
-      <c r="M83" t="b">
-        <v>0</v>
-      </c>
-      <c r="N83" t="b">
-        <v>0</v>
-      </c>
-      <c r="O83" t="s">
+      <c r="M85" t="b">
+        <v>0</v>
+      </c>
+      <c r="N85" t="b">
+        <v>0</v>
+      </c>
+      <c r="O85" t="s">
         <v>294</v>
       </c>
-      <c r="P83" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
+      <c r="P85" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="b">
+        <v>1</v>
+      </c>
+      <c r="R85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
         <v>55</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B86" t="s">
         <v>404</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C86" t="s">
         <v>186</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D86" t="s">
         <v>202</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E86" t="s">
         <v>203</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F86" t="s">
         <v>204</v>
       </c>
-      <c r="G84">
+      <c r="G86">
         <v>150</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H86" t="s">
         <v>35</v>
       </c>
-      <c r="I84" t="s">
+      <c r="I86" t="s">
         <v>191</v>
       </c>
-      <c r="J84" t="s">
+      <c r="J86" t="s">
         <v>192</v>
       </c>
-      <c r="K84" t="s">
-        <v>23</v>
-      </c>
-      <c r="L84">
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86">
         <v>12</v>
       </c>
-      <c r="M84" t="b">
-        <v>0</v>
-      </c>
-      <c r="N84" t="b">
-        <v>1</v>
-      </c>
-      <c r="O84" t="s">
+      <c r="M86" t="b">
+        <v>0</v>
+      </c>
+      <c r="N86" t="b">
+        <v>1</v>
+      </c>
+      <c r="O86" t="s">
         <v>295</v>
       </c>
-      <c r="P84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
+      <c r="P86" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="b">
+        <v>0</v>
+      </c>
+      <c r="R86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
         <v>56</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B87" t="s">
         <v>405</v>
-      </c>
-      <c r="C85" t="s">
-        <v>205</v>
-      </c>
-      <c r="D85" t="s">
-        <v>206</v>
-      </c>
-      <c r="E85" t="s">
-        <v>207</v>
-      </c>
-      <c r="F85" t="s">
-        <v>208</v>
-      </c>
-      <c r="G85">
-        <v>500</v>
-      </c>
-      <c r="H85" t="s">
-        <v>42</v>
-      </c>
-      <c r="I85" t="s">
-        <v>209</v>
-      </c>
-      <c r="J85" t="s">
-        <v>66</v>
-      </c>
-      <c r="K85" t="s">
-        <v>23</v>
-      </c>
-      <c r="L85">
-        <v>6</v>
-      </c>
-      <c r="M85" t="b">
-        <v>0</v>
-      </c>
-      <c r="N85" t="b">
-        <v>1</v>
-      </c>
-      <c r="O85" t="s">
-        <v>296</v>
-      </c>
-      <c r="P85" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>57</v>
-      </c>
-      <c r="B86" t="s">
-        <v>406</v>
-      </c>
-      <c r="C86" t="s">
-        <v>210</v>
-      </c>
-      <c r="D86" t="s">
-        <v>211</v>
-      </c>
-      <c r="E86" t="s">
-        <v>212</v>
-      </c>
-      <c r="F86" t="s">
-        <v>208</v>
-      </c>
-      <c r="G86">
-        <v>500</v>
-      </c>
-      <c r="H86" t="s">
-        <v>42</v>
-      </c>
-      <c r="I86" t="s">
-        <v>209</v>
-      </c>
-      <c r="J86" t="s">
-        <v>66</v>
-      </c>
-      <c r="K86" t="s">
-        <v>23</v>
-      </c>
-      <c r="L86">
-        <v>6</v>
-      </c>
-      <c r="M86" t="b">
-        <v>0</v>
-      </c>
-      <c r="N86" t="b">
-        <v>1</v>
-      </c>
-      <c r="O86" t="s">
-        <v>297</v>
-      </c>
-      <c r="P86" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>58</v>
-      </c>
-      <c r="B87" t="s">
-        <v>407</v>
       </c>
       <c r="C87" t="s">
         <v>205</v>
@@ -6664,7 +6956,7 @@
         <v>206</v>
       </c>
       <c r="E87" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F87" t="s">
         <v>208</v>
@@ -6685,7 +6977,7 @@
         <v>23</v>
       </c>
       <c r="L87">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -6694,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -6702,43 +6994,46 @@
       <c r="Q87" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B88" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C88" t="s">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="D88" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F88" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H88" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J88" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -6747,45 +7042,48 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="R88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B89" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C89" t="s">
-        <v>24</v>
+        <v>205</v>
       </c>
       <c r="D89" t="s">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="E89" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F89" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G89">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H89" t="s">
         <v>42</v>
       </c>
       <c r="I89" t="s">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="J89" t="s">
-        <v>557</v>
+        <v>66</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
@@ -6800,469 +7098,496 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="R89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B90" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C90" t="s">
-        <v>217</v>
+        <v>145</v>
       </c>
       <c r="D90" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E90" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F90" t="s">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="G90">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H90" t="s">
         <v>20</v>
       </c>
       <c r="I90" t="s">
+        <v>136</v>
+      </c>
+      <c r="J90" t="s">
+        <v>148</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90">
+        <v>12</v>
+      </c>
+      <c r="M90" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" t="b">
+        <v>1</v>
+      </c>
+      <c r="O90" t="s">
+        <v>299</v>
+      </c>
+      <c r="P90" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>60</v>
+      </c>
+      <c r="B91" t="s">
+        <v>409</v>
+      </c>
+      <c r="C91" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" t="s">
+        <v>81</v>
+      </c>
+      <c r="E91" t="s">
+        <v>55</v>
+      </c>
+      <c r="F91" t="s">
+        <v>216</v>
+      </c>
+      <c r="G91">
+        <v>800</v>
+      </c>
+      <c r="H91" t="s">
+        <v>42</v>
+      </c>
+      <c r="I91" t="s">
+        <v>60</v>
+      </c>
+      <c r="J91" t="s">
+        <v>557</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91">
+        <v>12</v>
+      </c>
+      <c r="M91" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" t="b">
+        <v>1</v>
+      </c>
+      <c r="O91" t="s">
+        <v>300</v>
+      </c>
+      <c r="P91" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="b">
+        <v>1</v>
+      </c>
+      <c r="R91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>61</v>
+      </c>
+      <c r="B92" t="s">
+        <v>410</v>
+      </c>
+      <c r="C92" t="s">
+        <v>217</v>
+      </c>
+      <c r="D92" t="s">
+        <v>218</v>
+      </c>
+      <c r="E92" t="s">
+        <v>219</v>
+      </c>
+      <c r="F92" t="s">
+        <v>220</v>
+      </c>
+      <c r="G92">
+        <v>20</v>
+      </c>
+      <c r="H92" t="s">
+        <v>20</v>
+      </c>
+      <c r="I92" t="s">
         <v>101</v>
       </c>
-      <c r="J90" t="s">
+      <c r="J92" t="s">
         <v>217</v>
       </c>
-      <c r="K90" t="s">
-        <v>23</v>
-      </c>
-      <c r="L90">
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92">
         <v>10</v>
       </c>
-      <c r="M90" t="b">
-        <v>0</v>
-      </c>
-      <c r="N90" t="b">
-        <v>0</v>
-      </c>
-      <c r="O90" t="s">
+      <c r="M92" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" t="b">
+        <v>0</v>
+      </c>
+      <c r="O92" t="s">
         <v>301</v>
       </c>
-      <c r="P90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q90" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
+      <c r="P92" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q92" t="b">
+        <v>1</v>
+      </c>
+      <c r="R92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
         <v>62</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B93" t="s">
         <v>411</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C93" t="s">
         <v>217</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D93" t="s">
         <v>221</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E93" t="s">
         <v>219</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F93" t="s">
         <v>222</v>
       </c>
-      <c r="G91">
+      <c r="G93">
         <v>20</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H93" t="s">
         <v>20</v>
       </c>
-      <c r="I91" t="s">
+      <c r="I93" t="s">
         <v>101</v>
       </c>
-      <c r="J91" t="s">
+      <c r="J93" t="s">
         <v>217</v>
       </c>
-      <c r="K91" t="s">
-        <v>23</v>
-      </c>
-      <c r="L91">
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93">
         <v>10</v>
       </c>
-      <c r="M91" t="b">
-        <v>0</v>
-      </c>
-      <c r="N91" t="b">
-        <v>0</v>
-      </c>
-      <c r="O91" t="s">
+      <c r="M93" t="b">
+        <v>0</v>
+      </c>
+      <c r="N93" t="b">
+        <v>0</v>
+      </c>
+      <c r="O93" t="s">
         <v>302</v>
       </c>
-      <c r="P91" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q91" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
+      <c r="P93" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q93" t="b">
+        <v>0</v>
+      </c>
+      <c r="R93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <v>63</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B94" t="s">
         <v>412</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C94" t="s">
         <v>223</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D94" t="s">
         <v>202</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E94" t="s">
         <v>203</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F94" t="s">
         <v>204</v>
       </c>
-      <c r="G92">
+      <c r="G94">
         <v>60</v>
       </c>
-      <c r="H92" t="s">
+      <c r="H94" t="s">
         <v>35</v>
       </c>
-      <c r="I92" t="s">
+      <c r="I94" t="s">
         <v>53</v>
       </c>
-      <c r="J92" t="s">
+      <c r="J94" t="s">
         <v>224</v>
       </c>
-      <c r="K92" t="s">
-        <v>23</v>
-      </c>
-      <c r="L92">
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94">
         <v>6</v>
       </c>
-      <c r="M92" t="b">
-        <v>0</v>
-      </c>
-      <c r="N92" t="b">
-        <v>1</v>
-      </c>
-      <c r="O92" t="s">
+      <c r="M94" t="b">
+        <v>0</v>
+      </c>
+      <c r="N94" t="b">
+        <v>1</v>
+      </c>
+      <c r="O94" t="s">
         <v>303</v>
       </c>
-      <c r="P92" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q92" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
+      <c r="P94" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q94" t="b">
+        <v>0</v>
+      </c>
+      <c r="R94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>64</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B95" t="s">
         <v>413</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C95" t="s">
         <v>225</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D95" t="s">
         <v>202</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E95" t="s">
         <v>32</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F95" t="s">
         <v>226</v>
       </c>
-      <c r="G93">
+      <c r="G95">
         <v>180</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H95" t="s">
         <v>42</v>
       </c>
-      <c r="I93" t="s">
+      <c r="I95" t="s">
         <v>36</v>
       </c>
-      <c r="J93" t="s">
+      <c r="J95" t="s">
         <v>192</v>
       </c>
-      <c r="K93" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93">
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95">
         <v>6</v>
       </c>
-      <c r="M93" t="b">
-        <v>0</v>
-      </c>
-      <c r="N93" t="b">
-        <v>1</v>
-      </c>
-      <c r="O93" t="s">
+      <c r="M95" t="b">
+        <v>0</v>
+      </c>
+      <c r="N95" t="b">
+        <v>1</v>
+      </c>
+      <c r="O95" t="s">
         <v>304</v>
       </c>
-      <c r="P93" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q93" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
+      <c r="P95" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q95" t="b">
+        <v>0</v>
+      </c>
+      <c r="R95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>65</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B96" t="s">
         <v>414</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C96" t="s">
         <v>227</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D96" t="s">
         <v>228</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E96" t="s">
         <v>229</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F96" t="s">
         <v>230</v>
       </c>
-      <c r="G94">
+      <c r="G96">
         <v>237</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H96" t="s">
         <v>42</v>
       </c>
-      <c r="I94" t="s">
+      <c r="I96" t="s">
         <v>124</v>
       </c>
-      <c r="J94" t="s">
+      <c r="J96" t="s">
         <v>125</v>
       </c>
-      <c r="K94" t="s">
-        <v>23</v>
-      </c>
-      <c r="L94">
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96">
         <v>24</v>
       </c>
-      <c r="M94" t="b">
-        <v>0</v>
-      </c>
-      <c r="N94" t="b">
-        <v>1</v>
-      </c>
-      <c r="O94" t="s">
+      <c r="M96" t="b">
+        <v>0</v>
+      </c>
+      <c r="N96" t="b">
+        <v>1</v>
+      </c>
+      <c r="O96" t="s">
         <v>305</v>
       </c>
-      <c r="P94" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q94" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
+      <c r="P96" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q96" t="b">
+        <v>1</v>
+      </c>
+      <c r="R96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>66</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B97" t="s">
         <v>415</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C97" t="s">
         <v>44</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D97" t="s">
         <v>231</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E97" t="s">
         <v>229</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F97" t="s">
         <v>47</v>
       </c>
-      <c r="G95">
-        <v>1</v>
-      </c>
-      <c r="H95" t="s">
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97" t="s">
         <v>48</v>
       </c>
-      <c r="I95" t="s">
+      <c r="I97" t="s">
         <v>60</v>
       </c>
-      <c r="J95" t="s">
+      <c r="J97" t="s">
         <v>44</v>
       </c>
-      <c r="K95" t="s">
-        <v>23</v>
-      </c>
-      <c r="L95">
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97">
         <v>10</v>
       </c>
-      <c r="M95" t="b">
-        <v>0</v>
-      </c>
-      <c r="N95" t="b">
-        <v>1</v>
-      </c>
-      <c r="O95" t="s">
+      <c r="M97" t="b">
+        <v>0</v>
+      </c>
+      <c r="N97" t="b">
+        <v>1</v>
+      </c>
+      <c r="O97" t="s">
         <v>306</v>
       </c>
-      <c r="P95" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q95" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
+      <c r="P97" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q97" t="b">
+        <v>1</v>
+      </c>
+      <c r="R97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
         <v>67</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B98" t="s">
         <v>416</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C98" t="s">
         <v>31</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D98" t="s">
         <v>194</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E98" t="s">
         <v>232</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F98" t="s">
         <v>196</v>
       </c>
-      <c r="G96">
+      <c r="G98">
         <v>1.5</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H98" t="s">
         <v>28</v>
       </c>
-      <c r="I96" t="s">
+      <c r="I98" t="s">
         <v>36</v>
       </c>
-      <c r="J96" t="s">
+      <c r="J98" t="s">
         <v>37</v>
-      </c>
-      <c r="K96" t="s">
-        <v>23</v>
-      </c>
-      <c r="L96">
-        <v>6</v>
-      </c>
-      <c r="M96" t="b">
-        <v>0</v>
-      </c>
-      <c r="N96" t="b">
-        <v>1</v>
-      </c>
-      <c r="O96" t="s">
-        <v>307</v>
-      </c>
-      <c r="P96" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q96" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>68</v>
-      </c>
-      <c r="B97" t="s">
-        <v>417</v>
-      </c>
-      <c r="C97" t="s">
-        <v>186</v>
-      </c>
-      <c r="D97" t="s">
-        <v>202</v>
-      </c>
-      <c r="E97" t="s">
-        <v>233</v>
-      </c>
-      <c r="F97" t="s">
-        <v>204</v>
-      </c>
-      <c r="G97">
-        <v>250</v>
-      </c>
-      <c r="H97" t="s">
-        <v>35</v>
-      </c>
-      <c r="I97" t="s">
-        <v>191</v>
-      </c>
-      <c r="J97" t="s">
-        <v>192</v>
-      </c>
-      <c r="K97" t="s">
-        <v>23</v>
-      </c>
-      <c r="L97">
-        <v>6</v>
-      </c>
-      <c r="M97" t="b">
-        <v>0</v>
-      </c>
-      <c r="N97" t="b">
-        <v>1</v>
-      </c>
-      <c r="O97" t="s">
-        <v>308</v>
-      </c>
-      <c r="P97" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q97" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
-        <v>69</v>
-      </c>
-      <c r="B98" t="s">
-        <v>418</v>
-      </c>
-      <c r="C98" t="s">
-        <v>186</v>
-      </c>
-      <c r="D98" t="s">
-        <v>202</v>
-      </c>
-      <c r="E98" t="s">
-        <v>234</v>
-      </c>
-      <c r="F98" t="s">
-        <v>204</v>
-      </c>
-      <c r="G98">
-        <v>150</v>
-      </c>
-      <c r="H98" t="s">
-        <v>35</v>
-      </c>
-      <c r="I98" t="s">
-        <v>191</v>
-      </c>
-      <c r="J98" t="s">
-        <v>192</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
@@ -7277,7 +7602,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7285,13 +7610,16 @@
       <c r="Q98" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B99" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C99" t="s">
         <v>186</v>
@@ -7300,7 +7628,7 @@
         <v>202</v>
       </c>
       <c r="E99" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F99" t="s">
         <v>204</v>
@@ -7330,119 +7658,240 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
+        <v>308</v>
+      </c>
+      <c r="P99" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q99" t="b">
+        <v>0</v>
+      </c>
+      <c r="R99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>69</v>
+      </c>
+      <c r="B100" t="s">
+        <v>418</v>
+      </c>
+      <c r="C100" t="s">
+        <v>186</v>
+      </c>
+      <c r="D100" t="s">
+        <v>202</v>
+      </c>
+      <c r="E100" t="s">
+        <v>234</v>
+      </c>
+      <c r="F100" t="s">
+        <v>204</v>
+      </c>
+      <c r="G100">
+        <v>150</v>
+      </c>
+      <c r="H100" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100" t="s">
+        <v>191</v>
+      </c>
+      <c r="J100" t="s">
+        <v>192</v>
+      </c>
+      <c r="K100" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100">
+        <v>6</v>
+      </c>
+      <c r="M100" t="b">
+        <v>0</v>
+      </c>
+      <c r="N100" t="b">
+        <v>1</v>
+      </c>
+      <c r="O100" t="s">
+        <v>309</v>
+      </c>
+      <c r="P100" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q100" t="b">
+        <v>0</v>
+      </c>
+      <c r="R100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>70</v>
+      </c>
+      <c r="B101" t="s">
+        <v>419</v>
+      </c>
+      <c r="C101" t="s">
+        <v>186</v>
+      </c>
+      <c r="D101" t="s">
+        <v>202</v>
+      </c>
+      <c r="E101" t="s">
+        <v>234</v>
+      </c>
+      <c r="F101" t="s">
+        <v>204</v>
+      </c>
+      <c r="G101">
+        <v>250</v>
+      </c>
+      <c r="H101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101" t="s">
+        <v>191</v>
+      </c>
+      <c r="J101" t="s">
+        <v>192</v>
+      </c>
+      <c r="K101" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101">
+        <v>6</v>
+      </c>
+      <c r="M101" t="b">
+        <v>0</v>
+      </c>
+      <c r="N101" t="b">
+        <v>1</v>
+      </c>
+      <c r="O101" t="s">
         <v>310</v>
       </c>
-      <c r="P99" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q99" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
+      <c r="P101" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="b">
+        <v>0</v>
+      </c>
+      <c r="R101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
         <v>71</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B102" t="s">
         <v>420</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C102" t="s">
         <v>235</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D102" t="s">
         <v>236</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E102" t="s">
         <v>237</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F102" t="s">
         <v>238</v>
       </c>
-      <c r="G100">
+      <c r="G102">
         <v>6</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H102" t="s">
         <v>20</v>
       </c>
-      <c r="I100" t="s">
+      <c r="I102" t="s">
         <v>239</v>
       </c>
-      <c r="J100" t="s">
+      <c r="J102" t="s">
         <v>235</v>
       </c>
-      <c r="K100" t="s">
-        <v>23</v>
-      </c>
-      <c r="L100">
-        <v>1</v>
-      </c>
-      <c r="M100" t="b">
-        <v>0</v>
-      </c>
-      <c r="N100" t="b">
-        <v>1</v>
-      </c>
-      <c r="O100" t="s">
+      <c r="K102" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102" t="b">
+        <v>0</v>
+      </c>
+      <c r="N102" t="b">
+        <v>1</v>
+      </c>
+      <c r="O102" t="s">
         <v>311</v>
       </c>
-      <c r="P100" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
+      <c r="P102" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="b">
+        <v>1</v>
+      </c>
+      <c r="R102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
         <v>72</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B103" t="s">
         <v>421</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C103" t="s">
         <v>197</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D103" t="s">
         <v>198</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E103" t="s">
         <v>199</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F103" t="s">
         <v>240</v>
       </c>
-      <c r="G101">
+      <c r="G103">
         <v>4</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H103" t="s">
         <v>20</v>
       </c>
-      <c r="I101" t="s">
+      <c r="I103" t="s">
         <v>21</v>
       </c>
-      <c r="J101" t="s">
+      <c r="J103" t="s">
         <v>201</v>
       </c>
-      <c r="K101" t="s">
-        <v>23</v>
-      </c>
-      <c r="L101">
+      <c r="K103" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103">
         <v>10</v>
       </c>
-      <c r="M101" t="b">
-        <v>0</v>
-      </c>
-      <c r="N101" t="b">
-        <v>0</v>
-      </c>
-      <c r="O101" t="s">
+      <c r="M103" t="b">
+        <v>0</v>
+      </c>
+      <c r="N103" t="b">
+        <v>0</v>
+      </c>
+      <c r="O103" t="s">
         <v>312</v>
       </c>
-      <c r="P101" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q101" t="b">
-        <v>1</v>
+      <c r="P103" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q103" t="b">
+        <v>1</v>
+      </c>
+      <c r="R103" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CB77B9-B69D-414A-B2A1-EA770B247578}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B527551-4142-4A82-94DC-80696B91DEEA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="48" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="49" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="582">
   <si>
     <t>Codigo</t>
   </si>
@@ -1751,6 +1751,27 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7793719000049.png</t>
+  </si>
+  <si>
+    <t>7798009931960</t>
+  </si>
+  <si>
+    <t>Avena</t>
+  </si>
+  <si>
+    <t>arrollada</t>
+  </si>
+  <si>
+    <t>tradicional</t>
+  </si>
+  <si>
+    <t>Sytari</t>
+  </si>
+  <si>
+    <t>Cereales</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7798009931960.png</t>
   </si>
 </sst>
 </file>
@@ -2102,8 +2123,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96C5FAB5-8367-426D-882E-8914F6852FF8}">
-  <dimension ref="A1:R103"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCB9547-7481-4BE9-9711-AD814F12BF2E}">
+  <dimension ref="A1:R104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2739,7 +2760,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -3243,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -3299,7 +3320,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -3579,7 +3600,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -4083,7 +4104,7 @@
         <v>1</v>
       </c>
       <c r="R35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -4699,7 +4720,7 @@
         <v>1</v>
       </c>
       <c r="R46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -4979,7 +5000,7 @@
         <v>0</v>
       </c>
       <c r="R51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
@@ -5203,7 +5224,7 @@
         <v>1</v>
       </c>
       <c r="R55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
@@ -5320,40 +5341,40 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="B58" t="s">
-        <v>376</v>
+        <v>575</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>576</v>
       </c>
       <c r="D58" t="s">
-        <v>89</v>
+        <v>577</v>
       </c>
       <c r="E58" t="s">
-        <v>90</v>
+        <v>578</v>
       </c>
       <c r="F58" t="s">
-        <v>91</v>
+        <v>579</v>
       </c>
       <c r="G58">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H58" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I58" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s">
-        <v>92</v>
+        <v>580</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -5362,54 +5383,54 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>267</v>
+        <v>581</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C59" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D59" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E59" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F59" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G59">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H59" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I59" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J59" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -5418,7 +5439,7 @@
         <v>1</v>
       </c>
       <c r="O59" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -5427,46 +5448,46 @@
         <v>0</v>
       </c>
       <c r="R59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B60" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C60" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D60" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E60" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F60" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H60" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I60" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J60" t="s">
+        <v>66</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60">
         <v>30</v>
       </c>
-      <c r="K60" t="s">
-        <v>23</v>
-      </c>
-      <c r="L60">
-        <v>12</v>
-      </c>
       <c r="M60" t="b">
         <v>0</v>
       </c>
@@ -5474,69 +5495,69 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
+        <v>29</v>
+      </c>
+      <c r="B61" t="s">
+        <v>378</v>
+      </c>
+      <c r="C61" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" t="s">
+        <v>54</v>
+      </c>
+      <c r="E61" t="s">
+        <v>55</v>
+      </c>
+      <c r="F61" t="s">
+        <v>61</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>28</v>
+      </c>
+      <c r="I61" t="s">
+        <v>96</v>
+      </c>
+      <c r="J61" t="s">
         <v>30</v>
       </c>
-      <c r="B61" t="s">
-        <v>379</v>
-      </c>
-      <c r="C61" t="s">
-        <v>97</v>
-      </c>
-      <c r="D61" t="s">
-        <v>98</v>
-      </c>
-      <c r="E61" t="s">
-        <v>99</v>
-      </c>
-      <c r="F61" t="s">
-        <v>100</v>
-      </c>
-      <c r="G61">
-        <v>100</v>
-      </c>
-      <c r="H61" t="s">
-        <v>20</v>
-      </c>
-      <c r="I61" t="s">
-        <v>101</v>
-      </c>
-      <c r="J61" t="s">
-        <v>102</v>
-      </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
       </c>
       <c r="N61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
@@ -5544,49 +5565,49 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D62" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E62" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F62" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G62">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H62" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I62" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J62" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
       </c>
       <c r="N62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5600,22 +5621,22 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E63" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F63" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G63">
         <v>500</v>
@@ -5627,13 +5648,13 @@
         <v>107</v>
       </c>
       <c r="J63" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
       </c>
       <c r="L63">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -5642,7 +5663,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5651,45 +5672,45 @@
         <v>0</v>
       </c>
       <c r="R63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C64" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D64" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E64" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F64" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H64" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J64" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
@@ -5698,13 +5719,13 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
@@ -5712,40 +5733,40 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G65">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I65" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -5754,13 +5775,13 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
@@ -5768,40 +5789,40 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
+        <v>34</v>
+      </c>
+      <c r="B66" t="s">
+        <v>383</v>
+      </c>
+      <c r="C66" t="s">
+        <v>112</v>
+      </c>
+      <c r="D66" t="s">
+        <v>113</v>
+      </c>
+      <c r="E66" t="s">
+        <v>114</v>
+      </c>
+      <c r="F66" t="s">
+        <v>115</v>
+      </c>
+      <c r="G66">
+        <v>300</v>
+      </c>
+      <c r="H66" t="s">
         <v>35</v>
       </c>
-      <c r="B66" t="s">
-        <v>384</v>
-      </c>
-      <c r="C66" t="s">
-        <v>117</v>
-      </c>
-      <c r="D66" t="s">
-        <v>118</v>
-      </c>
-      <c r="E66" t="s">
-        <v>119</v>
-      </c>
-      <c r="F66" t="s">
-        <v>120</v>
-      </c>
-      <c r="G66">
-        <v>500</v>
-      </c>
-      <c r="H66" t="s">
-        <v>42</v>
-      </c>
       <c r="I66" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J66" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5810,7 +5831,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5824,40 +5845,40 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B67" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C67" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D67" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E67" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F67" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G67">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H67" t="s">
         <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5866,13 +5887,13 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
@@ -5880,40 +5901,40 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C68" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D68" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E68" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F68" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G68">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H68" t="s">
         <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J68" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -5922,13 +5943,13 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
@@ -5936,34 +5957,34 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C69" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D69" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E69" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F69" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G69">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H69" t="s">
         <v>42</v>
       </c>
       <c r="I69" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J69" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
@@ -5978,54 +5999,54 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B70" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C70" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D70" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E70" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F70" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G70">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H70" t="s">
         <v>42</v>
       </c>
       <c r="I70" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6034,7 +6055,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -6043,45 +6064,45 @@
         <v>1</v>
       </c>
       <c r="R70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C71" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D71" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E71" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F71" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H71" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J71" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -6090,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -6104,66 +6125,66 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B72" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C72" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E72" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F72" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G72">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I72" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C73" t="s">
         <v>138</v>
@@ -6172,10 +6193,10 @@
         <v>139</v>
       </c>
       <c r="E73" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F73" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G73">
         <v>1000</v>
@@ -6199,10 +6220,10 @@
         <v>1</v>
       </c>
       <c r="N73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -6216,22 +6237,22 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C74" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D74" t="s">
         <v>139</v>
       </c>
       <c r="E74" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F74" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G74">
         <v>1000</v>
@@ -6243,7 +6264,7 @@
         <v>142</v>
       </c>
       <c r="J74" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
@@ -6258,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -6272,55 +6293,55 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B75" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C75" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D75" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E75" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F75" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G75">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H75" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J75" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -6328,55 +6349,55 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B76" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C76" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D76" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E76" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F76" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I76" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J76" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K76" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L76">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
       </c>
       <c r="N76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -6384,55 +6405,55 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C77" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D77" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E77" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F77" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G77">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I77" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J77" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K77" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L77">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
@@ -6440,34 +6461,34 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B78" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C78" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D78" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E78" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F78" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G78">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H78" t="s">
         <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J78" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
@@ -6482,7 +6503,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6496,22 +6517,22 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B79" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C79" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E79" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F79" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G79">
         <v>500</v>
@@ -6523,7 +6544,7 @@
         <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
@@ -6538,7 +6559,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6552,25 +6573,25 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B80" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C80" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D80" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E80" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F80" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G80">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H80" t="s">
         <v>42</v>
@@ -6579,7 +6600,7 @@
         <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
@@ -6594,7 +6615,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6603,42 +6624,42 @@
         <v>1</v>
       </c>
       <c r="R80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
+        <v>49</v>
+      </c>
+      <c r="B81" t="s">
+        <v>398</v>
+      </c>
+      <c r="C81" t="s">
+        <v>175</v>
+      </c>
+      <c r="D81" t="s">
+        <v>176</v>
+      </c>
+      <c r="E81" t="s">
+        <v>177</v>
+      </c>
+      <c r="F81" t="s">
+        <v>178</v>
+      </c>
+      <c r="G81">
         <v>50</v>
       </c>
-      <c r="B81" t="s">
-        <v>399</v>
-      </c>
-      <c r="C81" t="s">
-        <v>180</v>
-      </c>
-      <c r="D81" t="s">
-        <v>181</v>
-      </c>
-      <c r="E81" t="s">
-        <v>182</v>
-      </c>
-      <c r="F81" t="s">
-        <v>183</v>
-      </c>
-      <c r="G81">
-        <v>12</v>
-      </c>
       <c r="H81" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K81" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L81">
         <v>12</v>
@@ -6650,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6664,40 +6685,40 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B82" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C82" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E82" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F82" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G82">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H82" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J82" t="s">
-        <v>556</v>
+        <v>184</v>
       </c>
       <c r="K82" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L82">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -6706,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6720,40 +6741,40 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C83" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D83" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E83" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F83" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G83">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H83" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I83" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J83" t="s">
-        <v>184</v>
+        <v>556</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -6762,7 +6783,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6776,40 +6797,40 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
+        <v>52</v>
+      </c>
+      <c r="B84" t="s">
+        <v>401</v>
+      </c>
+      <c r="C84" t="s">
+        <v>193</v>
+      </c>
+      <c r="D84" t="s">
+        <v>181</v>
+      </c>
+      <c r="E84" t="s">
+        <v>182</v>
+      </c>
+      <c r="F84" t="s">
+        <v>183</v>
+      </c>
+      <c r="G84">
+        <v>24</v>
+      </c>
+      <c r="H84" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" t="s">
         <v>53</v>
       </c>
-      <c r="B84" t="s">
-        <v>402</v>
-      </c>
-      <c r="C84" t="s">
-        <v>31</v>
-      </c>
-      <c r="D84" t="s">
-        <v>194</v>
-      </c>
-      <c r="E84" t="s">
-        <v>195</v>
-      </c>
-      <c r="F84" t="s">
-        <v>196</v>
-      </c>
-      <c r="G84">
-        <v>1.5</v>
-      </c>
-      <c r="H84" t="s">
-        <v>28</v>
-      </c>
-      <c r="I84" t="s">
-        <v>36</v>
-      </c>
       <c r="J84" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -6818,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6832,52 +6853,52 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B85" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C85" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D85" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E85" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F85" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G85">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H85" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I85" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J85" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
       <c r="N85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="b">
         <v>1</v>
@@ -6888,55 +6909,55 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B86" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C86" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D86" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E86" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F86" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G86">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H86" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
       <c r="N86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
@@ -6944,40 +6965,40 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B87" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C87" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D87" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E87" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F87" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G87">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H87" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J87" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -6986,7 +7007,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7000,19 +7021,19 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B88" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C88" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D88" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E88" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F88" t="s">
         <v>208</v>
@@ -7042,7 +7063,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7056,19 +7077,19 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B89" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C89" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D89" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E89" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F89" t="s">
         <v>208</v>
@@ -7089,7 +7110,7 @@
         <v>23</v>
       </c>
       <c r="L89">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7098,7 +7119,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7112,34 +7133,34 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B90" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C90" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D90" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E90" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F90" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H90" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I90" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J90" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
@@ -7154,13 +7175,13 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
@@ -7168,34 +7189,34 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B91" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D91" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E91" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G91">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I91" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J91" t="s">
-        <v>557</v>
+        <v>148</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
@@ -7210,7 +7231,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7219,54 +7240,54 @@
         <v>1</v>
       </c>
       <c r="R91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B92" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C92" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D92" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E92" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F92" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G92">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H92" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J92" t="s">
-        <v>217</v>
+        <v>557</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
       </c>
       <c r="N92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7280,22 +7301,22 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B93" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C93" t="s">
         <v>217</v>
       </c>
       <c r="D93" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E93" t="s">
         <v>219</v>
       </c>
       <c r="F93" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G93">
         <v>20</v>
@@ -7322,63 +7343,63 @@
         <v>0</v>
       </c>
       <c r="O93" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B94" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C94" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D94" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E94" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F94" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G94">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H94" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I94" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J94" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
       </c>
       <c r="N94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7387,39 +7408,39 @@
         <v>0</v>
       </c>
       <c r="R94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B95" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C95" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D95" t="s">
         <v>202</v>
       </c>
       <c r="E95" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F95" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G95">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H95" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I95" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J95" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
@@ -7434,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7448,40 +7469,40 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B96" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C96" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D96" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E96" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F96" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G96">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H96" t="s">
         <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J96" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -7490,13 +7511,13 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
@@ -7504,40 +7525,40 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B97" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C97" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D97" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E97" t="s">
         <v>229</v>
       </c>
       <c r="F97" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H97" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I97" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J97" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -7546,7 +7567,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7555,45 +7576,45 @@
         <v>1</v>
       </c>
       <c r="R97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B98" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C98" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E98" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F98" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G98">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H98" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I98" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J98" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
@@ -7602,13 +7623,13 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
@@ -7616,34 +7637,34 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B99" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C99" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D99" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E99" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F99" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G99">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H99" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I99" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J99" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
@@ -7658,7 +7679,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7672,10 +7693,10 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B100" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C100" t="s">
         <v>186</v>
@@ -7684,13 +7705,13 @@
         <v>202</v>
       </c>
       <c r="E100" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F100" t="s">
         <v>204</v>
       </c>
       <c r="G100">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H100" t="s">
         <v>35</v>
@@ -7714,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -7728,10 +7749,10 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B101" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C101" t="s">
         <v>186</v>
@@ -7746,7 +7767,7 @@
         <v>204</v>
       </c>
       <c r="G101">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H101" t="s">
         <v>35</v>
@@ -7770,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -7784,41 +7805,41 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B102" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C102" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D102" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E102" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F102" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G102">
+        <v>250</v>
+      </c>
+      <c r="H102" t="s">
+        <v>35</v>
+      </c>
+      <c r="I102" t="s">
+        <v>191</v>
+      </c>
+      <c r="J102" t="s">
+        <v>192</v>
+      </c>
+      <c r="K102" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102">
         <v>6</v>
       </c>
-      <c r="H102" t="s">
-        <v>20</v>
-      </c>
-      <c r="I102" t="s">
-        <v>239</v>
-      </c>
-      <c r="J102" t="s">
-        <v>235</v>
-      </c>
-      <c r="K102" t="s">
-        <v>23</v>
-      </c>
-      <c r="L102">
-        <v>1</v>
-      </c>
       <c r="M102" t="b">
         <v>0</v>
       </c>
@@ -7826,71 +7847,127 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C103" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D103" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E103" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G103">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H103" t="s">
         <v>20</v>
       </c>
       <c r="I103" t="s">
+        <v>239</v>
+      </c>
+      <c r="J103" t="s">
+        <v>235</v>
+      </c>
+      <c r="K103" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="M103" t="b">
+        <v>0</v>
+      </c>
+      <c r="N103" t="b">
+        <v>1</v>
+      </c>
+      <c r="O103" t="s">
+        <v>311</v>
+      </c>
+      <c r="P103" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="b">
+        <v>1</v>
+      </c>
+      <c r="R103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>72</v>
+      </c>
+      <c r="B104" t="s">
+        <v>421</v>
+      </c>
+      <c r="C104" t="s">
+        <v>197</v>
+      </c>
+      <c r="D104" t="s">
+        <v>198</v>
+      </c>
+      <c r="E104" t="s">
+        <v>199</v>
+      </c>
+      <c r="F104" t="s">
+        <v>240</v>
+      </c>
+      <c r="G104">
+        <v>4</v>
+      </c>
+      <c r="H104" t="s">
+        <v>20</v>
+      </c>
+      <c r="I104" t="s">
         <v>21</v>
       </c>
-      <c r="J103" t="s">
+      <c r="J104" t="s">
         <v>201</v>
       </c>
-      <c r="K103" t="s">
-        <v>23</v>
-      </c>
-      <c r="L103">
+      <c r="K104" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104">
         <v>10</v>
       </c>
-      <c r="M103" t="b">
-        <v>0</v>
-      </c>
-      <c r="N103" t="b">
-        <v>0</v>
-      </c>
-      <c r="O103" t="s">
+      <c r="M104" t="b">
+        <v>0</v>
+      </c>
+      <c r="N104" t="b">
+        <v>0</v>
+      </c>
+      <c r="O104" t="s">
         <v>312</v>
       </c>
-      <c r="P103" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q103" t="b">
-        <v>1</v>
-      </c>
-      <c r="R103" t="b">
+      <c r="P104" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="b">
+        <v>1</v>
+      </c>
+      <c r="R104" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B527551-4142-4A82-94DC-80696B91DEEA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCD54BD-8382-4E02-B225-6B7754A99ADC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="49" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="50" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="588">
   <si>
     <t>Codigo</t>
   </si>
@@ -1772,6 +1772,24 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7798009931960.png</t>
+  </si>
+  <si>
+    <t>7798140257431</t>
+  </si>
+  <si>
+    <t>sabor arándano-pomelo</t>
+  </si>
+  <si>
+    <t>7790360720122</t>
+  </si>
+  <si>
+    <t>carne</t>
+  </si>
+  <si>
+    <t>La Blanca</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790360720122.png</t>
   </si>
 </sst>
 </file>
@@ -2123,8 +2141,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCB9547-7481-4BE9-9711-AD814F12BF2E}">
-  <dimension ref="A1:R104"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2B4194-19FB-42CB-BED2-3FCCA181DF9F}">
+  <dimension ref="A1:R106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2368,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -2424,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -2480,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -2592,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -2816,7 +2834,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -2928,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -3037,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="Q16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="b">
         <v>1</v>
@@ -3152,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -3208,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -3488,7 +3506,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -3544,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -3712,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3768,7 +3786,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -3824,7 +3842,7 @@
         <v>1</v>
       </c>
       <c r="R30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -3880,7 +3898,7 @@
         <v>1</v>
       </c>
       <c r="R31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -3936,7 +3954,7 @@
         <v>1</v>
       </c>
       <c r="R32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -3992,7 +4010,7 @@
         <v>1</v>
       </c>
       <c r="R33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -4048,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -4160,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="R36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -4272,7 +4290,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -4384,7 +4402,7 @@
         <v>1</v>
       </c>
       <c r="R40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -4440,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -4496,7 +4514,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -4552,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -4664,7 +4682,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -4776,7 +4794,7 @@
         <v>1</v>
       </c>
       <c r="R47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
@@ -4832,7 +4850,7 @@
         <v>1</v>
       </c>
       <c r="R48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
@@ -4885,10 +4903,10 @@
         <v>1</v>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
@@ -4944,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="R50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
@@ -5056,7 +5074,7 @@
         <v>1</v>
       </c>
       <c r="R52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -5168,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="R54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
@@ -5397,25 +5415,25 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="B59" t="s">
-        <v>376</v>
+        <v>582</v>
       </c>
       <c r="C59" t="s">
-        <v>88</v>
+        <v>566</v>
       </c>
       <c r="D59" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="E59" t="s">
-        <v>90</v>
+        <v>583</v>
       </c>
       <c r="F59" t="s">
-        <v>91</v>
+        <v>569</v>
       </c>
       <c r="G59">
-        <v>500</v>
+        <v>630</v>
       </c>
       <c r="H59" t="s">
         <v>35</v>
@@ -5424,13 +5442,13 @@
         <v>36</v>
       </c>
       <c r="J59" t="s">
-        <v>92</v>
+        <v>570</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -5438,55 +5456,52 @@
       <c r="N59" t="b">
         <v>1</v>
       </c>
-      <c r="O59" t="s">
-        <v>267</v>
-      </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="B60" t="s">
-        <v>377</v>
+        <v>584</v>
       </c>
       <c r="C60" t="s">
-        <v>62</v>
+        <v>544</v>
       </c>
       <c r="D60" t="s">
-        <v>93</v>
+        <v>538</v>
       </c>
       <c r="E60" t="s">
-        <v>94</v>
+        <v>585</v>
       </c>
       <c r="F60" t="s">
-        <v>95</v>
+        <v>586</v>
       </c>
       <c r="G60">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>60</v>
+        <v>318</v>
       </c>
       <c r="J60" t="s">
-        <v>66</v>
+        <v>522</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
       </c>
       <c r="L60">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M60" t="b">
         <v>0</v>
@@ -5495,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>268</v>
+        <v>587</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="b">
         <v>1</v>
@@ -5509,40 +5524,40 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="D61" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="E61" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="F61" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H61" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="J61" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -5551,63 +5566,63 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C62" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="D62" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E62" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F62" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G62">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="H62" t="s">
         <v>20</v>
       </c>
       <c r="I62" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J62" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
       </c>
       <c r="N62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5621,34 +5636,34 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B63" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="D63" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="E63" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="F63" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="G63">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I63" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="J63" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
@@ -5663,13 +5678,13 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="b">
         <v>1</v>
@@ -5677,34 +5692,34 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B64" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C64" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E64" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F64" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="G64">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H64" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I64" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J64" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
@@ -5716,10 +5731,10 @@
         <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5728,45 +5743,45 @@
         <v>0</v>
       </c>
       <c r="R64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B65" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C65" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="D65" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E65" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="F65" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H65" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J65" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -5775,48 +5790,48 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
+        <v>32</v>
+      </c>
+      <c r="B66" t="s">
+        <v>381</v>
+      </c>
+      <c r="C66" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" t="s">
+        <v>109</v>
+      </c>
+      <c r="E66" t="s">
+        <v>110</v>
+      </c>
+      <c r="F66" t="s">
         <v>34</v>
       </c>
-      <c r="B66" t="s">
-        <v>383</v>
-      </c>
-      <c r="C66" t="s">
-        <v>112</v>
-      </c>
-      <c r="D66" t="s">
-        <v>113</v>
-      </c>
-      <c r="E66" t="s">
-        <v>114</v>
-      </c>
-      <c r="F66" t="s">
-        <v>115</v>
-      </c>
       <c r="G66">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H66" t="s">
         <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="J66" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
@@ -5831,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5840,45 +5855,45 @@
         <v>0</v>
       </c>
       <c r="R66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C67" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="E67" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="F67" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G67">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I67" t="s">
         <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5887,48 +5902,48 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
+        <v>34</v>
+      </c>
+      <c r="B68" t="s">
+        <v>383</v>
+      </c>
+      <c r="C68" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" t="s">
+        <v>115</v>
+      </c>
+      <c r="G68">
+        <v>300</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68" t="s">
         <v>36</v>
       </c>
-      <c r="B68" t="s">
-        <v>385</v>
-      </c>
-      <c r="C68" t="s">
-        <v>121</v>
-      </c>
-      <c r="D68" t="s">
-        <v>122</v>
-      </c>
-      <c r="E68" t="s">
-        <v>32</v>
-      </c>
-      <c r="F68" t="s">
-        <v>123</v>
-      </c>
-      <c r="G68">
-        <v>250</v>
-      </c>
-      <c r="H68" t="s">
-        <v>42</v>
-      </c>
-      <c r="I68" t="s">
-        <v>124</v>
-      </c>
       <c r="J68" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
@@ -5943,54 +5958,54 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B69" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C69" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D69" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E69" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F69" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="G69">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="H69" t="s">
         <v>42</v>
       </c>
       <c r="I69" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -5999,7 +6014,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -6008,45 +6023,45 @@
         <v>0</v>
       </c>
       <c r="R69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B70" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C70" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="E70" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="F70" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="G70">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H70" t="s">
         <v>42</v>
       </c>
       <c r="I70" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="J70" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6055,7 +6070,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -6069,40 +6084,40 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B71" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C71" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E71" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F71" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G71">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="H71" t="s">
         <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J71" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -6111,54 +6126,54 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B72" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C72" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D72" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E72" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="F72" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="H72" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I72" t="s">
         <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6167,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -6176,60 +6191,60 @@
         <v>1</v>
       </c>
       <c r="R72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B73" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C73" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D73" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E73" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="F73" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G73">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="H73" t="s">
         <v>42</v>
       </c>
       <c r="I73" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="J73" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -6237,55 +6252,55 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B74" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D74" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E74" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="F74" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="G74">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I74" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74" t="b">
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
@@ -6293,22 +6308,22 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C75" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D75" t="s">
         <v>139</v>
       </c>
       <c r="E75" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F75" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G75">
         <v>1000</v>
@@ -6320,7 +6335,7 @@
         <v>142</v>
       </c>
       <c r="J75" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
@@ -6332,10 +6347,10 @@
         <v>1</v>
       </c>
       <c r="N75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6349,55 +6364,55 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B76" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C76" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D76" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E76" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F76" t="s">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="G76">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H76" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J76" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -6405,49 +6420,49 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C77" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D77" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="E77" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F77" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="H77" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J77" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="K77" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L77">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6461,34 +6476,34 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B78" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C78" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D78" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="E78" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="F78" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G78">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H78" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I78" t="s">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="J78" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
@@ -6503,7 +6518,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6517,55 +6532,55 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C79" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D79" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E79" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="F79" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="G79">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I79" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="J79" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="K79" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L79">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -6573,34 +6588,34 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B80" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C80" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D80" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E80" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F80" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="G80">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H80" t="s">
         <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J80" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
@@ -6615,7 +6630,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6629,25 +6644,25 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B81" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C81" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="D81" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="E81" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="F81" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="G81">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H81" t="s">
         <v>42</v>
@@ -6656,7 +6671,7 @@
         <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
@@ -6671,7 +6686,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6680,42 +6695,42 @@
         <v>1</v>
       </c>
       <c r="R81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B82" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C82" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D82" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="E82" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F82" t="s">
-        <v>183</v>
+        <v>70</v>
       </c>
       <c r="G82">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H82" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J82" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="K82" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L82">
         <v>12</v>
@@ -6727,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6736,45 +6751,45 @@
         <v>1</v>
       </c>
       <c r="R82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B83" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D83" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E83" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F83" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G83">
-        <v>360</v>
+        <v>50</v>
       </c>
       <c r="H83" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>556</v>
+        <v>179</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -6783,7 +6798,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6792,18 +6807,18 @@
         <v>1</v>
       </c>
       <c r="R83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B84" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C84" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D84" t="s">
         <v>181</v>
@@ -6815,7 +6830,7 @@
         <v>183</v>
       </c>
       <c r="G84">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H84" t="s">
         <v>20</v>
@@ -6827,10 +6842,10 @@
         <v>184</v>
       </c>
       <c r="K84" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L84">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -6839,7 +6854,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6848,39 +6863,39 @@
         <v>1</v>
       </c>
       <c r="R84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B85" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="D85" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E85" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F85" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G85">
-        <v>1.5</v>
+        <v>360</v>
       </c>
       <c r="H85" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="I85" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
       <c r="J85" t="s">
-        <v>37</v>
+        <v>556</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
@@ -6895,7 +6910,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6904,101 +6919,101 @@
         <v>1</v>
       </c>
       <c r="R85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B86" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C86" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D86" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="E86" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="F86" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="G86">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H86" t="s">
         <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J86" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
       <c r="N86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="b">
         <v>1</v>
       </c>
       <c r="R86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B87" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C87" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E87" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F87" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G87">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="H87" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I87" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J87" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -7007,110 +7022,110 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B88" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C88" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D88" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E88" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F88" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G88">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="H88" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I88" t="s">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
       <c r="N88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B89" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C89" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E89" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="F89" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G89">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H89" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J89" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7119,7 +7134,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7128,15 +7143,15 @@
         <v>0</v>
       </c>
       <c r="R89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B90" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C90" t="s">
         <v>205</v>
@@ -7145,7 +7160,7 @@
         <v>206</v>
       </c>
       <c r="E90" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F90" t="s">
         <v>208</v>
@@ -7166,7 +7181,7 @@
         <v>23</v>
       </c>
       <c r="L90">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7175,7 +7190,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7184,45 +7199,45 @@
         <v>0</v>
       </c>
       <c r="R90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B91" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C91" t="s">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="D91" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F91" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H91" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J91" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7231,13 +7246,13 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
@@ -7245,34 +7260,34 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B92" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>205</v>
       </c>
       <c r="D92" t="s">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="E92" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F92" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G92">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="H92" t="s">
         <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="J92" t="s">
-        <v>557</v>
+        <v>66</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
@@ -7287,13 +7302,13 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
@@ -7301,49 +7316,49 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B93" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C93" t="s">
-        <v>217</v>
+        <v>145</v>
       </c>
       <c r="D93" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E93" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F93" t="s">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="G93">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H93" t="s">
         <v>20</v>
       </c>
       <c r="I93" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="J93" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
       </c>
       <c r="N93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7357,55 +7372,55 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B94" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C94" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D94" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="E94" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F94" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="G94">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H94" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J94" t="s">
-        <v>217</v>
+        <v>557</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
       </c>
       <c r="N94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
@@ -7413,105 +7428,105 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B95" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C95" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D95" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E95" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F95" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="G95">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H95" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I95" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J95" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
       </c>
       <c r="N95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B96" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C96" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D96" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E96" t="s">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="F96" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G96">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="H96" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I96" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="J96" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
       </c>
       <c r="N96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7520,45 +7535,45 @@
         <v>0</v>
       </c>
       <c r="R96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B97" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C97" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D97" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E97" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="F97" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="G97">
-        <v>237</v>
+        <v>60</v>
       </c>
       <c r="H97" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I97" t="s">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="J97" t="s">
-        <v>125</v>
+        <v>224</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -7567,13 +7582,13 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -7581,40 +7596,40 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B98" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C98" t="s">
-        <v>44</v>
+        <v>225</v>
       </c>
       <c r="D98" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="E98" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F98" t="s">
-        <v>47</v>
+        <v>226</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H98" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I98" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J98" t="s">
-        <v>44</v>
+        <v>192</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
@@ -7623,54 +7638,54 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B99" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C99" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="D99" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="E99" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F99" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="G99">
-        <v>1.5</v>
+        <v>237</v>
       </c>
       <c r="H99" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I99" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="J99" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
       </c>
       <c r="L99">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -7679,54 +7694,54 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B100" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C100" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="E100" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F100" t="s">
-        <v>204</v>
+        <v>47</v>
       </c>
       <c r="G100">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="H100" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I100" t="s">
-        <v>191</v>
+        <v>60</v>
       </c>
       <c r="J100" t="s">
-        <v>192</v>
+        <v>44</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
       </c>
       <c r="L100">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
@@ -7735,48 +7750,48 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B101" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C101" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E101" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F101" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G101">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="H101" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I101" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J101" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
@@ -7791,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -7800,15 +7815,15 @@
         <v>0</v>
       </c>
       <c r="R101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B102" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C102" t="s">
         <v>186</v>
@@ -7817,7 +7832,7 @@
         <v>202</v>
       </c>
       <c r="E102" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F102" t="s">
         <v>204</v>
@@ -7847,7 +7862,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -7856,46 +7871,46 @@
         <v>0</v>
       </c>
       <c r="R102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B103" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C103" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E103" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F103" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G103">
+        <v>150</v>
+      </c>
+      <c r="H103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I103" t="s">
+        <v>191</v>
+      </c>
+      <c r="J103" t="s">
+        <v>192</v>
+      </c>
+      <c r="K103" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103">
         <v>6</v>
       </c>
-      <c r="H103" t="s">
-        <v>20</v>
-      </c>
-      <c r="I103" t="s">
-        <v>239</v>
-      </c>
-      <c r="J103" t="s">
-        <v>235</v>
-      </c>
-      <c r="K103" t="s">
-        <v>23</v>
-      </c>
-      <c r="L103">
-        <v>1</v>
-      </c>
       <c r="M103" t="b">
         <v>0</v>
       </c>
@@ -7903,13 +7918,13 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="b">
         <v>1</v>
@@ -7917,58 +7932,170 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
+        <v>70</v>
+      </c>
+      <c r="B104" t="s">
+        <v>419</v>
+      </c>
+      <c r="C104" t="s">
+        <v>186</v>
+      </c>
+      <c r="D104" t="s">
+        <v>202</v>
+      </c>
+      <c r="E104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F104" t="s">
+        <v>204</v>
+      </c>
+      <c r="G104">
+        <v>250</v>
+      </c>
+      <c r="H104" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104" t="s">
+        <v>191</v>
+      </c>
+      <c r="J104" t="s">
+        <v>192</v>
+      </c>
+      <c r="K104" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104">
+        <v>6</v>
+      </c>
+      <c r="M104" t="b">
+        <v>0</v>
+      </c>
+      <c r="N104" t="b">
+        <v>1</v>
+      </c>
+      <c r="O104" t="s">
+        <v>310</v>
+      </c>
+      <c r="P104" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="b">
+        <v>0</v>
+      </c>
+      <c r="R104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>71</v>
+      </c>
+      <c r="B105" t="s">
+        <v>420</v>
+      </c>
+      <c r="C105" t="s">
+        <v>235</v>
+      </c>
+      <c r="D105" t="s">
+        <v>236</v>
+      </c>
+      <c r="E105" t="s">
+        <v>237</v>
+      </c>
+      <c r="F105" t="s">
+        <v>238</v>
+      </c>
+      <c r="G105">
+        <v>6</v>
+      </c>
+      <c r="H105" t="s">
+        <v>20</v>
+      </c>
+      <c r="I105" t="s">
+        <v>239</v>
+      </c>
+      <c r="J105" t="s">
+        <v>235</v>
+      </c>
+      <c r="K105" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105" t="b">
+        <v>0</v>
+      </c>
+      <c r="N105" t="b">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>311</v>
+      </c>
+      <c r="P105" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="b">
+        <v>1</v>
+      </c>
+      <c r="R105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
         <v>72</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B106" t="s">
         <v>421</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C106" t="s">
         <v>197</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D106" t="s">
         <v>198</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E106" t="s">
         <v>199</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F106" t="s">
         <v>240</v>
       </c>
-      <c r="G104">
+      <c r="G106">
         <v>4</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H106" t="s">
         <v>20</v>
       </c>
-      <c r="I104" t="s">
+      <c r="I106" t="s">
         <v>21</v>
       </c>
-      <c r="J104" t="s">
+      <c r="J106" t="s">
         <v>201</v>
       </c>
-      <c r="K104" t="s">
-        <v>23</v>
-      </c>
-      <c r="L104">
+      <c r="K106" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106">
         <v>10</v>
       </c>
-      <c r="M104" t="b">
-        <v>0</v>
-      </c>
-      <c r="N104" t="b">
-        <v>0</v>
-      </c>
-      <c r="O104" t="s">
+      <c r="M106" t="b">
+        <v>0</v>
+      </c>
+      <c r="N106" t="b">
+        <v>0</v>
+      </c>
+      <c r="O106" t="s">
         <v>312</v>
       </c>
-      <c r="P104" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q104" t="b">
-        <v>1</v>
-      </c>
-      <c r="R104" t="b">
-        <v>0</v>
+      <c r="P106" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="b">
+        <v>1</v>
+      </c>
+      <c r="R106" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCD54BD-8382-4E02-B225-6B7754A99ADC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0903D8CC-E002-4A60-AA07-E1DBD37DF4E4}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="50" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="51" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="593">
   <si>
     <t>Codigo</t>
   </si>
@@ -1790,6 +1790,21 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790360720122.png</t>
+  </si>
+  <si>
+    <t>7790360026606</t>
+  </si>
+  <si>
+    <t>Hamburguesas</t>
+  </si>
+  <si>
+    <t>clásicas</t>
+  </si>
+  <si>
+    <t>Congelados</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790360026606.png</t>
   </si>
 </sst>
 </file>
@@ -2141,8 +2156,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2B4194-19FB-42CB-BED2-3FCCA181DF9F}">
-  <dimension ref="A1:R106"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F4E4AA1-73C9-4AC1-8D1B-3E479520A2BF}">
+  <dimension ref="A1:R107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -5524,40 +5539,40 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="B61" t="s">
-        <v>376</v>
+        <v>588</v>
       </c>
       <c r="C61" t="s">
-        <v>88</v>
+        <v>589</v>
       </c>
       <c r="D61" t="s">
-        <v>89</v>
+        <v>545</v>
       </c>
       <c r="E61" t="s">
-        <v>90</v>
+        <v>590</v>
       </c>
       <c r="F61" t="s">
-        <v>91</v>
+        <v>521</v>
       </c>
       <c r="G61">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="H61" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I61" t="s">
-        <v>36</v>
+        <v>494</v>
       </c>
       <c r="J61" t="s">
-        <v>92</v>
+        <v>591</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -5566,54 +5581,54 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>267</v>
+        <v>592</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C62" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D62" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E62" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F62" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G62">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H62" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I62" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J62" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -5622,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5636,41 +5651,41 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B63" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D63" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E63" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F63" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H63" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I63" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J63" t="s">
+        <v>66</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63">
         <v>30</v>
       </c>
-      <c r="K63" t="s">
-        <v>23</v>
-      </c>
-      <c r="L63">
-        <v>12</v>
-      </c>
       <c r="M63" t="b">
         <v>0</v>
       </c>
@@ -5678,13 +5693,13 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="b">
         <v>1</v>
@@ -5692,55 +5707,55 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
+        <v>29</v>
+      </c>
+      <c r="B64" t="s">
+        <v>378</v>
+      </c>
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" t="s">
+        <v>54</v>
+      </c>
+      <c r="E64" t="s">
+        <v>55</v>
+      </c>
+      <c r="F64" t="s">
+        <v>61</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>28</v>
+      </c>
+      <c r="I64" t="s">
+        <v>96</v>
+      </c>
+      <c r="J64" t="s">
         <v>30</v>
       </c>
-      <c r="B64" t="s">
-        <v>379</v>
-      </c>
-      <c r="C64" t="s">
-        <v>97</v>
-      </c>
-      <c r="D64" t="s">
-        <v>98</v>
-      </c>
-      <c r="E64" t="s">
-        <v>99</v>
-      </c>
-      <c r="F64" t="s">
-        <v>100</v>
-      </c>
-      <c r="G64">
-        <v>100</v>
-      </c>
-      <c r="H64" t="s">
-        <v>20</v>
-      </c>
-      <c r="I64" t="s">
-        <v>101</v>
-      </c>
-      <c r="J64" t="s">
-        <v>102</v>
-      </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" t="b">
         <v>1</v>
@@ -5748,49 +5763,49 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D65" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E65" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F65" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G65">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H65" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I65" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J65" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
       </c>
       <c r="N65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5804,22 +5819,22 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E66" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F66" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G66">
         <v>500</v>
@@ -5831,13 +5846,13 @@
         <v>107</v>
       </c>
       <c r="J66" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5846,7 +5861,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5860,40 +5875,40 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D67" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E67" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F67" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H67" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I67" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J67" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5902,13 +5917,13 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="b">
         <v>1</v>
@@ -5916,40 +5931,40 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E68" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G68">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I68" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -5958,13 +5973,13 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="b">
         <v>1</v>
@@ -5972,40 +5987,40 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
+        <v>34</v>
+      </c>
+      <c r="B69" t="s">
+        <v>383</v>
+      </c>
+      <c r="C69" t="s">
+        <v>112</v>
+      </c>
+      <c r="D69" t="s">
+        <v>113</v>
+      </c>
+      <c r="E69" t="s">
+        <v>114</v>
+      </c>
+      <c r="F69" t="s">
+        <v>115</v>
+      </c>
+      <c r="G69">
+        <v>300</v>
+      </c>
+      <c r="H69" t="s">
         <v>35</v>
       </c>
-      <c r="B69" t="s">
-        <v>384</v>
-      </c>
-      <c r="C69" t="s">
-        <v>117</v>
-      </c>
-      <c r="D69" t="s">
-        <v>118</v>
-      </c>
-      <c r="E69" t="s">
-        <v>119</v>
-      </c>
-      <c r="F69" t="s">
-        <v>120</v>
-      </c>
-      <c r="G69">
-        <v>500</v>
-      </c>
-      <c r="H69" t="s">
-        <v>42</v>
-      </c>
       <c r="I69" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J69" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -6014,7 +6029,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -6028,40 +6043,40 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C70" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D70" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E70" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F70" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G70">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H70" t="s">
         <v>42</v>
       </c>
       <c r="I70" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6070,13 +6085,13 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
@@ -6084,40 +6099,40 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B71" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E71" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F71" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G71">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H71" t="s">
         <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J71" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -6126,13 +6141,13 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
@@ -6140,34 +6155,34 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B72" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C72" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E72" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F72" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G72">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H72" t="s">
         <v>42</v>
       </c>
       <c r="I72" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J72" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
@@ -6182,13 +6197,13 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="b">
         <v>1</v>
@@ -6196,40 +6211,40 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B73" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C73" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D73" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E73" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F73" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G73">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H73" t="s">
         <v>42</v>
       </c>
       <c r="I73" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -6238,7 +6253,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -6252,40 +6267,40 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B74" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C74" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D74" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E74" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F74" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H74" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J74" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -6294,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -6308,55 +6323,55 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B75" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C75" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E75" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F75" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G75">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I75" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -6364,10 +6379,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C76" t="s">
         <v>138</v>
@@ -6376,10 +6391,10 @@
         <v>139</v>
       </c>
       <c r="E76" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F76" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G76">
         <v>1000</v>
@@ -6403,10 +6418,10 @@
         <v>1</v>
       </c>
       <c r="N76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6420,22 +6435,22 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B77" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C77" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D77" t="s">
         <v>139</v>
       </c>
       <c r="E77" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F77" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G77">
         <v>1000</v>
@@ -6447,7 +6462,7 @@
         <v>142</v>
       </c>
       <c r="J77" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
@@ -6462,7 +6477,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6476,55 +6491,55 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B78" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C78" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D78" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E78" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F78" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G78">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H78" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J78" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
@@ -6532,55 +6547,55 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B79" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C79" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D79" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E79" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F79" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H79" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I79" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J79" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K79" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L79">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -6588,55 +6603,55 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C80" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E80" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F80" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G80">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I80" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J80" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K80" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L80">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="b">
         <v>1</v>
@@ -6644,34 +6659,34 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B81" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C81" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D81" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E81" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F81" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G81">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H81" t="s">
         <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J81" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
@@ -6686,7 +6701,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6700,22 +6715,22 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B82" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C82" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D82" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E82" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F82" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G82">
         <v>500</v>
@@ -6727,7 +6742,7 @@
         <v>21</v>
       </c>
       <c r="J82" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -6742,7 +6757,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6756,25 +6771,25 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B83" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C83" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D83" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E83" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F83" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G83">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H83" t="s">
         <v>42</v>
@@ -6783,7 +6798,7 @@
         <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
@@ -6798,7 +6813,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6812,37 +6827,37 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
+        <v>49</v>
+      </c>
+      <c r="B84" t="s">
+        <v>398</v>
+      </c>
+      <c r="C84" t="s">
+        <v>175</v>
+      </c>
+      <c r="D84" t="s">
+        <v>176</v>
+      </c>
+      <c r="E84" t="s">
+        <v>177</v>
+      </c>
+      <c r="F84" t="s">
+        <v>178</v>
+      </c>
+      <c r="G84">
         <v>50</v>
       </c>
-      <c r="B84" t="s">
-        <v>399</v>
-      </c>
-      <c r="C84" t="s">
-        <v>180</v>
-      </c>
-      <c r="D84" t="s">
-        <v>181</v>
-      </c>
-      <c r="E84" t="s">
-        <v>182</v>
-      </c>
-      <c r="F84" t="s">
-        <v>183</v>
-      </c>
-      <c r="G84">
-        <v>12</v>
-      </c>
       <c r="H84" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K84" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L84">
         <v>12</v>
@@ -6854,7 +6869,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6868,40 +6883,40 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B85" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C85" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D85" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E85" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F85" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G85">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H85" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I85" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J85" t="s">
-        <v>556</v>
+        <v>184</v>
       </c>
       <c r="K85" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L85">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
@@ -6910,7 +6925,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6924,40 +6939,40 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B86" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C86" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D86" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E86" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F86" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G86">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H86" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I86" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J86" t="s">
-        <v>184</v>
+        <v>556</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -6966,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -6980,40 +6995,40 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
+        <v>52</v>
+      </c>
+      <c r="B87" t="s">
+        <v>401</v>
+      </c>
+      <c r="C87" t="s">
+        <v>193</v>
+      </c>
+      <c r="D87" t="s">
+        <v>181</v>
+      </c>
+      <c r="E87" t="s">
+        <v>182</v>
+      </c>
+      <c r="F87" t="s">
+        <v>183</v>
+      </c>
+      <c r="G87">
+        <v>24</v>
+      </c>
+      <c r="H87" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" t="s">
         <v>53</v>
       </c>
-      <c r="B87" t="s">
-        <v>402</v>
-      </c>
-      <c r="C87" t="s">
-        <v>31</v>
-      </c>
-      <c r="D87" t="s">
-        <v>194</v>
-      </c>
-      <c r="E87" t="s">
-        <v>195</v>
-      </c>
-      <c r="F87" t="s">
-        <v>196</v>
-      </c>
-      <c r="G87">
-        <v>1.5</v>
-      </c>
-      <c r="H87" t="s">
-        <v>28</v>
-      </c>
-      <c r="I87" t="s">
-        <v>36</v>
-      </c>
       <c r="J87" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -7022,7 +7037,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7036,52 +7051,52 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B88" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C88" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D88" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E88" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F88" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G88">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H88" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J88" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
       <c r="N88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="b">
         <v>1</v>
@@ -7092,55 +7107,55 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B89" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C89" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D89" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E89" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F89" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G89">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H89" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I89" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J89" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
       <c r="N89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -7148,40 +7163,40 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C90" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D90" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E90" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F90" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G90">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H90" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I90" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J90" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7190,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7204,19 +7219,19 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B91" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C91" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D91" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E91" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F91" t="s">
         <v>208</v>
@@ -7246,7 +7261,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7260,19 +7275,19 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B92" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C92" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D92" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E92" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F92" t="s">
         <v>208</v>
@@ -7293,7 +7308,7 @@
         <v>23</v>
       </c>
       <c r="L92">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7302,7 +7317,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7316,34 +7331,34 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B93" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C93" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D93" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E93" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F93" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H93" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I93" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J93" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
@@ -7358,13 +7373,13 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -7372,34 +7387,34 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B94" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C94" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D94" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E94" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F94" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G94">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I94" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J94" t="s">
-        <v>557</v>
+        <v>148</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
@@ -7414,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7428,49 +7443,49 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B95" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C95" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D95" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E95" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F95" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G95">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H95" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I95" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J95" t="s">
-        <v>217</v>
+        <v>557</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
       </c>
       <c r="N95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7484,22 +7499,22 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B96" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C96" t="s">
         <v>217</v>
       </c>
       <c r="D96" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E96" t="s">
         <v>219</v>
       </c>
       <c r="F96" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G96">
         <v>20</v>
@@ -7526,13 +7541,13 @@
         <v>0</v>
       </c>
       <c r="O96" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="b">
         <v>1</v>
@@ -7540,49 +7555,49 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B97" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C97" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D97" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E97" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F97" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G97">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H97" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I97" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J97" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7596,34 +7611,34 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B98" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C98" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D98" t="s">
         <v>202</v>
       </c>
       <c r="E98" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F98" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G98">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H98" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J98" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
@@ -7638,7 +7653,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7652,40 +7667,40 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B99" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C99" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D99" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E99" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F99" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G99">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H99" t="s">
         <v>42</v>
       </c>
       <c r="I99" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J99" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
       </c>
       <c r="L99">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -7694,13 +7709,13 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
@@ -7708,40 +7723,40 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B100" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D100" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E100" t="s">
         <v>229</v>
       </c>
       <c r="F100" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H100" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I100" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J100" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
       </c>
       <c r="L100">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
@@ -7750,7 +7765,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -7764,40 +7779,40 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B101" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C101" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E101" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F101" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G101">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I101" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J101" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
       </c>
       <c r="L101">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
@@ -7806,13 +7821,13 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>
@@ -7820,34 +7835,34 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B102" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C102" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E102" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F102" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G102">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H102" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I102" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J102" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
@@ -7862,7 +7877,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -7876,10 +7891,10 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B103" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C103" t="s">
         <v>186</v>
@@ -7888,13 +7903,13 @@
         <v>202</v>
       </c>
       <c r="E103" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F103" t="s">
         <v>204</v>
       </c>
       <c r="G103">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H103" t="s">
         <v>35</v>
@@ -7918,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -7932,10 +7947,10 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B104" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C104" t="s">
         <v>186</v>
@@ -7950,7 +7965,7 @@
         <v>204</v>
       </c>
       <c r="G104">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H104" t="s">
         <v>35</v>
@@ -7974,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -7988,41 +8003,41 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B105" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C105" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D105" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E105" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F105" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G105">
+        <v>250</v>
+      </c>
+      <c r="H105" t="s">
+        <v>35</v>
+      </c>
+      <c r="I105" t="s">
+        <v>191</v>
+      </c>
+      <c r="J105" t="s">
+        <v>192</v>
+      </c>
+      <c r="K105" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105">
         <v>6</v>
       </c>
-      <c r="H105" t="s">
-        <v>20</v>
-      </c>
-      <c r="I105" t="s">
-        <v>239</v>
-      </c>
-      <c r="J105" t="s">
-        <v>235</v>
-      </c>
-      <c r="K105" t="s">
-        <v>23</v>
-      </c>
-      <c r="L105">
-        <v>1</v>
-      </c>
       <c r="M105" t="b">
         <v>0</v>
       </c>
@@ -8030,13 +8045,13 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" t="b">
         <v>1</v>
@@ -8044,57 +8059,113 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C106" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D106" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E106" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F106" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G106">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H106" t="s">
         <v>20</v>
       </c>
       <c r="I106" t="s">
+        <v>239</v>
+      </c>
+      <c r="J106" t="s">
+        <v>235</v>
+      </c>
+      <c r="K106" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106" t="b">
+        <v>0</v>
+      </c>
+      <c r="N106" t="b">
+        <v>1</v>
+      </c>
+      <c r="O106" t="s">
+        <v>311</v>
+      </c>
+      <c r="P106" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="b">
+        <v>1</v>
+      </c>
+      <c r="R106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>72</v>
+      </c>
+      <c r="B107" t="s">
+        <v>421</v>
+      </c>
+      <c r="C107" t="s">
+        <v>197</v>
+      </c>
+      <c r="D107" t="s">
+        <v>198</v>
+      </c>
+      <c r="E107" t="s">
+        <v>199</v>
+      </c>
+      <c r="F107" t="s">
+        <v>240</v>
+      </c>
+      <c r="G107">
+        <v>4</v>
+      </c>
+      <c r="H107" t="s">
+        <v>20</v>
+      </c>
+      <c r="I107" t="s">
         <v>21</v>
       </c>
-      <c r="J106" t="s">
+      <c r="J107" t="s">
         <v>201</v>
       </c>
-      <c r="K106" t="s">
-        <v>23</v>
-      </c>
-      <c r="L106">
+      <c r="K107" t="s">
+        <v>23</v>
+      </c>
+      <c r="L107">
         <v>10</v>
       </c>
-      <c r="M106" t="b">
-        <v>0</v>
-      </c>
-      <c r="N106" t="b">
-        <v>0</v>
-      </c>
-      <c r="O106" t="s">
+      <c r="M107" t="b">
+        <v>0</v>
+      </c>
+      <c r="N107" t="b">
+        <v>0</v>
+      </c>
+      <c r="O107" t="s">
         <v>312</v>
       </c>
-      <c r="P106" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q106" t="b">
-        <v>1</v>
-      </c>
-      <c r="R106" t="b">
+      <c r="P107" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q107" t="b">
+        <v>1</v>
+      </c>
+      <c r="R107" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0903D8CC-E002-4A60-AA07-E1DBD37DF4E4}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C99B5D-6188-468B-9030-AB2F1646EEC9}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="51" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="52" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="601">
   <si>
     <t>Codigo</t>
   </si>
@@ -1805,6 +1805,30 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790360026606.png</t>
+  </si>
+  <si>
+    <t>7897707505524</t>
+  </si>
+  <si>
+    <t>Bujía</t>
+  </si>
+  <si>
+    <t>modelo</t>
+  </si>
+  <si>
+    <t>d8ea</t>
+  </si>
+  <si>
+    <t>Ngk</t>
+  </si>
+  <si>
+    <t>Automotor</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7897707505524.png</t>
   </si>
 </sst>
 </file>
@@ -2156,8 +2180,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F4E4AA1-73C9-4AC1-8D1B-3E479520A2BF}">
-  <dimension ref="A1:R107"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABE5652-07DE-4016-BD11-29B99A26956F}">
+  <dimension ref="A1:R108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -5590,60 +5614,60 @@
         <v>1</v>
       </c>
       <c r="R61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="B62" t="s">
-        <v>376</v>
+        <v>593</v>
       </c>
       <c r="C62" t="s">
-        <v>88</v>
+        <v>594</v>
       </c>
       <c r="D62" t="s">
-        <v>89</v>
+        <v>595</v>
       </c>
       <c r="E62" t="s">
-        <v>90</v>
+        <v>596</v>
       </c>
       <c r="F62" t="s">
-        <v>91</v>
+        <v>597</v>
       </c>
       <c r="G62">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I62" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J62" t="s">
-        <v>92</v>
+        <v>598</v>
       </c>
       <c r="K62" t="s">
-        <v>23</v>
+        <v>599</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
       </c>
       <c r="N62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>267</v>
+        <v>600</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" t="b">
         <v>1</v>
@@ -5651,40 +5675,40 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C63" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D63" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E63" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F63" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G63">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H63" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I63" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J63" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
       </c>
       <c r="L63">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -5693,7 +5717,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5707,41 +5731,41 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B64" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D64" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E64" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F64" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I64" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J64" t="s">
+        <v>66</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64">
         <v>30</v>
       </c>
-      <c r="K64" t="s">
-        <v>23</v>
-      </c>
-      <c r="L64">
-        <v>12</v>
-      </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
@@ -5749,13 +5773,13 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="b">
         <v>1</v>
@@ -5763,55 +5787,55 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
+        <v>29</v>
+      </c>
+      <c r="B65" t="s">
+        <v>378</v>
+      </c>
+      <c r="C65" t="s">
+        <v>24</v>
+      </c>
+      <c r="D65" t="s">
+        <v>54</v>
+      </c>
+      <c r="E65" t="s">
+        <v>55</v>
+      </c>
+      <c r="F65" t="s">
+        <v>61</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>28</v>
+      </c>
+      <c r="I65" t="s">
+        <v>96</v>
+      </c>
+      <c r="J65" t="s">
         <v>30</v>
       </c>
-      <c r="B65" t="s">
-        <v>379</v>
-      </c>
-      <c r="C65" t="s">
-        <v>97</v>
-      </c>
-      <c r="D65" t="s">
-        <v>98</v>
-      </c>
-      <c r="E65" t="s">
-        <v>99</v>
-      </c>
-      <c r="F65" t="s">
-        <v>100</v>
-      </c>
-      <c r="G65">
-        <v>100</v>
-      </c>
-      <c r="H65" t="s">
-        <v>20</v>
-      </c>
-      <c r="I65" t="s">
-        <v>101</v>
-      </c>
-      <c r="J65" t="s">
-        <v>102</v>
-      </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
       </c>
       <c r="N65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="b">
         <v>1</v>
@@ -5819,49 +5843,49 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B66" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D66" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E66" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F66" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G66">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H66" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I66" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J66" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
       </c>
       <c r="N66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5875,22 +5899,22 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B67" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C67" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D67" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E67" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F67" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G67">
         <v>500</v>
@@ -5902,13 +5926,13 @@
         <v>107</v>
       </c>
       <c r="J67" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5917,7 +5941,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5931,40 +5955,40 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C68" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D68" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E68" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F68" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H68" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I68" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J68" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -5973,13 +5997,13 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="b">
         <v>1</v>
@@ -5987,40 +6011,40 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E69" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F69" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G69">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I69" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -6029,13 +6053,13 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="b">
         <v>1</v>
@@ -6043,40 +6067,40 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
+        <v>34</v>
+      </c>
+      <c r="B70" t="s">
+        <v>383</v>
+      </c>
+      <c r="C70" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" t="s">
+        <v>113</v>
+      </c>
+      <c r="E70" t="s">
+        <v>114</v>
+      </c>
+      <c r="F70" t="s">
+        <v>115</v>
+      </c>
+      <c r="G70">
+        <v>300</v>
+      </c>
+      <c r="H70" t="s">
         <v>35</v>
       </c>
-      <c r="B70" t="s">
-        <v>384</v>
-      </c>
-      <c r="C70" t="s">
-        <v>117</v>
-      </c>
-      <c r="D70" t="s">
-        <v>118</v>
-      </c>
-      <c r="E70" t="s">
-        <v>119</v>
-      </c>
-      <c r="F70" t="s">
-        <v>120</v>
-      </c>
-      <c r="G70">
-        <v>500</v>
-      </c>
-      <c r="H70" t="s">
-        <v>42</v>
-      </c>
       <c r="I70" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6085,7 +6109,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -6099,40 +6123,40 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B71" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D71" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E71" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F71" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G71">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H71" t="s">
         <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J71" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -6141,13 +6165,13 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
@@ -6155,40 +6179,40 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D72" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E72" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F72" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G72">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H72" t="s">
         <v>42</v>
       </c>
       <c r="I72" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J72" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6197,13 +6221,13 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="b">
         <v>1</v>
@@ -6211,34 +6235,34 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B73" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C73" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E73" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F73" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G73">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H73" t="s">
         <v>42</v>
       </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J73" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
@@ -6253,13 +6277,13 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -6267,40 +6291,40 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B74" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D74" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E74" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F74" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G74">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H74" t="s">
         <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -6309,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -6323,40 +6347,40 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B75" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C75" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D75" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E75" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F75" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H75" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J75" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -6365,7 +6389,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6379,55 +6403,55 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B76" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C76" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E76" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F76" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G76">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I76" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -6435,10 +6459,10 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C77" t="s">
         <v>138</v>
@@ -6447,10 +6471,10 @@
         <v>139</v>
       </c>
       <c r="E77" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F77" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G77">
         <v>1000</v>
@@ -6474,10 +6498,10 @@
         <v>1</v>
       </c>
       <c r="N77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6491,22 +6515,22 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C78" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D78" t="s">
         <v>139</v>
       </c>
       <c r="E78" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F78" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G78">
         <v>1000</v>
@@ -6518,7 +6542,7 @@
         <v>142</v>
       </c>
       <c r="J78" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
@@ -6533,7 +6557,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6547,55 +6571,55 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C79" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D79" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E79" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F79" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G79">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H79" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J79" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -6603,55 +6627,55 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C80" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D80" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E80" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F80" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H80" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J80" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K80" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L80">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="b">
         <v>1</v>
@@ -6659,55 +6683,55 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C81" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D81" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E81" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F81" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G81">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I81" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J81" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K81" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L81">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -6715,34 +6739,34 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B82" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C82" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D82" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E82" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F82" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G82">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H82" t="s">
         <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J82" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -6757,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6771,22 +6795,22 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B83" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C83" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D83" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E83" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F83" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G83">
         <v>500</v>
@@ -6798,7 +6822,7 @@
         <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
@@ -6813,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6827,25 +6851,25 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B84" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C84" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D84" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E84" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F84" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G84">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H84" t="s">
         <v>42</v>
@@ -6854,7 +6878,7 @@
         <v>21</v>
       </c>
       <c r="J84" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
@@ -6869,7 +6893,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6883,37 +6907,37 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
+        <v>49</v>
+      </c>
+      <c r="B85" t="s">
+        <v>398</v>
+      </c>
+      <c r="C85" t="s">
+        <v>175</v>
+      </c>
+      <c r="D85" t="s">
+        <v>176</v>
+      </c>
+      <c r="E85" t="s">
+        <v>177</v>
+      </c>
+      <c r="F85" t="s">
+        <v>178</v>
+      </c>
+      <c r="G85">
         <v>50</v>
       </c>
-      <c r="B85" t="s">
-        <v>399</v>
-      </c>
-      <c r="C85" t="s">
-        <v>180</v>
-      </c>
-      <c r="D85" t="s">
-        <v>181</v>
-      </c>
-      <c r="E85" t="s">
-        <v>182</v>
-      </c>
-      <c r="F85" t="s">
-        <v>183</v>
-      </c>
-      <c r="G85">
-        <v>12</v>
-      </c>
       <c r="H85" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J85" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K85" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L85">
         <v>12</v>
@@ -6925,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6939,40 +6963,40 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B86" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C86" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D86" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E86" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F86" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G86">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H86" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J86" t="s">
-        <v>556</v>
+        <v>184</v>
       </c>
       <c r="K86" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L86">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -6981,7 +7005,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -6995,40 +7019,40 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B87" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C87" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D87" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E87" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F87" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G87">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H87" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I87" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J87" t="s">
-        <v>184</v>
+        <v>556</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -7037,7 +7061,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7051,40 +7075,40 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
+        <v>52</v>
+      </c>
+      <c r="B88" t="s">
+        <v>401</v>
+      </c>
+      <c r="C88" t="s">
+        <v>193</v>
+      </c>
+      <c r="D88" t="s">
+        <v>181</v>
+      </c>
+      <c r="E88" t="s">
+        <v>182</v>
+      </c>
+      <c r="F88" t="s">
+        <v>183</v>
+      </c>
+      <c r="G88">
+        <v>24</v>
+      </c>
+      <c r="H88" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" t="s">
         <v>53</v>
       </c>
-      <c r="B88" t="s">
-        <v>402</v>
-      </c>
-      <c r="C88" t="s">
-        <v>31</v>
-      </c>
-      <c r="D88" t="s">
-        <v>194</v>
-      </c>
-      <c r="E88" t="s">
-        <v>195</v>
-      </c>
-      <c r="F88" t="s">
-        <v>196</v>
-      </c>
-      <c r="G88">
-        <v>1.5</v>
-      </c>
-      <c r="H88" t="s">
-        <v>28</v>
-      </c>
-      <c r="I88" t="s">
-        <v>36</v>
-      </c>
       <c r="J88" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -7093,7 +7117,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7107,52 +7131,52 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B89" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C89" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E89" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F89" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G89">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H89" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I89" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J89" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
       <c r="N89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="b">
         <v>1</v>
@@ -7163,55 +7187,55 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B90" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C90" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E90" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F90" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G90">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H90" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I90" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
       </c>
       <c r="N90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="b">
         <v>1</v>
@@ -7219,40 +7243,40 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B91" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C91" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D91" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E91" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F91" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G91">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H91" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I91" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J91" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7261,7 +7285,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7275,19 +7299,19 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B92" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C92" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D92" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E92" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F92" t="s">
         <v>208</v>
@@ -7317,7 +7341,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7331,19 +7355,19 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B93" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C93" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D93" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F93" t="s">
         <v>208</v>
@@ -7364,7 +7388,7 @@
         <v>23</v>
       </c>
       <c r="L93">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7373,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7387,34 +7411,34 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B94" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C94" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D94" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E94" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F94" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H94" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J94" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
@@ -7429,13 +7453,13 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
@@ -7443,34 +7467,34 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B95" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C95" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D95" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E95" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F95" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G95">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H95" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I95" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J95" t="s">
-        <v>557</v>
+        <v>148</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
@@ -7485,7 +7509,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7499,49 +7523,49 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B96" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C96" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D96" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E96" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F96" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G96">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H96" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J96" t="s">
-        <v>217</v>
+        <v>557</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
       </c>
       <c r="N96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7555,22 +7579,22 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B97" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C97" t="s">
         <v>217</v>
       </c>
       <c r="D97" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E97" t="s">
         <v>219</v>
       </c>
       <c r="F97" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G97">
         <v>20</v>
@@ -7597,13 +7621,13 @@
         <v>0</v>
       </c>
       <c r="O97" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -7611,49 +7635,49 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B98" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C98" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D98" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E98" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F98" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G98">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H98" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I98" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J98" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
       </c>
       <c r="N98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7667,34 +7691,34 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B99" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C99" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D99" t="s">
         <v>202</v>
       </c>
       <c r="E99" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G99">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H99" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I99" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J99" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
@@ -7709,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7723,40 +7747,40 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B100" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C100" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D100" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E100" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F100" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G100">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H100" t="s">
         <v>42</v>
       </c>
       <c r="I100" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J100" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
       </c>
       <c r="L100">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
@@ -7765,13 +7789,13 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="b">
         <v>1</v>
@@ -7779,40 +7803,40 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B101" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C101" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D101" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E101" t="s">
         <v>229</v>
       </c>
       <c r="F101" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H101" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I101" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J101" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
       </c>
       <c r="L101">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
@@ -7821,7 +7845,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -7835,40 +7859,40 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B102" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C102" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D102" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E102" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F102" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G102">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I102" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J102" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
       </c>
       <c r="L102">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
@@ -7877,13 +7901,13 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" t="b">
         <v>1</v>
@@ -7891,34 +7915,34 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B103" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C103" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D103" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E103" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F103" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G103">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H103" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I103" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J103" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
@@ -7933,7 +7957,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -7947,10 +7971,10 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B104" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C104" t="s">
         <v>186</v>
@@ -7959,13 +7983,13 @@
         <v>202</v>
       </c>
       <c r="E104" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F104" t="s">
         <v>204</v>
       </c>
       <c r="G104">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H104" t="s">
         <v>35</v>
@@ -7989,7 +8013,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8003,10 +8027,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B105" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C105" t="s">
         <v>186</v>
@@ -8021,7 +8045,7 @@
         <v>204</v>
       </c>
       <c r="G105">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H105" t="s">
         <v>35</v>
@@ -8045,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8059,41 +8083,41 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B106" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C106" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D106" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E106" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F106" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G106">
+        <v>250</v>
+      </c>
+      <c r="H106" t="s">
+        <v>35</v>
+      </c>
+      <c r="I106" t="s">
+        <v>191</v>
+      </c>
+      <c r="J106" t="s">
+        <v>192</v>
+      </c>
+      <c r="K106" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106">
         <v>6</v>
       </c>
-      <c r="H106" t="s">
-        <v>20</v>
-      </c>
-      <c r="I106" t="s">
-        <v>239</v>
-      </c>
-      <c r="J106" t="s">
-        <v>235</v>
-      </c>
-      <c r="K106" t="s">
-        <v>23</v>
-      </c>
-      <c r="L106">
-        <v>1</v>
-      </c>
       <c r="M106" t="b">
         <v>0</v>
       </c>
@@ -8101,13 +8125,13 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" t="b">
         <v>1</v>
@@ -8115,57 +8139,113 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C107" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D107" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E107" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F107" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G107">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H107" t="s">
         <v>20</v>
       </c>
       <c r="I107" t="s">
+        <v>239</v>
+      </c>
+      <c r="J107" t="s">
+        <v>235</v>
+      </c>
+      <c r="K107" t="s">
+        <v>23</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107" t="b">
+        <v>0</v>
+      </c>
+      <c r="N107" t="b">
+        <v>1</v>
+      </c>
+      <c r="O107" t="s">
+        <v>311</v>
+      </c>
+      <c r="P107" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="b">
+        <v>1</v>
+      </c>
+      <c r="R107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>72</v>
+      </c>
+      <c r="B108" t="s">
+        <v>421</v>
+      </c>
+      <c r="C108" t="s">
+        <v>197</v>
+      </c>
+      <c r="D108" t="s">
+        <v>198</v>
+      </c>
+      <c r="E108" t="s">
+        <v>199</v>
+      </c>
+      <c r="F108" t="s">
+        <v>240</v>
+      </c>
+      <c r="G108">
+        <v>4</v>
+      </c>
+      <c r="H108" t="s">
+        <v>20</v>
+      </c>
+      <c r="I108" t="s">
         <v>21</v>
       </c>
-      <c r="J107" t="s">
+      <c r="J108" t="s">
         <v>201</v>
       </c>
-      <c r="K107" t="s">
-        <v>23</v>
-      </c>
-      <c r="L107">
+      <c r="K108" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108">
         <v>10</v>
       </c>
-      <c r="M107" t="b">
-        <v>0</v>
-      </c>
-      <c r="N107" t="b">
-        <v>0</v>
-      </c>
-      <c r="O107" t="s">
+      <c r="M108" t="b">
+        <v>0</v>
+      </c>
+      <c r="N108" t="b">
+        <v>0</v>
+      </c>
+      <c r="O108" t="s">
         <v>312</v>
       </c>
-      <c r="P107" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q107" t="b">
-        <v>1</v>
-      </c>
-      <c r="R107" t="b">
+      <c r="P108" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q108" t="b">
+        <v>1</v>
+      </c>
+      <c r="R108" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C99B5D-6188-468B-9030-AB2F1646EEC9}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6A0997-0C0D-4FE3-9E38-1AA16FF73135}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="52" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="53" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="606">
   <si>
     <t>Codigo</t>
   </si>
@@ -1829,6 +1829,21 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7897707505524.png</t>
+  </si>
+  <si>
+    <t>7509546692241</t>
+  </si>
+  <si>
+    <t>con flúor y calcio</t>
+  </si>
+  <si>
+    <t>doble acción</t>
+  </si>
+  <si>
+    <t>Odol</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7509546692241.png</t>
   </si>
 </sst>
 </file>
@@ -2180,8 +2195,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABE5652-07DE-4016-BD11-29B99A26956F}">
-  <dimension ref="A1:R108"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B05AE63-B6F2-4384-806E-D6ABA8443F38}">
+  <dimension ref="A1:R109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -5675,34 +5690,34 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>376</v>
+        <v>601</v>
       </c>
       <c r="C63" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D63" t="s">
-        <v>89</v>
+        <v>602</v>
       </c>
       <c r="E63" t="s">
-        <v>90</v>
+        <v>603</v>
       </c>
       <c r="F63" t="s">
-        <v>91</v>
+        <v>604</v>
       </c>
       <c r="G63">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="H63" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J63" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
@@ -5717,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>267</v>
+        <v>605</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5726,45 +5741,45 @@
         <v>0</v>
       </c>
       <c r="R63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C64" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D64" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E64" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F64" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G64">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H64" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J64" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
@@ -5773,7 +5788,7 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5787,41 +5802,41 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B65" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C65" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D65" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E65" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F65" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H65" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I65" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J65" t="s">
+        <v>66</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65">
         <v>30</v>
       </c>
-      <c r="K65" t="s">
-        <v>23</v>
-      </c>
-      <c r="L65">
-        <v>12</v>
-      </c>
       <c r="M65" t="b">
         <v>0</v>
       </c>
@@ -5829,13 +5844,13 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="b">
         <v>1</v>
@@ -5843,55 +5858,55 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
+        <v>29</v>
+      </c>
+      <c r="B66" t="s">
+        <v>378</v>
+      </c>
+      <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" t="s">
+        <v>54</v>
+      </c>
+      <c r="E66" t="s">
+        <v>55</v>
+      </c>
+      <c r="F66" t="s">
+        <v>61</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>28</v>
+      </c>
+      <c r="I66" t="s">
+        <v>96</v>
+      </c>
+      <c r="J66" t="s">
         <v>30</v>
       </c>
-      <c r="B66" t="s">
-        <v>379</v>
-      </c>
-      <c r="C66" t="s">
-        <v>97</v>
-      </c>
-      <c r="D66" t="s">
-        <v>98</v>
-      </c>
-      <c r="E66" t="s">
-        <v>99</v>
-      </c>
-      <c r="F66" t="s">
-        <v>100</v>
-      </c>
-      <c r="G66">
-        <v>100</v>
-      </c>
-      <c r="H66" t="s">
-        <v>20</v>
-      </c>
-      <c r="I66" t="s">
-        <v>101</v>
-      </c>
-      <c r="J66" t="s">
-        <v>102</v>
-      </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
       </c>
       <c r="N66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="b">
         <v>1</v>
@@ -5899,49 +5914,49 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D67" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E67" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F67" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G67">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H67" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I67" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J67" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
       </c>
       <c r="N67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -5955,22 +5970,22 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B68" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C68" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E68" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F68" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G68">
         <v>500</v>
@@ -5982,13 +5997,13 @@
         <v>107</v>
       </c>
       <c r="J68" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -5997,7 +6012,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -6011,40 +6026,40 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B69" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C69" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E69" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F69" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H69" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I69" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J69" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -6053,13 +6068,13 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="b">
         <v>1</v>
@@ -6067,40 +6082,40 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G70">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I70" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6109,13 +6124,13 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
@@ -6123,40 +6138,40 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
+        <v>34</v>
+      </c>
+      <c r="B71" t="s">
+        <v>383</v>
+      </c>
+      <c r="C71" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E71" t="s">
+        <v>114</v>
+      </c>
+      <c r="F71" t="s">
+        <v>115</v>
+      </c>
+      <c r="G71">
+        <v>300</v>
+      </c>
+      <c r="H71" t="s">
         <v>35</v>
       </c>
-      <c r="B71" t="s">
-        <v>384</v>
-      </c>
-      <c r="C71" t="s">
-        <v>117</v>
-      </c>
-      <c r="D71" t="s">
-        <v>118</v>
-      </c>
-      <c r="E71" t="s">
-        <v>119</v>
-      </c>
-      <c r="F71" t="s">
-        <v>120</v>
-      </c>
-      <c r="G71">
-        <v>500</v>
-      </c>
-      <c r="H71" t="s">
-        <v>42</v>
-      </c>
       <c r="I71" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J71" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -6165,7 +6180,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -6179,40 +6194,40 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B72" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C72" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D72" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E72" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F72" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G72">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H72" t="s">
         <v>42</v>
       </c>
       <c r="I72" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6221,13 +6236,13 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="b">
         <v>1</v>
@@ -6235,40 +6250,40 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B73" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D73" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E73" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F73" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G73">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H73" t="s">
         <v>42</v>
       </c>
       <c r="I73" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J73" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -6277,13 +6292,13 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -6291,34 +6306,34 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C74" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E74" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F74" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G74">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H74" t="s">
         <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J74" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
@@ -6333,13 +6348,13 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
@@ -6347,40 +6362,40 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B75" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C75" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E75" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F75" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G75">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H75" t="s">
         <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -6389,7 +6404,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6403,40 +6418,40 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B76" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D76" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E76" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F76" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H76" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J76" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6445,7 +6460,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6459,55 +6474,55 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B77" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C77" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E77" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F77" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G77">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I77" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
@@ -6515,10 +6530,10 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C78" t="s">
         <v>138</v>
@@ -6527,10 +6542,10 @@
         <v>139</v>
       </c>
       <c r="E78" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F78" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G78">
         <v>1000</v>
@@ -6554,10 +6569,10 @@
         <v>1</v>
       </c>
       <c r="N78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6571,22 +6586,22 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B79" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C79" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D79" t="s">
         <v>139</v>
       </c>
       <c r="E79" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F79" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G79">
         <v>1000</v>
@@ -6598,7 +6613,7 @@
         <v>142</v>
       </c>
       <c r="J79" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
@@ -6613,7 +6628,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6627,55 +6642,55 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B80" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C80" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D80" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E80" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F80" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G80">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H80" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J80" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="b">
         <v>1</v>
@@ -6683,55 +6698,55 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C81" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D81" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E81" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F81" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H81" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I81" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J81" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K81" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L81">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -6739,55 +6754,55 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C82" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E82" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F82" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G82">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J82" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K82" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L82">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
       <c r="N82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
@@ -6795,34 +6810,34 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B83" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C83" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D83" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E83" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F83" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G83">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H83" t="s">
         <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J83" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
@@ -6837,7 +6852,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6851,22 +6866,22 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B84" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C84" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D84" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E84" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F84" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G84">
         <v>500</v>
@@ -6878,7 +6893,7 @@
         <v>21</v>
       </c>
       <c r="J84" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
@@ -6893,7 +6908,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6907,25 +6922,25 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B85" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C85" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D85" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E85" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F85" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G85">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H85" t="s">
         <v>42</v>
@@ -6934,7 +6949,7 @@
         <v>21</v>
       </c>
       <c r="J85" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
@@ -6949,7 +6964,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6963,37 +6978,37 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
+        <v>49</v>
+      </c>
+      <c r="B86" t="s">
+        <v>398</v>
+      </c>
+      <c r="C86" t="s">
+        <v>175</v>
+      </c>
+      <c r="D86" t="s">
+        <v>176</v>
+      </c>
+      <c r="E86" t="s">
+        <v>177</v>
+      </c>
+      <c r="F86" t="s">
+        <v>178</v>
+      </c>
+      <c r="G86">
         <v>50</v>
       </c>
-      <c r="B86" t="s">
-        <v>399</v>
-      </c>
-      <c r="C86" t="s">
-        <v>180</v>
-      </c>
-      <c r="D86" t="s">
-        <v>181</v>
-      </c>
-      <c r="E86" t="s">
-        <v>182</v>
-      </c>
-      <c r="F86" t="s">
-        <v>183</v>
-      </c>
-      <c r="G86">
-        <v>12</v>
-      </c>
       <c r="H86" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I86" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K86" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L86">
         <v>12</v>
@@ -7005,7 +7020,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -7019,40 +7034,40 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B87" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C87" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D87" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E87" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F87" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G87">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H87" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I87" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J87" t="s">
-        <v>556</v>
+        <v>184</v>
       </c>
       <c r="K87" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L87">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
@@ -7061,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7075,40 +7090,40 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B88" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C88" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D88" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E88" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F88" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G88">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H88" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I88" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J88" t="s">
-        <v>184</v>
+        <v>556</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -7117,7 +7132,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7131,40 +7146,40 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
+        <v>52</v>
+      </c>
+      <c r="B89" t="s">
+        <v>401</v>
+      </c>
+      <c r="C89" t="s">
+        <v>193</v>
+      </c>
+      <c r="D89" t="s">
+        <v>181</v>
+      </c>
+      <c r="E89" t="s">
+        <v>182</v>
+      </c>
+      <c r="F89" t="s">
+        <v>183</v>
+      </c>
+      <c r="G89">
+        <v>24</v>
+      </c>
+      <c r="H89" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" t="s">
         <v>53</v>
       </c>
-      <c r="B89" t="s">
-        <v>402</v>
-      </c>
-      <c r="C89" t="s">
-        <v>31</v>
-      </c>
-      <c r="D89" t="s">
-        <v>194</v>
-      </c>
-      <c r="E89" t="s">
-        <v>195</v>
-      </c>
-      <c r="F89" t="s">
-        <v>196</v>
-      </c>
-      <c r="G89">
-        <v>1.5</v>
-      </c>
-      <c r="H89" t="s">
-        <v>28</v>
-      </c>
-      <c r="I89" t="s">
-        <v>36</v>
-      </c>
       <c r="J89" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7173,7 +7188,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7187,52 +7202,52 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B90" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C90" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D90" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E90" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F90" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G90">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H90" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I90" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J90" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
       </c>
       <c r="N90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="b">
         <v>1</v>
@@ -7243,55 +7258,55 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B91" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C91" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D91" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E91" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F91" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G91">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H91" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I91" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J91" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
       </c>
       <c r="N91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" t="b">
         <v>1</v>
@@ -7299,40 +7314,40 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B92" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C92" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D92" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E92" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F92" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G92">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H92" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I92" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J92" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7341,7 +7356,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7355,19 +7370,19 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B93" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C93" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D93" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E93" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F93" t="s">
         <v>208</v>
@@ -7397,7 +7412,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7411,19 +7426,19 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B94" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C94" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D94" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E94" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F94" t="s">
         <v>208</v>
@@ -7444,7 +7459,7 @@
         <v>23</v>
       </c>
       <c r="L94">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7453,7 +7468,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7467,34 +7482,34 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B95" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C95" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D95" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E95" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F95" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H95" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I95" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J95" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
@@ -7509,13 +7524,13 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
@@ -7523,34 +7538,34 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B96" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C96" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D96" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E96" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F96" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G96">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H96" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I96" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J96" t="s">
-        <v>557</v>
+        <v>148</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
@@ -7565,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7579,49 +7594,49 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B97" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C97" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D97" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E97" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F97" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G97">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H97" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I97" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J97" t="s">
-        <v>217</v>
+        <v>557</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7635,22 +7650,22 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B98" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C98" t="s">
         <v>217</v>
       </c>
       <c r="D98" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E98" t="s">
         <v>219</v>
       </c>
       <c r="F98" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G98">
         <v>20</v>
@@ -7677,13 +7692,13 @@
         <v>0</v>
       </c>
       <c r="O98" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
@@ -7691,49 +7706,49 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B99" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C99" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D99" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E99" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F99" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G99">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H99" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I99" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J99" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
       </c>
       <c r="L99">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
       </c>
       <c r="N99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7747,34 +7762,34 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B100" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C100" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D100" t="s">
         <v>202</v>
       </c>
       <c r="E100" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G100">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H100" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I100" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J100" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
@@ -7789,7 +7804,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -7803,40 +7818,40 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B101" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C101" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D101" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E101" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F101" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G101">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H101" t="s">
         <v>42</v>
       </c>
       <c r="I101" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J101" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
       </c>
       <c r="L101">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
@@ -7845,13 +7860,13 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>
@@ -7859,40 +7874,40 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B102" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C102" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D102" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E102" t="s">
         <v>229</v>
       </c>
       <c r="F102" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H102" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I102" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J102" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
       </c>
       <c r="L102">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
@@ -7901,7 +7916,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -7915,40 +7930,40 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B103" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C103" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E103" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F103" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G103">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I103" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J103" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
       </c>
       <c r="L103">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M103" t="b">
         <v>0</v>
@@ -7957,13 +7972,13 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R103" t="b">
         <v>1</v>
@@ -7971,34 +7986,34 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B104" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C104" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D104" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E104" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F104" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G104">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H104" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I104" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J104" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
@@ -8013,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8027,10 +8042,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B105" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C105" t="s">
         <v>186</v>
@@ -8039,13 +8054,13 @@
         <v>202</v>
       </c>
       <c r="E105" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F105" t="s">
         <v>204</v>
       </c>
       <c r="G105">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H105" t="s">
         <v>35</v>
@@ -8069,7 +8084,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8083,10 +8098,10 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B106" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C106" t="s">
         <v>186</v>
@@ -8101,7 +8116,7 @@
         <v>204</v>
       </c>
       <c r="G106">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H106" t="s">
         <v>35</v>
@@ -8125,7 +8140,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8139,41 +8154,41 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B107" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C107" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D107" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E107" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F107" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G107">
+        <v>250</v>
+      </c>
+      <c r="H107" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107" t="s">
+        <v>191</v>
+      </c>
+      <c r="J107" t="s">
+        <v>192</v>
+      </c>
+      <c r="K107" t="s">
+        <v>23</v>
+      </c>
+      <c r="L107">
         <v>6</v>
       </c>
-      <c r="H107" t="s">
-        <v>20</v>
-      </c>
-      <c r="I107" t="s">
-        <v>239</v>
-      </c>
-      <c r="J107" t="s">
-        <v>235</v>
-      </c>
-      <c r="K107" t="s">
-        <v>23</v>
-      </c>
-      <c r="L107">
-        <v>1</v>
-      </c>
       <c r="M107" t="b">
         <v>0</v>
       </c>
@@ -8181,13 +8196,13 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R107" t="b">
         <v>1</v>
@@ -8195,57 +8210,113 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C108" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D108" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E108" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F108" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G108">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H108" t="s">
         <v>20</v>
       </c>
       <c r="I108" t="s">
+        <v>239</v>
+      </c>
+      <c r="J108" t="s">
+        <v>235</v>
+      </c>
+      <c r="K108" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108" t="b">
+        <v>0</v>
+      </c>
+      <c r="N108" t="b">
+        <v>1</v>
+      </c>
+      <c r="O108" t="s">
+        <v>311</v>
+      </c>
+      <c r="P108" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="b">
+        <v>1</v>
+      </c>
+      <c r="R108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>72</v>
+      </c>
+      <c r="B109" t="s">
+        <v>421</v>
+      </c>
+      <c r="C109" t="s">
+        <v>197</v>
+      </c>
+      <c r="D109" t="s">
+        <v>198</v>
+      </c>
+      <c r="E109" t="s">
+        <v>199</v>
+      </c>
+      <c r="F109" t="s">
+        <v>240</v>
+      </c>
+      <c r="G109">
+        <v>4</v>
+      </c>
+      <c r="H109" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109" t="s">
         <v>21</v>
       </c>
-      <c r="J108" t="s">
+      <c r="J109" t="s">
         <v>201</v>
       </c>
-      <c r="K108" t="s">
-        <v>23</v>
-      </c>
-      <c r="L108">
+      <c r="K109" t="s">
+        <v>23</v>
+      </c>
+      <c r="L109">
         <v>10</v>
       </c>
-      <c r="M108" t="b">
-        <v>0</v>
-      </c>
-      <c r="N108" t="b">
-        <v>0</v>
-      </c>
-      <c r="O108" t="s">
+      <c r="M109" t="b">
+        <v>0</v>
+      </c>
+      <c r="N109" t="b">
+        <v>0</v>
+      </c>
+      <c r="O109" t="s">
         <v>312</v>
       </c>
-      <c r="P108" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q108" t="b">
-        <v>1</v>
-      </c>
-      <c r="R108" t="b">
+      <c r="P109" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="b">
+        <v>1</v>
+      </c>
+      <c r="R109" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6A0997-0C0D-4FE3-9E38-1AA16FF73135}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE936E8E-6F4D-40D6-9707-58BCDBDF93EA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="53" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="54" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="610">
   <si>
     <t>Codigo</t>
   </si>
@@ -1844,6 +1844,18 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7509546692241.png</t>
+  </si>
+  <si>
+    <t>7798130889178</t>
+  </si>
+  <si>
+    <t>blanco</t>
+  </si>
+  <si>
+    <t>Vual</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7798130889178.png</t>
   </si>
 </sst>
 </file>
@@ -2195,8 +2207,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B05AE63-B6F2-4384-806E-D6ABA8443F38}">
-  <dimension ref="A1:R109"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B5AAFA-D598-4591-A407-9E2412E6D8E1}">
+  <dimension ref="A1:R110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -5738,104 +5750,104 @@
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="B64" t="s">
-        <v>376</v>
+        <v>606</v>
       </c>
       <c r="C64" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="D64" t="s">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="E64" t="s">
-        <v>90</v>
+        <v>607</v>
       </c>
       <c r="F64" t="s">
-        <v>91</v>
+        <v>608</v>
       </c>
       <c r="G64">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I64" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>92</v>
+        <v>245</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>267</v>
+        <v>609</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C65" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E65" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F65" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G65">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H65" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J65" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -5844,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5858,41 +5870,41 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B66" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D66" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E66" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F66" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H66" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I66" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J66" t="s">
+        <v>66</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66">
         <v>30</v>
       </c>
-      <c r="K66" t="s">
-        <v>23</v>
-      </c>
-      <c r="L66">
-        <v>12</v>
-      </c>
       <c r="M66" t="b">
         <v>0</v>
       </c>
@@ -5900,13 +5912,13 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="b">
         <v>1</v>
@@ -5914,55 +5926,55 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
+        <v>29</v>
+      </c>
+      <c r="B67" t="s">
+        <v>378</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" t="s">
+        <v>54</v>
+      </c>
+      <c r="E67" t="s">
+        <v>55</v>
+      </c>
+      <c r="F67" t="s">
+        <v>61</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>28</v>
+      </c>
+      <c r="I67" t="s">
+        <v>96</v>
+      </c>
+      <c r="J67" t="s">
         <v>30</v>
       </c>
-      <c r="B67" t="s">
-        <v>379</v>
-      </c>
-      <c r="C67" t="s">
-        <v>97</v>
-      </c>
-      <c r="D67" t="s">
-        <v>98</v>
-      </c>
-      <c r="E67" t="s">
-        <v>99</v>
-      </c>
-      <c r="F67" t="s">
-        <v>100</v>
-      </c>
-      <c r="G67">
-        <v>100</v>
-      </c>
-      <c r="H67" t="s">
-        <v>20</v>
-      </c>
-      <c r="I67" t="s">
-        <v>101</v>
-      </c>
-      <c r="J67" t="s">
-        <v>102</v>
-      </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
       </c>
       <c r="N67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="b">
         <v>1</v>
@@ -5970,49 +5982,49 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D68" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E68" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F68" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G68">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H68" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I68" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J68" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
       </c>
       <c r="N68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -6026,22 +6038,22 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B69" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E69" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F69" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G69">
         <v>500</v>
@@ -6053,13 +6065,13 @@
         <v>107</v>
       </c>
       <c r="J69" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -6068,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -6082,40 +6094,40 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C70" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D70" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E70" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F70" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H70" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J70" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6124,13 +6136,13 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
@@ -6138,40 +6150,40 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B71" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E71" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G71">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I71" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J71" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -6180,13 +6192,13 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
@@ -6194,40 +6206,40 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
+        <v>34</v>
+      </c>
+      <c r="B72" t="s">
+        <v>383</v>
+      </c>
+      <c r="C72" t="s">
+        <v>112</v>
+      </c>
+      <c r="D72" t="s">
+        <v>113</v>
+      </c>
+      <c r="E72" t="s">
+        <v>114</v>
+      </c>
+      <c r="F72" t="s">
+        <v>115</v>
+      </c>
+      <c r="G72">
+        <v>300</v>
+      </c>
+      <c r="H72" t="s">
         <v>35</v>
       </c>
-      <c r="B72" t="s">
-        <v>384</v>
-      </c>
-      <c r="C72" t="s">
-        <v>117</v>
-      </c>
-      <c r="D72" t="s">
-        <v>118</v>
-      </c>
-      <c r="E72" t="s">
-        <v>119</v>
-      </c>
-      <c r="F72" t="s">
-        <v>120</v>
-      </c>
-      <c r="G72">
-        <v>500</v>
-      </c>
-      <c r="H72" t="s">
-        <v>42</v>
-      </c>
       <c r="I72" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6236,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -6250,40 +6262,40 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B73" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C73" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D73" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E73" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F73" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G73">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H73" t="s">
         <v>42</v>
       </c>
       <c r="I73" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -6292,13 +6304,13 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -6306,40 +6318,40 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B74" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C74" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D74" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E74" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F74" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G74">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H74" t="s">
         <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J74" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -6348,13 +6360,13 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
@@ -6362,34 +6374,34 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B75" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E75" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F75" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G75">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H75" t="s">
         <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J75" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
@@ -6404,13 +6416,13 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -6418,40 +6430,40 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C76" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D76" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E76" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F76" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G76">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H76" t="s">
         <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6460,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6474,40 +6486,40 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B77" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D77" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E77" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F77" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H77" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J77" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6516,7 +6528,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6530,55 +6542,55 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B78" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C78" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E78" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F78" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G78">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I78" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
@@ -6586,10 +6598,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C79" t="s">
         <v>138</v>
@@ -6598,10 +6610,10 @@
         <v>139</v>
       </c>
       <c r="E79" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F79" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G79">
         <v>1000</v>
@@ -6625,10 +6637,10 @@
         <v>1</v>
       </c>
       <c r="N79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6642,22 +6654,22 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B80" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C80" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D80" t="s">
         <v>139</v>
       </c>
       <c r="E80" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F80" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G80">
         <v>1000</v>
@@ -6669,7 +6681,7 @@
         <v>142</v>
       </c>
       <c r="J80" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
@@ -6684,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6698,55 +6710,55 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B81" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C81" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D81" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E81" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F81" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G81">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H81" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J81" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" t="b">
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -6754,55 +6766,55 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C82" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D82" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E82" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F82" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H82" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J82" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K82" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L82">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
       <c r="N82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
@@ -6810,55 +6822,55 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C83" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D83" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E83" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F83" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G83">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H83" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I83" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J83" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K83" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L83">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
       </c>
       <c r="N83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -6866,34 +6878,34 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B84" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C84" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D84" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E84" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F84" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G84">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H84" t="s">
         <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J84" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
@@ -6908,7 +6920,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6922,22 +6934,22 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B85" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C85" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D85" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E85" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F85" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G85">
         <v>500</v>
@@ -6949,7 +6961,7 @@
         <v>21</v>
       </c>
       <c r="J85" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
@@ -6964,7 +6976,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6978,25 +6990,25 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B86" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C86" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D86" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E86" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F86" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G86">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H86" t="s">
         <v>42</v>
@@ -7005,7 +7017,7 @@
         <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
@@ -7020,7 +7032,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -7034,37 +7046,37 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
+        <v>49</v>
+      </c>
+      <c r="B87" t="s">
+        <v>398</v>
+      </c>
+      <c r="C87" t="s">
+        <v>175</v>
+      </c>
+      <c r="D87" t="s">
+        <v>176</v>
+      </c>
+      <c r="E87" t="s">
+        <v>177</v>
+      </c>
+      <c r="F87" t="s">
+        <v>178</v>
+      </c>
+      <c r="G87">
         <v>50</v>
       </c>
-      <c r="B87" t="s">
-        <v>399</v>
-      </c>
-      <c r="C87" t="s">
-        <v>180</v>
-      </c>
-      <c r="D87" t="s">
-        <v>181</v>
-      </c>
-      <c r="E87" t="s">
-        <v>182</v>
-      </c>
-      <c r="F87" t="s">
-        <v>183</v>
-      </c>
-      <c r="G87">
-        <v>12</v>
-      </c>
       <c r="H87" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I87" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J87" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K87" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L87">
         <v>12</v>
@@ -7076,7 +7088,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7090,40 +7102,40 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B88" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C88" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D88" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E88" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F88" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G88">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H88" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I88" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J88" t="s">
-        <v>556</v>
+        <v>184</v>
       </c>
       <c r="K88" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L88">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
@@ -7132,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7146,40 +7158,40 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B89" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C89" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D89" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E89" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F89" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G89">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H89" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I89" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J89" t="s">
-        <v>184</v>
+        <v>556</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
       </c>
       <c r="L89">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7188,7 +7200,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7202,40 +7214,40 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
+        <v>52</v>
+      </c>
+      <c r="B90" t="s">
+        <v>401</v>
+      </c>
+      <c r="C90" t="s">
+        <v>193</v>
+      </c>
+      <c r="D90" t="s">
+        <v>181</v>
+      </c>
+      <c r="E90" t="s">
+        <v>182</v>
+      </c>
+      <c r="F90" t="s">
+        <v>183</v>
+      </c>
+      <c r="G90">
+        <v>24</v>
+      </c>
+      <c r="H90" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" t="s">
         <v>53</v>
       </c>
-      <c r="B90" t="s">
-        <v>402</v>
-      </c>
-      <c r="C90" t="s">
-        <v>31</v>
-      </c>
-      <c r="D90" t="s">
-        <v>194</v>
-      </c>
-      <c r="E90" t="s">
-        <v>195</v>
-      </c>
-      <c r="F90" t="s">
-        <v>196</v>
-      </c>
-      <c r="G90">
-        <v>1.5</v>
-      </c>
-      <c r="H90" t="s">
-        <v>28</v>
-      </c>
-      <c r="I90" t="s">
-        <v>36</v>
-      </c>
       <c r="J90" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7244,7 +7256,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7258,52 +7270,52 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B91" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C91" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E91" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F91" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G91">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H91" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J91" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
       </c>
       <c r="N91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="b">
         <v>1</v>
@@ -7314,55 +7326,55 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B92" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C92" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D92" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E92" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F92" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G92">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H92" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I92" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
       </c>
       <c r="N92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="b">
         <v>1</v>
@@ -7370,40 +7382,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B93" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C93" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D93" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E93" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F93" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G93">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H93" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I93" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J93" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7412,7 +7424,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7426,19 +7438,19 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B94" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C94" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D94" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E94" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F94" t="s">
         <v>208</v>
@@ -7468,7 +7480,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7482,19 +7494,19 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B95" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C95" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D95" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E95" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F95" t="s">
         <v>208</v>
@@ -7515,7 +7527,7 @@
         <v>23</v>
       </c>
       <c r="L95">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7524,7 +7536,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7538,34 +7550,34 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B96" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C96" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D96" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E96" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F96" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H96" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J96" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
@@ -7580,13 +7592,13 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" t="b">
         <v>1</v>
@@ -7594,34 +7606,34 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B97" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C97" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D97" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E97" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F97" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G97">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H97" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I97" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J97" t="s">
-        <v>557</v>
+        <v>148</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
@@ -7636,7 +7648,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7650,49 +7662,49 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B98" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C98" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D98" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E98" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F98" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G98">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H98" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I98" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J98" t="s">
-        <v>217</v>
+        <v>557</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
       </c>
       <c r="N98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7706,22 +7718,22 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B99" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C99" t="s">
         <v>217</v>
       </c>
       <c r="D99" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E99" t="s">
         <v>219</v>
       </c>
       <c r="F99" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G99">
         <v>20</v>
@@ -7748,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="O99" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
@@ -7762,49 +7774,49 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B100" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C100" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D100" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E100" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F100" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G100">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H100" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I100" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J100" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
       </c>
       <c r="L100">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
       </c>
       <c r="N100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -7818,34 +7830,34 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B101" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C101" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D101" t="s">
         <v>202</v>
       </c>
       <c r="E101" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G101">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H101" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I101" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J101" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
@@ -7860,7 +7872,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -7874,40 +7886,40 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B102" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C102" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D102" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E102" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F102" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G102">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H102" t="s">
         <v>42</v>
       </c>
       <c r="I102" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J102" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
       </c>
       <c r="L102">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
@@ -7916,13 +7928,13 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R102" t="b">
         <v>1</v>
@@ -7930,40 +7942,40 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B103" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C103" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D103" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E103" t="s">
         <v>229</v>
       </c>
       <c r="F103" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H103" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I103" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J103" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
       </c>
       <c r="L103">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M103" t="b">
         <v>0</v>
@@ -7972,7 +7984,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -7986,40 +7998,40 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B104" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C104" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D104" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E104" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F104" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G104">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I104" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J104" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
       </c>
       <c r="L104">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
@@ -8028,13 +8040,13 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
       </c>
       <c r="Q104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="b">
         <v>1</v>
@@ -8042,34 +8054,34 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B105" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C105" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E105" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F105" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G105">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H105" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I105" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J105" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
@@ -8084,7 +8096,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8098,10 +8110,10 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B106" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C106" t="s">
         <v>186</v>
@@ -8110,13 +8122,13 @@
         <v>202</v>
       </c>
       <c r="E106" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F106" t="s">
         <v>204</v>
       </c>
       <c r="G106">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H106" t="s">
         <v>35</v>
@@ -8140,7 +8152,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8154,10 +8166,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B107" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C107" t="s">
         <v>186</v>
@@ -8172,7 +8184,7 @@
         <v>204</v>
       </c>
       <c r="G107">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H107" t="s">
         <v>35</v>
@@ -8196,7 +8208,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8210,41 +8222,41 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B108" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C108" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D108" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E108" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F108" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G108">
+        <v>250</v>
+      </c>
+      <c r="H108" t="s">
+        <v>35</v>
+      </c>
+      <c r="I108" t="s">
+        <v>191</v>
+      </c>
+      <c r="J108" t="s">
+        <v>192</v>
+      </c>
+      <c r="K108" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108">
         <v>6</v>
       </c>
-      <c r="H108" t="s">
-        <v>20</v>
-      </c>
-      <c r="I108" t="s">
-        <v>239</v>
-      </c>
-      <c r="J108" t="s">
-        <v>235</v>
-      </c>
-      <c r="K108" t="s">
-        <v>23</v>
-      </c>
-      <c r="L108">
-        <v>1</v>
-      </c>
       <c r="M108" t="b">
         <v>0</v>
       </c>
@@ -8252,13 +8264,13 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R108" t="b">
         <v>1</v>
@@ -8266,57 +8278,113 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C109" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D109" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E109" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F109" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G109">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H109" t="s">
         <v>20</v>
       </c>
       <c r="I109" t="s">
+        <v>239</v>
+      </c>
+      <c r="J109" t="s">
+        <v>235</v>
+      </c>
+      <c r="K109" t="s">
+        <v>23</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="M109" t="b">
+        <v>0</v>
+      </c>
+      <c r="N109" t="b">
+        <v>1</v>
+      </c>
+      <c r="O109" t="s">
+        <v>311</v>
+      </c>
+      <c r="P109" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="b">
+        <v>1</v>
+      </c>
+      <c r="R109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>72</v>
+      </c>
+      <c r="B110" t="s">
+        <v>421</v>
+      </c>
+      <c r="C110" t="s">
+        <v>197</v>
+      </c>
+      <c r="D110" t="s">
+        <v>198</v>
+      </c>
+      <c r="E110" t="s">
+        <v>199</v>
+      </c>
+      <c r="F110" t="s">
+        <v>240</v>
+      </c>
+      <c r="G110">
+        <v>4</v>
+      </c>
+      <c r="H110" t="s">
+        <v>20</v>
+      </c>
+      <c r="I110" t="s">
         <v>21</v>
       </c>
-      <c r="J109" t="s">
+      <c r="J110" t="s">
         <v>201</v>
       </c>
-      <c r="K109" t="s">
-        <v>23</v>
-      </c>
-      <c r="L109">
+      <c r="K110" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110">
         <v>10</v>
       </c>
-      <c r="M109" t="b">
-        <v>0</v>
-      </c>
-      <c r="N109" t="b">
-        <v>0</v>
-      </c>
-      <c r="O109" t="s">
+      <c r="M110" t="b">
+        <v>0</v>
+      </c>
+      <c r="N110" t="b">
+        <v>0</v>
+      </c>
+      <c r="O110" t="s">
         <v>312</v>
       </c>
-      <c r="P109" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q109" t="b">
-        <v>1</v>
-      </c>
-      <c r="R109" t="b">
+      <c r="P110" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q110" t="b">
+        <v>1</v>
+      </c>
+      <c r="R110" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE936E8E-6F4D-40D6-9707-58BCDBDF93EA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14232DA-5E39-4B1C-AF78-782C7E2072D5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="54" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="55" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="617">
   <si>
     <t>Codigo</t>
   </si>
@@ -1856,6 +1856,27 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7798130889178.png</t>
+  </si>
+  <si>
+    <t>7794440000104</t>
+  </si>
+  <si>
+    <t>Esponja</t>
+  </si>
+  <si>
+    <t>abrasiva y antigrasa</t>
+  </si>
+  <si>
+    <t>fuerte</t>
+  </si>
+  <si>
+    <t>Virulana</t>
+  </si>
+  <si>
+    <t>Esponjas</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7794440000104.png</t>
   </si>
 </sst>
 </file>
@@ -2207,8 +2228,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B5AAFA-D598-4591-A407-9E2412E6D8E1}">
-  <dimension ref="A1:R110"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B6D2FD9-D109-4F39-AAE1-6278920779DE}">
+  <dimension ref="A1:R111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -5814,96 +5835,96 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="B65" t="s">
-        <v>376</v>
+        <v>610</v>
       </c>
       <c r="C65" t="s">
-        <v>88</v>
+        <v>611</v>
       </c>
       <c r="D65" t="s">
-        <v>89</v>
+        <v>612</v>
       </c>
       <c r="E65" t="s">
-        <v>90</v>
+        <v>613</v>
       </c>
       <c r="F65" t="s">
-        <v>91</v>
+        <v>614</v>
       </c>
       <c r="G65">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I65" t="s">
-        <v>36</v>
+        <v>494</v>
       </c>
       <c r="J65" t="s">
-        <v>92</v>
+        <v>615</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
       </c>
       <c r="N65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>267</v>
+        <v>616</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C66" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E66" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F66" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G66">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H66" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J66" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5912,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5926,41 +5947,41 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B67" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C67" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D67" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F67" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H67" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I67" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J67" t="s">
+        <v>66</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67">
         <v>30</v>
       </c>
-      <c r="K67" t="s">
-        <v>23</v>
-      </c>
-      <c r="L67">
-        <v>12</v>
-      </c>
       <c r="M67" t="b">
         <v>0</v>
       </c>
@@ -5968,13 +5989,13 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="b">
         <v>1</v>
@@ -5982,55 +6003,55 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
+        <v>29</v>
+      </c>
+      <c r="B68" t="s">
+        <v>378</v>
+      </c>
+      <c r="C68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" t="s">
+        <v>55</v>
+      </c>
+      <c r="F68" t="s">
+        <v>61</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68" t="s">
+        <v>28</v>
+      </c>
+      <c r="I68" t="s">
+        <v>96</v>
+      </c>
+      <c r="J68" t="s">
         <v>30</v>
       </c>
-      <c r="B68" t="s">
-        <v>379</v>
-      </c>
-      <c r="C68" t="s">
-        <v>97</v>
-      </c>
-      <c r="D68" t="s">
-        <v>98</v>
-      </c>
-      <c r="E68" t="s">
-        <v>99</v>
-      </c>
-      <c r="F68" t="s">
-        <v>100</v>
-      </c>
-      <c r="G68">
-        <v>100</v>
-      </c>
-      <c r="H68" t="s">
-        <v>20</v>
-      </c>
-      <c r="I68" t="s">
-        <v>101</v>
-      </c>
-      <c r="J68" t="s">
-        <v>102</v>
-      </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
       </c>
       <c r="N68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="b">
         <v>1</v>
@@ -6038,49 +6059,49 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D69" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E69" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F69" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G69">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H69" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J69" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
       </c>
       <c r="N69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -6094,22 +6115,22 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C70" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E70" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F70" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G70">
         <v>500</v>
@@ -6121,13 +6142,13 @@
         <v>107</v>
       </c>
       <c r="J70" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6136,7 +6157,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -6150,40 +6171,40 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C71" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D71" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E71" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F71" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H71" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J71" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -6192,13 +6213,13 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
@@ -6206,40 +6227,40 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C72" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E72" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F72" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G72">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I72" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J72" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6248,13 +6269,13 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="b">
         <v>1</v>
@@ -6262,40 +6283,40 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
+        <v>34</v>
+      </c>
+      <c r="B73" t="s">
+        <v>383</v>
+      </c>
+      <c r="C73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" t="s">
+        <v>114</v>
+      </c>
+      <c r="F73" t="s">
+        <v>115</v>
+      </c>
+      <c r="G73">
+        <v>300</v>
+      </c>
+      <c r="H73" t="s">
         <v>35</v>
       </c>
-      <c r="B73" t="s">
-        <v>384</v>
-      </c>
-      <c r="C73" t="s">
-        <v>117</v>
-      </c>
-      <c r="D73" t="s">
-        <v>118</v>
-      </c>
-      <c r="E73" t="s">
-        <v>119</v>
-      </c>
-      <c r="F73" t="s">
-        <v>120</v>
-      </c>
-      <c r="G73">
-        <v>500</v>
-      </c>
-      <c r="H73" t="s">
-        <v>42</v>
-      </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -6304,7 +6325,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -6318,40 +6339,40 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B74" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C74" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D74" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E74" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F74" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G74">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H74" t="s">
         <v>42</v>
       </c>
       <c r="I74" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -6360,13 +6381,13 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
@@ -6374,40 +6395,40 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B75" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D75" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E75" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F75" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G75">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H75" t="s">
         <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J75" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -6416,13 +6437,13 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -6430,34 +6451,34 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D76" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E76" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F76" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G76">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H76" t="s">
         <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J76" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
@@ -6472,13 +6493,13 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -6486,40 +6507,40 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B77" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C77" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D77" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E77" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F77" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G77">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H77" t="s">
         <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6528,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6542,40 +6563,40 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C78" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D78" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E78" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F78" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H78" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J78" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6584,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6598,55 +6619,55 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B79" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C79" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E79" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F79" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G79">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I79" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -6654,10 +6675,10 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C80" t="s">
         <v>138</v>
@@ -6666,10 +6687,10 @@
         <v>139</v>
       </c>
       <c r="E80" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F80" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G80">
         <v>1000</v>
@@ -6693,10 +6714,10 @@
         <v>1</v>
       </c>
       <c r="N80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6710,22 +6731,22 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B81" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C81" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D81" t="s">
         <v>139</v>
       </c>
       <c r="E81" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F81" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G81">
         <v>1000</v>
@@ -6737,7 +6758,7 @@
         <v>142</v>
       </c>
       <c r="J81" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
@@ -6752,7 +6773,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6766,55 +6787,55 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B82" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C82" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D82" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E82" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F82" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G82">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H82" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J82" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
@@ -6822,55 +6843,55 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C83" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D83" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E83" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F83" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H83" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I83" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J83" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K83" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L83">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
       </c>
       <c r="N83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -6878,55 +6899,55 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C84" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D84" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E84" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F84" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G84">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J84" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K84" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L84">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
       </c>
       <c r="N84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
@@ -6934,34 +6955,34 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B85" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C85" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D85" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E85" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F85" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G85">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H85" t="s">
         <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J85" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
@@ -6976,7 +6997,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -6990,22 +7011,22 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B86" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C86" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D86" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E86" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F86" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G86">
         <v>500</v>
@@ -7017,7 +7038,7 @@
         <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
@@ -7032,7 +7053,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -7046,25 +7067,25 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B87" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C87" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D87" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E87" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F87" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G87">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H87" t="s">
         <v>42</v>
@@ -7073,7 +7094,7 @@
         <v>21</v>
       </c>
       <c r="J87" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
@@ -7088,7 +7109,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7102,37 +7123,37 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
+        <v>49</v>
+      </c>
+      <c r="B88" t="s">
+        <v>398</v>
+      </c>
+      <c r="C88" t="s">
+        <v>175</v>
+      </c>
+      <c r="D88" t="s">
+        <v>176</v>
+      </c>
+      <c r="E88" t="s">
+        <v>177</v>
+      </c>
+      <c r="F88" t="s">
+        <v>178</v>
+      </c>
+      <c r="G88">
         <v>50</v>
       </c>
-      <c r="B88" t="s">
-        <v>399</v>
-      </c>
-      <c r="C88" t="s">
-        <v>180</v>
-      </c>
-      <c r="D88" t="s">
-        <v>181</v>
-      </c>
-      <c r="E88" t="s">
-        <v>182</v>
-      </c>
-      <c r="F88" t="s">
-        <v>183</v>
-      </c>
-      <c r="G88">
-        <v>12</v>
-      </c>
       <c r="H88" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K88" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L88">
         <v>12</v>
@@ -7144,7 +7165,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7158,40 +7179,40 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B89" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C89" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D89" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E89" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F89" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G89">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H89" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I89" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J89" t="s">
-        <v>556</v>
+        <v>184</v>
       </c>
       <c r="K89" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7200,7 +7221,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7214,40 +7235,40 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B90" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C90" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D90" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E90" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F90" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G90">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H90" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I90" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J90" t="s">
-        <v>184</v>
+        <v>556</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
       </c>
       <c r="L90">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7256,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7270,40 +7291,40 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
+        <v>52</v>
+      </c>
+      <c r="B91" t="s">
+        <v>401</v>
+      </c>
+      <c r="C91" t="s">
+        <v>193</v>
+      </c>
+      <c r="D91" t="s">
+        <v>181</v>
+      </c>
+      <c r="E91" t="s">
+        <v>182</v>
+      </c>
+      <c r="F91" t="s">
+        <v>183</v>
+      </c>
+      <c r="G91">
+        <v>24</v>
+      </c>
+      <c r="H91" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" t="s">
         <v>53</v>
       </c>
-      <c r="B91" t="s">
-        <v>402</v>
-      </c>
-      <c r="C91" t="s">
-        <v>31</v>
-      </c>
-      <c r="D91" t="s">
-        <v>194</v>
-      </c>
-      <c r="E91" t="s">
-        <v>195</v>
-      </c>
-      <c r="F91" t="s">
-        <v>196</v>
-      </c>
-      <c r="G91">
-        <v>1.5</v>
-      </c>
-      <c r="H91" t="s">
-        <v>28</v>
-      </c>
-      <c r="I91" t="s">
-        <v>36</v>
-      </c>
       <c r="J91" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7312,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7326,52 +7347,52 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B92" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C92" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E92" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F92" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G92">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H92" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J92" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
       </c>
       <c r="N92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="b">
         <v>1</v>
@@ -7382,55 +7403,55 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B93" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C93" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D93" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E93" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F93" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G93">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H93" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I93" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J93" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
       </c>
       <c r="N93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" t="b">
         <v>1</v>
@@ -7438,40 +7459,40 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B94" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C94" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D94" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E94" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F94" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G94">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H94" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I94" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J94" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7480,7 +7501,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7494,19 +7515,19 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B95" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C95" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D95" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E95" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F95" t="s">
         <v>208</v>
@@ -7536,7 +7557,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7550,19 +7571,19 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B96" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C96" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D96" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E96" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F96" t="s">
         <v>208</v>
@@ -7583,7 +7604,7 @@
         <v>23</v>
       </c>
       <c r="L96">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -7592,7 +7613,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7606,34 +7627,34 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B97" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C97" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D97" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E97" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F97" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H97" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I97" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J97" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
@@ -7648,13 +7669,13 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -7662,34 +7683,34 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B98" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C98" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D98" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E98" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F98" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G98">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H98" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I98" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J98" t="s">
-        <v>557</v>
+        <v>148</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
@@ -7704,7 +7725,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7718,49 +7739,49 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B99" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C99" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D99" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E99" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F99" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G99">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H99" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I99" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J99" t="s">
-        <v>217</v>
+        <v>557</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
       </c>
       <c r="L99">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
       </c>
       <c r="N99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7774,22 +7795,22 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B100" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C100" t="s">
         <v>217</v>
       </c>
       <c r="D100" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E100" t="s">
         <v>219</v>
       </c>
       <c r="F100" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G100">
         <v>20</v>
@@ -7816,13 +7837,13 @@
         <v>0</v>
       </c>
       <c r="O100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R100" t="b">
         <v>1</v>
@@ -7830,49 +7851,49 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B101" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C101" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D101" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E101" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F101" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G101">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H101" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I101" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J101" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
       </c>
       <c r="L101">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
       </c>
       <c r="N101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -7886,34 +7907,34 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B102" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C102" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D102" t="s">
         <v>202</v>
       </c>
       <c r="E102" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G102">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H102" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I102" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J102" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
@@ -7928,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -7942,40 +7963,40 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B103" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C103" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D103" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E103" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F103" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G103">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H103" t="s">
         <v>42</v>
       </c>
       <c r="I103" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J103" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
       </c>
       <c r="L103">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M103" t="b">
         <v>0</v>
@@ -7984,13 +8005,13 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="b">
         <v>1</v>
@@ -7998,40 +8019,40 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B104" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C104" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D104" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E104" t="s">
         <v>229</v>
       </c>
       <c r="F104" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H104" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I104" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J104" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
       </c>
       <c r="L104">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
@@ -8040,7 +8061,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8054,40 +8075,40 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B105" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C105" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E105" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F105" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G105">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H105" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I105" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J105" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
       </c>
       <c r="L105">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -8096,13 +8117,13 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
       </c>
       <c r="Q105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" t="b">
         <v>1</v>
@@ -8110,34 +8131,34 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B106" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C106" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D106" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E106" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F106" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G106">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H106" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I106" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J106" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
@@ -8152,7 +8173,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8166,10 +8187,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B107" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C107" t="s">
         <v>186</v>
@@ -8178,13 +8199,13 @@
         <v>202</v>
       </c>
       <c r="E107" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F107" t="s">
         <v>204</v>
       </c>
       <c r="G107">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H107" t="s">
         <v>35</v>
@@ -8208,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8222,10 +8243,10 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B108" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C108" t="s">
         <v>186</v>
@@ -8240,7 +8261,7 @@
         <v>204</v>
       </c>
       <c r="G108">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H108" t="s">
         <v>35</v>
@@ -8264,7 +8285,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8278,41 +8299,41 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B109" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C109" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D109" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E109" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F109" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G109">
+        <v>250</v>
+      </c>
+      <c r="H109" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109" t="s">
+        <v>191</v>
+      </c>
+      <c r="J109" t="s">
+        <v>192</v>
+      </c>
+      <c r="K109" t="s">
+        <v>23</v>
+      </c>
+      <c r="L109">
         <v>6</v>
       </c>
-      <c r="H109" t="s">
-        <v>20</v>
-      </c>
-      <c r="I109" t="s">
-        <v>239</v>
-      </c>
-      <c r="J109" t="s">
-        <v>235</v>
-      </c>
-      <c r="K109" t="s">
-        <v>23</v>
-      </c>
-      <c r="L109">
-        <v>1</v>
-      </c>
       <c r="M109" t="b">
         <v>0</v>
       </c>
@@ -8320,13 +8341,13 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" t="b">
         <v>1</v>
@@ -8334,57 +8355,113 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B110" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C110" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D110" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E110" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F110" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G110">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H110" t="s">
         <v>20</v>
       </c>
       <c r="I110" t="s">
+        <v>239</v>
+      </c>
+      <c r="J110" t="s">
+        <v>235</v>
+      </c>
+      <c r="K110" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="M110" t="b">
+        <v>0</v>
+      </c>
+      <c r="N110" t="b">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>311</v>
+      </c>
+      <c r="P110" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="b">
+        <v>1</v>
+      </c>
+      <c r="R110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>72</v>
+      </c>
+      <c r="B111" t="s">
+        <v>421</v>
+      </c>
+      <c r="C111" t="s">
+        <v>197</v>
+      </c>
+      <c r="D111" t="s">
+        <v>198</v>
+      </c>
+      <c r="E111" t="s">
+        <v>199</v>
+      </c>
+      <c r="F111" t="s">
+        <v>240</v>
+      </c>
+      <c r="G111">
+        <v>4</v>
+      </c>
+      <c r="H111" t="s">
+        <v>20</v>
+      </c>
+      <c r="I111" t="s">
         <v>21</v>
       </c>
-      <c r="J110" t="s">
+      <c r="J111" t="s">
         <v>201</v>
       </c>
-      <c r="K110" t="s">
-        <v>23</v>
-      </c>
-      <c r="L110">
+      <c r="K111" t="s">
+        <v>23</v>
+      </c>
+      <c r="L111">
         <v>10</v>
       </c>
-      <c r="M110" t="b">
-        <v>0</v>
-      </c>
-      <c r="N110" t="b">
-        <v>0</v>
-      </c>
-      <c r="O110" t="s">
+      <c r="M111" t="b">
+        <v>0</v>
+      </c>
+      <c r="N111" t="b">
+        <v>0</v>
+      </c>
+      <c r="O111" t="s">
         <v>312</v>
       </c>
-      <c r="P110" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q110" t="b">
-        <v>1</v>
-      </c>
-      <c r="R110" t="b">
+      <c r="P111" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q111" t="b">
+        <v>1</v>
+      </c>
+      <c r="R111" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14232DA-5E39-4B1C-AF78-782C7E2072D5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01882BD8-30AE-438A-BDB2-5D5E85BA8D28}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="55" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="56" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="622">
   <si>
     <t>Codigo</t>
   </si>
@@ -1877,6 +1877,21 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7794440000104.png</t>
+  </si>
+  <si>
+    <t>77915818</t>
+  </si>
+  <si>
+    <t>Barra de cereales</t>
+  </si>
+  <si>
+    <t>cereal mix</t>
+  </si>
+  <si>
+    <t>manzana y avena</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\77915818.png</t>
   </si>
 </sst>
 </file>
@@ -2228,8 +2243,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B6D2FD9-D109-4F39-AAE1-6278920779DE}">
-  <dimension ref="A1:R111"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8475CE68-F8C8-421F-9078-BB86E580598E}">
+  <dimension ref="A1:R112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -5886,45 +5901,45 @@
         <v>1</v>
       </c>
       <c r="R65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="B66" t="s">
-        <v>376</v>
+        <v>617</v>
       </c>
       <c r="C66" t="s">
-        <v>88</v>
+        <v>618</v>
       </c>
       <c r="D66" t="s">
-        <v>89</v>
+        <v>619</v>
       </c>
       <c r="E66" t="s">
-        <v>90</v>
+        <v>620</v>
       </c>
       <c r="F66" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="G66">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="H66" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>36</v>
+        <v>494</v>
       </c>
       <c r="J66" t="s">
-        <v>92</v>
+        <v>580</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5933,13 +5948,13 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>267</v>
+        <v>621</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="b">
         <v>1</v>
@@ -5947,40 +5962,40 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C67" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D67" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E67" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F67" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G67">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H67" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I67" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J67" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -5989,7 +6004,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -6003,41 +6018,41 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B68" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C68" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D68" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E68" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F68" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H68" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I68" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J68" t="s">
+        <v>66</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68">
         <v>30</v>
       </c>
-      <c r="K68" t="s">
-        <v>23</v>
-      </c>
-      <c r="L68">
-        <v>12</v>
-      </c>
       <c r="M68" t="b">
         <v>0</v>
       </c>
@@ -6045,13 +6060,13 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="b">
         <v>1</v>
@@ -6059,55 +6074,55 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
+        <v>29</v>
+      </c>
+      <c r="B69" t="s">
+        <v>378</v>
+      </c>
+      <c r="C69" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" t="s">
+        <v>54</v>
+      </c>
+      <c r="E69" t="s">
+        <v>55</v>
+      </c>
+      <c r="F69" t="s">
+        <v>61</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" t="s">
+        <v>96</v>
+      </c>
+      <c r="J69" t="s">
         <v>30</v>
       </c>
-      <c r="B69" t="s">
-        <v>379</v>
-      </c>
-      <c r="C69" t="s">
-        <v>97</v>
-      </c>
-      <c r="D69" t="s">
-        <v>98</v>
-      </c>
-      <c r="E69" t="s">
-        <v>99</v>
-      </c>
-      <c r="F69" t="s">
-        <v>100</v>
-      </c>
-      <c r="G69">
-        <v>100</v>
-      </c>
-      <c r="H69" t="s">
-        <v>20</v>
-      </c>
-      <c r="I69" t="s">
-        <v>101</v>
-      </c>
-      <c r="J69" t="s">
-        <v>102</v>
-      </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
       </c>
       <c r="N69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="b">
         <v>1</v>
@@ -6115,49 +6130,49 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D70" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E70" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F70" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G70">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H70" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I70" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J70" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
       </c>
       <c r="N70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -6171,22 +6186,22 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C71" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D71" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E71" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F71" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G71">
         <v>500</v>
@@ -6198,13 +6213,13 @@
         <v>107</v>
       </c>
       <c r="J71" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -6213,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -6227,40 +6242,40 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C72" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D72" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E72" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F72" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H72" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J72" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6269,13 +6284,13 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="b">
         <v>1</v>
@@ -6283,40 +6298,40 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G73">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I73" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -6325,13 +6340,13 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -6339,40 +6354,40 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
+        <v>34</v>
+      </c>
+      <c r="B74" t="s">
+        <v>383</v>
+      </c>
+      <c r="C74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" t="s">
+        <v>114</v>
+      </c>
+      <c r="F74" t="s">
+        <v>115</v>
+      </c>
+      <c r="G74">
+        <v>300</v>
+      </c>
+      <c r="H74" t="s">
         <v>35</v>
       </c>
-      <c r="B74" t="s">
-        <v>384</v>
-      </c>
-      <c r="C74" t="s">
-        <v>117</v>
-      </c>
-      <c r="D74" t="s">
-        <v>118</v>
-      </c>
-      <c r="E74" t="s">
-        <v>119</v>
-      </c>
-      <c r="F74" t="s">
-        <v>120</v>
-      </c>
-      <c r="G74">
-        <v>500</v>
-      </c>
-      <c r="H74" t="s">
-        <v>42</v>
-      </c>
       <c r="I74" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -6381,7 +6396,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -6395,40 +6410,40 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B75" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C75" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D75" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E75" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F75" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G75">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H75" t="s">
         <v>42</v>
       </c>
       <c r="I75" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -6437,13 +6452,13 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -6451,40 +6466,40 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B76" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D76" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E76" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F76" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G76">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H76" t="s">
         <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J76" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6493,13 +6508,13 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -6507,34 +6522,34 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B77" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D77" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E77" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F77" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G77">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H77" t="s">
         <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J77" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
@@ -6549,13 +6564,13 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
@@ -6563,40 +6578,40 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B78" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C78" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D78" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E78" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F78" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G78">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H78" t="s">
         <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6605,7 +6620,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6619,40 +6634,40 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B79" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C79" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D79" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E79" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F79" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H79" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J79" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6661,7 +6676,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6675,55 +6690,55 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C80" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D80" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E80" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F80" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G80">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I80" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="b">
         <v>1</v>
@@ -6731,10 +6746,10 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C81" t="s">
         <v>138</v>
@@ -6743,10 +6758,10 @@
         <v>139</v>
       </c>
       <c r="E81" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F81" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G81">
         <v>1000</v>
@@ -6770,10 +6785,10 @@
         <v>1</v>
       </c>
       <c r="N81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6787,22 +6802,22 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C82" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D82" t="s">
         <v>139</v>
       </c>
       <c r="E82" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F82" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G82">
         <v>1000</v>
@@ -6814,7 +6829,7 @@
         <v>142</v>
       </c>
       <c r="J82" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -6829,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6843,55 +6858,55 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B83" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C83" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D83" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E83" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F83" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G83">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H83" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J83" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -6899,55 +6914,55 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B84" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C84" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D84" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E84" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F84" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H84" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I84" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J84" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K84" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L84">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
       </c>
       <c r="N84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
@@ -6955,55 +6970,55 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C85" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D85" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E85" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F85" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G85">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I85" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J85" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K85" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L85">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
       <c r="N85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -7011,34 +7026,34 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C86" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D86" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E86" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F86" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G86">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H86" t="s">
         <v>42</v>
       </c>
       <c r="I86" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J86" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
@@ -7053,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -7067,22 +7082,22 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B87" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C87" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D87" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E87" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F87" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G87">
         <v>500</v>
@@ -7094,7 +7109,7 @@
         <v>21</v>
       </c>
       <c r="J87" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
@@ -7109,7 +7124,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7123,25 +7138,25 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B88" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C88" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D88" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E88" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F88" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G88">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H88" t="s">
         <v>42</v>
@@ -7150,7 +7165,7 @@
         <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
@@ -7165,7 +7180,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7179,37 +7194,37 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
+        <v>49</v>
+      </c>
+      <c r="B89" t="s">
+        <v>398</v>
+      </c>
+      <c r="C89" t="s">
+        <v>175</v>
+      </c>
+      <c r="D89" t="s">
+        <v>176</v>
+      </c>
+      <c r="E89" t="s">
+        <v>177</v>
+      </c>
+      <c r="F89" t="s">
+        <v>178</v>
+      </c>
+      <c r="G89">
         <v>50</v>
       </c>
-      <c r="B89" t="s">
-        <v>399</v>
-      </c>
-      <c r="C89" t="s">
-        <v>180</v>
-      </c>
-      <c r="D89" t="s">
-        <v>181</v>
-      </c>
-      <c r="E89" t="s">
-        <v>182</v>
-      </c>
-      <c r="F89" t="s">
-        <v>183</v>
-      </c>
-      <c r="G89">
-        <v>12</v>
-      </c>
       <c r="H89" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I89" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J89" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K89" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L89">
         <v>12</v>
@@ -7221,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7235,40 +7250,40 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B90" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C90" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D90" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E90" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F90" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G90">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H90" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I90" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J90" t="s">
-        <v>556</v>
+        <v>184</v>
       </c>
       <c r="K90" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="L90">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7277,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7291,40 +7306,40 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B91" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C91" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D91" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E91" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F91" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G91">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H91" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="I91" t="s">
-        <v>53</v>
+        <v>191</v>
       </c>
       <c r="J91" t="s">
-        <v>184</v>
+        <v>556</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
       </c>
       <c r="L91">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7333,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7347,40 +7362,40 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
+        <v>52</v>
+      </c>
+      <c r="B92" t="s">
+        <v>401</v>
+      </c>
+      <c r="C92" t="s">
+        <v>193</v>
+      </c>
+      <c r="D92" t="s">
+        <v>181</v>
+      </c>
+      <c r="E92" t="s">
+        <v>182</v>
+      </c>
+      <c r="F92" t="s">
+        <v>183</v>
+      </c>
+      <c r="G92">
+        <v>24</v>
+      </c>
+      <c r="H92" t="s">
+        <v>20</v>
+      </c>
+      <c r="I92" t="s">
         <v>53</v>
       </c>
-      <c r="B92" t="s">
-        <v>402</v>
-      </c>
-      <c r="C92" t="s">
-        <v>31</v>
-      </c>
-      <c r="D92" t="s">
-        <v>194</v>
-      </c>
-      <c r="E92" t="s">
-        <v>195</v>
-      </c>
-      <c r="F92" t="s">
-        <v>196</v>
-      </c>
-      <c r="G92">
-        <v>1.5</v>
-      </c>
-      <c r="H92" t="s">
-        <v>28</v>
-      </c>
-      <c r="I92" t="s">
-        <v>36</v>
-      </c>
       <c r="J92" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7389,7 +7404,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7403,52 +7418,52 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B93" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C93" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E93" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F93" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G93">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H93" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J93" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
       </c>
       <c r="N93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="b">
         <v>1</v>
@@ -7459,55 +7474,55 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B94" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C94" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D94" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E94" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F94" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G94">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H94" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I94" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J94" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
       </c>
       <c r="N94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="b">
         <v>1</v>
@@ -7515,40 +7530,40 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B95" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C95" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D95" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E95" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F95" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G95">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H95" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I95" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J95" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7557,7 +7572,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7571,19 +7586,19 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B96" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C96" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D96" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E96" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F96" t="s">
         <v>208</v>
@@ -7613,7 +7628,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7627,19 +7642,19 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B97" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C97" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D97" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F97" t="s">
         <v>208</v>
@@ -7660,7 +7675,7 @@
         <v>23</v>
       </c>
       <c r="L97">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -7669,7 +7684,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7683,34 +7698,34 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B98" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C98" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D98" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E98" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F98" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H98" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I98" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="J98" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
@@ -7725,13 +7740,13 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
@@ -7739,34 +7754,34 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B99" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D99" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="E99" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="F99" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G99">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H99" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I99" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J99" t="s">
-        <v>557</v>
+        <v>148</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
@@ -7781,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7795,49 +7810,49 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B100" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C100" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D100" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E100" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F100" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G100">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H100" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I100" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J100" t="s">
-        <v>217</v>
+        <v>557</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
       </c>
       <c r="L100">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
       </c>
       <c r="N100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -7851,22 +7866,22 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B101" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C101" t="s">
         <v>217</v>
       </c>
       <c r="D101" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E101" t="s">
         <v>219</v>
       </c>
       <c r="F101" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G101">
         <v>20</v>
@@ -7893,13 +7908,13 @@
         <v>0</v>
       </c>
       <c r="O101" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>
@@ -7907,49 +7922,49 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B102" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C102" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D102" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="E102" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F102" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G102">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H102" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I102" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J102" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
       </c>
       <c r="L102">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
       </c>
       <c r="N102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -7963,34 +7978,34 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B103" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C103" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D103" t="s">
         <v>202</v>
       </c>
       <c r="E103" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G103">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H103" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I103" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J103" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
@@ -8005,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8019,40 +8034,40 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B104" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C104" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D104" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E104" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F104" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G104">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H104" t="s">
         <v>42</v>
       </c>
       <c r="I104" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J104" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
       </c>
       <c r="L104">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
@@ -8061,13 +8076,13 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
       </c>
       <c r="Q104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="b">
         <v>1</v>
@@ -8075,40 +8090,40 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B105" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C105" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="D105" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E105" t="s">
         <v>229</v>
       </c>
       <c r="F105" t="s">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H105" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I105" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J105" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
       </c>
       <c r="L105">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -8117,7 +8132,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8131,40 +8146,40 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C106" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D106" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="E106" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F106" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G106">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H106" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I106" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J106" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
       </c>
       <c r="L106">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
@@ -8173,13 +8188,13 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
       </c>
       <c r="Q106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" t="b">
         <v>1</v>
@@ -8187,34 +8202,34 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B107" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C107" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E107" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F107" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G107">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H107" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I107" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J107" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
@@ -8229,7 +8244,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8243,10 +8258,10 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B108" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C108" t="s">
         <v>186</v>
@@ -8255,13 +8270,13 @@
         <v>202</v>
       </c>
       <c r="E108" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F108" t="s">
         <v>204</v>
       </c>
       <c r="G108">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H108" t="s">
         <v>35</v>
@@ -8285,7 +8300,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8299,10 +8314,10 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B109" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C109" t="s">
         <v>186</v>
@@ -8317,7 +8332,7 @@
         <v>204</v>
       </c>
       <c r="G109">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H109" t="s">
         <v>35</v>
@@ -8341,7 +8356,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8355,41 +8370,41 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B110" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C110" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D110" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="E110" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F110" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G110">
+        <v>250</v>
+      </c>
+      <c r="H110" t="s">
+        <v>35</v>
+      </c>
+      <c r="I110" t="s">
+        <v>191</v>
+      </c>
+      <c r="J110" t="s">
+        <v>192</v>
+      </c>
+      <c r="K110" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110">
         <v>6</v>
       </c>
-      <c r="H110" t="s">
-        <v>20</v>
-      </c>
-      <c r="I110" t="s">
-        <v>239</v>
-      </c>
-      <c r="J110" t="s">
-        <v>235</v>
-      </c>
-      <c r="K110" t="s">
-        <v>23</v>
-      </c>
-      <c r="L110">
-        <v>1</v>
-      </c>
       <c r="M110" t="b">
         <v>0</v>
       </c>
@@ -8397,13 +8412,13 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R110" t="b">
         <v>1</v>
@@ -8411,57 +8426,113 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C111" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="D111" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="E111" t="s">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="F111" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G111">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H111" t="s">
         <v>20</v>
       </c>
       <c r="I111" t="s">
+        <v>239</v>
+      </c>
+      <c r="J111" t="s">
+        <v>235</v>
+      </c>
+      <c r="K111" t="s">
+        <v>23</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="M111" t="b">
+        <v>0</v>
+      </c>
+      <c r="N111" t="b">
+        <v>1</v>
+      </c>
+      <c r="O111" t="s">
+        <v>311</v>
+      </c>
+      <c r="P111" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="b">
+        <v>1</v>
+      </c>
+      <c r="R111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>72</v>
+      </c>
+      <c r="B112" t="s">
+        <v>421</v>
+      </c>
+      <c r="C112" t="s">
+        <v>197</v>
+      </c>
+      <c r="D112" t="s">
+        <v>198</v>
+      </c>
+      <c r="E112" t="s">
+        <v>199</v>
+      </c>
+      <c r="F112" t="s">
+        <v>240</v>
+      </c>
+      <c r="G112">
+        <v>4</v>
+      </c>
+      <c r="H112" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112" t="s">
         <v>21</v>
       </c>
-      <c r="J111" t="s">
+      <c r="J112" t="s">
         <v>201</v>
       </c>
-      <c r="K111" t="s">
-        <v>23</v>
-      </c>
-      <c r="L111">
+      <c r="K112" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112">
         <v>10</v>
       </c>
-      <c r="M111" t="b">
-        <v>0</v>
-      </c>
-      <c r="N111" t="b">
-        <v>0</v>
-      </c>
-      <c r="O111" t="s">
+      <c r="M112" t="b">
+        <v>0</v>
+      </c>
+      <c r="N112" t="b">
+        <v>0</v>
+      </c>
+      <c r="O112" t="s">
         <v>312</v>
       </c>
-      <c r="P111" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q111" t="b">
-        <v>1</v>
-      </c>
-      <c r="R111" t="b">
+      <c r="P112" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q112" t="b">
+        <v>1</v>
+      </c>
+      <c r="R112" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01882BD8-30AE-438A-BDB2-5D5E85BA8D28}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77784C16-0B5F-46E5-82FF-C7EC7E066A46}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="56" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="58" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="626">
   <si>
     <t>Codigo</t>
   </si>
@@ -559,9 +559,6 @@
     <t>de sodio</t>
   </si>
   <si>
-    <t>en bolsa</t>
-  </si>
-  <si>
     <t>Alicante</t>
   </si>
   <si>
@@ -1892,6 +1889,21 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\77915818.png</t>
+  </si>
+  <si>
+    <t>7792389079991</t>
+  </si>
+  <si>
+    <t>uso culinario</t>
+  </si>
+  <si>
+    <t>Dumba</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7792389079991.png</t>
+  </si>
+  <si>
+    <t>sin gluten</t>
   </si>
 </sst>
 </file>
@@ -2243,8 +2255,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8475CE68-F8C8-421F-9078-BB86E580598E}">
-  <dimension ref="A1:R112"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2491E691-32D8-4EEA-9C6C-D4234EC859B7}">
+  <dimension ref="A1:R113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2269,7 +2281,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2320,7 +2332,7 @@
         <v>15</v>
       </c>
       <c r="R1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -2328,19 +2340,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C2" t="s">
         <v>88</v>
       </c>
       <c r="D2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E2" t="s">
         <v>335</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>336</v>
-      </c>
-      <c r="F2" t="s">
-        <v>337</v>
       </c>
       <c r="G2">
         <v>638</v>
@@ -2355,7 +2367,7 @@
         <v>92</v>
       </c>
       <c r="K2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2367,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -2384,16 +2396,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D3" t="s">
+        <v>441</v>
+      </c>
+      <c r="E3" t="s">
         <v>340</v>
-      </c>
-      <c r="C3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D3" t="s">
-        <v>442</v>
-      </c>
-      <c r="E3" t="s">
-        <v>341</v>
       </c>
       <c r="F3" t="s">
         <v>133</v>
@@ -2405,10 +2417,10 @@
         <v>42</v>
       </c>
       <c r="I3" t="s">
+        <v>328</v>
+      </c>
+      <c r="J3" t="s">
         <v>329</v>
-      </c>
-      <c r="J3" t="s">
-        <v>330</v>
       </c>
       <c r="K3" t="s">
         <v>23</v>
@@ -2423,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -2440,19 +2452,19 @@
         <v>73</v>
       </c>
       <c r="B4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C4" t="s">
         <v>343</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>344</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>345</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>346</v>
-      </c>
-      <c r="F4" t="s">
-        <v>347</v>
       </c>
       <c r="G4">
         <v>21</v>
@@ -2464,10 +2476,10 @@
         <v>53</v>
       </c>
       <c r="J4" t="s">
+        <v>347</v>
+      </c>
+      <c r="K4" t="s">
         <v>348</v>
-      </c>
-      <c r="K4" t="s">
-        <v>349</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -2479,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
@@ -2496,19 +2508,19 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C5" t="s">
         <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E5" t="s">
+        <v>422</v>
+      </c>
+      <c r="F5" t="s">
         <v>423</v>
-      </c>
-      <c r="F5" t="s">
-        <v>424</v>
       </c>
       <c r="G5">
         <v>35</v>
@@ -2517,7 +2529,7 @@
         <v>42</v>
       </c>
       <c r="I5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J5" t="s">
         <v>148</v>
@@ -2535,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
@@ -2552,19 +2564,19 @@
         <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D6" t="s">
         <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G6">
         <v>40</v>
@@ -2573,10 +2585,10 @@
         <v>42</v>
       </c>
       <c r="I6" t="s">
+        <v>328</v>
+      </c>
+      <c r="J6" t="s">
         <v>329</v>
-      </c>
-      <c r="J6" t="s">
-        <v>330</v>
       </c>
       <c r="K6" t="s">
         <v>23</v>
@@ -2591,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
@@ -2608,19 +2620,19 @@
         <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
       </c>
       <c r="D7" t="s">
+        <v>429</v>
+      </c>
+      <c r="E7" t="s">
         <v>430</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>431</v>
-      </c>
-      <c r="F7" t="s">
-        <v>432</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -2635,19 +2647,19 @@
         <v>44</v>
       </c>
       <c r="K7" t="s">
+        <v>432</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
         <v>433</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" t="s">
-        <v>434</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
@@ -2664,19 +2676,19 @@
         <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D8" t="s">
         <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G8">
         <v>40</v>
@@ -2685,10 +2697,10 @@
         <v>42</v>
       </c>
       <c r="I8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J8" t="s">
         <v>329</v>
-      </c>
-      <c r="J8" t="s">
-        <v>330</v>
       </c>
       <c r="K8" t="s">
         <v>23</v>
@@ -2703,7 +2715,7 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
@@ -2720,19 +2732,19 @@
         <v>78</v>
       </c>
       <c r="B9" t="s">
+        <v>436</v>
+      </c>
+      <c r="C9" t="s">
         <v>437</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>438</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>439</v>
       </c>
-      <c r="E9" t="s">
-        <v>440</v>
-      </c>
       <c r="F9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G9">
         <v>400</v>
@@ -2759,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
@@ -2776,19 +2788,19 @@
         <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C10" t="s">
         <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E10" t="s">
         <v>173</v>
       </c>
       <c r="F10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G10">
         <v>150</v>
@@ -2797,13 +2809,13 @@
         <v>42</v>
       </c>
       <c r="I10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J10" t="s">
         <v>174</v>
       </c>
       <c r="K10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L10">
         <v>12</v>
@@ -2815,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
@@ -2832,19 +2844,19 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C11" t="s">
         <v>171</v>
       </c>
       <c r="D11" t="s">
+        <v>449</v>
+      </c>
+      <c r="E11" t="s">
         <v>450</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>451</v>
-      </c>
-      <c r="F11" t="s">
-        <v>452</v>
       </c>
       <c r="G11">
         <v>453</v>
@@ -2853,13 +2865,13 @@
         <v>42</v>
       </c>
       <c r="I11" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J11" t="s">
         <v>174</v>
       </c>
       <c r="K11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L11">
         <v>12</v>
@@ -2871,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
@@ -2888,19 +2900,19 @@
         <v>81</v>
       </c>
       <c r="B12" t="s">
+        <v>453</v>
+      </c>
+      <c r="C12" t="s">
         <v>454</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>455</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>456</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>457</v>
-      </c>
-      <c r="F12" t="s">
-        <v>458</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2912,22 +2924,22 @@
         <v>53</v>
       </c>
       <c r="J12" t="s">
+        <v>458</v>
+      </c>
+      <c r="K12" t="s">
         <v>459</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
         <v>460</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>461</v>
       </c>
       <c r="P12" t="b">
         <v>1</v>
@@ -2944,19 +2956,19 @@
         <v>82</v>
       </c>
       <c r="B13" t="s">
+        <v>461</v>
+      </c>
+      <c r="C13" t="s">
         <v>462</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>463</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>464</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>465</v>
-      </c>
-      <c r="F13" t="s">
-        <v>466</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2968,10 +2980,10 @@
         <v>53</v>
       </c>
       <c r="J13" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -2983,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P13" t="b">
         <v>1</v>
@@ -3000,19 +3012,19 @@
         <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D14" t="s">
         <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G14">
         <v>40</v>
@@ -3021,10 +3033,10 @@
         <v>42</v>
       </c>
       <c r="I14" t="s">
+        <v>328</v>
+      </c>
+      <c r="J14" t="s">
         <v>329</v>
-      </c>
-      <c r="J14" t="s">
-        <v>330</v>
       </c>
       <c r="K14" t="s">
         <v>23</v>
@@ -3039,7 +3051,7 @@
         <v>1</v>
       </c>
       <c r="O14" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>
@@ -3056,19 +3068,19 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
+        <v>471</v>
+      </c>
+      <c r="C15" t="s">
         <v>472</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>473</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>474</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>475</v>
-      </c>
-      <c r="F15" t="s">
-        <v>476</v>
       </c>
       <c r="G15">
         <v>190</v>
@@ -3080,10 +3092,10 @@
         <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -3095,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P15" t="b">
         <v>1</v>
@@ -3112,16 +3124,16 @@
         <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D16" t="s">
         <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F16" t="s">
         <v>133</v>
@@ -3133,10 +3145,10 @@
         <v>42</v>
       </c>
       <c r="I16" t="s">
+        <v>328</v>
+      </c>
+      <c r="J16" t="s">
         <v>329</v>
-      </c>
-      <c r="J16" t="s">
-        <v>330</v>
       </c>
       <c r="K16" t="s">
         <v>23</v>
@@ -3151,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P16" t="b">
         <v>1</v>
@@ -3168,19 +3180,19 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D17" t="s">
+        <v>246</v>
+      </c>
+      <c r="E17" t="s">
         <v>247</v>
       </c>
-      <c r="E17" t="s">
-        <v>248</v>
-      </c>
       <c r="F17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G17">
         <v>20</v>
@@ -3192,7 +3204,7 @@
         <v>53</v>
       </c>
       <c r="J17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K17" t="s">
         <v>23</v>
@@ -3207,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P17" t="b">
         <v>1</v>
@@ -3224,7 +3236,7 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C18" t="s">
         <v>171</v>
@@ -3236,7 +3248,7 @@
         <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G18">
         <v>25</v>
@@ -3263,7 +3275,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -3280,31 +3292,31 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C19" t="s">
+        <v>313</v>
+      </c>
+      <c r="D19" t="s">
         <v>314</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>315</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>316</v>
-      </c>
-      <c r="F19" t="s">
-        <v>317</v>
       </c>
       <c r="G19">
         <v>355</v>
       </c>
       <c r="H19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I19" t="s">
+        <v>317</v>
+      </c>
+      <c r="J19" t="s">
         <v>318</v>
-      </c>
-      <c r="J19" t="s">
-        <v>319</v>
       </c>
       <c r="K19" t="s">
         <v>23</v>
@@ -3319,7 +3331,7 @@
         <v>1</v>
       </c>
       <c r="O19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
@@ -3336,19 +3348,19 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E20" t="s">
+        <v>320</v>
+      </c>
+      <c r="F20" t="s">
         <v>321</v>
-      </c>
-      <c r="F20" t="s">
-        <v>322</v>
       </c>
       <c r="G20">
         <v>20</v>
@@ -3360,10 +3372,10 @@
         <v>53</v>
       </c>
       <c r="J20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -3375,7 +3387,7 @@
         <v>1</v>
       </c>
       <c r="O20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P20" t="b">
         <v>1</v>
@@ -3392,19 +3404,19 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G21">
         <v>20</v>
@@ -3416,10 +3428,10 @@
         <v>53</v>
       </c>
       <c r="J21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -3431,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P21" t="b">
         <v>1</v>
@@ -3448,16 +3460,16 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D22" t="s">
         <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F22" t="s">
         <v>133</v>
@@ -3469,10 +3481,10 @@
         <v>42</v>
       </c>
       <c r="I22" t="s">
+        <v>328</v>
+      </c>
+      <c r="J22" t="s">
         <v>329</v>
-      </c>
-      <c r="J22" t="s">
-        <v>330</v>
       </c>
       <c r="K22" t="s">
         <v>23</v>
@@ -3487,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="O22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
@@ -3504,16 +3516,16 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C23" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D23" t="s">
         <v>81</v>
       </c>
       <c r="E23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F23" t="s">
         <v>133</v>
@@ -3525,10 +3537,10 @@
         <v>42</v>
       </c>
       <c r="I23" t="s">
+        <v>328</v>
+      </c>
+      <c r="J23" t="s">
         <v>329</v>
-      </c>
-      <c r="J23" t="s">
-        <v>330</v>
       </c>
       <c r="K23" t="s">
         <v>23</v>
@@ -3543,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
@@ -3560,19 +3572,19 @@
         <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C24" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D24" t="s">
         <v>81</v>
       </c>
       <c r="E24" t="s">
+        <v>482</v>
+      </c>
+      <c r="F24" t="s">
         <v>483</v>
-      </c>
-      <c r="F24" t="s">
-        <v>484</v>
       </c>
       <c r="G24">
         <v>42</v>
@@ -3581,10 +3593,10 @@
         <v>42</v>
       </c>
       <c r="I24" t="s">
+        <v>328</v>
+      </c>
+      <c r="J24" t="s">
         <v>329</v>
-      </c>
-      <c r="J24" t="s">
-        <v>330</v>
       </c>
       <c r="K24" t="s">
         <v>23</v>
@@ -3599,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
@@ -3616,7 +3628,7 @@
         <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
@@ -3625,7 +3637,7 @@
         <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -3655,7 +3667,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
@@ -3672,19 +3684,19 @@
         <v>88</v>
       </c>
       <c r="B26" t="s">
+        <v>488</v>
+      </c>
+      <c r="C26" t="s">
         <v>489</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>490</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>491</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>492</v>
-      </c>
-      <c r="F26" t="s">
-        <v>493</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3693,10 +3705,10 @@
         <v>20</v>
       </c>
       <c r="I26" t="s">
+        <v>493</v>
+      </c>
+      <c r="J26" t="s">
         <v>494</v>
-      </c>
-      <c r="J26" t="s">
-        <v>495</v>
       </c>
       <c r="K26" t="s">
         <v>23</v>
@@ -3711,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -3728,19 +3740,19 @@
         <v>89</v>
       </c>
       <c r="B27" t="s">
+        <v>496</v>
+      </c>
+      <c r="C27" t="s">
+        <v>489</v>
+      </c>
+      <c r="D27" t="s">
+        <v>490</v>
+      </c>
+      <c r="E27" t="s">
         <v>497</v>
       </c>
-      <c r="C27" t="s">
-        <v>490</v>
-      </c>
-      <c r="D27" t="s">
-        <v>491</v>
-      </c>
-      <c r="E27" t="s">
-        <v>498</v>
-      </c>
       <c r="F27" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3749,10 +3761,10 @@
         <v>20</v>
       </c>
       <c r="I27" t="s">
+        <v>493</v>
+      </c>
+      <c r="J27" t="s">
         <v>494</v>
-      </c>
-      <c r="J27" t="s">
-        <v>495</v>
       </c>
       <c r="K27" t="s">
         <v>23</v>
@@ -3767,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -3784,19 +3796,19 @@
         <v>90</v>
       </c>
       <c r="B28" t="s">
+        <v>499</v>
+      </c>
+      <c r="C28" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" t="s">
         <v>500</v>
-      </c>
-      <c r="C28" t="s">
-        <v>180</v>
-      </c>
-      <c r="D28" t="s">
-        <v>181</v>
-      </c>
-      <c r="E28" t="s">
-        <v>182</v>
-      </c>
-      <c r="F28" t="s">
-        <v>501</v>
       </c>
       <c r="G28">
         <v>12</v>
@@ -3808,10 +3820,10 @@
         <v>53</v>
       </c>
       <c r="J28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L28">
         <v>12</v>
@@ -3823,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -3840,7 +3852,7 @@
         <v>91</v>
       </c>
       <c r="B29" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
@@ -3849,10 +3861,10 @@
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F29" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G29">
         <v>4</v>
@@ -3879,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="P29" t="b">
         <v>0</v>
@@ -3896,19 +3908,19 @@
         <v>92</v>
       </c>
       <c r="B30" t="s">
+        <v>505</v>
+      </c>
+      <c r="C30" t="s">
         <v>506</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>507</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>508</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>509</v>
-      </c>
-      <c r="F30" t="s">
-        <v>510</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3920,7 +3932,7 @@
         <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K30" t="s">
         <v>23</v>
@@ -3935,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -3952,19 +3964,19 @@
         <v>93</v>
       </c>
       <c r="B31" t="s">
+        <v>512</v>
+      </c>
+      <c r="C31" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31" t="s">
         <v>513</v>
       </c>
-      <c r="C31" t="s">
-        <v>197</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>514</v>
       </c>
-      <c r="E31" t="s">
-        <v>515</v>
-      </c>
       <c r="F31" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -3976,7 +3988,7 @@
         <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K31" t="s">
         <v>23</v>
@@ -3991,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -4008,7 +4020,7 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C32" t="s">
         <v>16</v>
@@ -4047,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -4064,7 +4076,7 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C33" t="s">
         <v>24</v>
@@ -4103,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -4120,7 +4132,7 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C34" t="s">
         <v>31</v>
@@ -4159,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -4176,7 +4188,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C35" t="s">
         <v>38</v>
@@ -4215,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -4232,7 +4244,7 @@
         <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C36" t="s">
         <v>44</v>
@@ -4271,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -4288,19 +4300,19 @@
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C37" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" t="s">
         <v>241</v>
-      </c>
-      <c r="D37" t="s">
-        <v>242</v>
       </c>
       <c r="E37" t="s">
         <v>173</v>
       </c>
       <c r="F37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G37">
         <v>170</v>
@@ -4312,7 +4324,7 @@
         <v>21</v>
       </c>
       <c r="J37" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K37" t="s">
         <v>23</v>
@@ -4327,7 +4339,7 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -4344,19 +4356,19 @@
         <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C38" t="s">
+        <v>196</v>
+      </c>
+      <c r="D38" t="s">
         <v>197</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>198</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>199</v>
-      </c>
-      <c r="F38" t="s">
-        <v>200</v>
       </c>
       <c r="G38">
         <v>6</v>
@@ -4368,7 +4380,7 @@
         <v>21</v>
       </c>
       <c r="J38" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K38" t="s">
         <v>23</v>
@@ -4383,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -4400,19 +4412,19 @@
         <v>94</v>
       </c>
       <c r="B39" t="s">
+        <v>516</v>
+      </c>
+      <c r="C39" t="s">
         <v>517</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>518</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>519</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>520</v>
-      </c>
-      <c r="F39" t="s">
-        <v>521</v>
       </c>
       <c r="G39">
         <v>88</v>
@@ -4421,10 +4433,10 @@
         <v>42</v>
       </c>
       <c r="I39" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J39" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K39" t="s">
         <v>23</v>
@@ -4439,7 +4451,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
@@ -4456,19 +4468,19 @@
         <v>95</v>
       </c>
       <c r="B40" t="s">
+        <v>523</v>
+      </c>
+      <c r="C40" t="s">
         <v>524</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>525</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>526</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>527</v>
-      </c>
-      <c r="F40" t="s">
-        <v>528</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -4480,7 +4492,7 @@
         <v>36</v>
       </c>
       <c r="J40" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
@@ -4495,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
@@ -4512,19 +4524,19 @@
         <v>96</v>
       </c>
       <c r="B41" t="s">
+        <v>530</v>
+      </c>
+      <c r="C41" t="s">
         <v>531</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>532</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>533</v>
       </c>
-      <c r="E41" t="s">
-        <v>534</v>
-      </c>
       <c r="F41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G41">
         <v>25</v>
@@ -4536,7 +4548,7 @@
         <v>21</v>
       </c>
       <c r="J41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
@@ -4551,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
@@ -4568,19 +4580,19 @@
         <v>97</v>
       </c>
       <c r="B42" t="s">
+        <v>535</v>
+      </c>
+      <c r="C42" t="s">
         <v>536</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>537</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>538</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>539</v>
-      </c>
-      <c r="F42" t="s">
-        <v>540</v>
       </c>
       <c r="G42">
         <v>900</v>
@@ -4592,7 +4604,7 @@
         <v>36</v>
       </c>
       <c r="J42" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
@@ -4607,7 +4619,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="P42" t="b">
         <v>1</v>
@@ -4624,19 +4636,19 @@
         <v>98</v>
       </c>
       <c r="B43" t="s">
+        <v>542</v>
+      </c>
+      <c r="C43" t="s">
         <v>543</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>544</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>545</v>
       </c>
-      <c r="E43" t="s">
-        <v>546</v>
-      </c>
       <c r="F43" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G43">
         <v>90</v>
@@ -4645,10 +4657,10 @@
         <v>42</v>
       </c>
       <c r="I43" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J43" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
@@ -4663,7 +4675,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="P43" t="b">
         <v>1</v>
@@ -4680,19 +4692,19 @@
         <v>99</v>
       </c>
       <c r="B44" t="s">
+        <v>547</v>
+      </c>
+      <c r="C44" t="s">
         <v>548</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>549</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>550</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>551</v>
-      </c>
-      <c r="F44" t="s">
-        <v>552</v>
       </c>
       <c r="G44">
         <v>6</v>
@@ -4701,10 +4713,10 @@
         <v>20</v>
       </c>
       <c r="I44" t="s">
+        <v>552</v>
+      </c>
+      <c r="J44" t="s">
         <v>553</v>
-      </c>
-      <c r="J44" t="s">
-        <v>554</v>
       </c>
       <c r="K44" t="s">
         <v>23</v>
@@ -4719,7 +4731,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -4736,19 +4748,19 @@
         <v>100</v>
       </c>
       <c r="B45" t="s">
+        <v>557</v>
+      </c>
+      <c r="C45" t="s">
         <v>558</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>559</v>
-      </c>
-      <c r="D45" t="s">
-        <v>560</v>
       </c>
       <c r="E45" t="s">
         <v>173</v>
       </c>
       <c r="F45" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G45">
         <v>750</v>
@@ -4760,7 +4772,7 @@
         <v>36</v>
       </c>
       <c r="J45" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K45" t="s">
         <v>23</v>
@@ -4775,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -4792,19 +4804,19 @@
         <v>101</v>
       </c>
       <c r="B46" t="s">
+        <v>564</v>
+      </c>
+      <c r="C46" t="s">
         <v>565</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>566</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>567</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>568</v>
-      </c>
-      <c r="F46" t="s">
-        <v>569</v>
       </c>
       <c r="G46">
         <v>630</v>
@@ -4816,7 +4828,7 @@
         <v>36</v>
       </c>
       <c r="J46" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K46" t="s">
         <v>23</v>
@@ -4831,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="P46" t="b">
         <v>1</v>
@@ -4848,7 +4860,7 @@
         <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C47" t="s">
         <v>49</v>
@@ -4887,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P47" t="b">
         <v>1</v>
@@ -4904,7 +4916,7 @@
         <v>18</v>
       </c>
       <c r="B48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C48" t="s">
         <v>24</v>
@@ -4943,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
@@ -4960,7 +4972,7 @@
         <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C49" t="s">
         <v>16</v>
@@ -4999,7 +5011,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
@@ -5016,7 +5028,7 @@
         <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C50" t="s">
         <v>24</v>
@@ -5055,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P50" t="b">
         <v>1</v>
@@ -5072,7 +5084,7 @@
         <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C51" t="s">
         <v>62</v>
@@ -5111,7 +5123,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P51" t="b">
         <v>1</v>
@@ -5128,7 +5140,7 @@
         <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C52" t="s">
         <v>67</v>
@@ -5167,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -5184,7 +5196,7 @@
         <v>23</v>
       </c>
       <c r="B53" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C53" t="s">
         <v>72</v>
@@ -5223,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -5240,7 +5252,7 @@
         <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C54" t="s">
         <v>44</v>
@@ -5279,7 +5291,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -5296,7 +5308,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C55" t="s">
         <v>80</v>
@@ -5335,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="O55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
@@ -5352,7 +5364,7 @@
         <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C56" t="s">
         <v>84</v>
@@ -5391,7 +5403,7 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
@@ -5408,7 +5420,7 @@
         <v>102</v>
       </c>
       <c r="B57" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C57" t="s">
         <v>44</v>
@@ -5420,7 +5432,7 @@
         <v>78</v>
       </c>
       <c r="F57" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G57">
         <v>900</v>
@@ -5447,7 +5459,7 @@
         <v>1</v>
       </c>
       <c r="O57" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -5464,19 +5476,19 @@
         <v>103</v>
       </c>
       <c r="B58" t="s">
+        <v>574</v>
+      </c>
+      <c r="C58" t="s">
         <v>575</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>576</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>577</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>578</v>
-      </c>
-      <c r="F58" t="s">
-        <v>579</v>
       </c>
       <c r="G58">
         <v>300</v>
@@ -5488,7 +5500,7 @@
         <v>21</v>
       </c>
       <c r="J58" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K58" t="s">
         <v>23</v>
@@ -5503,7 +5515,7 @@
         <v>1</v>
       </c>
       <c r="O58" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -5520,19 +5532,19 @@
         <v>104</v>
       </c>
       <c r="B59" t="s">
+        <v>581</v>
+      </c>
+      <c r="C59" t="s">
+        <v>565</v>
+      </c>
+      <c r="D59" t="s">
+        <v>566</v>
+      </c>
+      <c r="E59" t="s">
         <v>582</v>
       </c>
-      <c r="C59" t="s">
-        <v>566</v>
-      </c>
-      <c r="D59" t="s">
-        <v>567</v>
-      </c>
-      <c r="E59" t="s">
-        <v>583</v>
-      </c>
       <c r="F59" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G59">
         <v>630</v>
@@ -5544,7 +5556,7 @@
         <v>36</v>
       </c>
       <c r="J59" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="K59" t="s">
         <v>23</v>
@@ -5573,19 +5585,19 @@
         <v>105</v>
       </c>
       <c r="B60" t="s">
+        <v>583</v>
+      </c>
+      <c r="C60" t="s">
+        <v>543</v>
+      </c>
+      <c r="D60" t="s">
+        <v>537</v>
+      </c>
+      <c r="E60" t="s">
         <v>584</v>
       </c>
-      <c r="C60" t="s">
-        <v>544</v>
-      </c>
-      <c r="D60" t="s">
-        <v>538</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>585</v>
-      </c>
-      <c r="F60" t="s">
-        <v>586</v>
       </c>
       <c r="G60">
         <v>90</v>
@@ -5594,10 +5606,10 @@
         <v>42</v>
       </c>
       <c r="I60" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J60" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K60" t="s">
         <v>23</v>
@@ -5612,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
@@ -5629,19 +5641,19 @@
         <v>106</v>
       </c>
       <c r="B61" t="s">
+        <v>587</v>
+      </c>
+      <c r="C61" t="s">
         <v>588</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
+        <v>544</v>
+      </c>
+      <c r="E61" t="s">
         <v>589</v>
       </c>
-      <c r="D61" t="s">
-        <v>545</v>
-      </c>
-      <c r="E61" t="s">
-        <v>590</v>
-      </c>
       <c r="F61" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G61">
         <v>2</v>
@@ -5650,10 +5662,10 @@
         <v>20</v>
       </c>
       <c r="I61" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J61" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
@@ -5668,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -5685,19 +5697,19 @@
         <v>107</v>
       </c>
       <c r="B62" t="s">
+        <v>592</v>
+      </c>
+      <c r="C62" t="s">
         <v>593</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>594</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>595</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>596</v>
-      </c>
-      <c r="F62" t="s">
-        <v>597</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5709,10 +5721,10 @@
         <v>53</v>
       </c>
       <c r="J62" t="s">
+        <v>597</v>
+      </c>
+      <c r="K62" t="s">
         <v>598</v>
-      </c>
-      <c r="K62" t="s">
-        <v>599</v>
       </c>
       <c r="L62">
         <v>12</v>
@@ -5724,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5741,19 +5753,19 @@
         <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C63" t="s">
         <v>72</v>
       </c>
       <c r="D63" t="s">
+        <v>601</v>
+      </c>
+      <c r="E63" t="s">
         <v>602</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>603</v>
-      </c>
-      <c r="F63" t="s">
-        <v>604</v>
       </c>
       <c r="G63">
         <v>180</v>
@@ -5780,7 +5792,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5797,19 +5809,19 @@
         <v>109</v>
       </c>
       <c r="B64" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C64" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D64" t="s">
         <v>173</v>
       </c>
       <c r="E64" t="s">
+        <v>606</v>
+      </c>
+      <c r="F64" t="s">
         <v>607</v>
-      </c>
-      <c r="F64" t="s">
-        <v>608</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -5821,7 +5833,7 @@
         <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
@@ -5836,7 +5848,7 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5853,19 +5865,19 @@
         <v>110</v>
       </c>
       <c r="B65" t="s">
+        <v>609</v>
+      </c>
+      <c r="C65" t="s">
         <v>610</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>611</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>612</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>613</v>
-      </c>
-      <c r="F65" t="s">
-        <v>614</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -5874,10 +5886,10 @@
         <v>20</v>
       </c>
       <c r="I65" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J65" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
@@ -5892,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5909,16 +5921,16 @@
         <v>111</v>
       </c>
       <c r="B66" t="s">
+        <v>616</v>
+      </c>
+      <c r="C66" t="s">
         <v>617</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>618</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>619</v>
-      </c>
-      <c r="E66" t="s">
-        <v>620</v>
       </c>
       <c r="F66" t="s">
         <v>111</v>
@@ -5930,10 +5942,10 @@
         <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J66" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
@@ -5948,7 +5960,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5962,40 +5974,40 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B67" t="s">
-        <v>376</v>
+        <v>621</v>
       </c>
       <c r="C67" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="D67" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="E67" t="s">
-        <v>90</v>
+        <v>622</v>
       </c>
       <c r="F67" t="s">
-        <v>91</v>
+        <v>623</v>
       </c>
       <c r="G67">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H67" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>36</v>
+        <v>493</v>
       </c>
       <c r="J67" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -6004,13 +6016,13 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>267</v>
+        <v>624</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="b">
         <v>1</v>
@@ -6018,40 +6030,40 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B68" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C68" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D68" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E68" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F68" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G68">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H68" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I68" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J68" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -6060,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -6074,41 +6086,41 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C69" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D69" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E69" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F69" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H69" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J69" t="s">
+        <v>66</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69">
         <v>30</v>
       </c>
-      <c r="K69" t="s">
-        <v>23</v>
-      </c>
-      <c r="L69">
-        <v>12</v>
-      </c>
       <c r="M69" t="b">
         <v>0</v>
       </c>
@@ -6116,13 +6128,13 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="b">
         <v>1</v>
@@ -6130,55 +6142,55 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
+        <v>29</v>
+      </c>
+      <c r="B70" t="s">
+        <v>377</v>
+      </c>
+      <c r="C70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" t="s">
+        <v>54</v>
+      </c>
+      <c r="E70" t="s">
+        <v>55</v>
+      </c>
+      <c r="F70" t="s">
+        <v>61</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>28</v>
+      </c>
+      <c r="I70" t="s">
+        <v>96</v>
+      </c>
+      <c r="J70" t="s">
         <v>30</v>
       </c>
-      <c r="B70" t="s">
-        <v>379</v>
-      </c>
-      <c r="C70" t="s">
-        <v>97</v>
-      </c>
-      <c r="D70" t="s">
-        <v>98</v>
-      </c>
-      <c r="E70" t="s">
-        <v>99</v>
-      </c>
-      <c r="F70" t="s">
-        <v>100</v>
-      </c>
-      <c r="G70">
-        <v>100</v>
-      </c>
-      <c r="H70" t="s">
-        <v>20</v>
-      </c>
-      <c r="I70" t="s">
-        <v>101</v>
-      </c>
-      <c r="J70" t="s">
-        <v>102</v>
-      </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
       </c>
       <c r="N70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
@@ -6186,49 +6198,49 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B71" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C71" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D71" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E71" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F71" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G71">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H71" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I71" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J71" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
       </c>
       <c r="N71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -6242,22 +6254,22 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D72" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E72" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F72" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G72">
         <v>500</v>
@@ -6269,13 +6281,13 @@
         <v>107</v>
       </c>
       <c r="J72" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6284,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -6298,40 +6310,40 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C73" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D73" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E73" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F73" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H73" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J73" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -6340,13 +6352,13 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -6354,40 +6366,40 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F74" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G74">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I74" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J74" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -6396,13 +6408,13 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
@@ -6410,40 +6422,40 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
+        <v>34</v>
+      </c>
+      <c r="B75" t="s">
+        <v>382</v>
+      </c>
+      <c r="C75" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" t="s">
+        <v>114</v>
+      </c>
+      <c r="F75" t="s">
+        <v>115</v>
+      </c>
+      <c r="G75">
+        <v>300</v>
+      </c>
+      <c r="H75" t="s">
         <v>35</v>
       </c>
-      <c r="B75" t="s">
-        <v>384</v>
-      </c>
-      <c r="C75" t="s">
-        <v>117</v>
-      </c>
-      <c r="D75" t="s">
-        <v>118</v>
-      </c>
-      <c r="E75" t="s">
-        <v>119</v>
-      </c>
-      <c r="F75" t="s">
-        <v>120</v>
-      </c>
-      <c r="G75">
-        <v>500</v>
-      </c>
-      <c r="H75" t="s">
-        <v>42</v>
-      </c>
       <c r="I75" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -6452,7 +6464,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6466,40 +6478,40 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B76" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C76" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D76" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E76" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F76" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G76">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H76" t="s">
         <v>42</v>
       </c>
       <c r="I76" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6508,13 +6520,13 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -6522,40 +6534,40 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B77" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D77" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E77" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F77" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G77">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H77" t="s">
         <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J77" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6564,13 +6576,13 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
@@ -6578,34 +6590,34 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B78" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C78" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E78" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F78" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G78">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H78" t="s">
         <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J78" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
@@ -6620,13 +6632,13 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
@@ -6634,40 +6646,40 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B79" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C79" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D79" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E79" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F79" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G79">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H79" t="s">
         <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6676,7 +6688,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6690,40 +6702,40 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B80" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C80" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D80" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E80" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F80" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H80" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J80" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6732,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6746,55 +6758,55 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B81" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C81" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E81" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F81" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G81">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I81" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -6802,10 +6814,10 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C82" t="s">
         <v>138</v>
@@ -6814,10 +6826,10 @@
         <v>139</v>
       </c>
       <c r="E82" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F82" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G82">
         <v>1000</v>
@@ -6841,10 +6853,10 @@
         <v>1</v>
       </c>
       <c r="N82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6858,22 +6870,22 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B83" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C83" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D83" t="s">
         <v>139</v>
       </c>
       <c r="E83" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F83" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G83">
         <v>1000</v>
@@ -6885,7 +6897,7 @@
         <v>142</v>
       </c>
       <c r="J83" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
@@ -6900,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6914,55 +6926,55 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B84" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C84" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D84" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E84" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F84" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G84">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H84" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J84" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" t="b">
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
@@ -6970,55 +6982,55 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B85" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C85" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D85" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E85" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F85" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H85" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I85" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J85" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K85" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L85">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
       <c r="N85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -7026,55 +7038,55 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C86" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D86" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E86" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F86" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G86">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J86" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K86" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L86">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
       <c r="N86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -7082,34 +7094,34 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C87" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D87" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E87" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F87" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G87">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H87" t="s">
         <v>42</v>
       </c>
       <c r="I87" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J87" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
@@ -7124,7 +7136,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7138,22 +7150,22 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B88" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C88" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D88" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E88" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F88" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G88">
         <v>500</v>
@@ -7165,7 +7177,7 @@
         <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
@@ -7180,7 +7192,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7194,25 +7206,25 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B89" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C89" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D89" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E89" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F89" t="s">
-        <v>178</v>
+        <v>70</v>
       </c>
       <c r="G89">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H89" t="s">
         <v>42</v>
@@ -7221,7 +7233,7 @@
         <v>21</v>
       </c>
       <c r="J89" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
@@ -7236,7 +7248,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7250,37 +7262,37 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
+        <v>49</v>
+      </c>
+      <c r="B90" t="s">
+        <v>397</v>
+      </c>
+      <c r="C90" t="s">
+        <v>175</v>
+      </c>
+      <c r="D90" t="s">
+        <v>176</v>
+      </c>
+      <c r="E90" t="s">
+        <v>625</v>
+      </c>
+      <c r="F90" t="s">
+        <v>177</v>
+      </c>
+      <c r="G90">
         <v>50</v>
       </c>
-      <c r="B90" t="s">
-        <v>399</v>
-      </c>
-      <c r="C90" t="s">
-        <v>180</v>
-      </c>
-      <c r="D90" t="s">
-        <v>181</v>
-      </c>
-      <c r="E90" t="s">
-        <v>182</v>
-      </c>
-      <c r="F90" t="s">
-        <v>183</v>
-      </c>
-      <c r="G90">
-        <v>12</v>
-      </c>
       <c r="H90" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I90" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="K90" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="L90">
         <v>12</v>
@@ -7292,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7301,45 +7313,45 @@
         <v>1</v>
       </c>
       <c r="R90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B91" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C91" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D91" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E91" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F91" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G91">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H91" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="I91" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="J91" t="s">
-        <v>556</v>
+        <v>183</v>
       </c>
       <c r="K91" t="s">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="L91">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -7348,7 +7360,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7362,40 +7374,40 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B92" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C92" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D92" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E92" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F92" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G92">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H92" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="I92" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="J92" t="s">
-        <v>184</v>
+        <v>555</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
       </c>
       <c r="L92">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7404,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7418,40 +7430,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
+        <v>52</v>
+      </c>
+      <c r="B93" t="s">
+        <v>400</v>
+      </c>
+      <c r="C93" t="s">
+        <v>192</v>
+      </c>
+      <c r="D93" t="s">
+        <v>180</v>
+      </c>
+      <c r="E93" t="s">
+        <v>181</v>
+      </c>
+      <c r="F93" t="s">
+        <v>182</v>
+      </c>
+      <c r="G93">
+        <v>24</v>
+      </c>
+      <c r="H93" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s">
         <v>53</v>
       </c>
-      <c r="B93" t="s">
-        <v>402</v>
-      </c>
-      <c r="C93" t="s">
-        <v>31</v>
-      </c>
-      <c r="D93" t="s">
-        <v>194</v>
-      </c>
-      <c r="E93" t="s">
-        <v>195</v>
-      </c>
-      <c r="F93" t="s">
-        <v>196</v>
-      </c>
-      <c r="G93">
-        <v>1.5</v>
-      </c>
-      <c r="H93" t="s">
-        <v>28</v>
-      </c>
-      <c r="I93" t="s">
-        <v>36</v>
-      </c>
       <c r="J93" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7460,7 +7472,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7474,52 +7486,52 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B94" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C94" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E94" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F94" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G94">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H94" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I94" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J94" t="s">
-        <v>201</v>
+        <v>37</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
       </c>
       <c r="N94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q94" t="b">
         <v>1</v>
@@ -7530,55 +7542,55 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B95" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C95" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D95" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E95" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F95" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G95">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H95" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I95" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J95" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
       </c>
       <c r="N95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" t="b">
         <v>1</v>
@@ -7586,40 +7598,40 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B96" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C96" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="D96" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E96" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F96" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G96">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H96" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I96" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="J96" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -7628,7 +7640,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7642,22 +7654,22 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B97" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C97" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D97" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E97" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="F97" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G97">
         <v>500</v>
@@ -7666,7 +7678,7 @@
         <v>42</v>
       </c>
       <c r="I97" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J97" t="s">
         <v>66</v>
@@ -7684,7 +7696,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7698,22 +7710,22 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B98" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C98" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D98" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E98" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F98" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G98">
         <v>500</v>
@@ -7722,7 +7734,7 @@
         <v>42</v>
       </c>
       <c r="I98" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J98" t="s">
         <v>66</v>
@@ -7731,7 +7743,7 @@
         <v>23</v>
       </c>
       <c r="L98">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
@@ -7740,7 +7752,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7754,34 +7766,34 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B99" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C99" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="D99" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="E99" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F99" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H99" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I99" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="J99" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
@@ -7796,13 +7808,13 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
@@ -7810,34 +7822,34 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B100" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C100" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D100" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E100" t="s">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="F100" t="s">
-        <v>216</v>
+        <v>56</v>
       </c>
       <c r="G100">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H100" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I100" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J100" t="s">
-        <v>557</v>
+        <v>148</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
@@ -7852,7 +7864,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -7866,49 +7878,49 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B101" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C101" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D101" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="E101" t="s">
-        <v>219</v>
+        <v>55</v>
       </c>
       <c r="F101" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G101">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H101" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I101" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J101" t="s">
-        <v>217</v>
+        <v>556</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
       </c>
       <c r="L101">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
       </c>
       <c r="N101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -7922,22 +7934,22 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B102" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C102" t="s">
+        <v>216</v>
+      </c>
+      <c r="D102" t="s">
         <v>217</v>
       </c>
-      <c r="D102" t="s">
-        <v>221</v>
-      </c>
       <c r="E102" t="s">
+        <v>218</v>
+      </c>
+      <c r="F102" t="s">
         <v>219</v>
-      </c>
-      <c r="F102" t="s">
-        <v>222</v>
       </c>
       <c r="G102">
         <v>20</v>
@@ -7949,7 +7961,7 @@
         <v>101</v>
       </c>
       <c r="J102" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
@@ -7964,13 +7976,13 @@
         <v>0</v>
       </c>
       <c r="O102" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" t="b">
         <v>1</v>
@@ -7978,49 +7990,49 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B103" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C103" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D103" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="E103" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="F103" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="G103">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H103" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I103" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J103" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
       </c>
       <c r="L103">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M103" t="b">
         <v>0</v>
       </c>
       <c r="N103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8034,34 +8046,34 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B104" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C104" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D104" t="s">
+        <v>201</v>
+      </c>
+      <c r="E104" t="s">
         <v>202</v>
       </c>
-      <c r="E104" t="s">
-        <v>32</v>
-      </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="G104">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H104" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I104" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J104" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
@@ -8076,7 +8088,7 @@
         <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8090,40 +8102,40 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B105" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C105" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D105" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="E105" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="F105" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G105">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H105" t="s">
         <v>42</v>
       </c>
       <c r="I105" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J105" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
       </c>
       <c r="L105">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
@@ -8132,13 +8144,13 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
       </c>
       <c r="Q105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" t="b">
         <v>1</v>
@@ -8146,40 +8158,40 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B106" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C106" t="s">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="D106" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E106" t="s">
+        <v>228</v>
+      </c>
+      <c r="F106" t="s">
         <v>229</v>
       </c>
-      <c r="F106" t="s">
-        <v>47</v>
-      </c>
       <c r="G106">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H106" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I106" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J106" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
       </c>
       <c r="L106">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
@@ -8188,7 +8200,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8202,40 +8214,40 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B107" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C107" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D107" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="E107" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F107" t="s">
-        <v>196</v>
+        <v>47</v>
       </c>
       <c r="G107">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H107" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I107" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J107" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
       </c>
       <c r="L107">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M107" t="b">
         <v>0</v>
@@ -8244,13 +8256,13 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
       </c>
       <c r="Q107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" t="b">
         <v>1</v>
@@ -8258,34 +8270,34 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B108" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C108" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E108" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F108" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G108">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H108" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I108" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
       <c r="J108" t="s">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
@@ -8300,7 +8312,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8314,34 +8326,34 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B109" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C109" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D109" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E109" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F109" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G109">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H109" t="s">
         <v>35</v>
       </c>
       <c r="I109" t="s">
+        <v>190</v>
+      </c>
+      <c r="J109" t="s">
         <v>191</v>
-      </c>
-      <c r="J109" t="s">
-        <v>192</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
@@ -8356,7 +8368,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8370,34 +8382,34 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B110" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C110" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D110" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E110" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F110" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G110">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H110" t="s">
         <v>35</v>
       </c>
       <c r="I110" t="s">
+        <v>190</v>
+      </c>
+      <c r="J110" t="s">
         <v>191</v>
-      </c>
-      <c r="J110" t="s">
-        <v>192</v>
       </c>
       <c r="K110" t="s">
         <v>23</v>
@@ -8412,7 +8424,7 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
@@ -8426,41 +8438,41 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B111" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C111" t="s">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="D111" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="E111" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F111" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="G111">
+        <v>250</v>
+      </c>
+      <c r="H111" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111" t="s">
+        <v>190</v>
+      </c>
+      <c r="J111" t="s">
+        <v>191</v>
+      </c>
+      <c r="K111" t="s">
+        <v>23</v>
+      </c>
+      <c r="L111">
         <v>6</v>
       </c>
-      <c r="H111" t="s">
-        <v>20</v>
-      </c>
-      <c r="I111" t="s">
-        <v>239</v>
-      </c>
-      <c r="J111" t="s">
-        <v>235</v>
-      </c>
-      <c r="K111" t="s">
-        <v>23</v>
-      </c>
-      <c r="L111">
-        <v>1</v>
-      </c>
       <c r="M111" t="b">
         <v>0</v>
       </c>
@@ -8468,13 +8480,13 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="P111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R111" t="b">
         <v>1</v>
@@ -8482,57 +8494,113 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B112" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C112" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="D112" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="E112" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="F112" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G112">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H112" t="s">
         <v>20</v>
       </c>
       <c r="I112" t="s">
+        <v>238</v>
+      </c>
+      <c r="J112" t="s">
+        <v>234</v>
+      </c>
+      <c r="K112" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="M112" t="b">
+        <v>0</v>
+      </c>
+      <c r="N112" t="b">
+        <v>1</v>
+      </c>
+      <c r="O112" t="s">
+        <v>310</v>
+      </c>
+      <c r="P112" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="b">
+        <v>1</v>
+      </c>
+      <c r="R112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>72</v>
+      </c>
+      <c r="B113" t="s">
+        <v>420</v>
+      </c>
+      <c r="C113" t="s">
+        <v>196</v>
+      </c>
+      <c r="D113" t="s">
+        <v>197</v>
+      </c>
+      <c r="E113" t="s">
+        <v>198</v>
+      </c>
+      <c r="F113" t="s">
+        <v>239</v>
+      </c>
+      <c r="G113">
+        <v>4</v>
+      </c>
+      <c r="H113" t="s">
+        <v>20</v>
+      </c>
+      <c r="I113" t="s">
         <v>21</v>
       </c>
-      <c r="J112" t="s">
-        <v>201</v>
-      </c>
-      <c r="K112" t="s">
-        <v>23</v>
-      </c>
-      <c r="L112">
+      <c r="J113" t="s">
+        <v>200</v>
+      </c>
+      <c r="K113" t="s">
+        <v>23</v>
+      </c>
+      <c r="L113">
         <v>10</v>
       </c>
-      <c r="M112" t="b">
-        <v>0</v>
-      </c>
-      <c r="N112" t="b">
-        <v>0</v>
-      </c>
-      <c r="O112" t="s">
-        <v>312</v>
-      </c>
-      <c r="P112" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q112" t="b">
-        <v>1</v>
-      </c>
-      <c r="R112" t="b">
+      <c r="M113" t="b">
+        <v>0</v>
+      </c>
+      <c r="N113" t="b">
+        <v>0</v>
+      </c>
+      <c r="O113" t="s">
+        <v>311</v>
+      </c>
+      <c r="P113" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q113" t="b">
+        <v>1</v>
+      </c>
+      <c r="R113" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77784C16-0B5F-46E5-82FF-C7EC7E066A46}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7B1938-FA9F-462D-9DDB-5FD2FFE55E8C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="58" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="59" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="632">
   <si>
     <t>Codigo</t>
   </si>
@@ -1904,6 +1904,24 @@
   </si>
   <si>
     <t>sin gluten</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7798140257431.png</t>
+  </si>
+  <si>
+    <t>7790127784510</t>
+  </si>
+  <si>
+    <t>Salsa</t>
+  </si>
+  <si>
+    <t>de ají</t>
+  </si>
+  <si>
+    <t>Vanoli</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790127784510.png</t>
   </si>
 </sst>
 </file>
@@ -2255,8 +2273,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2491E691-32D8-4EEA-9C6C-D4234EC859B7}">
-  <dimension ref="A1:R113"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC6EFCB-6F72-4E19-9EF3-CDC62E1FF231}">
+  <dimension ref="A1:R114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -5570,6 +5588,9 @@
       <c r="N59" t="b">
         <v>1</v>
       </c>
+      <c r="O59" t="s">
+        <v>626</v>
+      </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
@@ -5638,40 +5659,40 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B61" t="s">
-        <v>587</v>
+        <v>627</v>
       </c>
       <c r="C61" t="s">
-        <v>588</v>
+        <v>628</v>
       </c>
       <c r="D61" t="s">
-        <v>544</v>
+        <v>629</v>
       </c>
       <c r="E61" t="s">
-        <v>589</v>
+        <v>231</v>
       </c>
       <c r="F61" t="s">
-        <v>520</v>
+        <v>630</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I61" t="s">
-        <v>493</v>
+        <v>36</v>
       </c>
       <c r="J61" t="s">
-        <v>590</v>
+        <v>125</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
       </c>
       <c r="L61">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
@@ -5680,7 +5701,7 @@
         <v>1</v>
       </c>
       <c r="O61" t="s">
-        <v>591</v>
+        <v>631</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -5694,37 +5715,37 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B62" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C62" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D62" t="s">
-        <v>594</v>
+        <v>544</v>
       </c>
       <c r="E62" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="F62" t="s">
-        <v>596</v>
+        <v>520</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" t="s">
         <v>20</v>
       </c>
       <c r="I62" t="s">
-        <v>53</v>
+        <v>493</v>
       </c>
       <c r="J62" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="K62" t="s">
-        <v>598</v>
+        <v>23</v>
       </c>
       <c r="L62">
         <v>12</v>
@@ -5733,10 +5754,10 @@
         <v>0</v>
       </c>
       <c r="N62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5750,49 +5771,49 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B63" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C63" t="s">
-        <v>72</v>
+        <v>593</v>
       </c>
       <c r="D63" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="E63" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="F63" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="G63">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I63" t="s">
         <v>53</v>
       </c>
       <c r="J63" t="s">
-        <v>76</v>
+        <v>597</v>
       </c>
       <c r="K63" t="s">
-        <v>23</v>
+        <v>598</v>
       </c>
       <c r="L63">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
       </c>
       <c r="N63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5806,49 +5827,49 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B64" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C64" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="D64" t="s">
-        <v>173</v>
+        <v>601</v>
       </c>
       <c r="E64" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F64" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H64" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J64" t="s">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5857,27 +5878,27 @@
         <v>1</v>
       </c>
       <c r="R64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B65" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C65" t="s">
-        <v>610</v>
+        <v>196</v>
       </c>
       <c r="D65" t="s">
-        <v>611</v>
+        <v>173</v>
       </c>
       <c r="E65" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="F65" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -5886,16 +5907,16 @@
         <v>20</v>
       </c>
       <c r="I65" t="s">
-        <v>493</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s">
-        <v>614</v>
+        <v>244</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -5904,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5913,39 +5934,39 @@
         <v>1</v>
       </c>
       <c r="R65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B66" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C66" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="D66" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E66" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="F66" t="s">
-        <v>111</v>
+        <v>613</v>
       </c>
       <c r="G66">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I66" t="s">
         <v>493</v>
       </c>
       <c r="J66" t="s">
-        <v>579</v>
+        <v>614</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
@@ -5957,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="N66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5974,25 +5995,25 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B67" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C67" t="s">
-        <v>175</v>
+        <v>617</v>
       </c>
       <c r="D67" t="s">
-        <v>176</v>
+        <v>618</v>
       </c>
       <c r="E67" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F67" t="s">
-        <v>623</v>
+        <v>111</v>
       </c>
       <c r="G67">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H67" t="s">
         <v>42</v>
@@ -6001,13 +6022,13 @@
         <v>493</v>
       </c>
       <c r="J67" t="s">
-        <v>178</v>
+        <v>579</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -6016,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -6030,40 +6051,40 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B68" t="s">
-        <v>375</v>
+        <v>621</v>
       </c>
       <c r="C68" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="D68" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="E68" t="s">
-        <v>90</v>
+        <v>622</v>
       </c>
       <c r="F68" t="s">
-        <v>91</v>
+        <v>623</v>
       </c>
       <c r="G68">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H68" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>36</v>
+        <v>493</v>
       </c>
       <c r="J68" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -6072,13 +6093,13 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>266</v>
+        <v>624</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="b">
         <v>1</v>
@@ -6086,40 +6107,40 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B69" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C69" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D69" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E69" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F69" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G69">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H69" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I69" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J69" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -6128,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -6142,41 +6163,41 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C70" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D70" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F70" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H70" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I70" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J70" t="s">
+        <v>66</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70">
         <v>30</v>
       </c>
-      <c r="K70" t="s">
-        <v>23</v>
-      </c>
-      <c r="L70">
-        <v>12</v>
-      </c>
       <c r="M70" t="b">
         <v>0</v>
       </c>
@@ -6184,13 +6205,13 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
@@ -6198,55 +6219,55 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
+        <v>29</v>
+      </c>
+      <c r="B71" t="s">
+        <v>377</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" t="s">
+        <v>55</v>
+      </c>
+      <c r="F71" t="s">
+        <v>61</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>28</v>
+      </c>
+      <c r="I71" t="s">
+        <v>96</v>
+      </c>
+      <c r="J71" t="s">
         <v>30</v>
       </c>
-      <c r="B71" t="s">
-        <v>378</v>
-      </c>
-      <c r="C71" t="s">
-        <v>97</v>
-      </c>
-      <c r="D71" t="s">
-        <v>98</v>
-      </c>
-      <c r="E71" t="s">
-        <v>99</v>
-      </c>
-      <c r="F71" t="s">
-        <v>100</v>
-      </c>
-      <c r="G71">
-        <v>100</v>
-      </c>
-      <c r="H71" t="s">
-        <v>20</v>
-      </c>
-      <c r="I71" t="s">
-        <v>101</v>
-      </c>
-      <c r="J71" t="s">
-        <v>102</v>
-      </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
       </c>
       <c r="N71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
@@ -6254,49 +6275,49 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B72" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D72" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E72" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F72" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G72">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H72" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I72" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J72" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
       </c>
       <c r="N72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -6310,22 +6331,22 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B73" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D73" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E73" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F73" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G73">
         <v>500</v>
@@ -6337,13 +6358,13 @@
         <v>107</v>
       </c>
       <c r="J73" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -6352,7 +6373,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -6366,40 +6387,40 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C74" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D74" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E74" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F74" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H74" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I74" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J74" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -6408,13 +6429,13 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
@@ -6422,40 +6443,40 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F75" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G75">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I75" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -6464,13 +6485,13 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -6478,40 +6499,40 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
+        <v>34</v>
+      </c>
+      <c r="B76" t="s">
+        <v>382</v>
+      </c>
+      <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76" t="s">
+        <v>114</v>
+      </c>
+      <c r="F76" t="s">
+        <v>115</v>
+      </c>
+      <c r="G76">
+        <v>300</v>
+      </c>
+      <c r="H76" t="s">
         <v>35</v>
       </c>
-      <c r="B76" t="s">
-        <v>383</v>
-      </c>
-      <c r="C76" t="s">
-        <v>117</v>
-      </c>
-      <c r="D76" t="s">
-        <v>118</v>
-      </c>
-      <c r="E76" t="s">
-        <v>119</v>
-      </c>
-      <c r="F76" t="s">
-        <v>120</v>
-      </c>
-      <c r="G76">
-        <v>500</v>
-      </c>
-      <c r="H76" t="s">
-        <v>42</v>
-      </c>
       <c r="I76" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J76" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6520,7 +6541,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6534,40 +6555,40 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B77" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C77" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D77" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E77" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F77" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G77">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H77" t="s">
         <v>42</v>
       </c>
       <c r="I77" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6576,13 +6597,13 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
@@ -6590,40 +6611,40 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B78" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D78" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E78" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F78" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G78">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H78" t="s">
         <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J78" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6632,13 +6653,13 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
@@ -6646,34 +6667,34 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B79" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C79" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E79" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F79" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G79">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H79" t="s">
         <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J79" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
@@ -6688,13 +6709,13 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -6702,40 +6723,40 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B80" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C80" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D80" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E80" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F80" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G80">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H80" t="s">
         <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6744,7 +6765,7 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
@@ -6758,40 +6779,40 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B81" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C81" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D81" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E81" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F81" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H81" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J81" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6800,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6814,55 +6835,55 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B82" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C82" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D82" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E82" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F82" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G82">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I82" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J82" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
@@ -6870,10 +6891,10 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C83" t="s">
         <v>138</v>
@@ -6882,10 +6903,10 @@
         <v>139</v>
       </c>
       <c r="E83" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F83" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G83">
         <v>1000</v>
@@ -6909,10 +6930,10 @@
         <v>1</v>
       </c>
       <c r="N83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6926,22 +6947,22 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C84" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D84" t="s">
         <v>139</v>
       </c>
       <c r="E84" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F84" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G84">
         <v>1000</v>
@@ -6953,7 +6974,7 @@
         <v>142</v>
       </c>
       <c r="J84" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
@@ -6968,7 +6989,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -6982,55 +7003,55 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B85" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C85" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D85" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E85" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F85" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G85">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H85" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I85" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J85" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -7038,55 +7059,55 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B86" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C86" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D86" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E86" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F86" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H86" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I86" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J86" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K86" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L86">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
       <c r="N86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -7094,55 +7115,55 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C87" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D87" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E87" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F87" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G87">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I87" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J87" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K87" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L87">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
       </c>
       <c r="N87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -7150,34 +7171,34 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C88" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D88" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E88" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F88" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G88">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H88" t="s">
         <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J88" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
@@ -7192,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
@@ -7206,22 +7227,22 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B89" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C89" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D89" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E89" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F89" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G89">
         <v>500</v>
@@ -7233,7 +7254,7 @@
         <v>21</v>
       </c>
       <c r="J89" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
@@ -7248,7 +7269,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7262,25 +7283,25 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B90" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C90" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D90" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E90" t="s">
-        <v>625</v>
+        <v>173</v>
       </c>
       <c r="F90" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="G90">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H90" t="s">
         <v>42</v>
@@ -7289,7 +7310,7 @@
         <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
@@ -7304,7 +7325,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7313,42 +7334,42 @@
         <v>1</v>
       </c>
       <c r="R90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
+        <v>49</v>
+      </c>
+      <c r="B91" t="s">
+        <v>397</v>
+      </c>
+      <c r="C91" t="s">
+        <v>175</v>
+      </c>
+      <c r="D91" t="s">
+        <v>176</v>
+      </c>
+      <c r="E91" t="s">
+        <v>625</v>
+      </c>
+      <c r="F91" t="s">
+        <v>177</v>
+      </c>
+      <c r="G91">
         <v>50</v>
       </c>
-      <c r="B91" t="s">
-        <v>398</v>
-      </c>
-      <c r="C91" t="s">
-        <v>179</v>
-      </c>
-      <c r="D91" t="s">
-        <v>180</v>
-      </c>
-      <c r="E91" t="s">
-        <v>181</v>
-      </c>
-      <c r="F91" t="s">
-        <v>182</v>
-      </c>
-      <c r="G91">
-        <v>12</v>
-      </c>
       <c r="H91" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J91" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K91" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="L91">
         <v>12</v>
@@ -7360,7 +7381,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7369,45 +7390,45 @@
         <v>1</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B92" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C92" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D92" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E92" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F92" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G92">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H92" t="s">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="I92" t="s">
-        <v>190</v>
+        <v>53</v>
       </c>
       <c r="J92" t="s">
-        <v>555</v>
+        <v>183</v>
       </c>
       <c r="K92" t="s">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="L92">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -7416,7 +7437,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7430,40 +7451,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B93" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C93" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D93" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E93" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F93" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G93">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H93" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="I93" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="J93" t="s">
-        <v>183</v>
+        <v>555</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7472,7 +7493,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7486,40 +7507,40 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
+        <v>52</v>
+      </c>
+      <c r="B94" t="s">
+        <v>400</v>
+      </c>
+      <c r="C94" t="s">
+        <v>192</v>
+      </c>
+      <c r="D94" t="s">
+        <v>180</v>
+      </c>
+      <c r="E94" t="s">
+        <v>181</v>
+      </c>
+      <c r="F94" t="s">
+        <v>182</v>
+      </c>
+      <c r="G94">
+        <v>24</v>
+      </c>
+      <c r="H94" t="s">
+        <v>20</v>
+      </c>
+      <c r="I94" t="s">
         <v>53</v>
       </c>
-      <c r="B94" t="s">
-        <v>401</v>
-      </c>
-      <c r="C94" t="s">
-        <v>31</v>
-      </c>
-      <c r="D94" t="s">
-        <v>193</v>
-      </c>
-      <c r="E94" t="s">
-        <v>194</v>
-      </c>
-      <c r="F94" t="s">
-        <v>195</v>
-      </c>
-      <c r="G94">
-        <v>1.5</v>
-      </c>
-      <c r="H94" t="s">
-        <v>28</v>
-      </c>
-      <c r="I94" t="s">
-        <v>36</v>
-      </c>
       <c r="J94" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7528,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7542,52 +7563,52 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B95" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C95" t="s">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E95" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F95" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G95">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H95" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I95" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J95" t="s">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
       </c>
       <c r="N95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" t="b">
         <v>1</v>
@@ -7598,55 +7619,55 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B96" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C96" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D96" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E96" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F96" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G96">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H96" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I96" t="s">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="J96" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
       </c>
       <c r="N96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="b">
         <v>1</v>
@@ -7654,40 +7675,40 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B97" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="D97" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E97" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F97" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G97">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H97" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I97" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J97" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -7696,7 +7717,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7710,19 +7731,19 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B98" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C98" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D98" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E98" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F98" t="s">
         <v>207</v>
@@ -7752,7 +7773,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7766,19 +7787,19 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B99" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C99" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D99" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E99" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F99" t="s">
         <v>207</v>
@@ -7799,7 +7820,7 @@
         <v>23</v>
       </c>
       <c r="L99">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -7808,7 +7829,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7822,34 +7843,34 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B100" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C100" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="D100" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E100" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F100" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H100" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I100" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="J100" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
@@ -7864,13 +7885,13 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="b">
         <v>1</v>
@@ -7878,34 +7899,34 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B101" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C101" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D101" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E101" t="s">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="F101" t="s">
-        <v>215</v>
+        <v>56</v>
       </c>
       <c r="G101">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I101" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J101" t="s">
-        <v>556</v>
+        <v>148</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
@@ -7920,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -7934,49 +7955,49 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B102" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C102" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="D102" t="s">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="E102" t="s">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="F102" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G102">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H102" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I102" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J102" t="s">
-        <v>216</v>
+        <v>556</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
       </c>
       <c r="L102">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
       </c>
       <c r="N102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -7990,22 +8011,22 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B103" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C103" t="s">
         <v>216</v>
       </c>
       <c r="D103" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E103" t="s">
         <v>218</v>
       </c>
       <c r="F103" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G103">
         <v>20</v>
@@ -8032,13 +8053,13 @@
         <v>0</v>
       </c>
       <c r="O103" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R103" t="b">
         <v>1</v>
@@ -8046,49 +8067,49 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B104" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C104" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D104" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="E104" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="F104" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="G104">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H104" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I104" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J104" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
       </c>
       <c r="L104">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
       </c>
       <c r="N104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8102,34 +8123,34 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B105" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C105" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D105" t="s">
         <v>201</v>
       </c>
       <c r="E105" t="s">
-        <v>32</v>
+        <v>202</v>
       </c>
       <c r="F105" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="G105">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H105" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I105" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J105" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
@@ -8144,7 +8165,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8158,40 +8179,40 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B106" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C106" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D106" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="E106" t="s">
-        <v>228</v>
+        <v>32</v>
       </c>
       <c r="F106" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G106">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H106" t="s">
         <v>42</v>
       </c>
       <c r="I106" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J106" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
       </c>
       <c r="L106">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
@@ -8200,13 +8221,13 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
       </c>
       <c r="Q106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" t="b">
         <v>1</v>
@@ -8214,40 +8235,40 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B107" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C107" t="s">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="D107" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E107" t="s">
         <v>228</v>
       </c>
       <c r="F107" t="s">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H107" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I107" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J107" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
       </c>
       <c r="L107">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M107" t="b">
         <v>0</v>
@@ -8256,7 +8277,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8270,40 +8291,40 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B108" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C108" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D108" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="E108" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F108" t="s">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="G108">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H108" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I108" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J108" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
       </c>
       <c r="L108">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
@@ -8312,13 +8333,13 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
       </c>
       <c r="Q108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" t="b">
         <v>1</v>
@@ -8326,34 +8347,34 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B109" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C109" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E109" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F109" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G109">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H109" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I109" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="J109" t="s">
-        <v>191</v>
+        <v>37</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
@@ -8368,7 +8389,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8382,10 +8403,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B110" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C110" t="s">
         <v>185</v>
@@ -8394,13 +8415,13 @@
         <v>201</v>
       </c>
       <c r="E110" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F110" t="s">
         <v>203</v>
       </c>
       <c r="G110">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H110" t="s">
         <v>35</v>
@@ -8424,7 +8445,7 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
@@ -8438,10 +8459,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B111" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C111" t="s">
         <v>185</v>
@@ -8456,7 +8477,7 @@
         <v>203</v>
       </c>
       <c r="G111">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H111" t="s">
         <v>35</v>
@@ -8480,7 +8501,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
@@ -8494,41 +8515,41 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B112" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C112" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="D112" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="E112" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F112" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="G112">
+        <v>250</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112" t="s">
+        <v>190</v>
+      </c>
+      <c r="J112" t="s">
+        <v>191</v>
+      </c>
+      <c r="K112" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112">
         <v>6</v>
       </c>
-      <c r="H112" t="s">
-        <v>20</v>
-      </c>
-      <c r="I112" t="s">
-        <v>238</v>
-      </c>
-      <c r="J112" t="s">
-        <v>234</v>
-      </c>
-      <c r="K112" t="s">
-        <v>23</v>
-      </c>
-      <c r="L112">
-        <v>1</v>
-      </c>
       <c r="M112" t="b">
         <v>0</v>
       </c>
@@ -8536,13 +8557,13 @@
         <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R112" t="b">
         <v>1</v>
@@ -8550,57 +8571,113 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B113" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C113" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="D113" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="E113" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F113" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G113">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H113" t="s">
         <v>20</v>
       </c>
       <c r="I113" t="s">
+        <v>238</v>
+      </c>
+      <c r="J113" t="s">
+        <v>234</v>
+      </c>
+      <c r="K113" t="s">
+        <v>23</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113" t="b">
+        <v>0</v>
+      </c>
+      <c r="N113" t="b">
+        <v>1</v>
+      </c>
+      <c r="O113" t="s">
+        <v>310</v>
+      </c>
+      <c r="P113" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="b">
+        <v>1</v>
+      </c>
+      <c r="R113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>72</v>
+      </c>
+      <c r="B114" t="s">
+        <v>420</v>
+      </c>
+      <c r="C114" t="s">
+        <v>196</v>
+      </c>
+      <c r="D114" t="s">
+        <v>197</v>
+      </c>
+      <c r="E114" t="s">
+        <v>198</v>
+      </c>
+      <c r="F114" t="s">
+        <v>239</v>
+      </c>
+      <c r="G114">
+        <v>4</v>
+      </c>
+      <c r="H114" t="s">
+        <v>20</v>
+      </c>
+      <c r="I114" t="s">
         <v>21</v>
       </c>
-      <c r="J113" t="s">
+      <c r="J114" t="s">
         <v>200</v>
       </c>
-      <c r="K113" t="s">
-        <v>23</v>
-      </c>
-      <c r="L113">
+      <c r="K114" t="s">
+        <v>23</v>
+      </c>
+      <c r="L114">
         <v>10</v>
       </c>
-      <c r="M113" t="b">
-        <v>0</v>
-      </c>
-      <c r="N113" t="b">
-        <v>0</v>
-      </c>
-      <c r="O113" t="s">
+      <c r="M114" t="b">
+        <v>0</v>
+      </c>
+      <c r="N114" t="b">
+        <v>0</v>
+      </c>
+      <c r="O114" t="s">
         <v>311</v>
       </c>
-      <c r="P113" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q113" t="b">
-        <v>1</v>
-      </c>
-      <c r="R113" t="b">
+      <c r="P114" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q114" t="b">
+        <v>1</v>
+      </c>
+      <c r="R114" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7B1938-FA9F-462D-9DDB-5FD2FFE55E8C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F67C8B-CA92-4AEE-B8D8-DB20C34D4383}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="59" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="61" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="635">
   <si>
     <t>Codigo</t>
   </si>
@@ -1922,6 +1922,15 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790127784510.png</t>
+  </si>
+  <si>
+    <t>7790127784411</t>
+  </si>
+  <si>
+    <t>picante</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790127784411.png</t>
   </si>
 </sst>
 </file>
@@ -2273,8 +2282,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC6EFCB-6F72-4E19-9EF3-CDC62E1FF231}">
-  <dimension ref="A1:R114"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD8C519A-F7D0-43F0-9A26-47A135578724}">
+  <dimension ref="A1:R115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -5715,40 +5724,40 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B62" t="s">
-        <v>587</v>
+        <v>632</v>
       </c>
       <c r="C62" t="s">
-        <v>588</v>
+        <v>628</v>
       </c>
       <c r="D62" t="s">
-        <v>544</v>
+        <v>629</v>
       </c>
       <c r="E62" t="s">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="F62" t="s">
-        <v>520</v>
+        <v>630</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="H62" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I62" t="s">
-        <v>493</v>
+        <v>36</v>
       </c>
       <c r="J62" t="s">
-        <v>590</v>
+        <v>125</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
       </c>
       <c r="L62">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
@@ -5757,7 +5766,7 @@
         <v>1</v>
       </c>
       <c r="O62" t="s">
-        <v>591</v>
+        <v>634</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -5771,37 +5780,37 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B63" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C63" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D63" t="s">
-        <v>594</v>
+        <v>544</v>
       </c>
       <c r="E63" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="F63" t="s">
-        <v>596</v>
+        <v>520</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" t="s">
         <v>20</v>
       </c>
       <c r="I63" t="s">
-        <v>53</v>
+        <v>493</v>
       </c>
       <c r="J63" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="K63" t="s">
-        <v>598</v>
+        <v>23</v>
       </c>
       <c r="L63">
         <v>12</v>
@@ -5810,10 +5819,10 @@
         <v>0</v>
       </c>
       <c r="N63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5827,49 +5836,49 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B64" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>593</v>
       </c>
       <c r="D64" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="E64" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="F64" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="G64">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I64" t="s">
         <v>53</v>
       </c>
       <c r="J64" t="s">
-        <v>76</v>
+        <v>597</v>
       </c>
       <c r="K64" t="s">
-        <v>23</v>
+        <v>598</v>
       </c>
       <c r="L64">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5883,49 +5892,49 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B65" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C65" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="D65" t="s">
-        <v>173</v>
+        <v>601</v>
       </c>
       <c r="E65" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F65" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H65" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J65" t="s">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="K65" t="s">
         <v>23</v>
       </c>
       <c r="L65">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
       </c>
       <c r="N65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5934,27 +5943,27 @@
         <v>1</v>
       </c>
       <c r="R65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B66" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C66" t="s">
-        <v>610</v>
+        <v>196</v>
       </c>
       <c r="D66" t="s">
-        <v>611</v>
+        <v>173</v>
       </c>
       <c r="E66" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="F66" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -5963,16 +5972,16 @@
         <v>20</v>
       </c>
       <c r="I66" t="s">
-        <v>493</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s">
-        <v>614</v>
+        <v>244</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5981,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5990,39 +5999,39 @@
         <v>1</v>
       </c>
       <c r="R66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B67" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C67" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="D67" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E67" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="F67" t="s">
-        <v>111</v>
+        <v>613</v>
       </c>
       <c r="G67">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I67" t="s">
         <v>493</v>
       </c>
       <c r="J67" t="s">
-        <v>579</v>
+        <v>614</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
@@ -6034,10 +6043,10 @@
         <v>0</v>
       </c>
       <c r="N67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -6051,25 +6060,25 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B68" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C68" t="s">
-        <v>175</v>
+        <v>617</v>
       </c>
       <c r="D68" t="s">
-        <v>176</v>
+        <v>618</v>
       </c>
       <c r="E68" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F68" t="s">
-        <v>623</v>
+        <v>111</v>
       </c>
       <c r="G68">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H68" t="s">
         <v>42</v>
@@ -6078,13 +6087,13 @@
         <v>493</v>
       </c>
       <c r="J68" t="s">
-        <v>178</v>
+        <v>579</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -6093,7 +6102,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -6107,40 +6116,40 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B69" t="s">
-        <v>375</v>
+        <v>621</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="D69" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="E69" t="s">
-        <v>90</v>
+        <v>622</v>
       </c>
       <c r="F69" t="s">
-        <v>91</v>
+        <v>623</v>
       </c>
       <c r="G69">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H69" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I69" t="s">
-        <v>36</v>
+        <v>493</v>
       </c>
       <c r="J69" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -6149,13 +6158,13 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>266</v>
+        <v>624</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="b">
         <v>1</v>
@@ -6163,40 +6172,40 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C70" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D70" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E70" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F70" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G70">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H70" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J70" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6205,7 +6214,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -6219,41 +6228,41 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B71" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E71" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F71" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H71" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I71" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J71" t="s">
+        <v>66</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71">
         <v>30</v>
       </c>
-      <c r="K71" t="s">
-        <v>23</v>
-      </c>
-      <c r="L71">
-        <v>12</v>
-      </c>
       <c r="M71" t="b">
         <v>0</v>
       </c>
@@ -6261,13 +6270,13 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
@@ -6275,55 +6284,55 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
+        <v>29</v>
+      </c>
+      <c r="B72" t="s">
+        <v>377</v>
+      </c>
+      <c r="C72" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" t="s">
+        <v>54</v>
+      </c>
+      <c r="E72" t="s">
+        <v>55</v>
+      </c>
+      <c r="F72" t="s">
+        <v>61</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>28</v>
+      </c>
+      <c r="I72" t="s">
+        <v>96</v>
+      </c>
+      <c r="J72" t="s">
         <v>30</v>
       </c>
-      <c r="B72" t="s">
-        <v>378</v>
-      </c>
-      <c r="C72" t="s">
-        <v>97</v>
-      </c>
-      <c r="D72" t="s">
-        <v>98</v>
-      </c>
-      <c r="E72" t="s">
-        <v>99</v>
-      </c>
-      <c r="F72" t="s">
-        <v>100</v>
-      </c>
-      <c r="G72">
-        <v>100</v>
-      </c>
-      <c r="H72" t="s">
-        <v>20</v>
-      </c>
-      <c r="I72" t="s">
-        <v>101</v>
-      </c>
-      <c r="J72" t="s">
-        <v>102</v>
-      </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
       </c>
       <c r="N72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="b">
         <v>1</v>
@@ -6331,49 +6340,49 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B73" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D73" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E73" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F73" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G73">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H73" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I73" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J73" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
       </c>
       <c r="N73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
@@ -6387,22 +6396,22 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B74" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C74" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D74" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E74" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F74" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G74">
         <v>500</v>
@@ -6414,13 +6423,13 @@
         <v>107</v>
       </c>
       <c r="J74" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
@@ -6429,7 +6438,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -6443,40 +6452,40 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C75" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D75" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E75" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F75" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H75" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I75" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J75" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -6485,13 +6494,13 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -6499,40 +6508,40 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E76" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F76" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G76">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I76" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6541,13 +6550,13 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -6555,40 +6564,40 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
+        <v>34</v>
+      </c>
+      <c r="B77" t="s">
+        <v>382</v>
+      </c>
+      <c r="C77" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" t="s">
+        <v>113</v>
+      </c>
+      <c r="E77" t="s">
+        <v>114</v>
+      </c>
+      <c r="F77" t="s">
+        <v>115</v>
+      </c>
+      <c r="G77">
+        <v>300</v>
+      </c>
+      <c r="H77" t="s">
         <v>35</v>
       </c>
-      <c r="B77" t="s">
-        <v>383</v>
-      </c>
-      <c r="C77" t="s">
-        <v>117</v>
-      </c>
-      <c r="D77" t="s">
-        <v>118</v>
-      </c>
-      <c r="E77" t="s">
-        <v>119</v>
-      </c>
-      <c r="F77" t="s">
-        <v>120</v>
-      </c>
-      <c r="G77">
-        <v>500</v>
-      </c>
-      <c r="H77" t="s">
-        <v>42</v>
-      </c>
       <c r="I77" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J77" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6597,7 +6606,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
@@ -6611,40 +6620,40 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B78" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C78" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D78" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E78" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F78" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G78">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H78" t="s">
         <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6653,13 +6662,13 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
@@ -6667,40 +6676,40 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B79" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D79" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E79" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F79" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G79">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H79" t="s">
         <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J79" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6709,13 +6718,13 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -6723,34 +6732,34 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B80" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C80" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D80" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E80" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F80" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G80">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H80" t="s">
         <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J80" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
@@ -6765,13 +6774,13 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="b">
         <v>1</v>
@@ -6779,40 +6788,40 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B81" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C81" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D81" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E81" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F81" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G81">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H81" t="s">
         <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6821,7 +6830,7 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
@@ -6835,40 +6844,40 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B82" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C82" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D82" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E82" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F82" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H82" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J82" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -6877,7 +6886,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6891,55 +6900,55 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B83" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C83" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D83" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E83" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F83" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G83">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H83" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I83" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -6947,10 +6956,10 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C84" t="s">
         <v>138</v>
@@ -6959,10 +6968,10 @@
         <v>139</v>
       </c>
       <c r="E84" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F84" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G84">
         <v>1000</v>
@@ -6986,10 +6995,10 @@
         <v>1</v>
       </c>
       <c r="N84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -7003,22 +7012,22 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B85" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C85" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D85" t="s">
         <v>139</v>
       </c>
       <c r="E85" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F85" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G85">
         <v>1000</v>
@@ -7030,7 +7039,7 @@
         <v>142</v>
       </c>
       <c r="J85" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
@@ -7045,7 +7054,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -7059,55 +7068,55 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C86" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D86" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E86" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F86" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G86">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H86" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I86" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J86" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
       </c>
       <c r="L86">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -7115,55 +7124,55 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B87" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C87" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D87" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E87" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F87" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H87" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J87" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K87" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L87">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M87" t="b">
         <v>0</v>
       </c>
       <c r="N87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -7171,55 +7180,55 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C88" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D88" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E88" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F88" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G88">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I88" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J88" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K88" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L88">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
       <c r="N88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -7227,34 +7236,34 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C89" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D89" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E89" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F89" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G89">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H89" t="s">
         <v>42</v>
       </c>
       <c r="I89" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J89" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K89" t="s">
         <v>23</v>
@@ -7269,7 +7278,7 @@
         <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7283,22 +7292,22 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C90" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D90" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E90" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F90" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G90">
         <v>500</v>
@@ -7310,7 +7319,7 @@
         <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
@@ -7325,7 +7334,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7339,25 +7348,25 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B91" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C91" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D91" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E91" t="s">
-        <v>625</v>
+        <v>173</v>
       </c>
       <c r="F91" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="G91">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H91" t="s">
         <v>42</v>
@@ -7366,7 +7375,7 @@
         <v>21</v>
       </c>
       <c r="J91" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
@@ -7381,7 +7390,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7390,42 +7399,42 @@
         <v>1</v>
       </c>
       <c r="R91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
+        <v>49</v>
+      </c>
+      <c r="B92" t="s">
+        <v>397</v>
+      </c>
+      <c r="C92" t="s">
+        <v>175</v>
+      </c>
+      <c r="D92" t="s">
+        <v>176</v>
+      </c>
+      <c r="E92" t="s">
+        <v>625</v>
+      </c>
+      <c r="F92" t="s">
+        <v>177</v>
+      </c>
+      <c r="G92">
         <v>50</v>
       </c>
-      <c r="B92" t="s">
-        <v>398</v>
-      </c>
-      <c r="C92" t="s">
-        <v>179</v>
-      </c>
-      <c r="D92" t="s">
-        <v>180</v>
-      </c>
-      <c r="E92" t="s">
-        <v>181</v>
-      </c>
-      <c r="F92" t="s">
-        <v>182</v>
-      </c>
-      <c r="G92">
-        <v>12</v>
-      </c>
       <c r="H92" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K92" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="L92">
         <v>12</v>
@@ -7437,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7446,45 +7455,45 @@
         <v>1</v>
       </c>
       <c r="R92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B93" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C93" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D93" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E93" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F93" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G93">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H93" t="s">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="I93" t="s">
-        <v>190</v>
+        <v>53</v>
       </c>
       <c r="J93" t="s">
-        <v>555</v>
+        <v>183</v>
       </c>
       <c r="K93" t="s">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="L93">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -7493,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7507,40 +7516,40 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B94" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C94" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D94" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E94" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F94" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G94">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H94" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="I94" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="J94" t="s">
-        <v>183</v>
+        <v>555</v>
       </c>
       <c r="K94" t="s">
         <v>23</v>
       </c>
       <c r="L94">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7549,7 +7558,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7563,40 +7572,40 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
+        <v>52</v>
+      </c>
+      <c r="B95" t="s">
+        <v>400</v>
+      </c>
+      <c r="C95" t="s">
+        <v>192</v>
+      </c>
+      <c r="D95" t="s">
+        <v>180</v>
+      </c>
+      <c r="E95" t="s">
+        <v>181</v>
+      </c>
+      <c r="F95" t="s">
+        <v>182</v>
+      </c>
+      <c r="G95">
+        <v>24</v>
+      </c>
+      <c r="H95" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" t="s">
         <v>53</v>
       </c>
-      <c r="B95" t="s">
-        <v>401</v>
-      </c>
-      <c r="C95" t="s">
-        <v>31</v>
-      </c>
-      <c r="D95" t="s">
-        <v>193</v>
-      </c>
-      <c r="E95" t="s">
-        <v>194</v>
-      </c>
-      <c r="F95" t="s">
-        <v>195</v>
-      </c>
-      <c r="G95">
-        <v>1.5</v>
-      </c>
-      <c r="H95" t="s">
-        <v>28</v>
-      </c>
-      <c r="I95" t="s">
-        <v>36</v>
-      </c>
       <c r="J95" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7605,7 +7614,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7619,52 +7628,52 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B96" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C96" t="s">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E96" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F96" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G96">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H96" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I96" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J96" t="s">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
       </c>
       <c r="N96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q96" t="b">
         <v>1</v>
@@ -7675,55 +7684,55 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B97" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C97" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D97" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E97" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F97" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G97">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H97" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I97" t="s">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="J97" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="b">
         <v>1</v>
@@ -7731,40 +7740,40 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B98" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C98" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="D98" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E98" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F98" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G98">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H98" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J98" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
@@ -7773,7 +7782,7 @@
         <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
@@ -7787,19 +7796,19 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B99" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C99" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D99" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E99" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F99" t="s">
         <v>207</v>
@@ -7829,7 +7838,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7843,19 +7852,19 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B100" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C100" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D100" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E100" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F100" t="s">
         <v>207</v>
@@ -7876,7 +7885,7 @@
         <v>23</v>
       </c>
       <c r="L100">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
@@ -7885,7 +7894,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -7899,34 +7908,34 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B101" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C101" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="D101" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E101" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F101" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H101" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I101" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="J101" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K101" t="s">
         <v>23</v>
@@ -7941,13 +7950,13 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="b">
         <v>1</v>
@@ -7955,34 +7964,34 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B102" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C102" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D102" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E102" t="s">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="F102" t="s">
-        <v>215</v>
+        <v>56</v>
       </c>
       <c r="G102">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I102" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J102" t="s">
-        <v>556</v>
+        <v>148</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
@@ -7997,7 +8006,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -8011,49 +8020,49 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B103" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C103" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="D103" t="s">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="E103" t="s">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="F103" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G103">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H103" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I103" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J103" t="s">
-        <v>216</v>
+        <v>556</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
       </c>
       <c r="L103">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M103" t="b">
         <v>0</v>
       </c>
       <c r="N103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8067,22 +8076,22 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B104" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C104" t="s">
         <v>216</v>
       </c>
       <c r="D104" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E104" t="s">
         <v>218</v>
       </c>
       <c r="F104" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G104">
         <v>20</v>
@@ -8109,13 +8118,13 @@
         <v>0</v>
       </c>
       <c r="O104" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
       </c>
       <c r="Q104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="b">
         <v>1</v>
@@ -8123,49 +8132,49 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B105" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C105" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D105" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="E105" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="F105" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="G105">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H105" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I105" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J105" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="K105" t="s">
         <v>23</v>
       </c>
       <c r="L105">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M105" t="b">
         <v>0</v>
       </c>
       <c r="N105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
@@ -8179,34 +8188,34 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B106" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C106" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D106" t="s">
         <v>201</v>
       </c>
       <c r="E106" t="s">
-        <v>32</v>
+        <v>202</v>
       </c>
       <c r="F106" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="G106">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H106" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I106" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J106" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
@@ -8221,7 +8230,7 @@
         <v>1</v>
       </c>
       <c r="O106" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8235,40 +8244,40 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B107" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C107" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D107" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="E107" t="s">
-        <v>228</v>
+        <v>32</v>
       </c>
       <c r="F107" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G107">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H107" t="s">
         <v>42</v>
       </c>
       <c r="I107" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J107" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
       </c>
       <c r="L107">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M107" t="b">
         <v>0</v>
@@ -8277,13 +8286,13 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
       </c>
       <c r="Q107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R107" t="b">
         <v>1</v>
@@ -8291,40 +8300,40 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B108" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C108" t="s">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="D108" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E108" t="s">
         <v>228</v>
       </c>
       <c r="F108" t="s">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H108" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I108" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J108" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
       </c>
       <c r="L108">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
@@ -8333,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
@@ -8347,40 +8356,40 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B109" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C109" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D109" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="E109" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F109" t="s">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="G109">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H109" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I109" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J109" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
       </c>
       <c r="L109">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M109" t="b">
         <v>0</v>
@@ -8389,13 +8398,13 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
       </c>
       <c r="Q109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R109" t="b">
         <v>1</v>
@@ -8403,34 +8412,34 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B110" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C110" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E110" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F110" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G110">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H110" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="J110" t="s">
-        <v>191</v>
+        <v>37</v>
       </c>
       <c r="K110" t="s">
         <v>23</v>
@@ -8445,7 +8454,7 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
@@ -8459,10 +8468,10 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B111" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C111" t="s">
         <v>185</v>
@@ -8471,13 +8480,13 @@
         <v>201</v>
       </c>
       <c r="E111" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F111" t="s">
         <v>203</v>
       </c>
       <c r="G111">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H111" t="s">
         <v>35</v>
@@ -8501,7 +8510,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
@@ -8515,10 +8524,10 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B112" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C112" t="s">
         <v>185</v>
@@ -8533,7 +8542,7 @@
         <v>203</v>
       </c>
       <c r="G112">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H112" t="s">
         <v>35</v>
@@ -8557,7 +8566,7 @@
         <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
@@ -8571,41 +8580,41 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B113" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C113" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="D113" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="E113" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F113" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="G113">
+        <v>250</v>
+      </c>
+      <c r="H113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113" t="s">
+        <v>190</v>
+      </c>
+      <c r="J113" t="s">
+        <v>191</v>
+      </c>
+      <c r="K113" t="s">
+        <v>23</v>
+      </c>
+      <c r="L113">
         <v>6</v>
       </c>
-      <c r="H113" t="s">
-        <v>20</v>
-      </c>
-      <c r="I113" t="s">
-        <v>238</v>
-      </c>
-      <c r="J113" t="s">
-        <v>234</v>
-      </c>
-      <c r="K113" t="s">
-        <v>23</v>
-      </c>
-      <c r="L113">
-        <v>1</v>
-      </c>
       <c r="M113" t="b">
         <v>0</v>
       </c>
@@ -8613,13 +8622,13 @@
         <v>1</v>
       </c>
       <c r="O113" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" t="b">
         <v>1</v>
@@ -8627,57 +8636,113 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B114" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C114" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="D114" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="E114" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F114" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G114">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H114" t="s">
         <v>20</v>
       </c>
       <c r="I114" t="s">
+        <v>238</v>
+      </c>
+      <c r="J114" t="s">
+        <v>234</v>
+      </c>
+      <c r="K114" t="s">
+        <v>23</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114" t="b">
+        <v>0</v>
+      </c>
+      <c r="N114" t="b">
+        <v>1</v>
+      </c>
+      <c r="O114" t="s">
+        <v>310</v>
+      </c>
+      <c r="P114" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="b">
+        <v>1</v>
+      </c>
+      <c r="R114" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>72</v>
+      </c>
+      <c r="B115" t="s">
+        <v>420</v>
+      </c>
+      <c r="C115" t="s">
+        <v>196</v>
+      </c>
+      <c r="D115" t="s">
+        <v>197</v>
+      </c>
+      <c r="E115" t="s">
+        <v>198</v>
+      </c>
+      <c r="F115" t="s">
+        <v>239</v>
+      </c>
+      <c r="G115">
+        <v>4</v>
+      </c>
+      <c r="H115" t="s">
+        <v>20</v>
+      </c>
+      <c r="I115" t="s">
         <v>21</v>
       </c>
-      <c r="J114" t="s">
+      <c r="J115" t="s">
         <v>200</v>
       </c>
-      <c r="K114" t="s">
-        <v>23</v>
-      </c>
-      <c r="L114">
+      <c r="K115" t="s">
+        <v>23</v>
+      </c>
+      <c r="L115">
         <v>10</v>
       </c>
-      <c r="M114" t="b">
-        <v>0</v>
-      </c>
-      <c r="N114" t="b">
-        <v>0</v>
-      </c>
-      <c r="O114" t="s">
+      <c r="M115" t="b">
+        <v>0</v>
+      </c>
+      <c r="N115" t="b">
+        <v>0</v>
+      </c>
+      <c r="O115" t="s">
         <v>311</v>
       </c>
-      <c r="P114" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q114" t="b">
-        <v>1</v>
-      </c>
-      <c r="R114" t="b">
+      <c r="P115" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q115" t="b">
+        <v>1</v>
+      </c>
+      <c r="R115" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F67C8B-CA92-4AEE-B8D8-DB20C34D4383}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A186296-1D99-40EB-BF3A-04336CEB7F46}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="61" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="62" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -2282,7 +2282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD8C519A-F7D0-43F0-9A26-47A135578724}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE11F53C-2106-48CE-9E00-F9BA18AD12D5}">
   <dimension ref="A1:R115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5607,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="R59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A186296-1D99-40EB-BF3A-04336CEB7F46}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C178E6F6-918E-4C72-9777-7B3277CEECCC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="62" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="64" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="638">
   <si>
     <t>Codigo</t>
   </si>
@@ -1931,6 +1931,15 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790127784411.png</t>
+  </si>
+  <si>
+    <t>7790742335609</t>
+  </si>
+  <si>
+    <t>liviana 1%</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7790742335609.png</t>
   </si>
 </sst>
 </file>
@@ -2282,8 +2291,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE11F53C-2106-48CE-9E00-F9BA18AD12D5}">
-  <dimension ref="A1:R115"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E82549A7-EDAE-47C9-9286-630639225607}">
+  <dimension ref="A1:R116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -5607,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="R59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
@@ -5780,40 +5789,40 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B63" t="s">
-        <v>587</v>
+        <v>635</v>
       </c>
       <c r="C63" t="s">
-        <v>588</v>
+        <v>24</v>
       </c>
       <c r="D63" t="s">
-        <v>544</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>589</v>
+        <v>636</v>
       </c>
       <c r="F63" t="s">
-        <v>520</v>
+        <v>423</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I63" t="s">
-        <v>493</v>
+        <v>36</v>
       </c>
       <c r="J63" t="s">
-        <v>590</v>
+        <v>30</v>
       </c>
       <c r="K63" t="s">
         <v>23</v>
       </c>
       <c r="L63">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -5822,7 +5831,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>591</v>
+        <v>637</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -5831,42 +5840,42 @@
         <v>1</v>
       </c>
       <c r="R63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B64" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C64" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D64" t="s">
-        <v>594</v>
+        <v>544</v>
       </c>
       <c r="E64" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="F64" t="s">
-        <v>596</v>
+        <v>520</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64" t="s">
         <v>20</v>
       </c>
       <c r="I64" t="s">
-        <v>53</v>
+        <v>493</v>
       </c>
       <c r="J64" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="K64" t="s">
-        <v>598</v>
+        <v>23</v>
       </c>
       <c r="L64">
         <v>12</v>
@@ -5875,10 +5884,10 @@
         <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5892,49 +5901,49 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B65" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>593</v>
       </c>
       <c r="D65" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="E65" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="F65" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="G65">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I65" t="s">
         <v>53</v>
       </c>
       <c r="J65" t="s">
-        <v>76</v>
+        <v>597</v>
       </c>
       <c r="K65" t="s">
-        <v>23</v>
+        <v>598</v>
       </c>
       <c r="L65">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
       </c>
       <c r="N65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5948,49 +5957,49 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B66" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C66" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="D66" t="s">
-        <v>173</v>
+        <v>601</v>
       </c>
       <c r="E66" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F66" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H66" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I66" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J66" t="s">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="K66" t="s">
         <v>23</v>
       </c>
       <c r="L66">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
       </c>
       <c r="N66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -5999,27 +6008,27 @@
         <v>1</v>
       </c>
       <c r="R66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B67" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C67" t="s">
-        <v>610</v>
+        <v>196</v>
       </c>
       <c r="D67" t="s">
-        <v>611</v>
+        <v>173</v>
       </c>
       <c r="E67" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="F67" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6028,16 +6037,16 @@
         <v>20</v>
       </c>
       <c r="I67" t="s">
-        <v>493</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>614</v>
+        <v>244</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -6046,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -6055,39 +6064,39 @@
         <v>1</v>
       </c>
       <c r="R67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B68" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C68" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="D68" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E68" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="F68" t="s">
-        <v>111</v>
+        <v>613</v>
       </c>
       <c r="G68">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I68" t="s">
         <v>493</v>
       </c>
       <c r="J68" t="s">
-        <v>579</v>
+        <v>614</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
@@ -6099,10 +6108,10 @@
         <v>0</v>
       </c>
       <c r="N68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -6116,25 +6125,25 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B69" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C69" t="s">
-        <v>175</v>
+        <v>617</v>
       </c>
       <c r="D69" t="s">
-        <v>176</v>
+        <v>618</v>
       </c>
       <c r="E69" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F69" t="s">
-        <v>623</v>
+        <v>111</v>
       </c>
       <c r="G69">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H69" t="s">
         <v>42</v>
@@ -6143,13 +6152,13 @@
         <v>493</v>
       </c>
       <c r="J69" t="s">
-        <v>178</v>
+        <v>579</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
       </c>
       <c r="L69">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -6158,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -6172,40 +6181,40 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B70" t="s">
-        <v>375</v>
+        <v>621</v>
       </c>
       <c r="C70" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="D70" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="E70" t="s">
-        <v>90</v>
+        <v>622</v>
       </c>
       <c r="F70" t="s">
-        <v>91</v>
+        <v>623</v>
       </c>
       <c r="G70">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H70" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I70" t="s">
-        <v>36</v>
+        <v>493</v>
       </c>
       <c r="J70" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6214,13 +6223,13 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>266</v>
+        <v>624</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
@@ -6228,40 +6237,40 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C71" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D71" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E71" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F71" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G71">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H71" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I71" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J71" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -6270,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
@@ -6284,41 +6293,41 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B72" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D72" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F72" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H72" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I72" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J72" t="s">
+        <v>66</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72">
         <v>30</v>
       </c>
-      <c r="K72" t="s">
-        <v>23</v>
-      </c>
-      <c r="L72">
-        <v>12</v>
-      </c>
       <c r="M72" t="b">
         <v>0</v>
       </c>
@@ -6326,13 +6335,13 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="b">
         <v>1</v>
@@ -6340,55 +6349,55 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
+        <v>29</v>
+      </c>
+      <c r="B73" t="s">
+        <v>377</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" t="s">
+        <v>54</v>
+      </c>
+      <c r="E73" t="s">
+        <v>55</v>
+      </c>
+      <c r="F73" t="s">
+        <v>61</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>28</v>
+      </c>
+      <c r="I73" t="s">
+        <v>96</v>
+      </c>
+      <c r="J73" t="s">
         <v>30</v>
       </c>
-      <c r="B73" t="s">
-        <v>378</v>
-      </c>
-      <c r="C73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D73" t="s">
-        <v>98</v>
-      </c>
-      <c r="E73" t="s">
-        <v>99</v>
-      </c>
-      <c r="F73" t="s">
-        <v>100</v>
-      </c>
-      <c r="G73">
-        <v>100</v>
-      </c>
-      <c r="H73" t="s">
-        <v>20</v>
-      </c>
-      <c r="I73" t="s">
-        <v>101</v>
-      </c>
-      <c r="J73" t="s">
-        <v>102</v>
-      </c>
       <c r="K73" t="s">
         <v>23</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
       </c>
       <c r="N73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -6396,49 +6405,49 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B74" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C74" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E74" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F74" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G74">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H74" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I74" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J74" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
       </c>
       <c r="N74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
@@ -6452,22 +6461,22 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B75" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C75" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D75" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E75" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F75" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G75">
         <v>500</v>
@@ -6479,13 +6488,13 @@
         <v>107</v>
       </c>
       <c r="J75" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
@@ -6494,7 +6503,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6508,40 +6517,40 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D76" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E76" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F76" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H76" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I76" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J76" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6550,13 +6559,13 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -6564,40 +6573,40 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F77" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G77">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I77" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6606,13 +6615,13 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
@@ -6620,40 +6629,40 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
+        <v>34</v>
+      </c>
+      <c r="B78" t="s">
+        <v>382</v>
+      </c>
+      <c r="C78" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" t="s">
+        <v>114</v>
+      </c>
+      <c r="F78" t="s">
+        <v>115</v>
+      </c>
+      <c r="G78">
+        <v>300</v>
+      </c>
+      <c r="H78" t="s">
         <v>35</v>
       </c>
-      <c r="B78" t="s">
-        <v>383</v>
-      </c>
-      <c r="C78" t="s">
-        <v>117</v>
-      </c>
-      <c r="D78" t="s">
-        <v>118</v>
-      </c>
-      <c r="E78" t="s">
-        <v>119</v>
-      </c>
-      <c r="F78" t="s">
-        <v>120</v>
-      </c>
-      <c r="G78">
-        <v>500</v>
-      </c>
-      <c r="H78" t="s">
-        <v>42</v>
-      </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J78" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6662,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
@@ -6676,40 +6685,40 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B79" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C79" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E79" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F79" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G79">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H79" t="s">
         <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6718,13 +6727,13 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -6732,40 +6741,40 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B80" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E80" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F80" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G80">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H80" t="s">
         <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J80" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6774,13 +6783,13 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="b">
         <v>1</v>
@@ -6788,34 +6797,34 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B81" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C81" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D81" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E81" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F81" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G81">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H81" t="s">
         <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J81" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
@@ -6830,13 +6839,13 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -6844,40 +6853,40 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B82" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C82" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D82" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E82" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F82" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G82">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H82" t="s">
         <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J82" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
       </c>
       <c r="L82">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
@@ -6886,7 +6895,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
@@ -6900,40 +6909,40 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B83" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C83" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D83" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E83" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F83" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H83" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J83" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -6942,7 +6951,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6956,55 +6965,55 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B84" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C84" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E84" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F84" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G84">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I84" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
@@ -7012,10 +7021,10 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C85" t="s">
         <v>138</v>
@@ -7024,10 +7033,10 @@
         <v>139</v>
       </c>
       <c r="E85" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F85" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G85">
         <v>1000</v>
@@ -7051,10 +7060,10 @@
         <v>1</v>
       </c>
       <c r="N85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
@@ -7068,22 +7077,22 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B86" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C86" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D86" t="s">
         <v>139</v>
       </c>
       <c r="E86" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F86" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G86">
         <v>1000</v>
@@ -7095,7 +7104,7 @@
         <v>142</v>
       </c>
       <c r="J86" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K86" t="s">
         <v>23</v>
@@ -7110,7 +7119,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -7124,55 +7133,55 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B87" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C87" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E87" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F87" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G87">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H87" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I87" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J87" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
       </c>
       <c r="L87">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -7180,55 +7189,55 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C88" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D88" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E88" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F88" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H88" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J88" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K88" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L88">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
       <c r="N88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -7236,55 +7245,55 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C89" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D89" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E89" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F89" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G89">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H89" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I89" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J89" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K89" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L89">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
       <c r="N89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -7292,34 +7301,34 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B90" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C90" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D90" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E90" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F90" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G90">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H90" t="s">
         <v>42</v>
       </c>
       <c r="I90" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J90" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K90" t="s">
         <v>23</v>
@@ -7334,7 +7343,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
@@ -7348,22 +7357,22 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C91" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D91" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E91" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F91" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G91">
         <v>500</v>
@@ -7375,7 +7384,7 @@
         <v>21</v>
       </c>
       <c r="J91" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
@@ -7390,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7404,25 +7413,25 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B92" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C92" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D92" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E92" t="s">
-        <v>625</v>
+        <v>173</v>
       </c>
       <c r="F92" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="G92">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H92" t="s">
         <v>42</v>
@@ -7431,7 +7440,7 @@
         <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
@@ -7446,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7455,42 +7464,42 @@
         <v>1</v>
       </c>
       <c r="R92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
+        <v>49</v>
+      </c>
+      <c r="B93" t="s">
+        <v>397</v>
+      </c>
+      <c r="C93" t="s">
+        <v>175</v>
+      </c>
+      <c r="D93" t="s">
+        <v>176</v>
+      </c>
+      <c r="E93" t="s">
+        <v>625</v>
+      </c>
+      <c r="F93" t="s">
+        <v>177</v>
+      </c>
+      <c r="G93">
         <v>50</v>
       </c>
-      <c r="B93" t="s">
-        <v>398</v>
-      </c>
-      <c r="C93" t="s">
-        <v>179</v>
-      </c>
-      <c r="D93" t="s">
-        <v>180</v>
-      </c>
-      <c r="E93" t="s">
-        <v>181</v>
-      </c>
-      <c r="F93" t="s">
-        <v>182</v>
-      </c>
-      <c r="G93">
-        <v>12</v>
-      </c>
       <c r="H93" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I93" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J93" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K93" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="L93">
         <v>12</v>
@@ -7502,7 +7511,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7511,45 +7520,45 @@
         <v>1</v>
       </c>
       <c r="R93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B94" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C94" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D94" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E94" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F94" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G94">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H94" t="s">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="I94" t="s">
-        <v>190</v>
+        <v>53</v>
       </c>
       <c r="J94" t="s">
-        <v>555</v>
+        <v>183</v>
       </c>
       <c r="K94" t="s">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="L94">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -7558,7 +7567,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7572,40 +7581,40 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B95" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C95" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D95" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E95" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F95" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G95">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H95" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="I95" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="J95" t="s">
-        <v>183</v>
+        <v>555</v>
       </c>
       <c r="K95" t="s">
         <v>23</v>
       </c>
       <c r="L95">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7614,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7628,40 +7637,40 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
+        <v>52</v>
+      </c>
+      <c r="B96" t="s">
+        <v>400</v>
+      </c>
+      <c r="C96" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" t="s">
+        <v>180</v>
+      </c>
+      <c r="E96" t="s">
+        <v>181</v>
+      </c>
+      <c r="F96" t="s">
+        <v>182</v>
+      </c>
+      <c r="G96">
+        <v>24</v>
+      </c>
+      <c r="H96" t="s">
+        <v>20</v>
+      </c>
+      <c r="I96" t="s">
         <v>53</v>
       </c>
-      <c r="B96" t="s">
-        <v>401</v>
-      </c>
-      <c r="C96" t="s">
-        <v>31</v>
-      </c>
-      <c r="D96" t="s">
-        <v>193</v>
-      </c>
-      <c r="E96" t="s">
-        <v>194</v>
-      </c>
-      <c r="F96" t="s">
-        <v>195</v>
-      </c>
-      <c r="G96">
-        <v>1.5</v>
-      </c>
-      <c r="H96" t="s">
-        <v>28</v>
-      </c>
-      <c r="I96" t="s">
-        <v>36</v>
-      </c>
       <c r="J96" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -7670,7 +7679,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7684,52 +7693,52 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B97" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C97" t="s">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="D97" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E97" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F97" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G97">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H97" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I97" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J97" t="s">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
       <c r="N97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" t="b">
         <v>1</v>
@@ -7740,55 +7749,55 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B98" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C98" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D98" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E98" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F98" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G98">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H98" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I98" t="s">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="J98" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
       </c>
       <c r="N98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="b">
         <v>1</v>
@@ -7796,40 +7805,40 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B99" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C99" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="D99" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E99" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F99" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G99">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H99" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I99" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J99" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
       </c>
       <c r="L99">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -7838,7 +7847,7 @@
         <v>1</v>
       </c>
       <c r="O99" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
@@ -7852,19 +7861,19 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B100" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C100" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D100" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E100" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F100" t="s">
         <v>207</v>
@@ -7894,7 +7903,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -7908,19 +7917,19 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B101" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C101" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D101" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E101" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F101" t="s">
         <v>207</v>
@@ -7941,7 +7950,7 @@
         <v>23</v>
       </c>
       <c r="L101">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
@@ -7950,7 +7959,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -7964,34 +7973,34 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B102" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C102" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="D102" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E102" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F102" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H102" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I102" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="J102" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K102" t="s">
         <v>23</v>
@@ -8006,13 +8015,13 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R102" t="b">
         <v>1</v>
@@ -8020,34 +8029,34 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B103" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C103" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D103" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E103" t="s">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="F103" t="s">
-        <v>215</v>
+        <v>56</v>
       </c>
       <c r="G103">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I103" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="J103" t="s">
-        <v>556</v>
+        <v>148</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
@@ -8062,7 +8071,7 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
@@ -8076,49 +8085,49 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B104" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C104" t="s">
-        <v>216</v>
+        <v>24</v>
       </c>
       <c r="D104" t="s">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="E104" t="s">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="F104" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G104">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="H104" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I104" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="J104" t="s">
-        <v>216</v>
+        <v>556</v>
       </c>
       <c r="K104" t="s">
         <v>23</v>
       </c>
       <c r="L104">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
       </c>
       <c r="N104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
@@ -8132,22 +8141,22 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B105" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C105" t="s">
         <v>216</v>
       </c>
       <c r="D105" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E105" t="s">
         <v>218</v>
       </c>
       <c r="F105" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G105">
         <v>20</v>
@@ -8174,13 +8183,13 @@
         <v>0</v>
       </c>
       <c r="O105" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
       </c>
       <c r="Q105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" t="b">
         <v>1</v>
@@ -8188,49 +8197,49 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B106" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C106" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D106" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="E106" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="F106" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="G106">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H106" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I106" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="J106" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="K106" t="s">
         <v>23</v>
       </c>
       <c r="L106">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M106" t="b">
         <v>0</v>
       </c>
       <c r="N106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
@@ -8244,34 +8253,34 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B107" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C107" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D107" t="s">
         <v>201</v>
       </c>
       <c r="E107" t="s">
-        <v>32</v>
+        <v>202</v>
       </c>
       <c r="F107" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="G107">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H107" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I107" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J107" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
@@ -8286,7 +8295,7 @@
         <v>1</v>
       </c>
       <c r="O107" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
@@ -8300,40 +8309,40 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B108" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C108" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D108" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="E108" t="s">
-        <v>228</v>
+        <v>32</v>
       </c>
       <c r="F108" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G108">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="H108" t="s">
         <v>42</v>
       </c>
       <c r="I108" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="J108" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="K108" t="s">
         <v>23</v>
       </c>
       <c r="L108">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M108" t="b">
         <v>0</v>
@@ -8342,13 +8351,13 @@
         <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
       </c>
       <c r="Q108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R108" t="b">
         <v>1</v>
@@ -8356,40 +8365,40 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B109" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C109" t="s">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="D109" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E109" t="s">
         <v>228</v>
       </c>
       <c r="F109" t="s">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="G109">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="H109" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I109" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="J109" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K109" t="s">
         <v>23</v>
       </c>
       <c r="L109">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M109" t="b">
         <v>0</v>
@@ -8398,7 +8407,7 @@
         <v>1</v>
       </c>
       <c r="O109" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
@@ -8412,40 +8421,40 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B110" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C110" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="E110" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F110" t="s">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="G110">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H110" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I110" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J110" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K110" t="s">
         <v>23</v>
       </c>
       <c r="L110">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M110" t="b">
         <v>0</v>
@@ -8454,13 +8463,13 @@
         <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
       </c>
       <c r="Q110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" t="b">
         <v>1</v>
@@ -8468,34 +8477,34 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B111" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C111" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E111" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F111" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G111">
-        <v>250</v>
+        <v>1.5</v>
       </c>
       <c r="H111" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I111" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="J111" t="s">
-        <v>191</v>
+        <v>37</v>
       </c>
       <c r="K111" t="s">
         <v>23</v>
@@ -8510,7 +8519,7 @@
         <v>1</v>
       </c>
       <c r="O111" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
@@ -8524,10 +8533,10 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B112" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C112" t="s">
         <v>185</v>
@@ -8536,13 +8545,13 @@
         <v>201</v>
       </c>
       <c r="E112" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F112" t="s">
         <v>203</v>
       </c>
       <c r="G112">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H112" t="s">
         <v>35</v>
@@ -8566,7 +8575,7 @@
         <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
@@ -8580,10 +8589,10 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B113" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C113" t="s">
         <v>185</v>
@@ -8598,7 +8607,7 @@
         <v>203</v>
       </c>
       <c r="G113">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H113" t="s">
         <v>35</v>
@@ -8622,7 +8631,7 @@
         <v>1</v>
       </c>
       <c r="O113" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
@@ -8636,41 +8645,41 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B114" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C114" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="D114" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="E114" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F114" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="G114">
+        <v>250</v>
+      </c>
+      <c r="H114" t="s">
+        <v>35</v>
+      </c>
+      <c r="I114" t="s">
+        <v>190</v>
+      </c>
+      <c r="J114" t="s">
+        <v>191</v>
+      </c>
+      <c r="K114" t="s">
+        <v>23</v>
+      </c>
+      <c r="L114">
         <v>6</v>
       </c>
-      <c r="H114" t="s">
-        <v>20</v>
-      </c>
-      <c r="I114" t="s">
-        <v>238</v>
-      </c>
-      <c r="J114" t="s">
-        <v>234</v>
-      </c>
-      <c r="K114" t="s">
-        <v>23</v>
-      </c>
-      <c r="L114">
-        <v>1</v>
-      </c>
       <c r="M114" t="b">
         <v>0</v>
       </c>
@@ -8678,13 +8687,13 @@
         <v>1</v>
       </c>
       <c r="O114" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="b">
         <v>1</v>
@@ -8692,57 +8701,113 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B115" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C115" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="D115" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="E115" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="F115" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G115">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H115" t="s">
         <v>20</v>
       </c>
       <c r="I115" t="s">
+        <v>238</v>
+      </c>
+      <c r="J115" t="s">
+        <v>234</v>
+      </c>
+      <c r="K115" t="s">
+        <v>23</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115" t="b">
+        <v>0</v>
+      </c>
+      <c r="N115" t="b">
+        <v>1</v>
+      </c>
+      <c r="O115" t="s">
+        <v>310</v>
+      </c>
+      <c r="P115" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="b">
+        <v>1</v>
+      </c>
+      <c r="R115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>72</v>
+      </c>
+      <c r="B116" t="s">
+        <v>420</v>
+      </c>
+      <c r="C116" t="s">
+        <v>196</v>
+      </c>
+      <c r="D116" t="s">
+        <v>197</v>
+      </c>
+      <c r="E116" t="s">
+        <v>198</v>
+      </c>
+      <c r="F116" t="s">
+        <v>239</v>
+      </c>
+      <c r="G116">
+        <v>4</v>
+      </c>
+      <c r="H116" t="s">
+        <v>20</v>
+      </c>
+      <c r="I116" t="s">
         <v>21</v>
       </c>
-      <c r="J115" t="s">
+      <c r="J116" t="s">
         <v>200</v>
       </c>
-      <c r="K115" t="s">
-        <v>23</v>
-      </c>
-      <c r="L115">
+      <c r="K116" t="s">
+        <v>23</v>
+      </c>
+      <c r="L116">
         <v>10</v>
       </c>
-      <c r="M115" t="b">
-        <v>0</v>
-      </c>
-      <c r="N115" t="b">
-        <v>0</v>
-      </c>
-      <c r="O115" t="s">
+      <c r="M116" t="b">
+        <v>0</v>
+      </c>
+      <c r="N116" t="b">
+        <v>0</v>
+      </c>
+      <c r="O116" t="s">
         <v>311</v>
       </c>
-      <c r="P115" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q115" t="b">
-        <v>1</v>
-      </c>
-      <c r="R115" t="b">
+      <c r="P116" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q116" t="b">
+        <v>1</v>
+      </c>
+      <c r="R116" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Maestro.xlsx
+++ b/Maestro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EditaSoft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C178E6F6-918E-4C72-9777-7B3277CEECCC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA79DFFC-1F71-4D82-82E9-F000016856A7}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="6705" xr2:uid="{49D38AAD-95AF-42F1-BCD2-D3E6F45A78E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artículos" sheetId="64" r:id="rId1"/>
+    <sheet name="Artículos" sheetId="65" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179021"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="645">
   <si>
     <t>Codigo</t>
   </si>
@@ -1940,6 +1940,27 @@
   </si>
   <si>
     <t>C:\EditaSoft\Imágenes de artículos\7790742335609.png</t>
+  </si>
+  <si>
+    <t>7793913002423</t>
+  </si>
+  <si>
+    <t>Yogur</t>
+  </si>
+  <si>
+    <t>natural</t>
+  </si>
+  <si>
+    <t>entero endulzado</t>
+  </si>
+  <si>
+    <t>pote</t>
+  </si>
+  <si>
+    <t>Yogures</t>
+  </si>
+  <si>
+    <t>C:\EditaSoft\Imágenes de artículos\7793913002423.png</t>
   </si>
 </sst>
 </file>
@@ -2291,8 +2312,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E82549A7-EDAE-47C9-9286-630639225607}">
-  <dimension ref="A1:R116"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0297A324-C617-41BE-A9D5-175068E07901}">
+  <dimension ref="A1:R117"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -5840,45 +5861,45 @@
         <v>1</v>
       </c>
       <c r="R63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B64" t="s">
-        <v>587</v>
+        <v>638</v>
       </c>
       <c r="C64" t="s">
-        <v>588</v>
+        <v>639</v>
       </c>
       <c r="D64" t="s">
-        <v>544</v>
+        <v>640</v>
       </c>
       <c r="E64" t="s">
-        <v>589</v>
+        <v>641</v>
       </c>
       <c r="F64" t="s">
-        <v>520</v>
+        <v>56</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="H64" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I64" t="s">
-        <v>493</v>
+        <v>642</v>
       </c>
       <c r="J64" t="s">
-        <v>590</v>
+        <v>643</v>
       </c>
       <c r="K64" t="s">
         <v>23</v>
       </c>
       <c r="L64">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
@@ -5887,7 +5908,7 @@
         <v>1</v>
       </c>
       <c r="O64" t="s">
-        <v>591</v>
+        <v>644</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -5896,42 +5917,42 @@
         <v>1</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B65" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C65" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D65" t="s">
-        <v>594</v>
+        <v>544</v>
       </c>
       <c r="E65" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="F65" t="s">
-        <v>596</v>
+        <v>520</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="s">
         <v>20</v>
       </c>
       <c r="I65" t="s">
-        <v>53</v>
+        <v>493</v>
       </c>
       <c r="J65" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="K65" t="s">
-        <v>598</v>
+        <v>23</v>
       </c>
       <c r="L65">
         <v>12</v>
@@ -5940,10 +5961,10 @@
         <v>0</v>
       </c>
       <c r="N65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
@@ -5957,49 +5978,49 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B66" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
+        <v>593</v>
       </c>
       <c r="D66" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="E66" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="F66" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="G66">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I66" t="s">
         <v>53</v>
       </c>
       <c r="J66" t="s">
-        <v>76</v>
+        <v>597</v>
       </c>
       <c r="K66" t="s">
-        <v>23</v>
+        <v>598</v>
       </c>
       <c r="L66">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
       </c>
       <c r="N66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -6013,49 +6034,49 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B67" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C67" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="D67" t="s">
-        <v>173</v>
+        <v>601</v>
       </c>
       <c r="E67" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F67" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H67" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J67" t="s">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="K67" t="s">
         <v>23</v>
       </c>
       <c r="L67">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
       </c>
       <c r="N67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
@@ -6064,27 +6085,27 @@
         <v>1</v>
       </c>
       <c r="R67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B68" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C68" t="s">
-        <v>610</v>
+        <v>196</v>
       </c>
       <c r="D68" t="s">
-        <v>611</v>
+        <v>173</v>
       </c>
       <c r="E68" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="F68" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6093,16 +6114,16 @@
         <v>20</v>
       </c>
       <c r="I68" t="s">
-        <v>493</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>614</v>
+        <v>244</v>
       </c>
       <c r="K68" t="s">
         <v>23</v>
       </c>
       <c r="L68">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -6111,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
@@ -6120,39 +6141,39 @@
         <v>1</v>
       </c>
       <c r="R68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C69" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="D69" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E69" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="F69" t="s">
-        <v>111</v>
+        <v>613</v>
       </c>
       <c r="G69">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
         <v>493</v>
       </c>
       <c r="J69" t="s">
-        <v>579</v>
+        <v>614</v>
       </c>
       <c r="K69" t="s">
         <v>23</v>
@@ -6164,10 +6185,10 @@
         <v>0</v>
       </c>
       <c r="N69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
@@ -6181,25 +6202,25 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B70" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C70" t="s">
-        <v>175</v>
+        <v>617</v>
       </c>
       <c r="D70" t="s">
-        <v>176</v>
+        <v>618</v>
       </c>
       <c r="E70" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F70" t="s">
-        <v>623</v>
+        <v>111</v>
       </c>
       <c r="G70">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H70" t="s">
         <v>42</v>
@@ -6208,13 +6229,13 @@
         <v>493</v>
       </c>
       <c r="J70" t="s">
-        <v>178</v>
+        <v>579</v>
       </c>
       <c r="K70" t="s">
         <v>23</v>
       </c>
       <c r="L70">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M70" t="b">
         <v>0</v>
@@ -6223,7 +6244,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
@@ -6237,40 +6258,40 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="B71" t="s">
-        <v>375</v>
+        <v>621</v>
       </c>
       <c r="C71" t="s">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="D71" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="E71" t="s">
-        <v>90</v>
+        <v>622</v>
       </c>
       <c r="F71" t="s">
-        <v>91</v>
+        <v>623</v>
       </c>
       <c r="G71">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H71" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>36</v>
+        <v>493</v>
       </c>
       <c r="J71" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="K71" t="s">
         <v>23</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
@@ -6279,13 +6300,13 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>266</v>
+        <v>624</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
@@ -6293,40 +6314,40 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C72" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D72" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E72" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F72" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G72">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H72" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I72" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="J72" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="K72" t="s">
         <v>23</v>
       </c>
       <c r="L72">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6335,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
@@ -6349,41 +6370,41 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B73" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C73" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D73" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E73" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F73" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H73" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I73" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J73" t="s">
+        <v>66</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73">
         <v>30</v>
       </c>
-      <c r="K73" t="s">
-        <v>23</v>
-      </c>
-      <c r="L73">
-        <v>12</v>
-      </c>
       <c r="M73" t="b">
         <v>0</v>
       </c>
@@ -6391,13 +6412,13 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -6405,55 +6426,55 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
+        <v>29</v>
+      </c>
+      <c r="B74" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" t="s">
+        <v>54</v>
+      </c>
+      <c r="E74" t="s">
+        <v>55</v>
+      </c>
+      <c r="F74" t="s">
+        <v>61</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
+        <v>28</v>
+      </c>
+      <c r="I74" t="s">
+        <v>96</v>
+      </c>
+      <c r="J74" t="s">
         <v>30</v>
       </c>
-      <c r="B74" t="s">
-        <v>378</v>
-      </c>
-      <c r="C74" t="s">
-        <v>97</v>
-      </c>
-      <c r="D74" t="s">
-        <v>98</v>
-      </c>
-      <c r="E74" t="s">
-        <v>99</v>
-      </c>
-      <c r="F74" t="s">
-        <v>100</v>
-      </c>
-      <c r="G74">
-        <v>100</v>
-      </c>
-      <c r="H74" t="s">
-        <v>20</v>
-      </c>
-      <c r="I74" t="s">
-        <v>101</v>
-      </c>
-      <c r="J74" t="s">
-        <v>102</v>
-      </c>
       <c r="K74" t="s">
         <v>23</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M74" t="b">
         <v>0</v>
       </c>
       <c r="N74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="b">
         <v>1</v>
@@ -6461,49 +6482,49 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B75" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C75" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D75" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E75" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F75" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G75">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H75" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I75" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J75" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K75" t="s">
         <v>23</v>
       </c>
       <c r="L75">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
       <c r="N75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
@@ -6517,22 +6538,22 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C76" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D76" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E76" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F76" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="G76">
         <v>500</v>
@@ -6544,13 +6565,13 @@
         <v>107</v>
       </c>
       <c r="J76" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="K76" t="s">
         <v>23</v>
       </c>
       <c r="L76">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M76" t="b">
         <v>0</v>
@@ -6559,7 +6580,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
@@ -6573,40 +6594,40 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D77" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E77" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F77" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H77" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I77" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="J77" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K77" t="s">
         <v>23</v>
       </c>
       <c r="L77">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
@@ -6615,13 +6636,13 @@
         <v>1</v>
       </c>
       <c r="O77" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="b">
         <v>1</v>
@@ -6629,40 +6650,40 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E78" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F78" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G78">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I78" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="K78" t="s">
         <v>23</v>
       </c>
       <c r="L78">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6671,13 +6692,13 @@
         <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
@@ -6685,40 +6706,40 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
+        <v>34</v>
+      </c>
+      <c r="B79" t="s">
+        <v>382</v>
+      </c>
+      <c r="C79" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" t="s">
+        <v>113</v>
+      </c>
+      <c r="E79" t="s">
+        <v>114</v>
+      </c>
+      <c r="F79" t="s">
+        <v>115</v>
+      </c>
+      <c r="G79">
+        <v>300</v>
+      </c>
+      <c r="H79" t="s">
         <v>35</v>
       </c>
-      <c r="B79" t="s">
-        <v>383</v>
-      </c>
-      <c r="C79" t="s">
-        <v>117</v>
-      </c>
-      <c r="D79" t="s">
-        <v>118</v>
-      </c>
-      <c r="E79" t="s">
-        <v>119</v>
-      </c>
-      <c r="F79" t="s">
-        <v>120</v>
-      </c>
-      <c r="G79">
-        <v>500</v>
-      </c>
-      <c r="H79" t="s">
-        <v>42</v>
-      </c>
       <c r="I79" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J79" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K79" t="s">
         <v>23</v>
       </c>
       <c r="L79">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6727,7 +6748,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
@@ -6741,40 +6762,40 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B80" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C80" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D80" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E80" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F80" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G80">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H80" t="s">
         <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K80" t="s">
         <v>23</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
@@ -6783,13 +6804,13 @@
         <v>1</v>
       </c>
       <c r="O80" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="b">
         <v>1</v>
@@ -6797,40 +6818,40 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B81" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D81" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E81" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F81" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G81">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="H81" t="s">
         <v>42</v>
       </c>
       <c r="I81" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J81" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K81" t="s">
         <v>23</v>
       </c>
       <c r="L81">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
@@ -6839,13 +6860,13 @@
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -6853,34 +6874,34 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B82" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C82" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="D82" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E82" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F82" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G82">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H82" t="s">
         <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="J82" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="K82" t="s">
         <v>23</v>
@@ -6895,13 +6916,13 @@
         <v>1</v>
       </c>
       <c r="O82" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
@@ -6909,40 +6930,40 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B83" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C83" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D83" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E83" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="F83" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G83">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H83" t="s">
         <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="K83" t="s">
         <v>23</v>
       </c>
       <c r="L83">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M83" t="b">
         <v>0</v>
@@ -6951,7 +6972,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
@@ -6965,40 +6986,40 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B84" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C84" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D84" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E84" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="F84" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="H84" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="J84" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="K84" t="s">
         <v>23</v>
       </c>
       <c r="L84">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
@@ -7007,7 +7028,7 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
@@ -7021,55 +7042,55 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B85" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C85" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="D85" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="E85" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="F85" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G85">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I85" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="J85" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K85" t="s">
         <v>23</v>
       </c>
       <c r="L85">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -7077,10 +7098,10 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C86" t="s">
         <v>138</v>
@@ -7089,10 +7110,10 @@
         <v>139</v>
       </c>
       <c r="E86" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F86" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="G86">
         <v>1000</v>
@@ -7116,10 +7137,10 @@
         <v>1</v>
       </c>
       <c r="N86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
@@ -7133,22 +7154,22 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B87" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C87" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D87" t="s">
         <v>139</v>
       </c>
       <c r="E87" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F87" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="G87">
         <v>1000</v>
@@ -7160,7 +7181,7 @@
         <v>142</v>
       </c>
       <c r="J87" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K87" t="s">
         <v>23</v>
@@ -7175,7 +7196,7 @@
         <v>1</v>
       </c>
       <c r="O87" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
@@ -7189,55 +7210,55 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B88" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C88" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D88" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E88" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F88" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G88">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H88" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J88" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K88" t="s">
         <v>23</v>
       </c>
       <c r="L88">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N88" t="b">
         <v>1</v>
       </c>
       <c r="O88" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -7245,55 +7266,55 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C89" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D89" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E89" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F89" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H89" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J89" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K89" t="s">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="L89">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
       <c r="N89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -7301,55 +7322,55 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C90" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D90" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E90" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F90" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G90">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="H90" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I90" t="s">
-        <v>29</v>
+        <v>159</v>
       </c>
       <c r="J90" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K90" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="L90">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
       </c>
       <c r="N90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="b">
         <v>1</v>
@@ -7357,34 +7378,34 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B91" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C91" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D91" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E91" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F91" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G91">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="H91" t="s">
         <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J91" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K91" t="s">
         <v>23</v>
@@ -7399,7 +7420,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
@@ -7413,22 +7434,22 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C92" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D92" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E92" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F92" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="G92">
         <v>500</v>
@@ -7440,7 +7461,7 @@
         <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K92" t="s">
         <v>23</v>
@@ -7455,7 +7476,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
@@ -7469,25 +7490,25 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B93" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C93" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D93" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E93" t="s">
-        <v>625</v>
+        <v>173</v>
       </c>
       <c r="F93" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="G93">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H93" t="s">
         <v>42</v>
@@ -7496,7 +7517,7 @@
         <v>21</v>
       </c>
       <c r="J93" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
@@ -7511,7 +7532,7 @@
         <v>1</v>
       </c>
       <c r="O93" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
@@ -7520,42 +7541,42 @@
         <v>1</v>
       </c>
       <c r="R93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
+        <v>49</v>
+      </c>
+      <c r="B94" t="s">
+        <v>397</v>
+      </c>
+      <c r="C94" t="s">
+        <v>175</v>
+      </c>
+      <c r="D94" t="s">
+        <v>176</v>
+      </c>
+      <c r="E94" t="s">
+        <v>625</v>
+      </c>
+      <c r="F94" t="s">
+        <v>177</v>
+      </c>
+      <c r="G94">
         <v>50</v>
       </c>
-      <c r="B94" t="s">
-        <v>398</v>
-      </c>
-      <c r="C94" t="s">
-        <v>179</v>
-      </c>
-      <c r="D94" t="s">
-        <v>180</v>
-      </c>
-      <c r="E94" t="s">
-        <v>181</v>
-      </c>
-      <c r="F94" t="s">
-        <v>182</v>
-      </c>
-      <c r="G94">
-        <v>12</v>
-      </c>
       <c r="H94" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I94" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J94" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K94" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="L94">
         <v>12</v>
@@ -7567,7 +7588,7 @@
         <v>1</v>
       </c>
       <c r="O94" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
@@ -7576,45 +7597,45 @@
         <v>1</v>
       </c>
       <c r="R94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B95" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C95" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D95" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E95" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F95" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G95">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H95" t="s">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="I95" t="s">
-        <v>190</v>
+        <v>53</v>
       </c>
       <c r="J95" t="s">
-        <v>555</v>
+        <v>183</v>
       </c>
       <c r="K95" t="s">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="L95">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -7623,7 +7644,7 @@
         <v>1</v>
       </c>
       <c r="O95" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
@@ -7637,40 +7658,40 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B96" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C96" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D96" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E96" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F96" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G96">
-        <v>24</v>
+        <v>360</v>
       </c>
       <c r="H96" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="I96" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="J96" t="s">
-        <v>183</v>
+        <v>555</v>
       </c>
       <c r="K96" t="s">
         <v>23</v>
       </c>
       <c r="L96">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -7679,7 +7700,7 @@
         <v>1</v>
       </c>
       <c r="O96" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
@@ -7693,40 +7714,40 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
+        <v>52</v>
+      </c>
+      <c r="B97" t="s">
+        <v>400</v>
+      </c>
+      <c r="C97" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" t="s">
+        <v>180</v>
+      </c>
+      <c r="E97" t="s">
+        <v>181</v>
+      </c>
+      <c r="F97" t="s">
+        <v>182</v>
+      </c>
+      <c r="G97">
+        <v>24</v>
+      </c>
+      <c r="H97" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" t="s">
         <v>53</v>
       </c>
-      <c r="B97" t="s">
-        <v>401</v>
-      </c>
-      <c r="C97" t="s">
-        <v>31</v>
-      </c>
-      <c r="D97" t="s">
-        <v>193</v>
-      </c>
-      <c r="E97" t="s">
-        <v>194</v>
-      </c>
-      <c r="F97" t="s">
-        <v>195</v>
-      </c>
-      <c r="G97">
-        <v>1.5</v>
-      </c>
-      <c r="H97" t="s">
-        <v>28</v>
-      </c>
-      <c r="I97" t="s">
-        <v>36</v>
-      </c>
       <c r="J97" t="s">
-        <v>37</v>
+        <v>183</v>
       </c>
       <c r="K97" t="s">
         <v>23</v>
       </c>
       <c r="L97">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -7735,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
@@ -7749,52 +7770,52 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B98" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C98" t="s">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="D98" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E98" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F98" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G98">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="H98" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I98" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J98" t="s">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="K98" t="s">
         <v>23</v>
       </c>
       <c r="L98">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M98" t="b">
         <v>0</v>
       </c>
       <c r="N98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="b">
         <v>1</v>
@@ -7805,55 +7826,55 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B99" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C99" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D99" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E99" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F99" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G99">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H99" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I99" t="s">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="J99" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="K99" t="s">
         <v>23</v>
       </c>
       <c r="L99">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
       </c>
       <c r="N99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" t="b">
         <v>1</v>
@@ -7861,40 +7882,40 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B100" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C100" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="D100" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E100" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F100" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G100">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H100" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I100" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="J100" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="K100" t="s">
         <v>23</v>
       </c>
       <c r="L100">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
@@ -7903,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
@@ -7917,19 +7938,19 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B101" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C101" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D101" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E101" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F101" t="s">
         <v>207</v>
@@ -7959,7 +7980,7 @@
         <v>1</v>
       </c>
       <c r="O101" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
@@ -7973,19 +7994,19 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B102" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C102" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D102" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E102" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F102" t="s">
         <v>207</v>
@@ -8006,7 +8027,7 @@
         <v>23</v>
       </c>
       <c r="L102">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
@@ -8015,7 +8036,7 @@
         <v>1</v>
       </c>
       <c r="O102" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
@@ -8029,34 +8050,34 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B103" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C103" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="D103" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E103" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F103" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H103" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I103" t="s">
-        <v>136</v>
+        <v>208</v>
       </c>
       <c r="J103" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="K103" t="s">
         <v>23</v>
@@ -8071,13 +8092,13 @@
         <v>1</v>
       </c>
       <c r="O103" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="b">
         <v>1</v>
@@ -8085,34 +8106,34 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B104" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C104" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="D104" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="E104" t="s">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="F104" t="s">
-        <v>215</v>
+        <v>56</v>
       </c>
       <c r="G104">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I104" t="s">
- 